--- a/docs/anime/manga_research/works_database.xlsx
+++ b/docs/anime/manga_research/works_database.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$Y$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$Y$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y130"/>
+  <dimension ref="A1:Y133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>拳児</t>
+          <t>北斗の拳</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>けんじ</t>
+          <t>ほくとのけん</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>単独</t>
+          <t>北斗の拳シリーズ</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13573,87 +13573,87 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>松田隆智</t>
+          <t>武論尊</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>藤原芳秀</t>
+          <t>原哲夫</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>集英社（後年の版はコアミックス）</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>週刊少年ジャンプ</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>1988–1992（終了年は二次情報による）</t>
+          <t>1983–1988（1983年41号〜1988年35号）</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>全21巻（少年サンデーコミックス）／ワイド版・文庫版あり（巻数未確認）</t>
+          <t>全27巻（ジャンプ・コミックス）</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>中国武術／八極拳／修行／旅</t>
+          <t>格闘技／世紀末／アクション／ドラマ</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>北斗の拳 イチゴ味、北斗の拳 拳王軍ザコたちの挽歌、北斗の拳 世紀末ドラマ撮影伝、蒼黒の餓狼 北斗の拳 レイ外伝、北斗の拳 ラオウ外伝 天の覇王 など</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>武術の本質の探求、師との出会い、礼節と修行</t>
+          <t>文明崩壊後の世界での強さと哀しみ、弱い人を守る、宿命、兄弟、愛</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>元気な少年が各地の師に出会うたびに自分の未熟さを知り、謙虚さを学んでいく過程。</t>
+          <t>主人公はほとんど感情を表に出さず、怒りや哀しみを短い言葉と表情で示す。敵側にもそれぞれの過去と執着があり、最期に心情を明かす構成が多い</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>師匠たちが武術の理（り）を説明する教養的な台詞が多い。</t>
+          <t>主人公は極端に寡黙で短く言い切る。雑魚キャラは語尾を伸ばす叫びや奇声で荒々しさとコミカルさを出す。重いナレーションで時代背景を語る</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>実在の武術の型や套路を写実的に描く。旅先の風景描写。</t>
+          <t>荒野と砂嵐の背景、筋肉の誇張、逆光のシルエット、劇画調の太い線と黒ベタ、決め技の瞬間の大ゴマと集中線</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>少年のやんちゃさ、祖父とのやり取り。</t>
+          <t>本編はシリアスだが、雑魚キャラの過剰な悪役ぶりや奇声が結果的に笑いを生み、ネットのネタとして定着している</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>技法：技の『理屈』を丁寧に描き、読者が学べる漫画にする。FLATUP案：AIKAがパンチの体重移動を図解で教えるミニ漫画（教育コンテンツ）。</t>
+          <t>「202X年」から始まる重いナレーション、荒野、雑魚の叫び声というジャンルの型を、世紀末パロディのオープニングに使う。強い者が弱い者を守るという芯は、FLATUPの「強さは優しさ」と相性がよい。オリジナル案：「殴る相手はミットだけでいい」</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>主人公・師匠キャラの名前と外見、作中の流派・師弟系譜の描写を流用しない。</t>
+          <t>原作冒頭のナレーションの言い回し、有名な決めゼリフ、やられたときの叫び声、胸の七つの傷、トゲ付き肩パッド、拳法名・技名、経絡秘孔の設定、キャラクターの外見、主題歌、タイトルロゴの書体は使わない</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]武術ファンの間で『中国武術に興味を持つきっかけ』として語られることが多い。[推測]実在武術の描写の丁寧さが評価されている。</t>
+          <t>[事実] 累計発行部数は全世界1億部超（2019年11月時点の記事）とされる。 [事実] 雑魚キャラを主人公にしたギャグのスピンオフが公式に作られ、2026年1月にショートアニメ化された。 [感想] 雑魚キャラの叫び声がネットミームとして親しまれている。 X直接検索なし</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv</t>
+          <t>https://bestcalendar.jp/dates/kinenbi/3791 | https://comic.k-manga.jp/title/67231/pv | https://renote.net/tags/246/articles</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>空手バカ一代</t>
+          <t>北斗の拳 イチゴ味</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>からてばかいちだい</t>
+          <t>ほくとのけん いちごあじ</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -13690,97 +13690,97 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>単独</t>
+          <t>北斗の拳シリーズ</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>スピンオフ</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎</t>
+          <t>未確認（原作者の監修のもとで制作されたとされる）</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>つのだじろう（1〜11巻）、影丸譲也（12〜29巻）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>1971–1977</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>全29巻</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>空手／伝記風／修行</t>
+          <t>ギャグ／パロディ</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>原作者の他作：巨人の星、あしたのジョー（原作 高森朝雄名義）</t>
+          <t>北斗の拳（本編）。2015年にテレビアニメ化</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ひたむきな修行、武道家の一代記、強さへの執念</t>
+          <t>本編の悪役を主人公にした、自分をパロディにするギャグ</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>主人公の孤独な修行と挫折を、ナレーションで劇的に語る。</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>熱いナレーションが物語を引っ張る劇画調。誇張された語り。</t>
+          <t>本編の重い言い回しを、日常のくだらない場面で使って落差を作る（紹介記事の説明による）</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>劇画の濃い線と黒ベタ、修行場面の荒々しい自然描写。</t>
+          <t>原作のタッチやアニメ版をそっくり再現した作画で、ギャグとの落差を強めている（紹介記事の説明による）</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少ない。</t>
+          <t>シリアスな絵柄のまま、ばかばかしいことを大真面目にやる落差のギャグ</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>技法：ナレーションで物語の熱量を上げる劇画の手法。FLATUP案：ジム10周年の記念動画で、創設者の『最初の一日』を熱いナレーションで語る（実在人物の事実確認を前提に）。ただし『根性で痛みに耐える』表現は採らない。</t>
+          <t>劇画の絵柄のまま、ジムの日常（ストレッチで太ももが伸びて感動する、など）を大真面目に描く落差の技法に使える</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>実在の空手家をモデルにした人物像、劇画のナレーション文、修行エピソード（動物との対決など）を流用しない。</t>
+          <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]1973年にTVアニメ化（二次情報）。[感想]空手ブームに影響したと語られることが多い。[推測]実話と創作の境目について議論がある。</t>
+          <t>[事実] 2015年にテレビアニメ化された。 X直接検索なし</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Karate_Master | https://www.kodansha.co.jp/comic/new-releases/p?page=2201 | https://mangapedia.com/%E3%81%A4%E3%81%AE%E3%81%A0%E3%81%98%E3%82%8D%E3%81%86-3h7myqn64</t>
+          <t>https://mangapedia.com/gd/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3-chyqulnxj/</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>はじめの一歩</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>はじめのいっぽ</t>
+          <t>ほくとのけん けんおうぐんざこたちのばんか</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -13817,97 +13817,97 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>単独</t>
+          <t>北斗の拳シリーズ</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>スピンオフ</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>森川ジョージ</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>森川ジョージ</t>
+          <t>倉尾宏</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>1989–連載中（1989年43号開始）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>既刊145巻以上（145巻は2026年1月16日発売。以降の巻数は未確認）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／スポーツ／成長／ジム群像／ギャグ</t>
+          <t>ギャグ／パロディ／お仕事</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（複数シリーズ）、作中キャラの外伝的エピソード（鷹村・間柴など）は本編内。同作者の別作品は未確認</t>
+          <t>北斗の拳（本編）、北斗の拳 世紀末ドラマ撮影伝（同じ作画者）。2026年1月5日からショートアニメ放送</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>いじめられっ子が強さの意味を問い続ける成長、努力の積み重ね、師弟の信頼、ジム仲間の家族的な絆、強さとは何かという問い</t>
+          <t>悪の軍団に就職した下っ端の視点で、組織で働く悲哀を笑いにする</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>主人公の恐怖や自信のなさを丁寧に積み上げ、試合中の『怖いけど前に出る』瞬間を内面モノローグで細かく描く。敗者側の人生や引退後の葛藤にも章を割き、勝ち負けの後の心を描く。</t>
+          <t>主人公の下っ端が、組織や上司の理不尽にふり回される気持ちを描く（紹介記事の説明による）</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>主人公は丁寧語で控えめ、先輩格は粗野で豪快という対比がはっきり。試合中は短い叫びと解説役の説明的なセリフが交互に入り、技術を読者に分かりやすく伝える。</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>パンチの軌道を大きな効果線で見せる見開き、ダウン寸前の視界の揺れ、観客席の反応カットの挿入。練習パートは日常のコマ割り、試合はコマを大きくして緩急をつける。</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>ジムの先輩たちによるいじり、恋愛に奥手な主人公の勘違い、釣り船屋の日常ネタ。シリアスな試合の直後に脱力ギャグを置く落差が定番。</t>
+          <t>雑魚が次々にやられる「お約束」を、下っ端の側から描いて笑いにする</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>技法：初心者の『怖さ』をモノローグで正直に描き、小さな一歩を大きく演出する。練習→試合の緩急、ジム仲間のいじり合いで温かさを出す。オリジナル案：初めてミットを打った会員が『音が鳴った』だけで目を輝かせる回。セリフ案『上手くなくていい。今日来たのがもう勝ち』。</t>
+          <t>雑魚キャラの側から描く視点がとても参考になる。FLATUPの「ヒャッハー三人衆」を主人公にして、入会して少しずつ変わっていく話にできる</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>主人公や鷹村・宮田など主要キャラの外見・髪型、鴨川ジムの名称やロゴ、デンプシーロールなど作中固有の必殺技名と象徴的な動き、釣り船屋という主人公の家業設定をそのまま使わない。</t>
+          <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>[事実] 1989年から30年以上続く長期連載で、ボクシング漫画の代表作として紹介されることが多い。[感想] 序盤〜中盤の試合描写や脇役の名勝負を高く評価する声が多い。[推測] 近年は展開の遅さや主人公の引退〜復帰の流れに賛否があるとみられる。X直接検索なし。</t>
+          <t>[事実] 2026年1月5日からショートアニメが放送された。 X直接検索なし</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>https://bunshun.jp/articles/-/88272 | https://game.watch.impress.co.jp/docs/news/1333266.html | https://www.kodansha.co.jp/comic/products/0000422841 | https://dengekionline.com/articles/208950/</t>
+          <t>https://animeanime.jp/article/2025/12/25/94731.html | https://mangapedia.com/gd/ag0gpp5uc</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>がんばれ元気</t>
+          <t>拳児</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>がんばれげんき</t>
+          <t>けんじ</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>小山ゆう</t>
+          <t>松田隆智</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>小山ゆう</t>
+          <t>藤原芳秀</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -13974,67 +13974,67 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>1976–1981</t>
+          <t>1988–1992（終了年は二次情報による）</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>全28巻（少年サンデーコミックス）</t>
+          <t>全21巻（少年サンデーコミックス）／ワイド版・文庫版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／家族／成長／少年</t>
+          <t>中国武術／八極拳／修行／旅</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（1980年・全35話）。第22回小学館漫画賞受賞。同作者の『おれは直角』『あずみ』</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>亡き父の夢を継ぐ少年の成長、家族愛、まっすぐな努力、ライバルへの敬意</t>
+          <t>武術の本質の探求、師との出会い、礼節と修行</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>幼少期から青年期までを長く追い、父を失った寂しさや期待への重圧を、子どもの目線で素直に描く。泣く・笑うが分かりやすく、読者が感情移入しやすい。</t>
+          <t>元気な少年が各地の師に出会うたびに自分の未熟さを知り、謙虚さを学んでいく過程。</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>主人公は素直で元気な子ども言葉から始まり、成長とともに口調が落ち着く。大人たちは温かく説明的で、少年漫画らしい分かりやすさ。</t>
+          <t>師匠たちが武術の理（り）を説明する教養的な台詞が多い。</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>丸みのある柔らかい絵柄で、表情（特に涙や笑顔）を大きく見せる。試合は派手さよりも身体の動きの流れを丁寧に描く。</t>
+          <t>実在の武術の型や套路を写実的に描く。旅先の風景描写。</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>子ども時代の無邪気な失敗や、周囲の大人とのほのぼのしたやりとり。誇張は控えめで、日常のほっこり系。</t>
+          <t>少年のやんちゃさ、祖父とのやり取り。</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>技法：子ども時代から段階的に成長を見せる長期構成。柔らかい絵柄で格闘技の怖さを下げる。オリジナル案：キッズクラスの子が卒業までに少しずつ変わっていく年代記。セリフ案『昨日より一回多く、前に出られたね』。</t>
+          <t>技法：技の『理屈』を丁寧に描き、読者が学べる漫画にする。FLATUP案：AIKAがパンチの体重移動を図解で教えるミニ漫画（教育コンテンツ）。</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前や外見、父がボクサーで亡くなる設定の流用、作品タイトルのもじりを避ける。</t>
+          <t>主人公・師匠キャラの名前と外見、作中の流派・師弟系譜の描写を流用しない。</t>
         </is>
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>[事実] 女子ボクシングの金メダリストが競技を始めるきっかけに挙げたと報じられた。[感想] 優しい絵柄と家族ドラマで泣ける作品として語られる。[推測] 知名度は世代差が大きいとみられる。X直接検索なし。</t>
+          <t>X直接検索なし。[感想]武術ファンの間で『中国武術に興味を持つきっかけ』として語られることが多い。[推測]実在武術の描写の丁寧さが評価されている。</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>https://number.bunshun.jp/articles/-/849242 | https://www.cmoa.jp/title/528/ | https://mechacomic.jp/books/45940</t>
+          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
@@ -14056,12 +14056,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>B・B</t>
+          <t>空手バカ一代</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>びーびー</t>
+          <t>からてばかいちだい</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -14081,87 +14081,87 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>石渡治</t>
+          <t>梶原一騎</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>石渡治</t>
+          <t>つのだじろう（1〜11巻）、影丸譲也（12〜29巻）</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>週刊少年マガジン</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>1985–1991（1985年24号〜1991年9号）</t>
+          <t>1971–1977</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>全31巻（少年サンデーコミックス。巻数は二次情報）</t>
+          <t>全29巻</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／青春／音楽／アクション</t>
+          <t>空手／伝記風／修行</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>第34回小学館漫画賞受賞。同作者の『LOVe』『パスポート・ブルー』</t>
+          <t>原作者の他作：巨人の星、あしたのジョー（原作 高森朝雄名義）</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>自由に生きたい若者の反発、友情、ボクシングを通した自己表現、後半は戦場での生と死</t>
+          <t>ひたむきな修行、武道家の一代記、強さへの執念</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>屈折した主人公の怒りや喪失を大胆な展開で描き、ボクサーから傭兵へという急展開で極限状況の心を見せる。</t>
+          <t>主人公の孤独な修行と挫折を、ナレーションで劇的に語る。</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>ラフで挑発的な若者口調。サックスなど音楽を絡めた詩的な独白が混ざる。</t>
+          <t>熱いナレーションが物語を引っ張る劇画調。誇張された語り。</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>スピード感のある線、音楽的なリズムのコマ運び、後半は戦争アクションの硬質な画面。</t>
+          <t>劇画の濃い線と黒ベタ、修行場面の荒々しい自然描写。</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>前半は軽口と青春ドタバタ。後半は少なめ。</t>
+          <t>ギャグは少ない。</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>技法：音楽やリズムとボクシングのステップを重ねる演出。オリジナル案：会員がBGMに合わせてシャドーをするとステップが自然に良くなる回。セリフ案『リズムに乗れたら、体は勝手に動く』。</t>
+          <t>技法：ナレーションで物語の熱量を上げる劇画の手法。FLATUP案：ジム10周年の記念動画で、創設者の『最初の一日』を熱いナレーションで語る（実在人物の事実確認を前提に）。ただし『根性で痛みに耐える』表現は採らない。</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見、ボクサーが傭兵になる大筋、作中のサックス奏者設定をそのまま使わない。</t>
+          <t>実在の空手家をモデルにした人物像、劇画のナレーション文、修行エピソード（動物との対決など）を流用しない。</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>[事実] 作者インタビューで主人公が傭兵になる展開の誕生秘話が語られている。[感想] 前半のボクシングと後半の戦場編の落差が強く印象に残るという声。[推測] 現在の知名度は同時代のボクシング漫画より低めとみられる。X直接検索なし。</t>
+          <t>X直接検索なし。[事実]1973年にTVアニメ化（二次情報）。[感想]空手ブームに影響したと語られることが多い。[推測]実話と創作の境目について議論がある。</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>https://gendai.media/articles/-/100861 | https://mangapedia.com/gd/B%E3%83%BBB-9tbu6j1t4/ | https://ranking.net/rankings/best-shonensunday-comics/b6c541bd</t>
+          <t>https://en.wikipedia.org/wiki/Karate_Master | https://www.kodansha.co.jp/comic/new-releases/p?page=2201 | https://mangapedia.com/%E3%81%A4%E3%81%AE%E3%81%A0%E3%81%98%E3%82%8D%E3%81%86-3h7myqn64</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>オールラウンダー廻</t>
+          <t>はじめの一歩</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>おーるらうんだーめぐる</t>
+          <t>はじめのいっぽ</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>遠藤浩輝</t>
+          <t>森川ジョージ</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>遠藤浩輝</t>
+          <t>森川ジョージ</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -14223,72 +14223,72 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>イブニング</t>
+          <t>週刊少年マガジン</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>2008–2016（2008年24号〜2016年7号）</t>
+          <t>1989–連載中（1989年43号開始）</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>全19巻（イブニングKC）</t>
+          <t>既刊145巻以上（145巻は2026年1月16日発売。以降の巻数は未確認）</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>MMA／修斗／総合格闘技／青春／ジム</t>
+          <t>ボクシング／スポーツ／成長／ジム群像／ギャグ</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>同作者の『EDEN 〜It's an Endless World!〜』</t>
+          <t>TVアニメ（複数シリーズ）、作中キャラの外伝的エピソード（鷹村・間柴など）は本編内。同作者の別作品は未確認</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>普通の高校生が総合格闘技に打ち込む青春、幼なじみとの対立と和解、アマチュア競技のリアル</t>
+          <t>いじめられっ子が強さの意味を問い続ける成長、努力の積み重ね、師弟の信頼、ジム仲間の家族的な絆、強さとは何かという問い</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>勝ちたい気持ちと友情の揺れ、練習の地味さへの焦り、減量や試合前の不安を等身大に描く。</t>
+          <t>主人公の恐怖や自信のなさを丁寧に積み上げ、試合中の『怖いけど前に出る』瞬間を内面モノローグで細かく描く。敗者側の人生や引退後の葛藤にも章を割き、勝ち負けの後の心を描く。</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>日常会話は普通の高校生らしく軽い。技術解説は具体的で専門用語を噛み砕いて説明する。</t>
+          <t>主人公は丁寧語で控えめ、先輩格は粗野で豪快という対比がはっきり。試合中は短い叫びと解説役の説明的なセリフが交互に入り、技術を読者に分かりやすく伝える。</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>寝技・関節技の体勢を正確に描き、アマ修斗のルールや試合運びを丁寧に見せる。派手な誇張は控えめ。</t>
+          <t>パンチの軌道を大きな効果線で見せる見開き、ダウン寸前の視界の揺れ、観客席の反応カットの挿入。練習パートは日常のコマ割り、試合はコマを大きくして緩急をつける。</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>ジム仲間や家族とのゆるい日常ギャグ、恋愛まわりの照れ。</t>
+          <t>ジムの先輩たちによるいじり、恋愛に奥手な主人公の勘違い、釣り船屋の日常ネタ。シリアスな試合の直後に脱力ギャグを置く落差が定番。</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>技法：MMAのルールや技を初心者にも分かるよう噛み砕いて描く。地味な練習の積み重ねをドラマにする。オリジナル案：寝技の初体験で『怖い』が『おもしろい』に変わる瞬間を描く回。セリフ案『タップは負けじゃない。また練習できる合図だよ』。</t>
+          <t>技法：初心者の『怖さ』をモノローグで正直に描き、小さな一歩を大きく演出する。練習→試合の緩急、ジム仲間のいじり合いで温かさを出す。オリジナル案：初めてミットを打った会員が『音が鳴った』だけで目を輝かせる回。セリフ案『上手くなくていい。今日来たのがもう勝ち』。</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>主人公と幼なじみのキャラ造形、作中ジム名、実在団体（修斗）のロゴや公式表記の無断使用を避ける。</t>
+          <t>主人公や鷹村・宮田など主要キャラの外見・髪型、鴨川ジムの名称やロゴ、デンプシーロールなど作中固有の必殺技名と象徴的な動き、釣り船屋という主人公の家業設定をそのまま使わない。</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>[事実] 修斗を題材にした作品として格闘技ファンに紹介される。[感想] 格闘技経験者から描写のリアルさを評価する声。[推測] MMA漫画の入門として勧められやすいとみられる。X直接検索なし。</t>
+          <t>[事実] 1989年から30年以上続く長期連載で、ボクシング漫画の代表作として紹介されることが多い。[感想] 序盤〜中盤の試合描写や脇役の名勝負を高く評価する声が多い。[推測] 近年は展開の遅さや主人公の引退〜復帰の流れに賛否があるとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E3%82%AA%E3%83%BC%E3%83%AB%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%80%E3%83%BC%E5%BB%BB | https://www.kodansha.co.jp/comic/products/0000038657 | https://bookwalker.jp/de77e612eb-ae5e-4edd-acd0-e2eb92f4eff0/</t>
+          <t>https://bunshun.jp/articles/-/88272 | https://game.watch.impress.co.jp/docs/news/1333266.html | https://www.kodansha.co.jp/comic/products/0000422841 | https://dengekionline.com/articles/208950/</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>軍鶏</t>
+          <t>がんばれ元気</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>しゃも</t>
+          <t>がんばれげんき</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -14335,87 +14335,87 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>橋本以蔵（途中から作画者の単独名義とされる）</t>
+          <t>小山ゆう</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>たなか亜希夫</t>
+          <t>小山ゆう</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>双葉社 → 講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>漫画アクション → イブニング</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1998–2015（完結年は二次情報）</t>
+          <t>1976–1981</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>全34巻（講談社イブニングKC）。再編集版の極厚版は全22巻</t>
+          <t>全28巻（少年サンデーコミックス）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>空手／総合格闘技／犯罪／暴力／ダーク</t>
+          <t>ボクシング／家族／成長／少年</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>実写映画（2008年）</t>
+          <t>TVアニメ（1980年・全35話）。第22回小学館漫画賞受賞。同作者の『おれは直角』『あずみ』</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>罪を犯した少年が生き延びるために暴力を身につける、人間の暗部、孤独</t>
+          <t>亡き父の夢を継ぐ少年の成長、家族愛、まっすぐな努力、ライバルへの敬意</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>主人公の自己嫌悪・憎しみ・恐怖を容赦なく描く。救いの少ない心理描写。</t>
+          <t>幼少期から青年期までを長く追い、父を失った寂しさや期待への重圧を、子どもの目線で素直に描く。泣く・笑うが分かりやすく、読者が感情移入しやすい。</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>荒々しく冷たい言葉。内面語りは少なめで行動で示す。</t>
+          <t>主人公は素直で元気な子ども言葉から始まり、成長とともに口調が落ち着く。大人たちは温かく説明的で、少年漫画らしい分かりやすさ。</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>劇画調の濃い陰影、暴力の生々しい描写、閉塞感のある画面。</t>
+          <t>丸みのある柔らかい絵柄で、表情（特に涙や笑顔）を大きく見せる。試合は派手さよりも身体の動きの流れを丁寧に描く。</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>ほぼなし。</t>
+          <t>子ども時代の無邪気な失敗や、周囲の大人とのほのぼのしたやりとり。誇張は控えめで、日常のほっこり系。</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>技法：反面教師として、暴力だけの強さがいかに人を孤独にするかを示す作品。FLATUPの『強さ＝優しさ』の対比として、悪役側の心理の深さを学ぶ程度に留める。</t>
+          <t>技法：子ども時代から段階的に成長を見せる長期構成。柔らかい絵柄で格闘技の怖さを下げる。オリジナル案：キッズクラスの子が卒業までに少しずつ変わっていく年代記。セリフ案『昨日より一回多く、前に出られたね』。</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見、少年院から格闘家になる設定、過激な暴力・性暴力描写は絶対に真似しない（ブランドと完全に逆方向）。</t>
+          <t>主人公の名前や外見、父がボクサーで亡くなる設定の流用、作品タイトルのもじりを避ける。</t>
         </is>
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>[事実] 原作者と作画者の間で著作権をめぐる裁判があったとされる。[感想] 迫力は高いが重く暗いという声。[推測] 一般向け・子ども向けには勧めにくい作品とみられる。X直接検索なし。</t>
+          <t>[事実] 女子ボクシングの金メダリストが競技を始めるきっかけに挙げたと報じられた。[感想] 優しい絵柄と家族ドラマで泣ける作品として語られる。[推測] 知名度は世代差が大きいとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000038793 | https://renote.net/reviews/5254 | https://www.cmoa.jp/title/87790</t>
+          <t>https://number.bunshun.jp/articles/-/849242 | https://www.cmoa.jp/title/528/ | https://mechacomic.jp/books/45940</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>キックの鬼</t>
+          <t>B・B</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>きっくのおに</t>
+          <t>びーびー</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -14462,87 +14462,87 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎</t>
+          <t>石渡治</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>中城健（中城けんたろう）</t>
+          <t>石渡治</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>週刊少年キング または 少年画報（資料により食い違い）</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>1969–1971（開始時期は資料により異なる）</t>
+          <t>1985–1991（1985年24号〜1991年9号）</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>全6巻（英語版Wikipedia）。他に3巻とする記述もあり未確定</t>
+          <t>全31巻（少年サンデーコミックス。巻数は二次情報）</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／実録／梶原一騎</t>
+          <t>ボクシング／青春／音楽／アクション</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（1970年）。同原作者の『あしたのジョー』『紅の挑戦者』</t>
+          <t>第34回小学館漫画賞受賞。同作者の『LOVe』『パスポート・ブルー』</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>実在のキックボクサー沢村忠をモデルにした成り上がり、日本のキックボクシング黎明期</t>
+          <t>自由に生きたい若者の反発、友情、ボクシングを通した自己表現、後半は戦場での生と死</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>主人公の不屈の精神と根性を前面に出す。内面の弱さより覚悟を強調する昭和スポ根型。</t>
+          <t>屈折した主人公の怒りや喪失を大胆な展開で描き、ボクサーから傭兵へという急展開で極限状況の心を見せる。</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>熱血で大仰な語り口、ナレーションで事実風に語るセミドキュメンタリー調。</t>
+          <t>ラフで挑発的な若者口調。サックスなど音楽を絡めた詩的な独白が混ざる。</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>劇画調、飛び蹴りなど技の瞬間を大きく見せる。</t>
+          <t>スピード感のある線、音楽的なリズムのコマ運び、後半は戦争アクションの硬質な画面。</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>ほぼなし。</t>
+          <t>前半は軽口と青春ドタバタ。後半は少なめ。</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>技法：実在の歴史を背景にした『物語として語る格闘技史』。オリジナル案：日本のキックボクシングの歴史を、会員向けにやさしく紹介する短編漫画（実在人物の扱いは要注意）。</t>
+          <t>技法：音楽やリズムとボクシングのステップを重ねる演出。オリジナル案：会員がBGMに合わせてシャドーをするとステップが自然に良くなる回。セリフ案『リズムに乗れたら、体は勝手に動く』。</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
-          <t>実在人物（沢村忠）の肖像やエピソードの流用、作中の技名、タイトルのもじりを避ける。</t>
+          <t>主人公の外見、ボクサーが傭兵になる大筋、作中のサックス奏者設定をそのまま使わない。</t>
         </is>
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>[事実] 沢村忠をモデルにした作品で、1970年にアニメ化された。[感想] 昭和のキックボクシングブームを伝える作品として語られる。[推測] 現在の読者は少ないとみられる。X直接検索なし。</t>
+          <t>[事実] 作者インタビューで主人公が傭兵になる展開の誕生秘話が語られている。[感想] 前半のボクシングと後半の戦場編の落差が強く印象に残るという声。[推測] 現在の知名度は同時代のボクシング漫画より低めとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kick_no_Oni | https://mangapedia.com/%E3%82%AD%E3%83%83%E3%82%AF%E3%81%AE%E9%AC%BC-6rimm0fjt | https://comic.k-manga.jp/title/165/pv</t>
+          <t>https://gendai.media/articles/-/100861 | https://mangapedia.com/gd/B%E3%83%BBB-9tbu6j1t4/ | https://ranking.net/rankings/best-shonensunday-comics/b6c541bd</t>
         </is>
       </c>
       <c r="X111" s="2" t="inlineStr">
@@ -14564,12 +14564,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>モングレル</t>
+          <t>オールラウンダー廻</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>もんぐれる</t>
+          <t>おーるらうんだーめぐる</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14589,87 +14589,87 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>村瀬克俊</t>
+          <t>遠藤浩輝</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>村瀬克俊</t>
+          <t>遠藤浩輝</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>集英社</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングジャンプ</t>
+          <t>イブニング</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2013–2014（単行本1巻2013年12月〜4巻2014年6月）</t>
+          <t>2008–2016（2008年24号〜2016年7号）</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>全4巻（ヤングジャンプコミックス）</t>
+          <t>全19巻（イブニングKC）</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／青年／ジム／リアル</t>
+          <t>MMA／修斗／総合格闘技／青春／ジム</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>同作者の『K.O.SEN』『カラダ探し』（作画）</t>
+          <t>同作者の『EDEN 〜It's an Endless World!〜』</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>格闘経験のない若者がジムに入りアマチュアから始める、身体能力を活かした成長</t>
+          <t>普通の高校生が総合格闘技に打ち込む青春、幼なじみとの対立と和解、アマチュア競技のリアル</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>未経験者がジムに入る不安や、練習で少しずつ手応えを得る感覚をリアルに描く。</t>
+          <t>勝ちたい気持ちと友情の揺れ、練習の地味さへの焦り、減量や試合前の不安を等身大に描く。</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>等身大の若者口調、ジムの会話は現実的で落ち着いている。</t>
+          <t>日常会話は普通の高校生らしく軽い。技術解説は具体的で専門用語を噛み砕いて説明する。</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>必殺技に頼らず、実際のキックの動きやジム練習をリアルに描く。</t>
+          <t>寝技・関節技の体勢を正確に描き、アマ修斗のルールや試合運びを丁寧に見せる。派手な誇張は控えめ。</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>控えめ。日常の軽いやりとり程度。</t>
+          <t>ジム仲間や家族とのゆるい日常ギャグ、恋愛まわりの照れ。</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>技法：『ジムに入会する』ところから始めるリアルな導入。FLATUPの体験入会の流れとほぼ同じ構造なので、最も参考になる型。オリジナル案：体験レッスン当日の緊張→受付→初ミット→帰り道の高揚までを1話で描く。セリフ案『初日は誰でも初心者。それでいい』。</t>
+          <t>技法：MMAのルールや技を初心者にも分かるよう噛み砕いて描く。地味な練習の積み重ねをドラマにする。オリジナル案：寝技の初体験で『怖い』が『おもしろい』に変わる瞬間を描く回。セリフ案『タップは負けじゃない。また練習できる合図だよ』。</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見や体操経験者という設定、作中ジム名を使わない。</t>
+          <t>主人公と幼なじみのキャラ造形、作中ジム名、実在団体（修斗）のロゴや公式表記の無断使用を避ける。</t>
         </is>
       </c>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>[事実] 全4巻で終了。作者はキック王者との対談でリアルなキックを描きたかったと語った。[感想] もっと読みたかったという声がある。[推測] 短期終了のため知名度は低めとみられる。X直接検索なし。</t>
+          <t>[事実] 修斗を題材にした作品として格闘技ファンに紹介される。[感想] 格闘技経験者から描写のリアルさを評価する声。[推測] MMA漫画の入門として勧められやすいとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>https://comic.k-manga.jp/title/100297/pv | https://mangapedia.com/%E3%83%A2%E3%83%B3%E3%82%B0%E3%83%AC%E3%83%AB-e3btri2tc | https://sportiva.shueisha.co.jp/clm/othersports/fight/2013/12/19/___split_35/ | https://www.hatehate.jp/entry/mongrel</t>
+          <t>https://dic.nicovideo.jp/a/%E3%82%AA%E3%83%BC%E3%83%AB%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%80%E3%83%BC%E5%BB%BB | https://www.kodansha.co.jp/comic/products/0000038657 | https://bookwalker.jp/de77e612eb-ae5e-4edd-acd0-e2eb92f4eff0/</t>
         </is>
       </c>
       <c r="X112" s="2" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="Y112" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -14691,12 +14691,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>レッドブルー</t>
+          <t>軍鶏</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>れっどぶるー</t>
+          <t>しゃも</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -14716,87 +14716,87 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>波切敦</t>
+          <t>橋本以蔵（途中から作画者の単独名義とされる）</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>波切敦</t>
+          <t>たなか亜希夫</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>双葉社 → 講談社</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>漫画アクション → イブニング</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>2022–（2022年7号開始。現在の連載状況は未確認）</t>
+          <t>1998–2015（完結年は二次情報）</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>未確認（2023年11月時点で7巻）</t>
+          <t>全34巻（講談社イブニングKC）。再編集版の極厚版は全22巻</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>MMA／総合格闘技／学園／成長</t>
+          <t>空手／総合格闘技／犯罪／暴力／ダーク</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>実写ドラマ（2024年12月）</t>
+          <t>実写映画（2008年）</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>根暗で病弱な少年が天才への反発からMMAを始める、劣等感と向き合う成長</t>
+          <t>罪を犯した少年が生き延びるために暴力を身につける、人間の暗部、孤独</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>主人公の劣等感・ひねくれ・執念を正直に描き、『一発殴りたい』という負の動機が成長の原動力へ変わる過程を見せる。</t>
+          <t>主人公の自己嫌悪・憎しみ・恐怖を容赦なく描く。救いの少ない心理描写。</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>主人公の皮肉っぽい独白と、ライバルの爽やかな口調の対比。</t>
+          <t>荒々しく冷たい言葉。内面語りは少なめで行動で示す。</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>MMAの打・投・極の流れを分かりやすく描き、分析的なモノローグで戦術を見せる。</t>
+          <t>劇画調の濃い陰影、暴力の生々しい描写、閉塞感のある画面。</t>
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>主人公のひねくれたリアクションや陰キャ的な自虐。</t>
+          <t>ほぼなし。</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>技法：『かっこ悪い動機』から始めても成長できると示す。分析タイプの主人公で戦術を読者に解説。オリジナル案：運動が苦手な学生が、頭で考えるタイプとしてMMAで自分の勝ち方を見つける話。セリフ案『体力がないなら、考える力で一歩先に行こう』。</t>
+          <t>技法：反面教師として、暴力だけの強さがいかに人を孤独にするかを示す作品。FLATUPの『強さ＝優しさ』の対比として、悪役側の心理の深さを学ぶ程度に留める。</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
         <is>
-          <t>主人公とライバルの名前・外見、作中ジム名、赤と青の対比を軸にしたタイトル演出をそのまま使わない。</t>
+          <t>主人公の外見、少年院から格闘家になる設定、過激な暴力・性暴力描写は絶対に真似しない（ブランドと完全に逆方向）。</t>
         </is>
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>[事実] 2024年12月に実写ドラマ化された。[感想] 陰キャ主人公の成長がMMA初心者にも読みやすいという紹介がある。[推測] 近年の少年誌MMA漫画として注目度が高いとみられる。X直接検索なし。</t>
+          <t>[事実] 原作者と作画者の間で著作権をめぐる裁判があったとされる。[感想] 迫力は高いが重く暗いという声。[推測] 一般向け・子ども向けには勧めにくい作品とみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000038793 | https://renote.net/reviews/5254 | https://www.cmoa.jp/title/87790</t>
         </is>
       </c>
       <c r="X113" s="2" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>紅の挑戦者</t>
+          <t>キックの鬼</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>くれないのちょうせんしゃ</t>
+          <t>きっくのおに</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -14843,62 +14843,62 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎（高森朝雄名義とする資料もあるが未確認）</t>
+          <t>梶原一騎</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>中城健</t>
+          <t>中城健（中城けんたろう）</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>未確認（電子版の発行元はグループ・ゼロ）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン（まとめサイトの記載。未確認）</t>
+          <t>週刊少年キング または 少年画報（資料により食い違い）</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>1973–1975（まとめサイトの記載。未確認）</t>
+          <t>1969–1971（開始時期は資料により異なる）</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>全10巻（電子版）</t>
+          <t>全6巻（英語版Wikipedia）。他に3巻とする記述もあり未確定</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／ムエタイ／スポ根</t>
+          <t>キックボクシング／実録／梶原一騎</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>同原作者・作画者の『キックの鬼』</t>
+          <t>TVアニメ（1970年）。同原作者の『あしたのジョー』『紅の挑戦者』</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>高校サッカーのエースがキックボクシングに転向する挑戦、タイ・ムエタイとの対決</t>
+          <t>実在のキックボクサー沢村忠をモデルにした成り上がり、日本のキックボクシング黎明期</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>転向への迷いより、挑戦への覚悟を強調する昭和スポ根型。</t>
+          <t>主人公の不屈の精神と根性を前面に出す。内面の弱さより覚悟を強調する昭和スポ根型。</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>熱血で大げさな宣言調。</t>
+          <t>熱血で大仰な語り口、ナレーションで事実風に語るセミドキュメンタリー調。</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>劇画調、海外（タイ）を舞台にした異国感。</t>
+          <t>劇画調、飛び蹴りなど技の瞬間を大きく見せる。</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
@@ -14908,22 +14908,22 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>技法：別競技からの転向者を主人公にすると、技術の違いを読者に説明しやすい。オリジナル案：サッカー経験者の会員が『蹴り』の感覚の違いに戸惑い、やがて武器にする話。</t>
+          <t>技法：実在の歴史を背景にした『物語として語る格闘技史』。オリジナル案：日本のキックボクシングの歴史を、会員向けにやさしく紹介する短編漫画（実在人物の扱いは要注意）。</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前・外見、サッカーからキックへの転向をバンコクで宣言する導入をそのまま使わない。</t>
+          <t>実在人物（沢村忠）の肖像やエピソードの流用、作中の技名、タイトルのもじりを避ける。</t>
         </is>
       </c>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>[事実] 電子版で全10巻が配信されている。[感想] 梶原一騎のキックボクシング作品として紹介される。[推測] 現在の知名度は低いとみられる。X直接検索なし。</t>
+          <t>[事実] 沢村忠をモデルにした作品で、1970年にアニメ化された。[感想] 昭和のキックボクシングブームを伝える作品として語られる。[推測] 現在の読者は少ないとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
         <is>
-          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/</t>
+          <t>https://en.wikipedia.org/wiki/Kick_no_Oni | https://mangapedia.com/%E3%82%AD%E3%83%83%E3%82%AF%E3%81%AE%E9%AC%BC-6rimm0fjt | https://comic.k-manga.jp/title/165/pv</t>
         </is>
       </c>
       <c r="X114" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>YAWARA!</t>
+          <t>モングレル</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>やわら</t>
+          <t>もんぐれる</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -14970,87 +14970,87 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>浦沢直樹</t>
+          <t>村瀬克俊</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>浦沢直樹</t>
+          <t>村瀬克俊</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>集英社</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックスピリッツ</t>
+          <t>週刊ヤングジャンプ</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>1986–1993</t>
+          <t>2013–2014（単行本1巻2013年12月〜4巻2014年6月）</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックス全29巻／文庫版全19巻／完全版全20巻</t>
+          <t>全4巻（ヤングジャンプコミックス）</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>柔道／女子／青春／ラブコメ／スポーツ</t>
+          <t>キックボクシング／青年／ジム／リアル</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Happy!（同作者のスポーツもの）</t>
+          <t>同作者の『K.O.SEN』『カラダ探し』（作画）</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>才能と『普通の女の子でいたい』願いの葛藤、家族の期待、恋、自分で道を選ぶこと</t>
+          <t>格闘経験のない若者がジムに入りアマチュアから始める、身体能力を活かした成長</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>強さを隠したい本人の照れ・反発を丁寧に描き、周囲の期待とのズレを長期的な葛藤として育てる</t>
+          <t>未経験者がジムに入る不安や、練習で少しずつ手応えを得る感覚をリアルに描く。</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>日常会話中心の自然な口語。祖父キャラの大げさな物言いと主人公の控えめな返しの対比（引用なし）</t>
+          <t>等身大の若者口調、ジムの会話は現実的で落ち着いている。</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>日常パートは軽い線と多めの間、試合は一瞬の技を見開きで見せる。観客・記者のリアクションで凄さを伝える</t>
+          <t>必殺技に頼らず、実際のキックの動きやジム練習をリアルに描く。</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>強すぎる祖父の暴走、恋愛の勘違い、主人公が強さを隠そうとしてバレるお約束</t>
+          <t>控えめ。日常の軽いやりとり程度。</t>
         </is>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>技法：『強いのに普通でいたい』という主人公の心のズレで共感を作る。オリジナル案：家族に内緒で格闘技を始めた会社員女性が、通勤中に姿勢が良くなって同僚に気付かれるエピソード</t>
+          <t>技法：『ジムに入会する』ところから始めるリアルな導入。FLATUPの体験入会の流れとほぼ同じ構造なので、最も参考になる型。オリジナル案：体験レッスン当日の緊張→受付→初ミット→帰り道の高揚までを1話で描く。セリフ案『初日は誰でも初心者。それでいい』。</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
         <is>
-          <t>主人公名・祖父キャラの造形、作品タイトルロゴ、特定の決め技の見せ方は使わない</t>
+          <t>主人公の外見や体操経験者という設定、作中ジム名を使わない。</t>
         </is>
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>[事実]小学館漫画賞受賞作として紹介され、女子柔道ブームと結び付けて語られることが多い（X直接検索なし） [感想]ラブコメとしても楽しめるという声が多い</t>
+          <t>[事実] 全4巻で終了。作者はキック王者との対談でリアルなキックを描きたかったと語った。[感想] もっと読みたかったという声がある。[推測] 短期終了のため知名度は低めとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Yawara! | https://nlab.itmedia.co.jp/research/articles/128892/ | https://ranking.net/items/7c982a</t>
+          <t>https://comic.k-manga.jp/title/100297/pv | https://mangapedia.com/%E3%83%A2%E3%83%B3%E3%82%B0%E3%83%AC%E3%83%AB-e3btri2tc | https://sportiva.shueisha.co.jp/clm/othersports/fight/2013/12/19/___split_35/ | https://www.hatehate.jp/entry/mongrel</t>
         </is>
       </c>
       <c r="X115" s="2" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>帯をギュッとね!</t>
+          <t>レッドブルー</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>おびをぎゅっとね</t>
+          <t>れっどぶるー</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -15097,12 +15097,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>河合克敏</t>
+          <t>波切敦</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>河合克敏</t>
+          <t>波切敦</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -15117,67 +15117,67 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>1988または1989–1995（1995年52号終了。開始年は資料で食い違い）</t>
+          <t>2022–（2022年7号開始。現在の連載状況は未確認）</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>少年サンデーコミックス全30巻／ワイド版全15巻／小学館文庫全16巻</t>
+          <t>未確認（2023年11月時点で7巻）</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>柔道／学園／部活／青春／ギャグ</t>
+          <t>MMA／総合格闘技／学園／成長</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>モンキーターン（同作者）</t>
+          <t>実写ドラマ（2024年12月）</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ゼロから部を作る楽しさ、仲間、合理的な練習、楽しみながら強くなること</t>
+          <t>根暗で病弱な少年が天才への反発からMMAを始める、劣等感と向き合う成長</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>苦しさよりも工夫と仲間との時間を前面に出し、負けの悔しさは短く強く描いて次へ切り替える</t>
+          <t>主人公の劣等感・ひねくれ・執念を正直に描き、『一発殴りたい』という負の動機が成長の原動力へ変わる過程を見せる。</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>明るくテンポの良い掛け合い。技術解説を会話に溶け込ませる（引用なし）</t>
+          <t>主人公の皮肉っぽい独白と、ライバルの爽やかな口調の対比。</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>作者の柔道経験を生かした技の分解描写、練習メニューの図解的コマ</t>
+          <t>MMAの打・投・極の流れを分かりやすく描き、分析的なモノローグで戦術を見せる。</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>部員同士のボケとツッコミ、恋愛がらみの勘違い、ゆるいキャラの脱力</t>
+          <t>主人公のひねくれたリアクションや陰キャ的な自虐。</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>技法：技術の『なぜ』をキャラの会話で自然に説明する。オリジナル案：初心者が受け身を習う回で、コーチが『転び方が上手い人は人生でもケガしにくい』と語る短い場面</t>
+          <t>技法：『かっこ悪い動機』から始めても成長できると示す。分析タイプの主人公で戦術を読者に解説。オリジナル案：運動が苦手な学生が、頭で考えるタイプとしてMMAで自分の勝ち方を見つける話。セリフ案『体力がないなら、考える力で一歩先に行こう』。</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
-          <t>主要部員の外見・あだ名、部の名前、作中の学校名は使わない</t>
+          <t>主人公とライバルの名前・外見、作中ジム名、赤と青の対比を軸にしたタイトル演出をそのまま使わない。</t>
         </is>
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>[事実]第1回コミックグランプリ受賞作として紹介されている（X直接検索なし） [感想]『楽しい部活もの』として明るさを評価する声が多い</t>
+          <t>[事実] 2024年12月に実写ドラマ化された。[感想] 陰キャ主人公の成長がMMA初心者にも読みやすいという紹介がある。[推測] 近年の少年誌MMA漫画として注目度が高いとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>https://ranking.net/items/14d871 | https://comic.k-manga.jp/title/12315/pv | https://shopping.bookoff.co.jp/s/8800000124</t>
+          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986</t>
         </is>
       </c>
       <c r="X116" s="2" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>火ノ丸相撲</t>
+          <t>紅の挑戦者</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ひのまるずもう</t>
+          <t>くれないのちょうせんしゃ</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -15224,87 +15224,87 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>川田</t>
+          <t>梶原一騎（高森朝雄名義とする資料もあるが未確認）</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>川田</t>
+          <t>中城健</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>集英社</t>
+          <t>未確認（電子版の発行元はグループ・ゼロ）</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>週刊少年ジャンプ</t>
+          <t>週刊少年マガジン（まとめサイトの記載。未確認）</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2014–2019（2014年26号〜2019年34号）</t>
+          <t>1973–1975（まとめサイトの記載。未確認）</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>ジャンプ・コミックス全28巻</t>
+          <t>全10巻（電子版）</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>相撲／学園／部活／スポーツ／王道少年</t>
+          <t>キックボクシング／ムエタイ／スポ根</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（GONZO制作）</t>
+          <t>同原作者・作画者の『キックの鬼』</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>体格のハンデを努力と技術で越える、仲間を集めて部を立て直す、誇り</t>
+          <t>高校サッカーのエースがキックボクシングに転向する挑戦、タイ・ムエタイとの対決</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>小柄な主人公の『足りなさ』を真正面から描き、負けの痛みと周囲の支えで立ち上がる</t>
+          <t>転向への迷いより、挑戦への覚悟を強調する昭和スポ根型。</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>熱量の高い独白と仲間の叫び、決意表明を短く重ねる（引用なし）</t>
+          <t>熱血で大げさな宣言調。</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>立ち合いの一瞬を大ゴマと集中線で強調、土俵際の粘りを連続コマで引き延ばす</t>
+          <t>劇画調、海外（タイ）を舞台にした異国感。</t>
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>部員の個性の掛け合い、日常パートの軽い誇張</t>
+          <t>ほぼなし。</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>技法：『小さい・弱いからこそ工夫する』を主題にする。オリジナル案：小柄な女性会員が、体格差を技術でかわすコツを覚えて笑顔になる回</t>
+          <t>技法：別競技からの転向者を主人公にすると、技術の違いを読者に説明しやすい。オリジナル案：サッカー経験者の会員が『蹴り』の感覚の違いに戸惑い、やがて武器にする話。</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見・四股名・必殺技名・部の名称は使わない</t>
+          <t>主人公の名前・外見、サッカーからキックへの転向をバンコクで宣言する導入をそのまま使わない。</t>
         </is>
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>[事実]相撲漫画ランキングで上位に紹介されている（X直接検索なし） [感想]熱い王道スポーツ漫画として評価が高い</t>
+          <t>[事実] 電子版で全10巻が配信されている。[感想] 梶原一騎のキックボクシング作品として紹介される。[推測] 現在の知名度は低いとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2 | https://mangapedia.com/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2-yq1wzu8h2 | https://www.b-ch.com/titles/6297/</t>
+          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/</t>
         </is>
       </c>
       <c r="X117" s="2" t="inlineStr">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ダンベル何キロ持てる？</t>
+          <t>YAWARA!</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>だんべるなんきろもてる</t>
+          <t>やわら</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -15351,12 +15351,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>サンドロビッチ・ヤバ子</t>
+          <t>浦沢直樹</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>MAAM</t>
+          <t>浦沢直樹</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -15366,72 +15366,72 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>マンガワン／裏サンデー</t>
+          <t>ビッグコミックスピリッツ</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2016–（連載中かどうかは未確認）</t>
+          <t>1986–1993</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>裏少年サンデーコミックス既刊20巻（2025年時点の資料。最新巻は未確認）</t>
+          <t>ビッグコミックス全29巻／文庫版全19巻／完全版全20巻</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>フィットネス／筋トレ／女子／ジム／ギャグ／教育</t>
+          <t>柔道／女子／青春／ラブコメ／スポーツ</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ化</t>
+          <t>Happy!（同作者のスポーツもの）</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>運動が苦手な人がジムに通い続ける楽しさ、正しい知識、仲間と続けること</t>
+          <t>才能と『普通の女の子でいたい』願いの葛藤、家族の期待、恋、自分で道を選ぶこと</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>ダイエット目的など軽い動機から始めて、できることが増える喜びに変わる過程</t>
+          <t>強さを隠したい本人の照れ・反発を丁寧に描き、周囲の期待とのズレを長期的な葛藤として育てる</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>トレーナーの解説とキャラの素直なリアクションの掛け合い、ハイテンション（引用なし）</t>
+          <t>日常会話中心の自然な口語。祖父キャラの大げさな物言いと主人公の控えめな返しの対比（引用なし）</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>筋肉の誇張表現と正しいフォームの図解を同じページで見せる</t>
+          <t>日常パートは軽い線と多めの間、試合は一瞬の技を見開きで見せる。観客・記者のリアクションで凄さを伝える</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>筋肉キャラの過剰さ、主人公の食欲・怠けとのギャップ、真面目な解説へのズレたリアクション</t>
+          <t>強すぎる祖父の暴走、恋愛の勘違い、主人公が強さを隠そうとしてバレるお約束</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>技法：笑いの中に正しい運動知識を一つずつ入れる『学べるギャグ』。オリジナル案：体験に来た女性が『格闘技＝痛い』と思い込み、実際はストレッチから始まって拍子抜けする回</t>
+          <t>技法：『強いのに普通でいたい』という主人公の心のズレで共感を作る。オリジナル案：家族に内緒で格闘技を始めた会社員女性が、通勤中に姿勢が良くなって同僚に気付かれるエピソード</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
-          <t>主人公・トレーナーのキャラデザ、ジム名、作中の掛け声や歌は使わない</t>
+          <t>主人公名・祖父キャラの造形、作品タイトルロゴ、特定の決め技の見せ方は使わない</t>
         </is>
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>[事実]アニメ化され、Kindle全巻セールが報じられている（X直接検索なし） [感想]筋トレ入門として役に立つという声が多い</t>
+          <t>[事実]小学館漫画賞受賞作として紹介され、女子柔道ブームと結び付けて語られることが多い（X直接検索なし） [感想]ラブコメとしても楽しめるという声が多い</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c</t>
+          <t>https://en.wikipedia.org/wiki/Yawara! | https://nlab.itmedia.co.jp/research/articles/128892/ | https://ranking.net/items/7c982a</t>
         </is>
       </c>
       <c r="X118" s="2" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ブラジュ～</t>
+          <t>帯をギュッとね!</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ぶらじゅ</t>
+          <t>おびをぎゅっとね</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -15478,87 +15478,87 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>クリスティー田村</t>
+          <t>河合克敏</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>クリスティー田村</t>
+          <t>河合克敏</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>ヤンマガWeb</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>2024–（連載中かどうかは未確認）</t>
+          <t>1988または1989–1995（1995年52号終了。開始年は資料で食い違い）</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>1巻は2024年11月20日発売。既刊数は未確認</t>
+          <t>少年サンデーコミックス全30巻／ワイド版全15巻／小学館文庫全16巻</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>ブラジリアン柔術／初心者／学園／青春</t>
+          <t>柔道／学園／部活／青春／ギャグ</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>モンキーターン（同作者）</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>格闘技を始めては辞めてきた高校生が柔術で続ける理由を見つける、知恵と経験が力に勝つ</t>
+          <t>ゼロから部を作る楽しさ、仲間、合理的な練習、楽しみながら強くなること</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>『どうせ続かない』という自己評価の低さから、小さな成功体験で変わる過程が軸（本編未読のため詳細は未確認）</t>
+          <t>苦しさよりも工夫と仲間との時間を前面に出し、負けの悔しさは短く強く描いて次へ切り替える</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>明るくテンポの良い掛け合い。技術解説を会話に溶け込ませる（引用なし）</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>作者の柔道経験を生かした技の分解描写、練習メニューの図解的コマ</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>部員同士のボケとツッコミ、恋愛がらみの勘違い、ゆるいキャラの脱力</t>
         </is>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>技法：『飽きっぽい初心者が続く理由』を物語の芯にする。オリジナル案：三日坊主の中学生が、毎回1つだけ技を覚えて帰る『今日のひとつ』ノートで続けられるようになる話</t>
+          <t>技法：技術の『なぜ』をキャラの会話で自然に説明する。オリジナル案：初心者が受け身を習う回で、コーチが『転び方が上手い人は人生でもケガしにくい』と語る短い場面</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
         <is>
-          <t>主人公名・先輩キャラの造形、作品タイトルの言い回しは使わない</t>
+          <t>主要部員の外見・あだ名、部の名前、作中の学校名は使わない</t>
         </is>
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>[事実]柔術関係者のブログで連載開始が好意的に取り上げられている（X直接検索なし） [推測]柔術を正面から描く漫画が少ないため競技者の注目度は高い</t>
+          <t>[事実]第1回コミックグランプリ受賞作として紹介されている（X直接検索なし） [感想]『楽しい部活もの』として明るさを評価する声が多い</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/labels/ymweb?page=15 | https://bookwalker.jp/de2c689ec9-3c95-40fb-9398-b5d5c42cf5d4/ | https://m-dojo.hatenadiary.com/entry/2024/08/26/215830</t>
+          <t>https://ranking.net/items/14d871 | https://comic.k-manga.jp/title/12315/pv | https://shopping.bookoff.co.jp/s/8800000124</t>
         </is>
       </c>
       <c r="X119" s="2" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -15580,12 +15580,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>ROLLS</t>
+          <t>火ノ丸相撲</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ろーるず</t>
+          <t>ひのまるずもう</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -15605,87 +15605,87 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>カズ・ヤンセ</t>
+          <t>川田</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>カズ・ヤンセ</t>
+          <t>川田</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>少年画報社</t>
+          <t>集英社</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>ヤングキングBULL</t>
+          <t>週刊少年ジャンプ</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>未確認（2026年時点で連載中とする報道あり）</t>
+          <t>2014–2019（2014年26号〜2019年34号）</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>1巻は2026年5月18日発売（YKコミックス）。既刊数は未確認</t>
+          <t>ジャンプ・コミックス全28巻</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>ブラジリアン柔術／学園／青春／格闘技</t>
+          <t>相撲／学園／部活／スポーツ／王道少年</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>TVアニメ（GONZO制作）</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>高校1年生が柔術を嗜む先輩と出会って始まる青春格闘ストーリー（詳細は未確認）</t>
+          <t>体格のハンデを努力と技術で越える、仲間を集めて部を立て直す、誇り</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>小柄な主人公の『足りなさ』を真正面から描き、負けの痛みと周囲の支えで立ち上がる</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>熱量の高い独白と仲間の叫び、決意表明を短く重ねる（引用なし）</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>立ち合いの一瞬を大ゴマと集中線で強調、土俵際の粘りを連続コマで引き延ばす</t>
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>部員の個性の掛け合い、日常パートの軽い誇張</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>技法：『先輩との出会い』を入口にした入門もの。オリジナル案：帯の色が違う先輩が、初日の後輩に寝技の『逃げ方』だけを教えて安心させる場面</t>
+          <t>技法：『小さい・弱いからこそ工夫する』を主題にする。オリジナル案：小柄な女性会員が、体格差を技術でかわすコツを覚えて笑顔になる回</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">
         <is>
-          <t>主人公・先輩の名前と外見、作品ロゴは使わない</t>
+          <t>主人公の外見・四股名・必殺技名・部の名称は使わない</t>
         </is>
       </c>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>[事実]作者がXで柔術漫画として告知している（X直接検索なし、Web検索結果で確認） [推測]刊行直後のため評判の蓄積は少ない</t>
+          <t>[事実]相撲漫画ランキングで上位に紹介されている（X直接検索なし） [感想]熱い王道スポーツ漫画として評価が高い</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
         <is>
-          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE</t>
+          <t>https://dic.nicovideo.jp/a/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2 | https://mangapedia.com/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2-yq1wzu8h2 | https://www.b-ch.com/titles/6297/</t>
         </is>
       </c>
       <c r="X120" s="2" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>鉄風</t>
+          <t>ダンベル何キロ持てる？</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>てっぷう</t>
+          <t>だんべるなんきろもてる</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -15732,87 +15732,87 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>太田モアレ</t>
+          <t>サンドロビッチ・ヤバ子</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>太田モアレ</t>
+          <t>MAAM</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>good!アフタヌーン</t>
+          <t>マンガワン／裏サンデー</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>未確認–2015（2015年8号で完結とする資料あり）</t>
+          <t>2016–（連載中かどうかは未確認）</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>全8巻</t>
+          <t>裏少年サンデーコミックス既刊20巻（2025年時点の資料。最新巻は未確認）</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>総合格闘技／女子／グラップリング／青春</t>
+          <t>フィットネス／筋トレ／女子／ジム／ギャグ／教育</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>TVアニメ化</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>才能ある少女が総合格闘技に出会い、勝ちたい・強くなりたい欲と向き合う</t>
+          <t>運動が苦手な人がジムに通い続ける楽しさ、正しい知識、仲間と続けること</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>主人公の傲慢さや退屈さなど、きれいではない動機を隠さずに描く点が特徴（詳細は要再確認）</t>
+          <t>ダイエット目的など軽い動機から始めて、できることが増える喜びに変わる過程</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>淡々とした会話と短い心の声（引用なし。詳細は要再確認）</t>
+          <t>トレーナーの解説とキャラの素直なリアクションの掛け合い、ハイテンション（引用なし）</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>組み技・関節技の体の絡みを細かく描く（詳細は要再確認）</t>
+          <t>筋肉の誇張表現と正しいフォームの図解を同じページで見せる</t>
         </is>
       </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>筋肉キャラの過剰さ、主人公の食欲・怠けとのギャップ、真面目な解説へのズレたリアクション</t>
         </is>
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>技法：女子が格闘技にのめり込む理由を『かっこいい』だけでなく本音で描く。オリジナル案：負けず嫌いな女子高生が、勝つことより『昨日の自分に勝つ』ことに価値を見つける話</t>
+          <t>技法：笑いの中に正しい運動知識を一つずつ入れる『学べるギャグ』。オリジナル案：体験に来た女性が『格闘技＝痛い』と思い込み、実際はストレッチから始まって拍子抜けする回</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見・ジム名・対戦相手キャラの造形は使わない</t>
+          <t>主人公・トレーナーのキャラデザ、ジム名、作中の掛け声や歌は使わない</t>
         </is>
       </c>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>[感想]女子格闘技漫画のおすすめ記事で紹介されることがある（X直接検索なし） [推測]完結済みで知名度は中程度</t>
+          <t>[事実]アニメ化され、Kindle全巻セールが報じられている（X直接検索なし） [感想]筋トレ入門として役に立つという声が多い</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/</t>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c</t>
         </is>
       </c>
       <c r="X121" s="2" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -15834,12 +15834,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>もういっぽん！</t>
+          <t>ブラジュ～</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>もういっぽん</t>
+          <t>ぶらじゅ</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -15859,87 +15859,87 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>村岡ユウ</t>
+          <t>クリスティー田村</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>村岡ユウ</t>
+          <t>クリスティー田村</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>秋田書店</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン</t>
+          <t>ヤンマガWeb</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2018–（終了時期は未確認）</t>
+          <t>2024–（連載中かどうかは未確認）</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>少年チャンピオン・コミックス。総巻数・完結有無は未確認</t>
+          <t>1巻は2024年11月20日発売。既刊数は未確認</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>柔道／女子／部活／青春／初心者</t>
+          <t>ブラジリアン柔術／初心者／学園／青春</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（2023年冬、全13話）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>一度やめかけた柔道をもう一度好きになる、女子部員の友情、楽しむ気持ち</t>
+          <t>格闘技を始めては辞めてきた高校生が柔術で続ける理由を見つける、知恵と経験が力に勝つ</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>勝ち負けより『好き』を取り戻す気持ちの揺れを、友達との会話の中で自然に描く</t>
+          <t>『どうせ続かない』という自己評価の低さから、小さな成功体験で変わる過程が軸（本編未読のため詳細は未確認）</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>女子高生らしい明るい会話のテンポ、試合中は短い声かけ（引用なし）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>表情のアップを多用し、技の瞬間は爽やかな効果線で見せる</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>仲間同士のじゃれ合い、日常のゆるい会話のズレ</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>技法：『また来たくなる』気持ちを友達の存在で描く。オリジナル案：一度辞めたママ会員が子どもの練習を見学して『もう一回やりたい』と言い出す話</t>
+          <t>技法：『飽きっぽい初心者が続く理由』を物語の芯にする。オリジナル案：三日坊主の中学生が、毎回1つだけ技を覚えて帰る『今日のひとつ』ノートで続けられるようになる話</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
-          <t>主人公たちの外見・校名・部のユニフォームデザインは使わない</t>
+          <t>主人公名・先輩キャラの造形、作品タイトルの言い回しは使わない</t>
         </is>
       </c>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>[事実]アニメ化されている（X直接検索なし） [感想]女子部活ものとして爽やかで読みやすいという声</t>
+          <t>[事実]柔術関係者のブログで連載開始が好意的に取り上げられている（X直接検索なし） [推測]柔術を正面から描く漫画が少ないため競技者の注目度は高い</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
         <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253228039 | https://www.b-ch.com/titles/8013 | https://en.wikipedia.org/wiki/Ippon_Again!</t>
+          <t>https://www.kodansha.co.jp/comic/labels/ymweb?page=15 | https://bookwalker.jp/de2c689ec9-3c95-40fb-9398-b5d5c42cf5d4/ | https://m-dojo.hatenadiary.com/entry/2024/08/26/215830</t>
         </is>
       </c>
       <c r="X122" s="2" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -15961,12 +15961,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>あさひなぐ</t>
+          <t>ROLLS</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>あさひなぐ</t>
+          <t>ろーるず</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -15986,87 +15986,87 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>こざき亜衣</t>
+          <t>カズ・ヤンセ</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>こざき亜衣</t>
+          <t>カズ・ヤンセ</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>少年画報社</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックスピリッツ</t>
+          <t>ヤングキングBULL</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>2011–2020（2020年41号で完結）</t>
+          <t>未確認（2026年時点で連載中とする報道あり）</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックス全34巻</t>
+          <t>1巻は2026年5月18日発売（YKコミックス）。既刊数は未確認</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>薙刀／女子／部活／初心者／青春</t>
+          <t>ブラジリアン柔術／学園／青春／格闘技</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>実写映画・舞台（2017年）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>運動経験ゼロの少女が武道を始め、弱さを認めながら強くなる</t>
+          <t>高校1年生が柔術を嗜む先輩と出会って始まる青春格闘ストーリー（詳細は未確認）</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>運動音痴の劣等感、仲間との差、怖さを丁寧に積み、少しずつ自信を得る過程を長く描く</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>等身大の女子高生の会話、心の声で弱気と強がりを交互に見せる（引用なし）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>日常の柔らかい絵柄と、試合での鋭い目線・構えのアップの落差</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>主人公のドジ、先輩の個性の誇張、真剣な稽古中のズレたリアクション</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>技法：『運動ができない子が主人公』で読者の入口を広げる。オリジナル案：体育が苦手だった女の子が、初めてミットを鳴らした音に自分でびっくりする場面</t>
+          <t>技法：『先輩との出会い』を入口にした入門もの。オリジナル案：帯の色が違う先輩が、初日の後輩に寝技の『逃げ方』だけを教えて安心させる場面</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
         <is>
-          <t>主人公の眼鏡キャラ造形・名前、校名、薙刀部の固有設定は使わない</t>
+          <t>主人公・先輩の名前と外見、作品ロゴは使わない</t>
         </is>
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>[事実]小学館漫画賞（第60回）を受賞し、実写映画化された（X直接検索なし） [感想]運動が苦手な人ほど共感できるという声</t>
+          <t>[事実]作者がXで柔術漫画として告知している（X直接検索なし、Web検索結果で確認） [推測]刊行直後のため評判の蓄積は少ない</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>https://www.crank-in.net/news/80665 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=18369 | https://comic.k-manga.jp/title/57348/pv</t>
+          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE</t>
         </is>
       </c>
       <c r="X123" s="2" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>クロオビ！隼太</t>
+          <t>鉄風</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>くろおびはやた</t>
+          <t>てっぷう</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>作田和哉</t>
+          <t>太田モアレ</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>作田和哉</t>
+          <t>太田モアレ</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -16128,72 +16128,72 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>月刊少年ライバル</t>
+          <t>good!アフタヌーン</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
+          <t>未確認–2015（2015年8号で完結とする資料あり）</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>全8巻</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>総合格闘技／女子／グラップリング／青春</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>全9巻</t>
-        </is>
-      </c>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>空手／キッズ／小学生／伝統派空手／道場</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>才能ある少女が総合格闘技に出会い、勝ちたい・強くなりたい欲と向き合う</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>主人公の傲慢さや退屈さなど、きれいではない動機を隠さずに描く点が特徴（詳細は要再確認）</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>淡々とした会話と短い心の声（引用なし。詳細は要再確認）</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>組み技・関節技の体の絡みを細かく描く（詳細は要再確認）</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>アニメヒーローに憧れる小学5年生が空手と出会い、道場で成長する</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>子どもらしい憧れを入口に、稽古の地道さと向き合う過程（詳細は未確認）</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>未確認（本編未読）</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="inlineStr">
-        <is>
-          <t>未確認（本編未読）</t>
-        </is>
-      </c>
-      <c r="S124" s="2" t="inlineStr">
-        <is>
-          <t>未確認（本編未読）</t>
-        </is>
-      </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>技法：『ヒーローへの憧れ』を入門の動機にする。オリジナル案：変身ヒーローごっこが好きな小1が、本物の構えを習って家で保護者に見せる回</t>
+          <t>技法：女子が格闘技にのめり込む理由を『かっこいい』だけでなく本音で描く。オリジナル案：負けず嫌いな女子高生が、勝つことより『昨日の自分に勝つ』ことに価値を見つける話</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前・外見、作中の流派名や道場名は使わない</t>
+          <t>主人公の外見・ジム名・対戦相手キャラの造形は使わない</t>
         </is>
       </c>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>[感想]キッズ空手サイトのおすすめ空手漫画として紹介されている（X直接検索なし）</t>
+          <t>[感想]女子格闘技漫画のおすすめ記事で紹介されることがある（X直接検索なし） [推測]完結済みで知名度は中程度</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/</t>
         </is>
       </c>
       <c r="X124" s="2" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -16215,12 +16215,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>柔道部物語</t>
+          <t>もういっぽん！</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>じゅうどうぶものがたり</t>
+          <t>もういっぽん</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>単独（小林まこと柔道作品群）</t>
+          <t>単独</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -16240,87 +16240,87 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>小林まこと</t>
+          <t>村岡ユウ</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>小林まこと</t>
+          <t>村岡ユウ</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>秋田書店</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングマガジン</t>
+          <t>週刊少年チャンピオン</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>1985–1991（1985年18号〜1991年32号とする資料あり）</t>
+          <t>2018–（終了時期は未確認）</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>ヤンマガKCスペシャル全11巻／文庫版全7巻</t>
+          <t>少年チャンピオン・コミックス。総巻数・完結有無は未確認</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>柔道／学園／部活／ギャグ／スポ根</t>
+          <t>柔道／女子／部活／青春／初心者</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>JJM 女子柔道部物語（同作者の女子柔道もの）／1・2の三四郎（同作者）</t>
+          <t>TVアニメ（2023年冬、全13話）</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>素人が理不尽な部活文化の中で本物の強さを身につける成長、仲間意識、努力の積み重ね</t>
+          <t>一度やめかけた柔道をもう一度好きになる、女子部員の友情、楽しむ気持ち</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>入部直後の恐怖・場違い感を笑いで包みつつ、しごきを経て自信が芽生える過程を段階的に描く。勝負前の緊張は短い独白と表情で処理し、重くしすぎない</t>
+          <t>勝ち負けより『好き』を取り戻す気持ちの揺れを、友達との会話の中で自然に描く</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>体育会系の掛け声と短い命令口調、方言まじりの軽口。真剣な場面ほどセリフを削る（引用なし）</t>
+          <t>女子高生らしい明るい会話のテンポ、試合中は短い声かけ（引用なし）</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>投げ技の瞬間を大ゴマで止め、直前直後は小ゴマで畳みかける緩急。汗・畳の音などの描き文字で臨場感を出す</t>
+          <t>表情のアップを多用し、技の瞬間は爽やかな効果線で見せる</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>先輩後輩の上下関係の誇張、真顔で起きるズレ、極端なしごきを淡々と描く落差ギャグ</t>
+          <t>仲間同士のじゃれ合い、日常のゆるい会話のズレ</t>
         </is>
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>技法：初心者の『怖い→できた』を1話完結の小さな成功で積む構成。FLATUPでは逆に『しごきゼロ』を明示し、昔の部活の怖さと対比させる。オリジナル案：昔の部活トラウマを持つ大人会員が、優しいコーチに戸惑う『怒られないの？』ギャグ</t>
+          <t>技法：『また来たくなる』気持ちを友達の存在で描く。オリジナル案：一度辞めたママ会員が子どもの練習を見学して『もう一回やりたい』と言い出す話</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
         <is>
-          <t>主人公・先輩キャラの外見や髪型、校名・部の固有名、特徴的な歌や儀式ネタは使わない</t>
+          <t>主人公たちの外見・校名・部のユニフォームデザインは使わない</t>
         </is>
       </c>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>[事実]柔道漫画ランキング記事で上位常連として紹介されている（X直接検索なし） [感想]経験者から『柔道部のリアル』と評されることが多い [推測]しごき描写は現代の価値観では賛否が分かれる</t>
+          <t>[事実]アニメ化されている（X直接検索なし） [感想]女子部活ものとして爽やかで読みやすいという声</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E | https://www.nihon-u.ac.jp/sports_sciences/files/news/689/pdf1.pdf | https://www.cmoa.jp/title/5030/</t>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253228039 | https://www.b-ch.com/titles/8013 | https://en.wikipedia.org/wiki/Ippon_Again!</t>
         </is>
       </c>
       <c r="X125" s="2" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売</t>
+          <t>あさひなぐ</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>けんかしょうばい</t>
+          <t>あさひなぐ</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売シリーズ</t>
+          <t>単独</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -16367,87 +16367,87 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>こざき亜衣</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>こざき亜衣</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングマガジン</t>
+          <t>ビッグコミックスピリッツ</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2005–2010（2005年6月〜2010年9月、第一部）</t>
+          <t>2011–2020（2020年41号で完結）</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>全24巻（ヤングマガジンコミックス）</t>
+          <t>ビッグコミックス全34巻</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>格闘技／喧嘩／ギャグ／心理戦</t>
+          <t>薙刀／女子／部活／初心者／青春</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>喧嘩稼業（第二部）。同じ作者に幕張、泣くようぐいす</t>
+          <t>実写映画・舞台（2017年）</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>勝つための知恵と準備、恐怖の克服、強さへの執着</t>
+          <t>運動経験ゼロの少女が武道を始め、弱さを認めながら強くなる</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>勝負の前の情報戦・読み合いを内面の思考で細かく描き、追い詰められた時の恐怖や覚悟を強調する</t>
+          <t>運動音痴の劣等感、仲間との差、怖さを丁寧に積み、少しずつ自信を得る過程を長く描く</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>格闘パートは理詰めの解説と短い言葉の読み合い、ギャグパートは下品さも含む過激なボケが続く</t>
+          <t>等身大の女子高生の会話、心の声で弱気と強がりを交互に見せる（引用なし）</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>技の仕組みを図解的に見せるコマ、決着の瞬間の大ゴマ。格闘とギャグで絵のタッチの密度を変える</t>
+          <t>日常の柔らかい絵柄と、試合での鋭い目線・構えのアップの落差</t>
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>実在人物いじりや下ネタなど過激な落差ギャグ（FLATUPでは使わない種類）</t>
+          <t>主人公のドジ、先輩の個性の誇張、真剣な稽古中のズレたリアクション</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>技法：技の理屈を図解で見せて読者に『なるほど』と思わせる解説コマ、試合前の作戦会議で緊張を高める構成。アイデア：トレーナーが初心者に、ジャブがなぜ大事かを図解で説明する学習まんが風の回。オリジナルの一言案「勝ち方より、ケガしない負け方から覚えよう」</t>
+          <t>技法：『運動ができない子が主人公』で読者の入口を広げる。オリジナル案：体育が苦手だった女の子が、初めてミットを鳴らした音に自分でびっくりする場面</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
-          <t>主人公・師匠の外見、作中の流派名や秘技名、トーナメント名、実在人物いじりの手法を使わない。過激な下ネタや他者を傷つけるギャグはブランド方針に反する</t>
+          <t>主人公の眼鏡キャラ造形・名前、校名、薙刀部の固有設定は使わない</t>
         </is>
       </c>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>[事実] 第一部24巻で完結し、第二部の喧嘩稼業へ続いた。[感想] 格闘の読み合いが面白いという声と、ギャグの過激さが好みを分けるという声がある。[推測] 格闘ファンの間でカルト的人気。X直接検索なし</t>
+          <t>[事実]小学館漫画賞（第60回）を受賞し、実写映画化された（X直接検索なし） [感想]運動が苦手な人ほど共感できるという声</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000011088 | https://comic.k-manga.jp/title/103703/pv | https://dic.nicovideo.jp/a/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD</t>
+          <t>https://www.crank-in.net/news/80665 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=18369 | https://comic.k-manga.jp/title/57348/pv</t>
         </is>
       </c>
       <c r="X126" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Y126" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -16469,12 +16469,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>喧嘩稼業</t>
+          <t>クロオビ！隼太</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>けんかかぎょう</t>
+          <t>くろおびはやた</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -16484,22 +16484,22 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売シリーズ</t>
+          <t>単独</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>作田和哉</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>作田和哉</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -16509,72 +16509,72 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングマガジン</t>
+          <t>月刊少年ライバル</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>2013年12月発売号（2014年2・3合併号）〜。長期休載があり現在の状況は未確認</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>未確認（講談社ページで5巻・7巻の刊行を確認。7巻は2016年6月発売）</t>
+          <t>全9巻</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>格闘技／トーナメント／心理戦／ギャグ</t>
+          <t>空手／キッズ／小学生／伝統派空手／道場</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売（第一部）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>最強を決めるトーナメント、勝利への執念、師弟、因縁</t>
+          <t>アニメヒーローに憧れる小学5年生が空手と出会い、道場で成長する</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>各選手の過去と動機を試合ごとに掘り下げ、試合中の思考を細かく追う。読み合いの裏切りで緊張を保つ</t>
+          <t>子どもらしい憧れを入口に、稽古の地道さと向き合う過程（詳細は未確認）</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>解説役の分析と選手の内心が交互に入り、短いやり取りで駆け引きを見せる</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>トーナメントの一試合を長く描き、決着の一撃に向けてコマを細かく刻んでから大ゴマで解放する</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
         <is>
-          <t>第一部よりギャグは減るが、試合の合間に過激な落差ギャグが入る</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>技法：試合前に選手の背景回を入れて応援したくなる構造、細かいコマで時間を引き延ばしてから大ゴマで決める。アイデア：ジム内の初心者マス大会で、出場者それぞれの『始めた理由』を一話ずつ描く。オリジナルの一言案「ここに立った時点で、もう昨日の自分には勝ってる」</t>
+          <t>技法：『ヒーローへの憧れ』を入門の動機にする。オリジナル案：変身ヒーローごっこが好きな小1が、本物の構えを習って家で保護者に見せる回</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
         <is>
-          <t>トーナメント名・出場者の外見や実在格闘家を思わせる造形、技名、試合カードの組み方を使わない</t>
+          <t>主人公の名前・外見、作中の流派名や道場名は使わない</t>
         </is>
       </c>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>[事実] 長期休載が多い作品として記事で触れられている。[感想] 続きを待ち続けているという声が多い。[推測] 再開のたびに話題になる。X直接検索なし</t>
+          <t>[感想]キッズ空手サイトのおすすめ空手漫画として紹介されている（X直接検索なし）</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q</t>
+          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic</t>
         </is>
       </c>
       <c r="X127" s="2" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>鉄拳チンミ</t>
+          <t>柔道部物語</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>てっけんちんみ</t>
+          <t>じゅうどうぶものがたり</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>鉄拳チンミシリーズ</t>
+          <t>単独（小林まこと柔道作品群）</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16621,12 +16621,12 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>小林まこと</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>小林まこと</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -16636,72 +16636,72 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>月刊少年マガジン</t>
+          <t>週刊ヤングマガジン</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>1983–1997（開始は1983年。終了年は二次情報による）</t>
+          <t>1985–1991（1985年18号〜1991年32号とする資料あり）</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>全35巻（講談社コミックス）</t>
+          <t>ヤンマガKCスペシャル全11巻／文庫版全7巻</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>カンフー／修行／冒険／少年</t>
+          <t>柔道／学園／部活／ギャグ／スポ根</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>続編：新・鉄拳チンミ、鉄拳チンミLegends。外伝：鉄拳チンミ外伝</t>
+          <t>JJM 女子柔道部物語（同作者の女子柔道もの）／1・2の三四郎（同作者）</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>修行による成長、師弟関係、優しさと強さ、仲間との友情</t>
+          <t>素人が理不尽な部活文化の中で本物の強さを身につける成長、仲間意識、努力の積み重ね</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>小さな少年が恐怖を感じながらも一歩踏み出す勇気を、素直な表情で描く。暴力的になりすぎず、相手を思いやる気持ちを大切にする。</t>
+          <t>入部直後の恐怖・場違い感を笑いで包みつつ、しごきを経て自信が芽生える過程を段階的に描く。勝負前の緊張は短い独白と表情で処理し、重くしすぎない</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>やさしく分かりやすい言葉。師匠は短い言葉で教え、弟子は素直に返す。</t>
+          <t>体育会系の掛け声と短い命令口調、方言まじりの軽口。真剣な場面ほどセリフを削る（引用なし）</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>丸みのある親しみやすい絵柄。技のコツを図解のように見せるコマ。動物キャラ（相棒）の表情で緊張をほぐす。</t>
+          <t>投げ技の瞬間を大ゴマで止め、直前直後は小ゴマで畳みかける緩急。汗・畳の音などの描き文字で臨場感を出す</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>相棒の小動物のリアクション、子どもらしい食いしん坊さ、大人たちの大げさな驚き。</t>
+          <t>先輩後輩の上下関係の誇張、真顔で起きるズレ、極端なしごきを淡々と描く落差ギャグ</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>技法：『初心者が一歩ずつ上達する』を素直に描く少年漫画の型。FLATUPに最も近い思想の作品。FLATUP案：キッズ会員が受け身を覚えるまでの3話シリーズ。オリジナル台詞案『こわいって言えたら、もう一歩目だよ』。</t>
+          <t>技法：初心者の『怖い→できた』を1話完結の小さな成功で積む構成。FLATUPでは逆に『しごきゼロ』を明示し、昔の部活の怖さと対比させる。オリジナル案：昔の部活トラウマを持つ大人会員が、優しいコーチに戸惑う『怒られないの？』ギャグ</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+          <t>主人公・先輩キャラの外見や髪型、校名・部の固有名、特徴的な歌や儀式ネタは使わない</t>
         </is>
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]1987年に講談社漫画賞を受賞。[事実]1988年にTVアニメ化（二次情報）。[感想]子どもでも読める王道カンフー漫画として長く愛されている。</t>
+          <t>[事実]柔道漫画ランキング記事で上位常連として紹介されている（X直接検索なし） [感想]経験者から『柔道部のリアル』と評されることが多い [推測]しごき描写は現代の価値観では賛否が分かれる</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000043199 | https://www.cmoa.jp/title/5029</t>
+          <t>https://dic.nicovideo.jp/a/%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E | https://www.nihon-u.ac.jp/sports_sciences/files/news/689/pdf1.pdf | https://www.cmoa.jp/title/5030/</t>
         </is>
       </c>
       <c r="X128" s="2" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -16723,12 +16723,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>新・鉄拳チンミ</t>
+          <t>喧嘩商売</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>しん・てっけんちんみ</t>
+          <t>けんかしょうばい</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -16738,22 +16738,22 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>鉄拳チンミシリーズ</t>
+          <t>喧嘩商売シリーズ</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>木多康昭</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>木多康昭</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -16763,72 +16763,72 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>月刊少年マガジン</t>
+          <t>週刊ヤングマガジン</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>1990年代後半–2004年頃（第20巻の初出が2004年7月号–11月号。開始年は未確認）</t>
+          <t>2005–2010（2005年6月〜2010年9月、第一部）</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）</t>
+          <t>全24巻（ヤングマガジンコミックス）</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>カンフー／冒険／少年</t>
+          <t>格闘技／喧嘩／ギャグ／心理戦</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>前作：鉄拳チンミ。次作：鉄拳チンミLegends</t>
+          <t>喧嘩稼業（第二部）。同じ作者に幕張、泣くようぐいす</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>成長した主人公の旅、守るための強さ</t>
+          <t>勝つための知恵と準備、恐怖の克服、強さへの執着</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>少年から青年へ成長する主人公が、弟子や年下を守る側に回る責任感を描く。</t>
+          <t>勝負の前の情報戦・読み合いを内面の思考で細かく描き、追い詰められた時の恐怖や覚悟を強調する</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>前作同様、分かりやすくやさしい語り口。</t>
+          <t>格闘パートは理詰めの解説と短い言葉の読み合い、ギャグパートは下品さも含む過激なボケが続く</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>編（エピソード）ごとに舞台を変える冒険構成。</t>
+          <t>技の仕組みを図解的に見せるコマ、決着の瞬間の大ゴマ。格闘とギャグで絵のタッチの密度を変える</t>
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>相棒動物や旅の仲間の掛け合い。</t>
+          <t>実在人物いじりや下ネタなど過激な落差ギャグ（FLATUPでは使わない種類）</t>
         </is>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>技法：教わる側から教える側へ回る成長の描き方。FLATUP案：入会2年目の会員が、新しく来た初心者に準備運動を教える回。</t>
+          <t>技法：技の理屈を図解で見せて読者に『なるほど』と思わせる解説コマ、試合前の作戦会議で緊張を高める構成。アイデア：トレーナーが初心者に、ジャブがなぜ大事かを図解で説明する学習まんが風の回。オリジナルの一言案「勝ち方より、ケガしない負け方から覚えよう」</t>
         </is>
       </c>
       <c r="U129" s="2" t="inlineStr">
         <is>
-          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+          <t>主人公・師匠の外見、作中の流派名や秘技名、トーナメント名、実在人物いじりの手法を使わない。過激な下ネタや他者を傷つけるギャグはブランド方針に反する</t>
         </is>
       </c>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]前作の雰囲気を引き継いだ続編として読まれている。[推測]前作ほどの知名度はない。</t>
+          <t>[事実] 第一部24巻で完結し、第二部の喧嘩稼業へ続いた。[感想] 格闘の読み合いが面白いという声と、ギャグの過激さが好みを分けるという声がある。[推測] 格闘ファンの間でカルト的人気。X直接検索なし</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000011088 | https://comic.k-manga.jp/title/103703/pv | https://dic.nicovideo.jp/a/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD</t>
         </is>
       </c>
       <c r="X129" s="2" t="inlineStr">
@@ -16850,127 +16850,508 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
+          <t>喧嘩稼業</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>けんかかぎょう</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>格闘技・武道</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>喧嘩商売シリーズ</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>続編</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>木多康昭</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>木多康昭</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>講談社</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>週刊ヤングマガジン</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>2013年12月発売号（2014年2・3合併号）〜。長期休載があり現在の状況は未確認</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>未確認（講談社ページで5巻・7巻の刊行を確認。7巻は2016年6月発売）</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>格闘技／トーナメント／心理戦／ギャグ</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>喧嘩商売（第一部）</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>最強を決めるトーナメント、勝利への執念、師弟、因縁</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>各選手の過去と動機を試合ごとに掘り下げ、試合中の思考を細かく追う。読み合いの裏切りで緊張を保つ</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>解説役の分析と選手の内心が交互に入り、短いやり取りで駆け引きを見せる</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>トーナメントの一試合を長く描き、決着の一撃に向けてコマを細かく刻んでから大ゴマで解放する</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>第一部よりギャグは減るが、試合の合間に過激な落差ギャグが入る</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>技法：試合前に選手の背景回を入れて応援したくなる構造、細かいコマで時間を引き延ばしてから大ゴマで決める。アイデア：ジム内の初心者マス大会で、出場者それぞれの『始めた理由』を一話ずつ描く。オリジナルの一言案「ここに立った時点で、もう昨日の自分には勝ってる」</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>トーナメント名・出場者の外見や実在格闘家を思わせる造形、技名、試合カードの組み方を使わない</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>[事実] 長期休載が多い作品として記事で触れられている。[感想] 続きを待ち続けているという声が多い。[推測] 再開のたびに話題になる。X直接検索なし</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>W130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>鉄拳チンミ</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>てっけんちんみ</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>格闘技・武道</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>鉄拳チンミシリーズ</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>本編</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>講談社</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>月刊少年マガジン</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>1983–1997（開始は1983年。終了年は二次情報による）</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>全35巻（講談社コミックス）</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>カンフー／修行／冒険／少年</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>続編：新・鉄拳チンミ、鉄拳チンミLegends。外伝：鉄拳チンミ外伝</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>修行による成長、師弟関係、優しさと強さ、仲間との友情</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>小さな少年が恐怖を感じながらも一歩踏み出す勇気を、素直な表情で描く。暴力的になりすぎず、相手を思いやる気持ちを大切にする。</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>やさしく分かりやすい言葉。師匠は短い言葉で教え、弟子は素直に返す。</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>丸みのある親しみやすい絵柄。技のコツを図解のように見せるコマ。動物キャラ（相棒）の表情で緊張をほぐす。</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>相棒の小動物のリアクション、子どもらしい食いしん坊さ、大人たちの大げさな驚き。</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>技法：『初心者が一歩ずつ上達する』を素直に描く少年漫画の型。FLATUPに最も近い思想の作品。FLATUP案：キッズ会員が受け身を覚えるまでの3話シリーズ。オリジナル台詞案『こわいって言えたら、もう一歩目だよ』。</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>X直接検索なし。[事実]1987年に講談社漫画賞を受賞。[事実]1988年にTVアニメ化（二次情報）。[感想]子どもでも読める王道カンフー漫画として長く愛されている。</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000043199 | https://www.cmoa.jp/title/5029</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>W131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>新・鉄拳チンミ</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>しん・てっけんちんみ</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>格闘技・武道</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>鉄拳チンミシリーズ</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>続編</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>講談社</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>月刊少年マガジン</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>1990年代後半–2004年頃（第20巻の初出が2004年7月号–11月号。開始年は未確認）</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>カンフー／冒険／少年</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>前作：鉄拳チンミ。次作：鉄拳チンミLegends</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>成長した主人公の旅、守るための強さ</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>少年から青年へ成長する主人公が、弟子や年下を守る側に回る責任感を描く。</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>前作同様、分かりやすくやさしい語り口。</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>編（エピソード）ごとに舞台を変える冒険構成。</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>相棒動物や旅の仲間の掛け合い。</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>技法：教わる側から教える側へ回る成長の描き方。FLATUP案：入会2年目の会員が、新しく来た初心者に準備運動を教える回。</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>X直接検索なし。[感想]前作の雰囲気を引き継いだ続編として読まれている。[推測]前作ほどの知名度はない。</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>W132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>鉄拳チンミLegends</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>てっけんちんみれじぇんず</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>格闘技・武道</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>鉄拳チンミシリーズ</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>続編</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>前川たけし</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>前川たけし</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>講談社</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>月刊少年マガジン</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>2006–連載中（第1巻初出 2006年9月号〜。休載期間あり）</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="L133" s="2" t="inlineStr">
         <is>
           <t>既刊29巻（第29巻 2026年6月刊行）</t>
         </is>
       </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="M133" s="2" t="inlineStr">
         <is>
           <t>カンフー／冒険／少年</t>
         </is>
       </c>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="N133" s="2" t="inlineStr">
         <is>
           <t>前作：鉄拳チンミ、新・鉄拳チンミ</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>伝説となった武術家の旅、正義と思いやり</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr">
+      <c r="P133" s="2" t="inlineStr">
         <is>
           <t>長い連載の中で、主人公の落ち着きと周囲の若者の未熟さを対比させる。</t>
         </is>
       </c>
-      <c r="Q130" s="2" t="inlineStr">
+      <c r="Q133" s="2" t="inlineStr">
         <is>
           <t>シリーズ共通のやさしい語り口。</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr">
+      <c r="R133" s="2" t="inlineStr">
         <is>
           <t>冒険活劇の構成と、技の見せ場の大ゴマ。</t>
         </is>
       </c>
-      <c r="S130" s="2" t="inlineStr">
+      <c r="S133" s="2" t="inlineStr">
         <is>
           <t>相棒動物・仲間の掛け合い。</t>
         </is>
       </c>
-      <c r="T130" s="2" t="inlineStr">
+      <c r="T133" s="2" t="inlineStr">
         <is>
           <t>技法：長期シリーズでも『やさしい強さ』の芯をぶらさない。FLATUP案：ブランドの思想（強さ＝やさしさ）を毎話の結末で確認する構成ルール。</t>
         </is>
       </c>
-      <c r="U130" s="2" t="inlineStr">
+      <c r="U133" s="2" t="inlineStr">
         <is>
           <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
         </is>
       </c>
-      <c r="V130" s="2" t="inlineStr">
+      <c r="V133" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]第28巻（2021年）から第29巻（2026年）まで刊行間隔が空き、連載再開が講談社から告知された。[感想]再開を喜ぶ長年の読者の声がある。</t>
         </is>
       </c>
-      <c r="W130" s="2" t="inlineStr">
+      <c r="W133" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000426730 | https://news.kodansha.co.jp/comics/8666 | https://www.kodansha.co.jp/comic/products/0000041420</t>
         </is>
       </c>
-      <c r="X130" s="2" t="inlineStr">
+      <c r="X133" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y130" s="2" t="inlineStr">
+      <c r="Y133" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y130"/>
+  <autoFilter ref="A1:Y133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17009,11 +17390,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ヤンキー・不良</t>
+          <t>格闘技・武道</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -17024,11 +17405,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>格闘技・武道</t>
+          <t>ヤンキー・不良</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -17058,7 +17439,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -17099,7 +17480,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/docs/anime/manga_research/works_database.xlsx
+++ b/docs/anime/manga_research/works_database.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$Y$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$Y$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y133"/>
+  <dimension ref="A1:Y134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>ジョジョの奇妙な冒険</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>たふ</t>
+          <t>じょじょのきみょうなぼうけん</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10642,22 +10642,22 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>タフシリーズ</t>
+          <t>ジョジョの奇妙な冒険シリーズ</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>猿渡哲也</t>
+          <t>荒木飛呂彦</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>猿渡哲也</t>
+          <t>荒木飛呂彦</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -10667,72 +10667,72 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングジャンプ</t>
+          <t>週刊少年ジャンプ（第1部〜第6部）→ ウルトラジャンプ（2005年〜、第7部以降）</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>2003–2012（2003年35号〜2012年34号）</t>
+          <t>1987–（週刊少年ジャンプ 1987年1・2号〜2004年47号、ウルトラジャンプ 2005年4月号〜）</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>全39巻（電子版で38巻表記の情報もあり）</t>
+          <t>シリーズ通算130巻超（第9部『The JOJOLands』は通算第132巻〜。最新巻は未確認）</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>古武術／格闘技／バトル／親子</t>
+          <t>能力バトル／冒険／ホラー／格闘</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>前作『高校鉄拳伝タフ』、続編『TOUGH 龍を継ぐ男』</t>
+          <t>第7部 スティール・ボール・ラン、第8部 ジョジョリオン、第9部 The JOJOLands（2023年2月〜）、岸辺露伴は動かない などのスピンオフ</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>古武術の宿命、父と叔父の因縁、最強を目指す戦い</t>
+          <t>血統と継承、人間の勇気、知恵で強敵に勝つ、正しい心を受け継ぐ</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>前作より因縁や裏切りなど重いドラマが増え、家族の対立を軸にする。</t>
+          <t>絶体絶命の状況で、恐怖を自覚しながら知恵と覚悟で一歩を踏み出す姿を、長い心の声で細かく描く。敵の側の執着や美学も丁寧に描く</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>前作同様の誇張された言い回しと独特の擬音。</t>
+          <t>大げさで芝居がかった言い回し、決めの場面での独特の言い切り、感嘆符を重ねた叫び、外国語の混ざった語感。解説役の登場人物が、何が起きたかを詳しく説明する</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>劇画調の筋肉描写、衝撃的な展開での見開き。</t>
+          <t>背景に大きく置かれた擬音の文字、体を大きくひねった独特の立ちポーズ、劇的なパース、ファッション誌のような構図と色彩、部ごとに舞台と主人公が替わる構成</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>誇張表現が笑いになる。</t>
+          <t>極限のシリアスさの中で、言い回しやポーズの過剰さが結果として笑いになる。ネットのミームとして多く引用されている</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>技法：家族の因縁を軸にした長期ドラマ構成。オリジナル案：親子で入会した家族が、互いの頑張りを見て関係が変わる短編。</t>
+          <t>①シリーズを「部」に分け、主人公が代替わりしても「やさしい強さ」が受け継がれる構成にする。②解説役が、マサキの半歩の意味（重心を読む、ケガをさせない）を大げさに解説する。③背景いっぱいの擬音の文字と、オリジナルのキメポーズ。オリジナル案：「震えるぜミット！ 鳴り響くほどビート!!」（※匂わせが強いので公開前に要確認）</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>流派名・技名・キャラの外見・語録化した言い回しを使わない。</t>
+          <t>原作の名ゼリフそのもの（有名な決めゼリフ、叫び声、口ぐせ）、『スタンド』などの固有の用語、キャラクターの外見・衣装・特定のポーズの再現、作品名・ロゴ・書体は使わない。擬音やポーズは、作品を特定できない一般的な形にする</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>[事実] 『高校鉄拳伝タフ』の続編。[感想] 衝撃的な展開がネットでネタにされることが多い。[推測] シリーズ全体で熱心なファンが多いとみられる。X直接検索なし。</t>
+          <t>[事実] 1987年から続く長期シリーズで、部ごとに主人公と舞台が替わる。 [感想] 独特のセリフ回しと擬音、立ちポーズがネットミームとして広く親しまれている。 X直接検索なし</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>https://ranking.net/items/48e26a | https://bookwalker.jp/de0a604124-940e-46f8-9adc-bc6deee96a2a/ | https://www.goodreads.com/series/364786</t>
+          <t>https://www.rere.jp/359256/ | https://dic.nicovideo.jp/a/%E3%82%B8%E3%83%A7%E3%82%B8%E3%83%A7%E3%81%AE%E5%A5%87%E5%A6%99%E3%81%AA%E5%86%92%E9%99%BA | https://news.mynavi.jp/article/20230323-2622596/</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>TOUGH 龍を継ぐ男</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>たふ りゅうをつぐおとこ</t>
+          <t>たふ</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>外伝</t>
+          <t>続編</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -10794,72 +10794,72 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>週刊プレイボーイ</t>
+          <t>週刊ヤングジャンプ</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2015年12月–2025年（2025年9月に完結巻配信）</t>
+          <t>2003–2012（2003年35号〜2012年34号）</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>全35巻</t>
+          <t>全39巻（電子版で38巻表記の情報もあり）</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>古武術／格闘技／バトル</t>
+          <t>古武術／格闘技／バトル／親子</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>『高校鉄拳伝タフ』『TOUGH』、後続『TOUGH 第二章』（週刊プレイボーイ、1巻2025年5月発売、主人公が総合格闘技のリングへ）</t>
+          <t>前作『高校鉄拳伝タフ』、続編『TOUGH 龍を継ぐ男』</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>受け継がれる血と技、新世代の主人公と前作主人公の関係</t>
+          <t>古武術の宿命、父と叔父の因縁、最強を目指す戦い</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>新主人公の出自の謎と苦悩を軸に、前作キャラが導き手として関わる。</t>
+          <t>前作より因縁や裏切りなど重いドラマが増え、家族の対立を軸にする。</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>シリーズ同様の誇張した語りと擬音。</t>
+          <t>前作同様の誇張された言い回しと独特の擬音。</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>劇画調、強敵登場時の大ゴマ。</t>
+          <t>劇画調の筋肉描写、衝撃的な展開での見開き。</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>誇張が笑いになるシリーズの持ち味を継続。</t>
+          <t>誇張表現が笑いになる。</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>技法：前作主人公を『先輩・師』として新主人公を導かせる世代交代の構成。オリジナル案：古参会員が新しい会員を自然と面倒見る『バトン』の物語。</t>
+          <t>技法：家族の因縁を軸にした長期ドラマ構成。オリジナル案：親子で入会した家族が、互いの頑張りを見て関係が変わる短編。</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>主人公たちの外見、流派名、出生の秘密などの設定、語録化した言い回しを使わない。</t>
+          <t>流派名・技名・キャラの外見・語録化した言い回しを使わない。</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>[事実] 2025年9月に完結し、『TOUGH 第二章』へ続いた。[感想] シリーズ恒例の展開をネタ込みで楽しむ読者が多い。[推測] 新規読者より既存ファン中心とみられる。X直接検索なし。</t>
+          <t>[事実] 『高校鉄拳伝タフ』の続編。[感想] 衝撃的な展開がネットでネタにされることが多い。[推測] シリーズ全体で熱心なファンが多いとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>https://booklive.jp/bkmr/comic_m_completed_202509 | https://natalie.mu/comic/news/672517 | https://bookwalker.jp/series/513852/</t>
+          <t>https://ranking.net/items/48e26a | https://bookwalker.jp/de0a604124-940e-46f8-9adc-bc6deee96a2a/ | https://www.goodreads.com/series/364786</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>リングにかけろ</t>
+          <t>TOUGH 龍を継ぐ男</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>りんぐにかけろ</t>
+          <t>たふ りゅうをつぐおとこ</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10896,22 +10896,22 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>リングにかけろシリーズ</t>
+          <t>タフシリーズ</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>外伝</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>車田正美</t>
+          <t>猿渡哲也</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>車田正美</t>
+          <t>猿渡哲也</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -10921,72 +10921,72 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>週刊少年ジャンプ</t>
+          <t>週刊プレイボーイ</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>1977–1981（開始年を1976年とする資料もあり）</t>
+          <t>2015年12月–2025年（2025年9月に完結巻配信）</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>全25巻（ジャンプ・コミックス）</t>
+          <t>全35巻</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／必殺技／少年／バトル</t>
+          <t>古武術／格闘技／バトル</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>続編『リングにかけろ2』（スーパージャンプ、2000年または2001年開始・巻数は未確認）、TVアニメ（2004年〜）。同作者の『聖闘士星矢』『風魔の小次郎』『男坂』</t>
+          <t>『高校鉄拳伝タフ』『TOUGH』、後続『TOUGH 第二章』（週刊プレイボーイ、1巻2025年5月発売、主人公が総合格闘技のリングへ）</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>亡き父の夢、姉弟の絆、仲間との友情、ライバルとの決戦</t>
+          <t>受け継がれる血と技、新世代の主人公と前作主人公の関係</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>内面描写は少なめで、気合と決意を大きな叫びと構図で表現する。迷いより『覚悟』を前面に出す。</t>
+          <t>新主人公の出自の謎と苦悩を軸に、前作キャラが導き手として関わる。</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>決めの場面で大仰な名乗りや宣言が入り、文字自体を大きく描く。短く断定的な言い切りが多い。</t>
+          <t>シリーズ同様の誇張した語りと擬音。</t>
         </is>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>必殺パンチを宇宙的な背景や見開きで描く超人バトル演出。途中からリアル路線から必殺技路線へ大きく舵を切った。</t>
+          <t>劇画調、強敵登場時の大ゴマ。</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少なめ。真剣すぎる誇張表現そのものが後年ネタとして楽しまれている。</t>
+          <t>誇張が笑いになるシリーズの持ち味を継続。</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>技法：一つの技を『名前＋ポーズ＋背景』でブランド化する見せ方。オリジナル案：FLATUPの基本コンビネーションを、子どもたちが自分で名前をつけて覚える回（安全な基本技のみ）。</t>
+          <t>技法：前作主人公を『先輩・師』として新主人公を導かせる世代交代の構成。オリジナル案：古参会員が新しい会員を自然と面倒見る『バトン』の物語。</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>作中の必殺技名（ブーメランなど）とその背景演出、黄金のジュニアなどチーム名、主人公と姉のキャラ造形を使わない。</t>
+          <t>主人公たちの外見、流派名、出生の秘密などの設定、語録化した言い回しを使わない。</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>[事実] 大ヒットし集英社の社屋建て替えに貢献したと語られる。[感想] リアルなボクシングから必殺技バトルへ転じた作品として語り草。[推測] 後のジャンプ式トーナメントバトルの原型と見る声が多い。X直接検索なし。</t>
+          <t>[事実] 2025年9月に完結し、『TOUGH 第二章』へ続いた。[感想] シリーズ恒例の展開をネタ込みで楽しむ読者が多い。[推測] 新規読者より既存ファン中心とみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E8%BB%8A%E7%94%B0%E6%AD%A3%E7%BE%8E | https://gendai.media/articles/-/99299 | https://bunshun.jp/articles/-/44683 | https://nlab.itmedia.co.jp/research/articles/190504/</t>
+          <t>https://booklive.jp/bkmr/comic_m_completed_202509 | https://natalie.mu/comic/news/672517 | https://bookwalker.jp/series/513852/</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>修羅の門</t>
+          <t>リングにかけろ</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>しゅらのもん</t>
+          <t>りんぐにかけろ</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>修羅の門シリーズ</t>
+          <t>リングにかけろシリーズ</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -11033,87 +11033,87 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>川原正敏</t>
+          <t>車田正美</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>川原正敏</t>
+          <t>車田正美</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>集英社</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>月刊少年マガジン</t>
+          <t>週刊少年ジャンプ</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>1987–1996（1987年5月号–1996年12月号）</t>
+          <t>1977–1981（開始年を1976年とする資料もあり）</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>全31巻（講談社コミックス）／文庫版・超合本版あり（巻数未確認）</t>
+          <t>全25巻（ジャンプ・コミックス）</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>格闘技／古流武術／異種格闘技／ボクシング</t>
+          <t>ボクシング／必殺技／少年／バトル</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>続編：修羅の門 第弐門。外伝：修羅の刻。同作者：海皇紀、龍帥の翼</t>
+          <t>続編『リングにかけろ2』（スーパージャンプ、2000年または2001年開始・巻数は未確認）、TVアニメ（2004年〜）。同作者の『聖闘士星矢』『風魔の小次郎』『男坂』</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>千年不敗の流派の継承者が世界の強者と戦う、強さの証明、敗北の意味</t>
+          <t>亡き父の夢、姉弟の絆、仲間との友情、ライバルとの決戦</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>主人公は感情をあまり表に出さず、戦いの中でだけ本心がのぞく。対戦相手の背景や家族を丁寧に描いて、相手側の葛藤も重く見せる。</t>
+          <t>内面描写は少なめで、気合と決意を大きな叫びと構図で表現する。迷いより『覚悟』を前面に出す。</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>主人公は飄々とした軽口と、戦いの最中の短い宣言の落差。解説役の格闘家が観客席で状況を説明する。</t>
+          <t>決めの場面で大仰な名乗りや宣言が入り、文字自体を大きく描く。短く断定的な言い切りが多い。</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>細い線の端正な絵柄。技の決まる瞬間を静止画のように切り取り、白い余白を多く使う。試合ごとに競技のルールを丁寧に描く。</t>
+          <t>必殺パンチを宇宙的な背景や見開きで描く超人バトル演出。途中からリアル路線から必殺技路線へ大きく舵を切った。</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>主人公の食いしん坊・のんきな日常と、戦いの鬼気迫る姿の落差。</t>
+          <t>ギャグは少なめ。真剣すぎる誇張表現そのものが後年ネタとして楽しまれている。</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>技法：対戦相手にも人生の背景を与え、どちらにも感情移入させる。FLATUP案：大会で初心者会員が戦う相手にも『家族に見せたい』理由があると描き、勝ち負けより互いの礼で締める。</t>
+          <t>技法：一つの技を『名前＋ポーズ＋背景』でブランド化する見せ方。オリジナル案：FLATUPの基本コンビネーションを、子どもたちが自分で名前をつけて覚える回（安全な基本技のみ）。</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。</t>
+          <t>作中の必殺技名（ブーメランなど）とその背景演出、黄金のジュニアなどチーム名、主人公と姉のキャラ造形を使わない。</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]講談社漫画賞を受賞したとの記載が二次情報にある（要確認）。[感想]格闘漫画の名作として挙げる声が多い。[推測]長期休載を経た続編で再評価された。</t>
+          <t>[事実] 大ヒットし集英社の社屋建て替えに貢献したと語られる。[感想] リアルなボクシングから必殺技バトルへ転じた作品として語り草。[推測] 後のジャンプ式トーナメントバトルの原型と見る声が多い。X直接検索なし。</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000033723 | https://www.kodansha.co.jp/comic/products/0000346993 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
+          <t>https://dic.nicovideo.jp/a/%E8%BB%8A%E7%94%B0%E6%AD%A3%E7%BE%8E | https://gendai.media/articles/-/99299 | https://bunshun.jp/articles/-/44683 | https://nlab.itmedia.co.jp/research/articles/190504/</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -11135,12 +11135,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>修羅の門 第弐門</t>
+          <t>修羅の門</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>しゅらのもん だいにもん</t>
+          <t>しゅらのもん</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -11180,52 +11180,52 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2010–2015（2010年11月号–2015年7月号）</t>
+          <t>1987–1996（1987年5月号–1996年12月号）</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>全18巻（講談社コミックス／講談社プラチナコミックス版あり）</t>
+          <t>全31巻（講談社コミックス）／文庫版・超合本版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>格闘技／総合格闘技／古流武術</t>
+          <t>格闘技／古流武術／異種格闘技／ボクシング</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>前作：修羅の門。外伝：修羅の刻</t>
+          <t>続編：修羅の門 第弐門。外伝：修羅の刻。同作者：海皇紀、龍帥の翼</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>空白の時間を経た主人公の帰還、待ち続けた者たちの思い</t>
+          <t>千年不敗の流派の継承者が世界の強者と戦う、強さの証明、敗北の意味</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>長い不在の理由を伏せたまま進め、周囲の『待っていた』気持ちで主人公の存在の大きさを示す。</t>
+          <t>主人公は感情をあまり表に出さず、戦いの中でだけ本心がのぞく。対戦相手の背景や家族を丁寧に描いて、相手側の葛藤も重く見せる。</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>前作同様、軽口と短い宣言の落差。</t>
+          <t>主人公は飄々とした軽口と、戦いの最中の短い宣言の落差。解説役の格闘家が観客席で状況を説明する。</t>
         </is>
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>総合格闘技のケージやリングの描写。前作より余白を活かした静かなコマ運び。</t>
+          <t>細い線の端正な絵柄。技の決まる瞬間を静止画のように切り取り、白い余白を多く使う。試合ごとに競技のルールを丁寧に描く。</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>前作キャラとの再会時のずれた会話。</t>
+          <t>主人公の食いしん坊・のんきな日常と、戦いの鬼気迫る姿の落差。</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>技法：『帰ってくる』物語の作り方。FLATUP案：ケガで休会していた会員が復帰する日、仲間が名前を覚えていてくれた場面。オリジナル台詞案『おかえり。サンドバッグも待ってたよ』。</t>
+          <t>技法：対戦相手にも人生の背景を与え、どちらにも感情移入させる。FLATUP案：大会で初心者会員が戦う相手にも『家族に見せたい』理由があると描き、勝ち負けより互いの礼で締める。</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]長期休載後の再開を喜ぶ声が多かった。[推測]結末については賛否がある。</t>
+          <t>X直接検索なし。[事実]講談社漫画賞を受賞したとの記載が二次情報にある（要確認）。[感想]格闘漫画の名作として挙げる声が多い。[推測]長期休載を経た続編で再評価された。</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000053262 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000033723 | https://www.kodansha.co.jp/comic/products/0000346993 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>陸奥圓明流外伝 修羅の刻</t>
+          <t>修羅の門 第弐門</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>むつえんめいりゅうがいでん しゅらのとき</t>
+          <t>しゅらのもん だいにもん</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>外伝</t>
+          <t>続編</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -11307,67 +11307,67 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1989–（1989年7月号以降、断続的に発表）</t>
+          <t>2010–2015（2010年11月号–2015年7月号）</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>既刊は資料により25〜27巻程度（正確な既刊数は未確認）／新装版（編ごと）あり</t>
+          <t>全18巻（講談社コミックス／講談社プラチナコミックス版あり）</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>格闘技／時代劇／歴史</t>
+          <t>格闘技／総合格闘技／古流武術</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>本編：修羅の門、修羅の門 第弐門</t>
+          <t>前作：修羅の門。外伝：修羅の刻</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>歴史の陰に名もなき強者がいた、という想像。歴史上の人物との出会いと別れ</t>
+          <t>空白の時間を経た主人公の帰還、待ち続けた者たちの思い</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>各編の語り手（歴史上の人物側）の目を通して主人公の一族を描き、憧れと畏れを重ねる。</t>
+          <t>長い不在の理由を伏せたまま進め、周囲の『待っていた』気持ちで主人公の存在の大きさを示す。</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>時代ごとの言葉づかいを取り入れつつ、主人公は現代的な軽さを残す。</t>
+          <t>前作同様、軽口と短い宣言の落差。</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>歴史絵巻的な背景と、一騎打ちの静かなコマの対比。</t>
+          <t>総合格闘技のケージやリングの描写。前作より余白を活かした静かなコマ運び。</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>歴史上の有名人物の意外な一面を見せるずれ。</t>
+          <t>前作キャラとの再会時のずれた会話。</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>技法：1編完結の時代別オムニバス。FLATUP案：『昭和・平成・令和のFLATUP』のように、時代ごとの格闘技ジムの空気を描く短編シリーズ（実在人物は使わない）。</t>
+          <t>技法：『帰ってくる』物語の作り方。FLATUP案：ケガで休会していた会員が復帰する日、仲間が名前を覚えていてくれた場面。オリジナル台詞案『おかえり。サンドバッグも待ってたよ』。</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。実在の歴史人物と架空の流派を絡める構成をそのまま真似しない。</t>
+          <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2004年にTVアニメ化された（二次情報）。[感想]本編より好きという声もある。[推測]歴史好きにも読まれている。</t>
+          <t>X直接検索なし。[感想]長期休載後の再開を喜ぶ声が多かった。[推測]結末については賛否がある。</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000319630 | https://www.kodansha.co.jp/comic/products/0000325453 | https://www.hulu.jp/comic/series/103896</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000053262 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
@@ -11389,12 +11389,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>グラップラー刃牙</t>
+          <t>陸奥圓明流外伝 修羅の刻</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ぐらっぷらーばき</t>
+          <t>むつえんめいりゅうがいでん しゅらのとき</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -11404,97 +11404,97 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>刃牙シリーズ</t>
+          <t>修羅の門シリーズ</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>外伝</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介</t>
+          <t>川原正敏</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介</t>
+          <t>川原正敏</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>秋田書店</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン</t>
+          <t>月刊少年マガジン</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>1991–1999（1991年43号–1999年29号とされる）</t>
+          <t>1989–（1989年7月号以降、断続的に発表）</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>全42巻（少年チャンピオン・コミックス）／完全版 全24巻（外伝含むとされる）</t>
+          <t>既刊は資料により25〜27巻程度（正確な既刊数は未確認）／新装版（編ごと）あり</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>格闘技／バトル／地下格闘技／親子</t>
+          <t>格闘技／時代劇／歴史</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>続編：バキ、範馬刃牙、刃牙道、バキ道、刃牙らへん。外伝：グラップラー刃牙外伝 ほか</t>
+          <t>本編：修羅の門、修羅の門 第弐門</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>最強への渇望、父と子の確執、強さの多様性（流派・競技を越えた比較）、敗北からの再起</t>
+          <t>歴史の陰に名もなき強者がいた、という想像。歴史上の人物との出会いと別れ</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>強者が恐怖や敗北を自覚する瞬間を、観客・解説役のリアクションで外側から描き、内面を誇張した比喩で見せる。主人公の成長は修行と敗北の繰り返しで段階的に示し、父への恐怖と憧れが同居する葛藤を軸にする。</t>
+          <t>各編の語り手（歴史上の人物側）の目を通して主人公の一族を描き、憧れと畏れを重ねる。</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
+          <t>時代ごとの言葉づかいを取り入れつつ、主人公は現代的な軽さを残す。</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
+          <t>歴史絵巻的な背景と、一騎打ちの静かなコマの対比。</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>真顔で語られる誇張（あり得ない筋力・食事量など）が読者には笑いになる『シリアスな誇張ギャグ』。解説役の過剰な驚き方。</t>
+          <t>歴史上の有名人物の意外な一面を見せるずれ。</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>技法：解説役を置いて技の凄さを第三者に語らせる／強さを観客の表情で伝える。FLATUP案：初心者の会員が初めてミットを鳴らした瞬間を、先輩会員が驚く顔で見せる。オリジナル台詞案『今の音、自分で出したんだよ』。</t>
+          <t>技法：1編完結の時代別オムニバス。FLATUP案：『昭和・平成・令和のFLATUP』のように、時代ごとの格闘技ジムの空気を描く短編シリーズ（実在人物は使わない）。</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。実在の歴史人物と架空の流派を絡める構成をそのまま真似しない。</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]シリーズ累計発行部数1億部突破と報じられた（2024年）。[事実]複数回アニメ化。[感想]誇張表現がネットミーム化しやすく、真面目さと笑いの両面で愛されている印象。[推測]初期作は格闘技ファン以外の入口になっている。</t>
+          <t>X直接検索なし。[事実]2004年にTVアニメ化された（二次情報）。[感想]本編より好きという声もある。[推測]歴史好きにも読まれている。</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/54 | https://realsound.jp/book/2024/05/post-1667170.html | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000319630 | https://www.kodansha.co.jp/comic/products/0000325453 | https://www.hulu.jp/comic/series/103896</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>バキ</t>
+          <t>グラップラー刃牙</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ばき</t>
+          <t>ぐらっぷらーばき</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>1999–2005</t>
+          <t>1991–1999（1991年43号–1999年29号とされる）</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>全31巻（少年チャンピオン・コミックス）／完全版 全17巻（バキ完全版）／新装版あり（巻数未確認）</t>
+          <t>全42巻（少年チャンピオン・コミックス）／完全版 全24巻（外伝含むとされる）</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>格闘技／バトル／死刑囚編／中国拳法</t>
+          <t>格闘技／バトル／地下格闘技／親子</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>前作：グラップラー刃牙。次作：範馬刃牙。外伝：バキ特別編SAGA[性]</t>
+          <t>続編：バキ、範馬刃牙、刃牙道、バキ道、刃牙らへん。外伝：グラップラー刃牙外伝 ほか</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>敗北を知らない者が敗北を知ること、勝ち負けの定義、恋愛と強さ</t>
+          <t>最強への渇望、父と子の確執、強さの多様性（流派・競技を越えた比較）、敗北からの再起</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>『負けを知りたい』という逆説的な動機を持つ敵を置き、勝敗の意味そのものを揺らす。主人公の精神的な不調と回復も描く。</t>
+          <t>強者が恐怖や敗北を自覚する瞬間を、観客・解説役のリアクションで外側から描き、内面を誇張した比喩で見せる。主人公の成長は修行と敗北の繰り返しで段階的に示し、父への恐怖と憧れが同居する葛藤を軸にする。</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。街中・日常空間での奇襲が多く、場所の意外性で緊張を作る。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>日常場面に格闘の論理を持ち込むずれ。強者同士の妙に礼儀正しいやり取り。</t>
+          <t>真顔で語られる誇張（あり得ない筋力・食事量など）が読者には笑いになる『シリアスな誇張ギャグ』。解説役の過剰な驚き方。</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>技法：勝敗の定義を問い直す構成。FLATUP案：『試合で勝つ』ではなく『昨日の自分に勝つ』を勝利と定義するエピソード。オリジナル台詞案『今日の勝ちは、来たことだよ』。</t>
+          <t>技法：解説役を置いて技の凄さを第三者に語らせる／強さを観客の表情で伝える。FLATUP案：初心者の会員が初めてミットを鳴らした瞬間を、先輩会員が驚く顔で見せる。オリジナル台詞案『今の音、自分で出したんだよ』。</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。死刑囚5人という構成・設定も流用不可。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2018年にNetflixでアニメ化（バキ）。[感想]死刑囚編は人気が高いという声が多い。[推測]後半は評価が分かれやすい。</t>
+          <t>X直接検索なし。[事実]シリーズ累計発行部数1億部突破と報じられた（2024年）。[事実]複数回アニメ化。[感想]誇張表現がネットミーム化しやすく、真面目さと笑いの両面で愛されている印象。[推測]初期作は格闘技ファン以外の入口になっている。</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/8817 | https://www.akitashoten.co.jp/comics/4253218881 | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
+          <t>https://www.akitashoten.co.jp/series/54 | https://realsound.jp/book/2024/05/post-1667170.html | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>範馬刃牙</t>
+          <t>バキ</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>はんまばき</t>
+          <t>ばき</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11688,32 +11688,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2006–2012</t>
+          <t>1999–2005</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>全37巻（少年チャンピオン・コミックス）／新装版あり（巻数未確認）</t>
+          <t>全31巻（少年チャンピオン・コミックス）／完全版 全17巻（バキ完全版）／新装版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>格闘技／親子／原始人</t>
+          <t>格闘技／バトル／死刑囚編／中国拳法</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>前作：バキ。次作：刃牙道</t>
+          <t>前作：グラップラー刃牙。次作：範馬刃牙。外伝：バキ特別編SAGA[性]</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>父と子の決着、強さの頂点、家族とは何か</t>
+          <t>敗北を知らない者が敗北を知ること、勝ち負けの定義、恋愛と強さ</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>シリーズを通した父への恐怖と承認欲求を、最終決戦で正面から描く。敵役の原始人には言葉がなく、表情と行動だけで心理を伝える。</t>
+          <t>『負けを知りたい』という逆説的な動機を持つ敵を置き、勝敗の意味そのものを揺らす。主人公の精神的な不調と回復も描く。</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。言葉を持たないキャラは目と口元のアップで感情を表す。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。街中・日常空間での奇襲が多く、場所の意外性で緊張を作る。</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>親子喧嘩に家庭的な要素（食卓など）を混ぜる落差。</t>
+          <t>日常場面に格闘の論理を持ち込むずれ。強者同士の妙に礼儀正しいやり取り。</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>技法：言葉に頼らず表情だけで心情を伝えるコマ。FLATUP案：口下手な父親会員が、子どもの帯昇級の日に何も言わず肩に手を置く場面。</t>
+          <t>技法：勝敗の定義を問い直す構成。FLATUP案：『試合で勝つ』ではなく『昨日の自分に勝つ』を勝利と定義するエピソード。オリジナル台詞案『今日の勝ちは、来たことだよ』。</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。原始人キャラの設定（化石からの蘇生など）も流用不可。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。死刑囚5人という構成・設定も流用不可。</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2023年にアニメ化（範馬刃牙）。[感想]親子対決の結末は賛否が分かれるという声がある。[推測]シリーズの一区切りとして読まれることが多い。</t>
+          <t>X直接検索なし。[事実]2018年にNetflixでアニメ化（バキ）。[感想]死刑囚編は人気が高いという声が多い。[推測]後半は評価が分かれやすい。</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/1976 | https://www.akitashoten.co.jp/comics/4253211178 | https://championcross.jp/series/83c15f6be5628</t>
+          <t>https://www.akitashoten.co.jp/series/8817 | https://www.akitashoten.co.jp/comics/4253218881 | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
@@ -11770,12 +11770,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>刃牙道</t>
+          <t>範馬刃牙</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ばきどう</t>
+          <t>はんまばき</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11815,67 +11815,67 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2014–2018</t>
+          <t>2006–2012</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>全22巻（少年チャンピオン・コミックス）</t>
+          <t>全37巻（少年チャンピオン・コミックス）／新装版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>格闘技／剣豪／クローン</t>
+          <t>格闘技／親子／原始人</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>前作：範馬刃牙。次作：バキ道。外伝：バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
+          <t>前作：バキ。次作：刃牙道</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>現代格闘技と古流武術・剣術の比較、命を懸けることの重さ</t>
+          <t>父と子の決着、強さの頂点、家族とは何か</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>素手の格闘家が刃物を持つ相手に向き合う恐怖を丁寧に描く。人気キャラの退場で読者の喪失感も演出に使う。</t>
+          <t>シリーズを通した父への恐怖と承認欲求を、最終決戦で正面から描く。敵役の原始人には言葉がなく、表情と行動だけで心理を伝える。</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。古風な言葉づかいの剣豪と現代人の会話の時代差。</t>
+          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。刃物の『斬れる』緊張を、空白と静止のコマで表す。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。言葉を持たないキャラは目と口元のアップで感情を表す。</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>過去の人物が現代の生活に戸惑う時代ギャップ。</t>
+          <t>親子喧嘩に家庭的な要素（食卓など）を混ぜる落差。</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>技法：時代や文化の違う者同士の会話ギャップ。FLATUP案：70代の新入会員と10代の会員が、互いの『当たり前』の違いで笑い合う回。</t>
+          <t>技法：言葉に頼らず表情だけで心情を伝えるコマ。FLATUP案：口下手な父親会員が、子どもの帯昇級の日に何も言わず肩に手を置く場面。</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在の剣豪を現代に蘇らせる設定の組み立て方もそのままなぞらない。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。原始人キャラの設定（化石からの蘇生など）も流用不可。</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2026年にアニメ配信が始まったとの記載がWebにある（要確認）。[感想]主要キャラの退場が大きな話題になった。[推測]シリーズ内でも賛否が強い作品。</t>
+          <t>X直接検索なし。[事実]2023年にアニメ化（範馬刃牙）。[感想]親子対決の結末は賛否が分かれるという声がある。[推測]シリーズの一区切りとして読まれることが多い。</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/4380 | https://www.akitashoten.co.jp/comics/4253223621</t>
+          <t>https://www.akitashoten.co.jp/series/1976 | https://www.akitashoten.co.jp/comics/4253211178 | https://championcross.jp/series/83c15f6be5628</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>バキ道</t>
+          <t>刃牙道</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -11942,67 +11942,67 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>2018–2023</t>
+          <t>2014–2018</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>全17巻（少年チャンピオン・コミックス）</t>
+          <t>全22巻（少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>格闘技／相撲</t>
+          <t>格闘技／剣豪／クローン</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>前作：刃牙道。次作：刃牙らへん</t>
+          <t>前作：範馬刃牙。次作：バキ道。外伝：バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>相撲という競技への敬意、古代と現代の強さ比べ</t>
+          <t>現代格闘技と古流武術・剣術の比較、命を懸けることの重さ</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>伝統競技の担い手の誇りと、外部の格闘家に挑まれる側の動揺を描く。</t>
+          <t>素手の格闘家が刃物を持つ相手に向き合う恐怖を丁寧に描く。人気キャラの退場で読者の喪失感も演出に使う。</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
+          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。古風な言葉づかいの剣豪と現代人の会話の時代差。</t>
         </is>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。巨体の重さを、低いアングルと足元の描写で表す。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。刃物の『斬れる』緊張を、空白と静止のコマで表す。</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>大真面目な格闘論が飛躍していく誇張。</t>
+          <t>過去の人物が現代の生活に戸惑う時代ギャップ。</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>技法：一つの競技を深掘りして『その競技ならではの強さ』を見せる。FLATUP案：キックボクシングとレスリング出身の会員が互いの基本動作を教え合う回。</t>
+          <t>技法：時代や文化の違う者同士の会話ギャップ。FLATUP案：70代の新入会員と10代の会員が、互いの『当たり前』の違いで笑い合う回。</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。古代相撲の継承者という設定は流用不可。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在の剣豪を現代に蘇らせる設定の組み立て方もそのままなぞらない。</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2023年9月刊行の第17巻で完結。[感想]相撲題材は好みが分かれるという声がある。[推測]シリーズ固定ファン中心に読まれている。</t>
+          <t>X直接検索なし。[事実]2026年にアニメ配信が始まったとの記載がWebにある（要確認）。[感想]主要キャラの退場が大きな話題になった。[推測]シリーズ内でも賛否が強い作品。</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/9084 | https://www.akitashoten.co.jp/comics/4253281273</t>
+          <t>https://www.akitashoten.co.jp/series/4380 | https://www.akitashoten.co.jp/comics/4253223621</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
@@ -12024,12 +12024,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>刃牙らへん</t>
+          <t>バキ道</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ばきらへん</t>
+          <t>ばきどう</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2023年頃開始（開始号は未確認）–連載中</t>
+          <t>2018–2023</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>既刊7巻（第7巻 2026年7月刊行、少年チャンピオン・コミックス）</t>
+          <t>全17巻（少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>格闘技／群像</t>
+          <t>格闘技／相撲</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>前作：バキ道</t>
+          <t>前作：刃牙道。次作：刃牙らへん</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>主人公の周辺（＝らへん）のキャラ同士の流儀の違い</t>
+          <t>相撲という競技への敬意、古代と現代の強さ比べ</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>主人公以外の脇役同士をぶつけ、それぞれの『戦う流儀』の違いから葛藤を生む。</t>
+          <t>伝統競技の担い手の誇りと、外部の格闘家に挑まれる側の動揺を描く。</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。巨体の重さを、低いアングルと足元の描写で表す。</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>タイトル自体の脱力感と、本編の重さの落差。</t>
+          <t>大真面目な格闘論が飛躍していく誇張。</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>技法：主役ではなく脇役に焦点を当てる群像回。FLATUP案：受付スタッフや送迎の保護者が主役になる『ジムのらへん』的な短編。オリジナル台詞案『主役じゃなくても、ここは居場所』。</t>
+          <t>技法：一つの競技を深掘りして『その競技ならではの強さ』を見せる。FLATUP案：キックボクシングとレスリング出身の会員が互いの基本動作を教え合う回。</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。タイトルの言い回しを模した作品名も避ける。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。古代相撲の継承者という設定は流用不可。</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2024年の累計1億部記念で巻頭カラー掲載があったと報じられた。[感想]タイトルのゆるさが話題になった。[推測]連載中のため評価は今後変わりうる。</t>
+          <t>X直接検索なし。[事実]2023年9月刊行の第17巻で完結。[感想]相撲題材は好みが分かれるという声がある。[推測]シリーズ固定ファン中心に読まれている。</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/12823 | https://www.akitashoten.co.jp/comics/4253284213 | https://www.akitashoten.co.jp/comics/4253011373</t>
+          <t>https://www.akitashoten.co.jp/series/9084 | https://www.akitashoten.co.jp/comics/4253281273</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
@@ -12151,12 +12151,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>グラップラー刃牙外伝</t>
+          <t>刃牙らへん</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ぐらっぷらーばきがいでん</t>
+          <t>ばきらへん</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>外伝</t>
+          <t>続編</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -12196,67 +12196,67 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>1999（1999年30号–42号とされる）</t>
+          <t>2023年頃開始（開始号は未確認）–連載中</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>全1巻（全9話とされる）</t>
+          <t>既刊7巻（第7巻 2026年7月刊行、少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>格闘技／プロレス</t>
+          <t>格闘技／群像</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>本編：グラップラー刃牙</t>
+          <t>前作：バキ道</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>プロレスラー同士の因縁と決着、興行と本気の境目</t>
+          <t>主人公の周辺（＝らへん）のキャラ同士の流儀の違い</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>長年の因縁を抱えた中年レスラーの意地と老い、観客の期待とのはざまを描く。</t>
+          <t>主人公以外の脇役同士をぶつけ、それぞれの『戦う流儀』の違いから葛藤を生む。</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。プロレス的なマイクパフォーマンス風の大げささ。</t>
+          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
         </is>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。大会場の群衆を背景にした大ゴマ。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>実在レスラーを思わせるパロディ的な人物造形。</t>
+          <t>タイトル自体の脱力感と、本編の重さの落差。</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>技法：脇役の因縁だけで1冊を作るスピンオフ構成。FLATUP案：昔ライバルだった中年会員2人の『引退前の一戦』をスパーリング大会で描く。</t>
+          <t>技法：主役ではなく脇役に焦点を当てる群像回。FLATUP案：受付スタッフや送迎の保護者が主役になる『ジムのらへん』的な短編。オリジナル台詞案『主役じゃなくても、ここは居場所』。</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在人物を連想させるパロディ造形（名前のもじり）はFLATUPでは使わない。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。タイトルの言い回しを模した作品名も避ける。</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]プロレス好きの読者に評価されているという声がある。[推測]知名度は本編より低い。</t>
+          <t>X直接検索なし。[事実]2024年の累計1億部記念で巻頭カラー掲載があったと報じられた。[感想]タイトルのゆるさが話題になった。[推測]連載中のため評価は今後変わりうる。</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>https://ciatr.jp/topics/326476 | https://mangapedia.com/gd/%E3%82%B0%E3%83%A9%E3%83%83%E3%83%97%E3%83%A9%E3%83%BC%E5%88%83%E7%89%99%E5%A4%96%E4%BC%9D-dc4q37bo9/1</t>
+          <t>https://www.akitashoten.co.jp/series/12823 | https://www.akitashoten.co.jp/comics/4253284213 | https://www.akitashoten.co.jp/comics/4253011373</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>バキ特別編SAGA[性]</t>
+          <t>グラップラー刃牙外伝</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ばきとくべつへんさが</t>
+          <t>ぐらっぷらーばきがいでん</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -12318,72 +12318,72 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>ヤングチャンピオン</t>
+          <t>週刊少年チャンピオン</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2002（2002年12号–15号とされる）</t>
+          <t>1999（1999年30号–42号とされる）</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>全1巻（全4話とされる）</t>
+          <t>全1巻（全9話とされる）</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>格闘技／恋愛／青年向け</t>
+          <t>格闘技／プロレス</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>本編：バキ（本編の途中に入るエピソードとされる）</t>
+          <t>本編：グラップラー刃牙</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>恋愛と強さ、若者の成長</t>
+          <t>プロレスラー同士の因縁と決着、興行と本気の境目</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>恋愛感情を格闘の比喩で語る誇張表現。</t>
+          <t>長年の因縁を抱えた中年レスラーの意地と老い、観客の期待とのはざまを描く。</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
+          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。プロレス的なマイクパフォーマンス風の大げささ。</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。大会場の群衆を背景にした大ゴマ。</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>格闘描写の文法を恋愛場面に転用する落差。</t>
+          <t>実在レスラーを思わせるパロディ的な人物造形。</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>技法：本編と別媒体に分けて描くことで、作品のトーンを守る判断。FLATUP案：ブランドの本編（初心者向け・全年齢）と、大人向けの別企画を明確に分ける運用ルールの参考にする。性的表現はFLATUP作品では扱わない。</t>
+          <t>技法：脇役の因縁だけで1冊を作るスピンオフ構成。FLATUP案：昔ライバルだった中年会員2人の『引退前の一戦』をスパーリング大会で描く。</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。性的描写を含むため、内容・構成ともFLATUPでは参考にしない。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在人物を連想させるパロディ造形（名前のもじり）はFLATUPでは使わない。</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]本編とのギャップで話題に上ることが多い。[推測]青年誌掲載のため本編より読者は限られる。</t>
+          <t>X直接検索なし。[感想]プロレス好きの読者に評価されているという声がある。[推測]知名度は本編より低い。</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E3%83%90%E3%82%AD%E7%89%B9%E5%88%A5%E7%B7%A8%20saga%5B%E6%80%A7%5D | https://ciatr.jp/topics/326476</t>
+          <t>https://ciatr.jp/topics/326476 | https://mangapedia.com/gd/%E3%82%B0%E3%83%A9%E3%83%83%E3%83%97%E3%83%A9%E3%83%BC%E5%88%83%E7%89%99%E5%A4%96%E4%BC%9D-dc4q37bo9/1</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 疵面 -スカーフェイス-</t>
+          <t>バキ特別編SAGA[性]</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん すかーふぇいす</t>
+          <t>ばきとくべつへんさが</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原案）</t>
+          <t>板垣恵介</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>山内雪奈生</t>
+          <t>板垣恵介</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -12445,72 +12445,72 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>チャンピオンRED</t>
+          <t>ヤングチャンピオン</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>第1巻 2005年8月刊行（連載期間の詳細は未確認）</t>
+          <t>2002（2002年12号–15号とされる）</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>既刊8巻（チャンピオンREDコミックス）</t>
+          <t>全1巻（全4話とされる）</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>格闘技／喧嘩／任侠</t>
+          <t>格闘技／恋愛／青年向け</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>前日譚：バキ外伝 創面。本編：刃牙シリーズ</t>
+          <t>本編：バキ（本編の途中に入るエピソードとされる）</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>喧嘩師の美学、技に頼らない素手の強さ、男の矜持</t>
+          <t>恋愛と強さ、若者の成長</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>技術を拒み、受けて耐えることを誇りとする主人公の揺るがなさを、周囲の恐れと敬意で浮かび上がらせる。</t>
+          <t>恋愛感情を格闘の比喩で語る誇張表現。</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>主人公は極端に寡黙で、周囲が語ることで人物像が立つ。</t>
+          <t>短い断言、促音記号を重ねた叫び、解説役が理屈を語る長台詞の対比。妙に丁寧な敬語と荒い言葉の落差。</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>大きな背中、無言の立ち姿、傷のアップ。静止した大ゴマで存在感を出す。</t>
+          <t>筋肉の極端な描き込み、見開きの一撃、解説役の顔アップ、黒ベタと集中線で『強さ』の圧を作る。技の説明を挟んで間を取る。</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少なめ。無口な主人公の反応のなさが間として笑いを生む場面がある。</t>
+          <t>格闘描写の文法を恋愛場面に転用する落差。</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>技法：寡黙な主人公を周囲の反応で語らせる。FLATUP案：無口なベテラン会員が、初心者が転んだときだけ黙って手を差し出す。ただし『暴力の美学』は採らず、『耐える強さ＝やさしさ』に置き換える。</t>
+          <t>技法：本編と別媒体に分けて描くことで、作品のトーンを守る判断。FLATUP案：ブランドの本編（初心者向け・全年齢）と、大人向けの別企画を明確に分ける運用ルールの参考にする。性的表現はFLATUP作品では扱わない。</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見（大柄・顔や背中の傷・白スーツ）、任侠組織の設定、『喧嘩師』という肩書きの使い方をそのまま流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。性的描写を含むため、内容・構成ともFLATUPでは参考にしない。</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]花山薫ファンに支持される外伝という声がある。[推測]暴力団設定があるためFLATUPの思想とは距離がある。</t>
+          <t>X直接検索なし。[感想]本編とのギャップで話題に上ることが多い。[推測]青年誌掲載のため本編より読者は限られる。</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/1909 | https://www.akitashoten.co.jp/comics/4253231713 | https://www.cmoa.jp/title/41006/</t>
+          <t>https://dic.nicovideo.jp/a/%E3%83%90%E3%82%AD%E7%89%B9%E5%88%A5%E7%B7%A8%20saga%5B%E6%80%A7%5D | https://ciatr.jp/topics/326476</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -12532,12 +12532,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 創面</t>
+          <t>バキ外伝 疵面 -スカーフェイス-</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん きずづら</t>
+          <t>ばきがいでん すかーふぇいす</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -12552,12 +12552,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>前日譚</t>
+          <t>外伝</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原案）、浦秀光</t>
+          <t>板垣恵介（原案）</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -12572,72 +12572,72 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>未確認（レーベルは少年チャンピオン・コミックス・エクストラ）</t>
+          <t>チャンピオンRED</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>第1巻 2005年8月刊行（連載期間の詳細は未確認）</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>既刊3巻（第3巻で第一部完結）</t>
+          <t>既刊8巻（チャンピオンREDコミックス）</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>学園／コメディ／格闘技</t>
+          <t>格闘技／喧嘩／任侠</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 疵面 -スカーフェイス-（本作はその主人公の若き日を描く）</t>
+          <t>前日譚：バキ外伝 創面。本編：刃牙シリーズ</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>規格外の少年が学校という日常に入る違和感、成長</t>
+          <t>喧嘩師の美学、技に頼らない素手の強さ、男の矜持</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>強すぎる少年が普通の学生生活に戸惑う様子を、周囲の同級生の目線で描く。</t>
+          <t>技術を拒み、受けて耐えることを誇りとする主人公の揺るがなさを、周囲の恐れと敬意で浮かび上がらせる。</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>寡黙な主人公と、よくしゃべる同級生の対比。</t>
+          <t>主人公は極端に寡黙で、周囲が語ることで人物像が立つ。</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>学園の日常風景に、場違いな迫力の人物を置く構図。</t>
+          <t>大きな背中、無言の立ち姿、傷のアップ。静止した大ゴマで存在感を出す。</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>格闘漫画の文法を学園コメディに持ち込むずれ（大げさな迫力で些細なことをする）。</t>
+          <t>ギャグは少なめ。無口な主人公の反応のなさが間として笑いを生む場面がある。</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>技法：強いキャラを日常に置いて笑いにする『場違いギャグ』。FLATUP案：プロ選手のトレーナーがキッズクラスで子どもに負けて本気で悔しがる回。</t>
+          <t>技法：寡黙な主人公を周囲の反応で語らせる。FLATUP案：無口なベテラン会員が、初心者が転んだときだけ黙って手を差し出す。ただし『暴力の美学』は採らず、『耐える強さ＝やさしさ』に置き換える。</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>主人公の15歳時の外見・設定、学園の固有設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>主人公の外見（大柄・顔や背中の傷・白スーツ）、任侠組織の設定、『喧嘩師』という肩書きの使い方をそのまま流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]前作と雰囲気が違う学園コメディとして紹介されている。[推測]シリアス目当ての読者には好みが分かれる。</t>
+          <t>X直接検索なし。[感想]花山薫ファンに支持される外伝という声がある。[推測]暴力団設定があるためFLATUPの思想とは距離がある。</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/2957 | https://www.akitashoten.co.jp/comics/4253132618 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E5%89%B5%E9%9D%A2-652afhpws</t>
+          <t>https://www.akitashoten.co.jp/series/1909 | https://www.akitashoten.co.jp/comics/4253231713 | https://www.cmoa.jp/title/41006/</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 拳刃</t>
+          <t>バキ外伝 創面</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん けんじん</t>
+          <t>ばきがいでん きずづら</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -12679,17 +12679,17 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>外伝</t>
+          <t>前日譚</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原作・構成）、浦秀光（原作協力）</t>
+          <t>板垣恵介（原案）、浦秀光</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>宮谷拳豪</t>
+          <t>山内雪奈生</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -12699,72 +12699,72 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>チャンピオンRED</t>
+          <t>未確認（レーベルは少年チャンピオン・コミックス・エクストラ）</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>2013–2014（2013年8月号–2014年1月号とされる）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>全1巻（2014年1月刊行、チャンピオンREDコミックス）</t>
+          <t>既刊3巻（第3巻で第一部完結）</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>格闘技／空手／青春</t>
+          <t>学園／コメディ／格闘技</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>本編：刃牙シリーズ。同じ人物の外伝：バキ外伝 独歩 -独り飲み喰い歩き-</t>
+          <t>バキ外伝 疵面 -スカーフェイス-（本作はその主人公の若き日を描く）</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>若き空手家の修行と野心、武の道</t>
+          <t>規格外の少年が学校という日常に入る違和感、成長</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>若い頃の未熟さと野心を描き、のちの『武神』像との距離で成長を感じさせる。</t>
+          <t>強すぎる少年が普通の学生生活に戸惑う様子を、周囲の同級生の目線で描く。</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>血気盛んな若者らしい荒い言葉づかい。</t>
+          <t>寡黙な主人公と、よくしゃべる同級生の対比。</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>空手の型と打撃を力強い線で描く。</t>
+          <t>学園の日常風景に、場違いな迫力の人物を置く構図。</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少なめ。</t>
+          <t>格闘漫画の文法を学園コメディに持ち込むずれ（大げさな迫力で些細なことをする）。</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>技法：ベテランキャラの『若い頃』を描く前日譚。FLATUP案：今は穏やかなジムの会長が、若い頃は負けず嫌いで失敗ばかりだった話を会員に語る回。</t>
+          <t>技法：強いキャラを日常に置いて笑いにする『場違いギャグ』。FLATUP案：プロ選手のトレーナーがキッズクラスで子どもに負けて本気で悔しがる回。</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>愚地独歩の外見（スキンヘッド・眼帯）、神心会という流派名を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>主人公の15歳時の外見・設定、学園の固有設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[推測]全1巻の短期作のため知名度は高くない。[感想]独歩の若き日が見られる点を評価する声がある。</t>
+          <t>X直接検索なし。[感想]前作と雰囲気が違う学園コメディとして紹介されている。[推測]シリアス目当ての読者には好みが分かれる。</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>https://championcross.jp/series/f4d643b0590d6 | https://www.akitashoten.co.jp/comics/4253236219 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E6%8B%B3%E5%88%83-r2t7o70mk</t>
+          <t>https://www.akitashoten.co.jp/series/2957 | https://www.akitashoten.co.jp/comics/4253132618 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E5%89%B5%E9%9D%A2-652afhpws</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
@@ -12786,12 +12786,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>バキどもえ</t>
+          <t>バキ外伝 拳刃</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ばきどもえ</t>
+          <t>ばきがいでん けんじん</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -12806,17 +12806,17 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>スピンオフ</t>
+          <t>外伝</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>さいとうなおき（板垣恵介公認とされる）</t>
+          <t>板垣恵介（原作・構成）、浦秀光（原作協力）</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>さいとうなおき</t>
+          <t>宮谷拳豪</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -12826,72 +12826,72 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン（電子書店の分類による。未確認）</t>
+          <t>チャンピオンRED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>2013–2014（2013年8月号–2014年1月号とされる）</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>全3巻（少年チャンピオン・コミックス）</t>
+          <t>全1巻（2014年1月刊行、チャンピオンREDコミックス）</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>ギャグ／パロディ／4コマ風ショート</t>
+          <t>格闘技／空手／青春</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>刃牙シリーズ全般（パロディ元）</t>
+          <t>本編：刃牙シリーズ。同じ人物の外伝：バキ外伝 独歩 -独り飲み喰い歩き-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>名キャラ・名場面のパロディ</t>
+          <t>若き空手家の修行と野心、武の道</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>心理描写より、原作キャラのイメージを裏切るずらしが中心。</t>
+          <t>若い頃の未熟さと野心を描き、のちの『武神』像との距離で成長を感じさせる。</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>短いショートギャグのテンポ。原作の大げさな語調をゆるい場面で使う。</t>
+          <t>血気盛んな若者らしい荒い言葉づかい。</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>1話完結のショート形式。デフォルメした絵柄。</t>
+          <t>空手の型と打撃を力強い線で描く。</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>原作の誇張表現を日常の小さな出来事に当てはめる落差ギャグ。</t>
+          <t>ギャグは少なめ。</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>技法：シリアス作品のキャラを使った公式ショートギャグで、SNS向けの軽い入口を作る。FLATUP案：AIKAやコーチ陣のデフォルメ4コマ『今日のジムあるある』。</t>
+          <t>技法：ベテランキャラの『若い頃』を描く前日譚。FLATUP案：今は穏やかなジムの会長が、若い頃は負けず嫌いで失敗ばかりだった話を会員に語る回。</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>刃牙キャラのデフォルメ絵や、原作名場面のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>愚地独歩の外見（スキンヘッド・眼帯）、神心会という流派名を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]原作ファン向けのパロディとして楽しまれているという声がある。[推測]原作を知らない読者には伝わりにくい。</t>
+          <t>X直接検索なし。[推測]全1巻の短期作のため知名度は高くない。[感想]独歩の若き日が見られる点を評価する声がある。</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/%E3%83%90%E3%82%AD%E3%81%A9%E3%82%82%E3%81%88-b9klm5pzx | https://mechacomic.jp/books/147011/reviews?score=1&amp;submitted=1</t>
+          <t>https://championcross.jp/series/f4d643b0590d6 | https://www.akitashoten.co.jp/comics/4253236219 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E6%8B%B3%E5%88%83-r2t7o70mk</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -12913,12 +12913,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
+          <t>バキどもえ</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん れつかいおうはいせかいてんせいしてもいっこうにかまわんっっ</t>
+          <t>ばきどもえ</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原案）、猪原賽（原作）</t>
+          <t>さいとうなおき（板垣恵介公認とされる）</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>陸井栄史</t>
+          <t>さいとうなおき</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -12953,72 +12953,72 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>月刊少年チャンピオン（開始時の掲載媒体は未確認）</t>
+          <t>週刊少年チャンピオン（電子書店の分類による。未確認）</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2020年代前半開始（開始時期の詳細は未確認）–連載中</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>既刊16巻（第16巻 2026年3月刊行、少年チャンピオン・コミックス）</t>
+          <t>全3巻（少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>異世界／格闘技／ファンタジー／ギャグ</t>
+          <t>ギャグ／パロディ／4コマ風ショート</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>本編：刃牙道（本作の前提となる出来事を含む）</t>
+          <t>刃牙シリーズ全般（パロディ元）</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>武人の誇りを異世界でも貫くこと、魔法と拳法の対比</t>
+          <t>名キャラ・名場面のパロディ</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>異世界の常識に戸惑うより、自分の武の理屈で押し通す主人公の揺るがなさ。</t>
+          <t>心理描写より、原作キャラのイメージを裏切るずらしが中心。</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>格闘漫画の硬い語り口を、ファンタジー世界の住人に向けるずれ。</t>
+          <t>短いショートギャグのテンポ。原作の大げさな語調をゆるい場面で使う。</t>
         </is>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>異世界ファンタジーの背景に、格闘漫画的な筋肉と集中線を持ち込む。</t>
+          <t>1話完結のショート形式。デフォルメした絵柄。</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>魔法や魔物に対して素手の拳法理論で真顔で対処する、ジャンル混合の落差ギャグ。</t>
+          <t>原作の誇張表現を日常の小さな出来事に当てはめる落差ギャグ。</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>技法：ジャンルを混ぜる『場違い』の面白さ。FLATUP案：AIKAがゲーム世界に入り込み、ジムで習った受け身で危機を切り抜ける短編（オリジナル世界観で）。</t>
+          <t>技法：シリアス作品のキャラを使った公式ショートギャグで、SNS向けの軽い入口を作る。FLATUP案：AIKAやコーチ陣のデフォルメ4コマ『今日のジムあるある』。</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>烈海王の外見（辮髪・中国拳法着）、タイトルの言い回し、異世界転生の筋立てをそのまま使わない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>刃牙キャラのデフォルメ絵や、原作名場面のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]チャンピオンクロスの全話無料キャンペーンで外伝の一つとして公開された（2024年）。[感想]タイトルのインパクトで話題になった。[推測]異世界ものファンと刃牙ファンの両方に読まれている。</t>
+          <t>X直接検索なし。[感想]原作ファン向けのパロディとして楽しまれているという声がある。[推測]原作を知らない読者には伝わりにくい。</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/comics/4253012191 | https://landing.akitashoten.co.jp/isekairetsu/ | https://dengekionline.com/article/202405/5717</t>
+          <t>https://mangapedia.com/%E3%83%90%E3%82%AD%E3%81%A9%E3%82%82%E3%81%88-b9klm5pzx | https://mechacomic.jp/books/147011/reviews?score=1&amp;submitted=1</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -13040,12 +13040,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>漫画 ゆうえんち -バキ外伝-</t>
+          <t>バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>まんが ゆうえんち ばきがいでん</t>
+          <t>ばきがいでん れつかいおうはいせかいてんせいしてもいっこうにかまわんっっ</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -13060,17 +13060,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>外伝</t>
+          <t>スピンオフ</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>夢枕獏（原作）、板垣恵介（原案）</t>
+          <t>板垣恵介（原案）、猪原賽（原作）</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>藤田勇利亜</t>
+          <t>陸井栄史</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -13080,72 +13080,72 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン（月1回ペースの連載とされる）</t>
+          <t>月刊少年チャンピオン（開始時の掲載媒体は未確認）</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2022（2022年16号開始）–（現在の連載状況は未確認）</t>
+          <t>2020年代前半開始（開始時期の詳細は未確認）–連載中</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>既刊10巻（少年チャンピオン・コミックス）</t>
+          <t>既刊16巻（第16巻 2026年3月刊行、少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>格闘技／異種格闘技／小説コミカライズ</t>
+          <t>異世界／格闘技／ファンタジー／ギャグ</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>原作：小説 ゆうえんち -バキ外伝-（夢枕獏）</t>
+          <t>本編：刃牙道（本作の前提となる出来事を含む）</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>さまざまな格闘家が集う闘い、強さの比較</t>
+          <t>武人の誇りを異世界でも貫くこと、魔法と拳法の対比</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>小説原作らしく、格闘家の内面の独白や思考の流れを丁寧に描く。</t>
+          <t>異世界の常識に戸惑うより、自分の武の理屈で押し通す主人公の揺るがなさ。</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>小説由来の語りの多さ。地の文的なナレーション。</t>
+          <t>格闘漫画の硬い語り口を、ファンタジー世界の住人に向けるずれ。</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>技の細部を分解して見せる描写。</t>
+          <t>異世界ファンタジーの背景に、格闘漫画的な筋肉と集中線を持ち込む。</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少なめ。</t>
+          <t>魔法や魔物に対して素手の拳法理論で真顔で対処する、ジャンル混合の落差ギャグ。</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>技法：ナレーションで技の理屈を一つずつ解説する。FLATUP案：初心者向け動画マニュアルで、ジャブの動きを3段階に分けて語りで解説する構成。</t>
+          <t>技法：ジャンルを混ぜる『場違い』の面白さ。FLATUP案：AIKAがゲーム世界に入り込み、ジムで習った受け身で危機を切り抜ける短編（オリジナル世界観で）。</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>原作小説・漫画のキャラ・設定・ナレーション文を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>烈海王の外見（辮髪・中国拳法着）、タイトルの言い回し、異世界転生の筋立てをそのまま使わない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]夢枕獏と刃牙の組み合わせを喜ぶ声がある。[推測]格闘小説ファン寄りの読者層。</t>
+          <t>X直接検索なし。[事実]チャンピオンクロスの全話無料キャンペーンで外伝の一つとして公開された（2024年）。[感想]タイトルのインパクトで話題になった。[推測]異世界ものファンと刃牙ファンの両方に読まれている。</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/series/11820 | https://www.akitashoten.co.jp/comics/4253015913 | https://championcross.jp/series/8a3b23bd8c6ce</t>
+          <t>https://www.akitashoten.co.jp/comics/4253012191 | https://landing.akitashoten.co.jp/isekairetsu/ | https://dengekionline.com/article/202405/5717</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>小説 ゆうえんち -バキ外伝-</t>
+          <t>漫画 ゆうえんち -バキ外伝-</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>しょうせつ ゆうえんち ばきがいでん</t>
+          <t>まんが ゆうえんち ばきがいでん</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -13192,12 +13192,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>夢枕獏</t>
+          <t>夢枕獏（原作）、板垣恵介（原案）</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>未確認（小説のため作画なし。挿絵の有無は未確認）</t>
+          <t>藤田勇利亜</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -13207,72 +13207,72 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>少年チャンピオン・ノベルズ（初出媒体は未確認）</t>
+          <t>週刊少年チャンピオン（月1回ペースの連載とされる）</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>2022（2022年16号開始）–（現在の連載状況は未確認）</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>少なくとも2巻を確認（総巻数は未確認、新書判）</t>
+          <t>既刊10巻（少年チャンピオン・コミックス）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>格闘小説／異種格闘技</t>
+          <t>格闘技／異種格闘技／小説コミカライズ</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>コミカライズ：漫画 ゆうえんち -バキ外伝-</t>
+          <t>原作：小説 ゆうえんち -バキ外伝-（夢枕獏）</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>格闘家同士の闘いと強さの探求</t>
+          <t>さまざまな格闘家が集う闘い、強さの比較</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>小説ならではの内面描写（恐怖、期待、身体感覚）を言葉で積み上げる。</t>
+          <t>小説原作らしく、格闘家の内面の独白や思考の流れを丁寧に描く。</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>短い文の連打で緊張を高める文体とされる（要確認）。</t>
+          <t>小説由来の語りの多さ。地の文的なナレーション。</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>小説のため、改行と擬音で間を作る。</t>
+          <t>技の細部を分解して見せる描写。</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>ギャグは少なめ。</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>技法：身体感覚を言葉で描く。FLATUP案：SNSの短文投稿で『初めてミットを打った時の手のしびれ』など体験を言葉で伝える。</t>
+          <t>技法：ナレーションで技の理屈を一つずつ解説する。FLATUP案：初心者向け動画マニュアルで、ジャブの動きを3段階に分けて語りで解説する構成。</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>小説本文・キャラ・設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>原作小説・漫画のキャラ・設定・ナレーション文を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[推測]漫画版の原作として知られる。評判の詳細は未確認。</t>
+          <t>X直接検索なし。[感想]夢枕獏と刃牙の組み合わせを喜ぶ声がある。[推測]格闘小説ファン寄りの読者層。</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253107617 | https://www.kinokuniya.co.jp/f/dsg-01-9784253107624</t>
+          <t>https://www.akitashoten.co.jp/series/11820 | https://www.akitashoten.co.jp/comics/4253015913 | https://championcross.jp/series/8a3b23bd8c6ce</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 ガイアとシコルスキー ～ときどきノムラ 二人だけど三人暮らし～</t>
+          <t>小説 ゆうえんち -バキ外伝-</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん がいあとしこるすきー ときどきのむら ふたりだけどさんにんぐらし</t>
+          <t>しょうせつ ゆうえんち ばきがいでん</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -13314,17 +13314,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>スピンオフ</t>
+          <t>外伝</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原案）</t>
+          <t>夢枕獏</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>林たかあき</t>
+          <t>未確認（小説のため作画なし。挿絵の有無は未確認）</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -13334,72 +13334,72 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>月刊少年チャンピオン</t>
+          <t>少年チャンピオン・ノベルズ（初出媒体は未確認）</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2020年代前半開始（第1巻 2023年3月刊行）–連載中</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>既刊巻数は未確認（第1巻 2023年3月刊行。二次情報では5巻以上）</t>
+          <t>少なくとも2巻を確認（総巻数は未確認、新書判）</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>ギャグ／日常／同居もの</t>
+          <t>格闘小説／異種格闘技</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>本編：バキ（両キャラの初出）</t>
+          <t>コミカライズ：漫画 ゆうえんち -バキ外伝-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>かつての敵同士の同居生活、奇妙な友情</t>
+          <t>格闘家同士の闘いと強さの探求</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>宿敵同士がぎこちなく共同生活する中で、少しずつ相手を認めていく過程。</t>
+          <t>小説ならではの内面描写（恐怖、期待、身体感覚）を言葉で積み上げる。</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>生活の小さな問題を、格闘家らしい大げさな言葉で語るずれ。</t>
+          <t>短い文の連打で緊張を高める文体とされる（要確認）。</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>狭い部屋に大男2人を詰め込む構図の窮屈さ。</t>
+          <t>小説のため、改行と擬音で間を作る。</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>殺伐とした本編キャラが家事や近所付き合いをするギャップ、二重人格的な設定の勘違いギャグ。</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>技法：ライバル同士の同居・日常コメディ。FLATUP案：スパーで勝ち負けを競う会員2人が、ジムの掃除当番でペアになる回。オリジナル台詞案『拭き掃除でも、負けたくないんだよな』。</t>
+          <t>技法：身体感覚を言葉で描く。FLATUP案：SNSの短文投稿で『初めてミットを打った時の手のしびれ』など体験を言葉で伝える。</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>ガイア・シコルスキーの外見、軍人・死刑囚という設定、人格切り替えの設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>小説本文・キャラ・設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]週刊少年チャンピオンにも特別掲載された記録がある。[感想]意外な組み合わせの日常ギャグとして話題になった。[推測]本編を読んでいるほど笑える作り。</t>
+          <t>X直接検索なし。[推測]漫画版の原作として知られる。評判の詳細は未確認。</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>https://www.akitashoten.co.jp/comics/4253294162 | https://arc.akitashoten.co.jp/comics/gaishiko/1 | https://championcross.jp/series/e76cd5db52ef2</t>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253107617 | https://www.kinokuniya.co.jp/f/dsg-01-9784253107624</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -13421,12 +13421,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>バキ外伝 独歩 -独り飲み喰い歩き-</t>
+          <t>バキ外伝 ガイアとシコルスキー ～ときどきノムラ 二人だけど三人暮らし～</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ばきがいでん どっぽ ひとりのみくいあるき</t>
+          <t>ばきがいでん がいあとしこるすきー ときどきのむら ふたりだけどさんにんぐらし</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>板垣恵介（原案）、浜岡賢次（ネーム原作）</t>
+          <t>板垣恵介（原案）</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -13461,72 +13461,72 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>チャンピオンRED</t>
+          <t>月刊少年チャンピオン</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2026（チャンピオンRED 2026年7月号開始）–連載中</t>
+          <t>2020年代前半開始（第1巻 2023年3月刊行）–連載中</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>未確認（単行本未確認）</t>
+          <t>既刊巻数は未確認（第1巻 2023年3月刊行。二次情報では5巻以上）</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>グルメ／日常／格闘技</t>
+          <t>ギャグ／日常／同居もの</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>同じ人物の外伝：バキ外伝 拳刃。作画者の他作：バキ外伝 ガイアとシコルスキー</t>
+          <t>本編：バキ（両キャラの初出）</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>武人の一人飲み・食べ歩き、日常の楽しみ</t>
+          <t>かつての敵同士の同居生活、奇妙な友情</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>強者が一人で食事を味わう静かな時間を描くとされる（詳細未確認）。</t>
+          <t>宿敵同士がぎこちなく共同生活する中で、少しずつ相手を認めていく過程。</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>生活の小さな問題を、格闘家らしい大げさな言葉で語るずれ。</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>狭い部屋に大男2人を詰め込む構図の窮屈さ。</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>武の達人が食事に武道の理屈を持ち込むずれと推測される（未確認）。</t>
+          <t>殺伐とした本編キャラが家事や近所付き合いをするギャップ、二重人格的な設定の勘違いギャグ。</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>技法：格闘キャラのグルメ・日常スピンオフ。FLATUP案：練習後にコーチが『減量中でも食べていいもの』を紹介する食レポ風SNS漫画。</t>
+          <t>技法：ライバル同士の同居・日常コメディ。FLATUP案：スパーで勝ち負けを競う会員2人が、ジムの掃除当番でペアになる回。オリジナル台詞案『拭き掃除でも、負けたくないんだよな』。</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>愚地独歩の外見、神心会の名称、グルメ漫画のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
+          <t>ガイア・シコルスキーの外見、軍人・死刑囚という設定、人格切り替えの設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]2026年5月に連載開始が発表され、初回は表紙・巻頭カラー・3話掲載。[推測]評判はまだ未確認。</t>
+          <t>X直接検索なし。[事実]週刊少年チャンピオンにも特別掲載された記録がある。[感想]意外な組み合わせの日常ギャグとして話題になった。[推測]本編を読んでいるほど笑える作り。</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>https://prtimes.jp/main/html/rd/p/000000854.000040601.html | https://dengekionline.com/article/202604/72212 | https://x.com/teambaki/status/2056570540148588645</t>
+          <t>https://www.akitashoten.co.jp/comics/4253294162 | https://arc.akitashoten.co.jp/comics/gaishiko/1 | https://championcross.jp/series/e76cd5db52ef2</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳</t>
+          <t>バキ外伝 独歩 -独り飲み喰い歩き-</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ほくとのけん</t>
+          <t>ばきがいでん どっぽ ひとりのみくいあるき</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -13563,97 +13563,97 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳シリーズ</t>
+          <t>刃牙シリーズ</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>スピンオフ</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>武論尊</t>
+          <t>板垣恵介（原案）、浜岡賢次（ネーム原作）</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>原哲夫</t>
+          <t>林たかあき</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>集英社（後年の版はコアミックス）</t>
+          <t>秋田書店</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>週刊少年ジャンプ</t>
+          <t>チャンピオンRED</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>1983–1988（1983年41号〜1988年35号）</t>
+          <t>2026（チャンピオンRED 2026年7月号開始）–連載中</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>全27巻（ジャンプ・コミックス）</t>
+          <t>未確認（単行本未確認）</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>格闘技／世紀末／アクション／ドラマ</t>
+          <t>グルメ／日常／格闘技</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳 イチゴ味、北斗の拳 拳王軍ザコたちの挽歌、北斗の拳 世紀末ドラマ撮影伝、蒼黒の餓狼 北斗の拳 レイ外伝、北斗の拳 ラオウ外伝 天の覇王 など</t>
+          <t>同じ人物の外伝：バキ外伝 拳刃。作画者の他作：バキ外伝 ガイアとシコルスキー</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>文明崩壊後の世界での強さと哀しみ、弱い人を守る、宿命、兄弟、愛</t>
+          <t>武人の一人飲み・食べ歩き、日常の楽しみ</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>主人公はほとんど感情を表に出さず、怒りや哀しみを短い言葉と表情で示す。敵側にもそれぞれの過去と執着があり、最期に心情を明かす構成が多い</t>
+          <t>強者が一人で食事を味わう静かな時間を描くとされる（詳細未確認）。</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>主人公は極端に寡黙で短く言い切る。雑魚キャラは語尾を伸ばす叫びや奇声で荒々しさとコミカルさを出す。重いナレーションで時代背景を語る</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>荒野と砂嵐の背景、筋肉の誇張、逆光のシルエット、劇画調の太い線と黒ベタ、決め技の瞬間の大ゴマと集中線</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>本編はシリアスだが、雑魚キャラの過剰な悪役ぶりや奇声が結果的に笑いを生み、ネットのネタとして定着している</t>
+          <t>武の達人が食事に武道の理屈を持ち込むずれと推測される（未確認）。</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>「202X年」から始まる重いナレーション、荒野、雑魚の叫び声というジャンルの型を、世紀末パロディのオープニングに使う。強い者が弱い者を守るという芯は、FLATUPの「強さは優しさ」と相性がよい。オリジナル案：「殴る相手はミットだけでいい」</t>
+          <t>技法：格闘キャラのグルメ・日常スピンオフ。FLATUP案：練習後にコーチが『減量中でも食べていいもの』を紹介する食レポ風SNS漫画。</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>原作冒頭のナレーションの言い回し、有名な決めゼリフ、やられたときの叫び声、胸の七つの傷、トゲ付き肩パッド、拳法名・技名、経絡秘孔の設定、キャラクターの外見、主題歌、タイトルロゴの書体は使わない</t>
+          <t>愚地独歩の外見、神心会の名称、グルメ漫画のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>[事実] 累計発行部数は全世界1億部超（2019年11月時点の記事）とされる。 [事実] 雑魚キャラを主人公にしたギャグのスピンオフが公式に作られ、2026年1月にショートアニメ化された。 [感想] 雑魚キャラの叫び声がネットミームとして親しまれている。 X直接検索なし</t>
+          <t>X直接検索なし。[事実]2026年5月に連載開始が発表され、初回は表紙・巻頭カラー・3話掲載。[推測]評判はまだ未確認。</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>https://bestcalendar.jp/dates/kinenbi/3791 | https://comic.k-manga.jp/title/67231/pv | https://renote.net/tags/246/articles</t>
+          <t>https://prtimes.jp/main/html/rd/p/000000854.000040601.html | https://dengekionline.com/article/202604/72212 | https://x.com/teambaki/status/2056570540148588645</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -13675,12 +13675,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳 イチゴ味</t>
+          <t>北斗の拳</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ほくとのけん いちごあじ</t>
+          <t>ほくとのけん</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -13695,92 +13695,92 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>スピンオフ</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>未確認（原作者の監修のもとで制作されたとされる）</t>
+          <t>武論尊</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>原哲夫</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>集英社（後年の版はコアミックス）</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>週刊少年ジャンプ</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>1983–1988（1983年41号〜1988年35号）</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>全27巻（ジャンプ・コミックス）</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>ギャグ／パロディ</t>
+          <t>格闘技／世紀末／アクション／ドラマ</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳（本編）。2015年にテレビアニメ化</t>
+          <t>北斗の拳 イチゴ味、北斗の拳 拳王軍ザコたちの挽歌、北斗の拳 世紀末ドラマ撮影伝、蒼黒の餓狼 北斗の拳 レイ外伝、北斗の拳 ラオウ外伝 天の覇王 など</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>本編の悪役を主人公にした、自分をパロディにするギャグ</t>
+          <t>文明崩壊後の世界での強さと哀しみ、弱い人を守る、宿命、兄弟、愛</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>主人公はほとんど感情を表に出さず、怒りや哀しみを短い言葉と表情で示す。敵側にもそれぞれの過去と執着があり、最期に心情を明かす構成が多い</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>本編の重い言い回しを、日常のくだらない場面で使って落差を作る（紹介記事の説明による）</t>
+          <t>主人公は極端に寡黙で短く言い切る。雑魚キャラは語尾を伸ばす叫びや奇声で荒々しさとコミカルさを出す。重いナレーションで時代背景を語る</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>原作のタッチやアニメ版をそっくり再現した作画で、ギャグとの落差を強めている（紹介記事の説明による）</t>
+          <t>荒野と砂嵐の背景、筋肉の誇張、逆光のシルエット、劇画調の太い線と黒ベタ、決め技の瞬間の大ゴマと集中線</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>シリアスな絵柄のまま、ばかばかしいことを大真面目にやる落差のギャグ</t>
+          <t>本編はシリアスだが、雑魚キャラの過剰な悪役ぶりや奇声が結果的に笑いを生み、ネットのネタとして定着している</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>劇画の絵柄のまま、ジムの日常（ストレッチで太ももが伸びて感動する、など）を大真面目に描く落差の技法に使える</t>
+          <t>「202X年」から始まる重いナレーション、荒野、雑魚の叫び声というジャンルの型を、世紀末パロディのオープニングに使う。強い者が弱い者を守るという芯は、FLATUPの「強さは優しさ」と相性がよい。オリジナル案：「殴る相手はミットだけでいい」</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
+          <t>原作冒頭のナレーションの言い回し、有名な決めゼリフ、やられたときの叫び声、胸の七つの傷、トゲ付き肩パッド、拳法名・技名、経絡秘孔の設定、キャラクターの外見、主題歌、タイトルロゴの書体は使わない</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>[事実] 2015年にテレビアニメ化された。 X直接検索なし</t>
+          <t>[事実] 累計発行部数は全世界1億部超（2019年11月時点の記事）とされる。 [事実] 雑魚キャラを主人公にしたギャグのスピンオフが公式に作られ、2026年1月にショートアニメ化された。 [感想] 雑魚キャラの叫び声がネットミームとして親しまれている。 X直接検索なし</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/gd/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3-chyqulnxj/</t>
+          <t>https://bestcalendar.jp/dates/kinenbi/3791 | https://comic.k-manga.jp/title/67231/pv | https://renote.net/tags/246/articles</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳 拳王軍ザコたちの挽歌</t>
+          <t>北斗の拳 イチゴ味</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ほくとのけん けんおうぐんざこたちのばんか</t>
+          <t>ほくとのけん いちごあじ</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -13827,14 +13827,14 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
+          <t>未確認（原作者の監修のもとで制作されたとされる）</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>倉尾宏</t>
-        </is>
-      </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
@@ -13857,42 +13857,42 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>ギャグ／パロディ／お仕事</t>
+          <t>ギャグ／パロディ</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>北斗の拳（本編）、北斗の拳 世紀末ドラマ撮影伝（同じ作画者）。2026年1月5日からショートアニメ放送</t>
+          <t>北斗の拳（本編）。2015年にテレビアニメ化</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>悪の軍団に就職した下っ端の視点で、組織で働く悲哀を笑いにする</t>
+          <t>本編の悪役を主人公にした、自分をパロディにするギャグ</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>主人公の下っ端が、組織や上司の理不尽にふり回される気持ちを描く（紹介記事の説明による）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>本編の重い言い回しを、日常のくだらない場面で使って落差を作る（紹介記事の説明による）</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>原作のタッチやアニメ版をそっくり再現した作画で、ギャグとの落差を強めている（紹介記事の説明による）</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>雑魚が次々にやられる「お約束」を、下っ端の側から描いて笑いにする</t>
+          <t>シリアスな絵柄のまま、ばかばかしいことを大真面目にやる落差のギャグ</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>雑魚キャラの側から描く視点がとても参考になる。FLATUPの「ヒャッハー三人衆」を主人公にして、入会して少しずつ変わっていく話にできる</t>
+          <t>劇画の絵柄のまま、ジムの日常（ストレッチで太ももが伸びて感動する、など）を大真面目に描く落差の技法に使える</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -13902,12 +13902,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>[事実] 2026年1月5日からショートアニメが放送された。 X直接検索なし</t>
+          <t>[事実] 2015年にテレビアニメ化された。 X直接検索なし</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>https://animeanime.jp/article/2025/12/25/94731.html | https://mangapedia.com/gd/ag0gpp5uc</t>
+          <t>https://mangapedia.com/gd/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3-chyqulnxj/</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>拳児</t>
+          <t>北斗の拳 拳王軍ザコたちの挽歌</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>けんじ</t>
+          <t>ほくとのけん けんおうぐんざこたちのばんか</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -13944,97 +13944,97 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>単独</t>
+          <t>北斗の拳シリーズ</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>スピンオフ</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>松田隆智</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>藤原芳秀</t>
+          <t>倉尾宏</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>1988–1992（終了年は二次情報による）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>全21巻（少年サンデーコミックス）／ワイド版・文庫版あり（巻数未確認）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>中国武術／八極拳／修行／旅</t>
+          <t>ギャグ／パロディ／お仕事</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
+          <t>北斗の拳（本編）、北斗の拳 世紀末ドラマ撮影伝（同じ作画者）。2026年1月5日からショートアニメ放送</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>悪の軍団に就職した下っ端の視点で、組織で働く悲哀を笑いにする</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>主人公の下っ端が、組織や上司の理不尽にふり回される気持ちを描く（紹介記事の説明による）</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>武術の本質の探求、師との出会い、礼節と修行</t>
-        </is>
-      </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>元気な少年が各地の師に出会うたびに自分の未熟さを知り、謙虚さを学んでいく過程。</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>師匠たちが武術の理（り）を説明する教養的な台詞が多い。</t>
-        </is>
-      </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>実在の武術の型や套路を写実的に描く。旅先の風景描写。</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>少年のやんちゃさ、祖父とのやり取り。</t>
+          <t>雑魚が次々にやられる「お約束」を、下っ端の側から描いて笑いにする</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>技法：技の『理屈』を丁寧に描き、読者が学べる漫画にする。FLATUP案：AIKAがパンチの体重移動を図解で教えるミニ漫画（教育コンテンツ）。</t>
+          <t>雑魚キャラの側から描く視点がとても参考になる。FLATUPの「ヒャッハー三人衆」を主人公にして、入会して少しずつ変わっていく話にできる</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>主人公・師匠キャラの名前と外見、作中の流派・師弟系譜の描写を流用しない。</t>
+          <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
         </is>
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]武術ファンの間で『中国武術に興味を持つきっかけ』として語られることが多い。[推測]実在武術の描写の丁寧さが評価されている。</t>
+          <t>[事実] 2026年1月5日からショートアニメが放送された。 X直接検索なし</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv</t>
+          <t>https://animeanime.jp/article/2025/12/25/94731.html | https://mangapedia.com/gd/ag0gpp5uc</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
@@ -14056,12 +14056,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>空手バカ一代</t>
+          <t>拳児</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>からてばかいちだい</t>
+          <t>けんじ</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -14081,87 +14081,87 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎</t>
+          <t>松田隆智</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>つのだじろう（1〜11巻）、影丸譲也（12〜29巻）</t>
+          <t>藤原芳秀</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>1971–1977</t>
+          <t>1988–1992（終了年は二次情報による）</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>全29巻</t>
+          <t>全21巻（少年サンデーコミックス）／ワイド版・文庫版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>空手／伝記風／修行</t>
+          <t>中国武術／八極拳／修行／旅</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>原作者の他作：巨人の星、あしたのジョー（原作 高森朝雄名義）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ひたむきな修行、武道家の一代記、強さへの執念</t>
+          <t>武術の本質の探求、師との出会い、礼節と修行</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>主人公の孤独な修行と挫折を、ナレーションで劇的に語る。</t>
+          <t>元気な少年が各地の師に出会うたびに自分の未熟さを知り、謙虚さを学んでいく過程。</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>熱いナレーションが物語を引っ張る劇画調。誇張された語り。</t>
+          <t>師匠たちが武術の理（り）を説明する教養的な台詞が多い。</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>劇画の濃い線と黒ベタ、修行場面の荒々しい自然描写。</t>
+          <t>実在の武術の型や套路を写実的に描く。旅先の風景描写。</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>ギャグは少ない。</t>
+          <t>少年のやんちゃさ、祖父とのやり取り。</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>技法：ナレーションで物語の熱量を上げる劇画の手法。FLATUP案：ジム10周年の記念動画で、創設者の『最初の一日』を熱いナレーションで語る（実在人物の事実確認を前提に）。ただし『根性で痛みに耐える』表現は採らない。</t>
+          <t>技法：技の『理屈』を丁寧に描き、読者が学べる漫画にする。FLATUP案：AIKAがパンチの体重移動を図解で教えるミニ漫画（教育コンテンツ）。</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>実在の空手家をモデルにした人物像、劇画のナレーション文、修行エピソード（動物との対決など）を流用しない。</t>
+          <t>主人公・師匠キャラの名前と外見、作中の流派・師弟系譜の描写を流用しない。</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]1973年にTVアニメ化（二次情報）。[感想]空手ブームに影響したと語られることが多い。[推測]実話と創作の境目について議論がある。</t>
+          <t>X直接検索なし。[感想]武術ファンの間で『中国武術に興味を持つきっかけ』として語られることが多い。[推測]実在武術の描写の丁寧さが評価されている。</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Karate_Master | https://www.kodansha.co.jp/comic/new-releases/p?page=2201 | https://mangapedia.com/%E3%81%A4%E3%81%AE%E3%81%A0%E3%81%98%E3%82%8D%E3%81%86-3h7myqn64</t>
+          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>はじめの一歩</t>
+          <t>空手バカ一代</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>はじめのいっぽ</t>
+          <t>からてばかいちだい</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>森川ジョージ</t>
+          <t>梶原一騎</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>森川ジョージ</t>
+          <t>つのだじろう（1〜11巻）、影丸譲也（12〜29巻）</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -14228,67 +14228,67 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>1989–連載中（1989年43号開始）</t>
+          <t>1971–1977</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>既刊145巻以上（145巻は2026年1月16日発売。以降の巻数は未確認）</t>
+          <t>全29巻</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／スポーツ／成長／ジム群像／ギャグ</t>
+          <t>空手／伝記風／修行</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（複数シリーズ）、作中キャラの外伝的エピソード（鷹村・間柴など）は本編内。同作者の別作品は未確認</t>
+          <t>原作者の他作：巨人の星、あしたのジョー（原作 高森朝雄名義）</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>いじめられっ子が強さの意味を問い続ける成長、努力の積み重ね、師弟の信頼、ジム仲間の家族的な絆、強さとは何かという問い</t>
+          <t>ひたむきな修行、武道家の一代記、強さへの執念</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>主人公の恐怖や自信のなさを丁寧に積み上げ、試合中の『怖いけど前に出る』瞬間を内面モノローグで細かく描く。敗者側の人生や引退後の葛藤にも章を割き、勝ち負けの後の心を描く。</t>
+          <t>主人公の孤独な修行と挫折を、ナレーションで劇的に語る。</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>主人公は丁寧語で控えめ、先輩格は粗野で豪快という対比がはっきり。試合中は短い叫びと解説役の説明的なセリフが交互に入り、技術を読者に分かりやすく伝える。</t>
+          <t>熱いナレーションが物語を引っ張る劇画調。誇張された語り。</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>パンチの軌道を大きな効果線で見せる見開き、ダウン寸前の視界の揺れ、観客席の反応カットの挿入。練習パートは日常のコマ割り、試合はコマを大きくして緩急をつける。</t>
+          <t>劇画の濃い線と黒ベタ、修行場面の荒々しい自然描写。</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>ジムの先輩たちによるいじり、恋愛に奥手な主人公の勘違い、釣り船屋の日常ネタ。シリアスな試合の直後に脱力ギャグを置く落差が定番。</t>
+          <t>ギャグは少ない。</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>技法：初心者の『怖さ』をモノローグで正直に描き、小さな一歩を大きく演出する。練習→試合の緩急、ジム仲間のいじり合いで温かさを出す。オリジナル案：初めてミットを打った会員が『音が鳴った』だけで目を輝かせる回。セリフ案『上手くなくていい。今日来たのがもう勝ち』。</t>
+          <t>技法：ナレーションで物語の熱量を上げる劇画の手法。FLATUP案：ジム10周年の記念動画で、創設者の『最初の一日』を熱いナレーションで語る（実在人物の事実確認を前提に）。ただし『根性で痛みに耐える』表現は採らない。</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>主人公や鷹村・宮田など主要キャラの外見・髪型、鴨川ジムの名称やロゴ、デンプシーロールなど作中固有の必殺技名と象徴的な動き、釣り船屋という主人公の家業設定をそのまま使わない。</t>
+          <t>実在の空手家をモデルにした人物像、劇画のナレーション文、修行エピソード（動物との対決など）を流用しない。</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>[事実] 1989年から30年以上続く長期連載で、ボクシング漫画の代表作として紹介されることが多い。[感想] 序盤〜中盤の試合描写や脇役の名勝負を高く評価する声が多い。[推測] 近年は展開の遅さや主人公の引退〜復帰の流れに賛否があるとみられる。X直接検索なし。</t>
+          <t>X直接検索なし。[事実]1973年にTVアニメ化（二次情報）。[感想]空手ブームに影響したと語られることが多い。[推測]実話と創作の境目について議論がある。</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>https://bunshun.jp/articles/-/88272 | https://game.watch.impress.co.jp/docs/news/1333266.html | https://www.kodansha.co.jp/comic/products/0000422841 | https://dengekionline.com/articles/208950/</t>
+          <t>https://en.wikipedia.org/wiki/Karate_Master | https://www.kodansha.co.jp/comic/new-releases/p?page=2201 | https://mangapedia.com/%E3%81%A4%E3%81%AE%E3%81%A0%E3%81%98%E3%82%8D%E3%81%86-3h7myqn64</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -14310,12 +14310,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>がんばれ元気</t>
+          <t>はじめの一歩</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>がんばれげんき</t>
+          <t>はじめのいっぽ</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -14335,87 +14335,87 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>小山ゆう</t>
+          <t>森川ジョージ</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>小山ゆう</t>
+          <t>森川ジョージ</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>週刊少年マガジン</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1976–1981</t>
+          <t>1989–連載中（1989年43号開始）</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>全28巻（少年サンデーコミックス）</t>
+          <t>既刊145巻以上（145巻は2026年1月16日発売。以降の巻数は未確認）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／家族／成長／少年</t>
+          <t>ボクシング／スポーツ／成長／ジム群像／ギャグ</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（1980年・全35話）。第22回小学館漫画賞受賞。同作者の『おれは直角』『あずみ』</t>
+          <t>TVアニメ（複数シリーズ）、作中キャラの外伝的エピソード（鷹村・間柴など）は本編内。同作者の別作品は未確認</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>亡き父の夢を継ぐ少年の成長、家族愛、まっすぐな努力、ライバルへの敬意</t>
+          <t>いじめられっ子が強さの意味を問い続ける成長、努力の積み重ね、師弟の信頼、ジム仲間の家族的な絆、強さとは何かという問い</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>幼少期から青年期までを長く追い、父を失った寂しさや期待への重圧を、子どもの目線で素直に描く。泣く・笑うが分かりやすく、読者が感情移入しやすい。</t>
+          <t>主人公の恐怖や自信のなさを丁寧に積み上げ、試合中の『怖いけど前に出る』瞬間を内面モノローグで細かく描く。敗者側の人生や引退後の葛藤にも章を割き、勝ち負けの後の心を描く。</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>主人公は素直で元気な子ども言葉から始まり、成長とともに口調が落ち着く。大人たちは温かく説明的で、少年漫画らしい分かりやすさ。</t>
+          <t>主人公は丁寧語で控えめ、先輩格は粗野で豪快という対比がはっきり。試合中は短い叫びと解説役の説明的なセリフが交互に入り、技術を読者に分かりやすく伝える。</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>丸みのある柔らかい絵柄で、表情（特に涙や笑顔）を大きく見せる。試合は派手さよりも身体の動きの流れを丁寧に描く。</t>
+          <t>パンチの軌道を大きな効果線で見せる見開き、ダウン寸前の視界の揺れ、観客席の反応カットの挿入。練習パートは日常のコマ割り、試合はコマを大きくして緩急をつける。</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>子ども時代の無邪気な失敗や、周囲の大人とのほのぼのしたやりとり。誇張は控えめで、日常のほっこり系。</t>
+          <t>ジムの先輩たちによるいじり、恋愛に奥手な主人公の勘違い、釣り船屋の日常ネタ。シリアスな試合の直後に脱力ギャグを置く落差が定番。</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>技法：子ども時代から段階的に成長を見せる長期構成。柔らかい絵柄で格闘技の怖さを下げる。オリジナル案：キッズクラスの子が卒業までに少しずつ変わっていく年代記。セリフ案『昨日より一回多く、前に出られたね』。</t>
+          <t>技法：初心者の『怖さ』をモノローグで正直に描き、小さな一歩を大きく演出する。練習→試合の緩急、ジム仲間のいじり合いで温かさを出す。オリジナル案：初めてミットを打った会員が『音が鳴った』だけで目を輝かせる回。セリフ案『上手くなくていい。今日来たのがもう勝ち』。</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前や外見、父がボクサーで亡くなる設定の流用、作品タイトルのもじりを避ける。</t>
+          <t>主人公や鷹村・宮田など主要キャラの外見・髪型、鴨川ジムの名称やロゴ、デンプシーロールなど作中固有の必殺技名と象徴的な動き、釣り船屋という主人公の家業設定をそのまま使わない。</t>
         </is>
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>[事実] 女子ボクシングの金メダリストが競技を始めるきっかけに挙げたと報じられた。[感想] 優しい絵柄と家族ドラマで泣ける作品として語られる。[推測] 知名度は世代差が大きいとみられる。X直接検索なし。</t>
+          <t>[事実] 1989年から30年以上続く長期連載で、ボクシング漫画の代表作として紹介されることが多い。[感想] 序盤〜中盤の試合描写や脇役の名勝負を高く評価する声が多い。[推測] 近年は展開の遅さや主人公の引退〜復帰の流れに賛否があるとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>https://number.bunshun.jp/articles/-/849242 | https://www.cmoa.jp/title/528/ | https://mechacomic.jp/books/45940</t>
+          <t>https://bunshun.jp/articles/-/88272 | https://game.watch.impress.co.jp/docs/news/1333266.html | https://www.kodansha.co.jp/comic/products/0000422841 | https://dengekionline.com/articles/208950/</t>
         </is>
       </c>
       <c r="X110" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>B・B</t>
+          <t>がんばれ元気</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>びーびー</t>
+          <t>がんばれげんき</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>石渡治</t>
+          <t>小山ゆう</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>石渡治</t>
+          <t>小山ゆう</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -14482,67 +14482,67 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>1985–1991（1985年24号〜1991年9号）</t>
+          <t>1976–1981</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>全31巻（少年サンデーコミックス。巻数は二次情報）</t>
+          <t>全28巻（少年サンデーコミックス）</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>ボクシング／青春／音楽／アクション</t>
+          <t>ボクシング／家族／成長／少年</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>第34回小学館漫画賞受賞。同作者の『LOVe』『パスポート・ブルー』</t>
+          <t>TVアニメ（1980年・全35話）。第22回小学館漫画賞受賞。同作者の『おれは直角』『あずみ』</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>自由に生きたい若者の反発、友情、ボクシングを通した自己表現、後半は戦場での生と死</t>
+          <t>亡き父の夢を継ぐ少年の成長、家族愛、まっすぐな努力、ライバルへの敬意</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>屈折した主人公の怒りや喪失を大胆な展開で描き、ボクサーから傭兵へという急展開で極限状況の心を見せる。</t>
+          <t>幼少期から青年期までを長く追い、父を失った寂しさや期待への重圧を、子どもの目線で素直に描く。泣く・笑うが分かりやすく、読者が感情移入しやすい。</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>ラフで挑発的な若者口調。サックスなど音楽を絡めた詩的な独白が混ざる。</t>
+          <t>主人公は素直で元気な子ども言葉から始まり、成長とともに口調が落ち着く。大人たちは温かく説明的で、少年漫画らしい分かりやすさ。</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>スピード感のある線、音楽的なリズムのコマ運び、後半は戦争アクションの硬質な画面。</t>
+          <t>丸みのある柔らかい絵柄で、表情（特に涙や笑顔）を大きく見せる。試合は派手さよりも身体の動きの流れを丁寧に描く。</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>前半は軽口と青春ドタバタ。後半は少なめ。</t>
+          <t>子ども時代の無邪気な失敗や、周囲の大人とのほのぼのしたやりとり。誇張は控えめで、日常のほっこり系。</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>技法：音楽やリズムとボクシングのステップを重ねる演出。オリジナル案：会員がBGMに合わせてシャドーをするとステップが自然に良くなる回。セリフ案『リズムに乗れたら、体は勝手に動く』。</t>
+          <t>技法：子ども時代から段階的に成長を見せる長期構成。柔らかい絵柄で格闘技の怖さを下げる。オリジナル案：キッズクラスの子が卒業までに少しずつ変わっていく年代記。セリフ案『昨日より一回多く、前に出られたね』。</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見、ボクサーが傭兵になる大筋、作中のサックス奏者設定をそのまま使わない。</t>
+          <t>主人公の名前や外見、父がボクサーで亡くなる設定の流用、作品タイトルのもじりを避ける。</t>
         </is>
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>[事実] 作者インタビューで主人公が傭兵になる展開の誕生秘話が語られている。[感想] 前半のボクシングと後半の戦場編の落差が強く印象に残るという声。[推測] 現在の知名度は同時代のボクシング漫画より低めとみられる。X直接検索なし。</t>
+          <t>[事実] 女子ボクシングの金メダリストが競技を始めるきっかけに挙げたと報じられた。[感想] 優しい絵柄と家族ドラマで泣ける作品として語られる。[推測] 知名度は世代差が大きいとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>https://gendai.media/articles/-/100861 | https://mangapedia.com/gd/B%E3%83%BBB-9tbu6j1t4/ | https://ranking.net/rankings/best-shonensunday-comics/b6c541bd</t>
+          <t>https://number.bunshun.jp/articles/-/849242 | https://www.cmoa.jp/title/528/ | https://mechacomic.jp/books/45940</t>
         </is>
       </c>
       <c r="X111" s="2" t="inlineStr">
@@ -14564,12 +14564,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>オールラウンダー廻</t>
+          <t>B・B</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>おーるらうんだーめぐる</t>
+          <t>びーびー</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14589,87 +14589,87 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>遠藤浩輝</t>
+          <t>石渡治</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>遠藤浩輝</t>
+          <t>石渡治</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>イブニング</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2008–2016（2008年24号〜2016年7号）</t>
+          <t>1985–1991（1985年24号〜1991年9号）</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>全19巻（イブニングKC）</t>
+          <t>全31巻（少年サンデーコミックス。巻数は二次情報）</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>MMA／修斗／総合格闘技／青春／ジム</t>
+          <t>ボクシング／青春／音楽／アクション</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>同作者の『EDEN 〜It's an Endless World!〜』</t>
+          <t>第34回小学館漫画賞受賞。同作者の『LOVe』『パスポート・ブルー』</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>普通の高校生が総合格闘技に打ち込む青春、幼なじみとの対立と和解、アマチュア競技のリアル</t>
+          <t>自由に生きたい若者の反発、友情、ボクシングを通した自己表現、後半は戦場での生と死</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>勝ちたい気持ちと友情の揺れ、練習の地味さへの焦り、減量や試合前の不安を等身大に描く。</t>
+          <t>屈折した主人公の怒りや喪失を大胆な展開で描き、ボクサーから傭兵へという急展開で極限状況の心を見せる。</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>日常会話は普通の高校生らしく軽い。技術解説は具体的で専門用語を噛み砕いて説明する。</t>
+          <t>ラフで挑発的な若者口調。サックスなど音楽を絡めた詩的な独白が混ざる。</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>寝技・関節技の体勢を正確に描き、アマ修斗のルールや試合運びを丁寧に見せる。派手な誇張は控えめ。</t>
+          <t>スピード感のある線、音楽的なリズムのコマ運び、後半は戦争アクションの硬質な画面。</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>ジム仲間や家族とのゆるい日常ギャグ、恋愛まわりの照れ。</t>
+          <t>前半は軽口と青春ドタバタ。後半は少なめ。</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>技法：MMAのルールや技を初心者にも分かるよう噛み砕いて描く。地味な練習の積み重ねをドラマにする。オリジナル案：寝技の初体験で『怖い』が『おもしろい』に変わる瞬間を描く回。セリフ案『タップは負けじゃない。また練習できる合図だよ』。</t>
+          <t>技法：音楽やリズムとボクシングのステップを重ねる演出。オリジナル案：会員がBGMに合わせてシャドーをするとステップが自然に良くなる回。セリフ案『リズムに乗れたら、体は勝手に動く』。</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
-          <t>主人公と幼なじみのキャラ造形、作中ジム名、実在団体（修斗）のロゴや公式表記の無断使用を避ける。</t>
+          <t>主人公の外見、ボクサーが傭兵になる大筋、作中のサックス奏者設定をそのまま使わない。</t>
         </is>
       </c>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>[事実] 修斗を題材にした作品として格闘技ファンに紹介される。[感想] 格闘技経験者から描写のリアルさを評価する声。[推測] MMA漫画の入門として勧められやすいとみられる。X直接検索なし。</t>
+          <t>[事実] 作者インタビューで主人公が傭兵になる展開の誕生秘話が語られている。[感想] 前半のボクシングと後半の戦場編の落差が強く印象に残るという声。[推測] 現在の知名度は同時代のボクシング漫画より低めとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E3%82%AA%E3%83%BC%E3%83%AB%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%80%E3%83%BC%E5%BB%BB | https://www.kodansha.co.jp/comic/products/0000038657 | https://bookwalker.jp/de77e612eb-ae5e-4edd-acd0-e2eb92f4eff0/</t>
+          <t>https://gendai.media/articles/-/100861 | https://mangapedia.com/gd/B%E3%83%BBB-9tbu6j1t4/ | https://ranking.net/rankings/best-shonensunday-comics/b6c541bd</t>
         </is>
       </c>
       <c r="X112" s="2" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="Y112" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -14691,12 +14691,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>軍鶏</t>
+          <t>オールラウンダー廻</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>しゃも</t>
+          <t>おーるらうんだーめぐる</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -14716,87 +14716,87 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>橋本以蔵（途中から作画者の単独名義とされる）</t>
+          <t>遠藤浩輝</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>たなか亜希夫</t>
+          <t>遠藤浩輝</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>双葉社 → 講談社</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>漫画アクション → イブニング</t>
+          <t>イブニング</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>1998–2015（完結年は二次情報）</t>
+          <t>2008–2016（2008年24号〜2016年7号）</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>全34巻（講談社イブニングKC）。再編集版の極厚版は全22巻</t>
+          <t>全19巻（イブニングKC）</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>空手／総合格闘技／犯罪／暴力／ダーク</t>
+          <t>MMA／修斗／総合格闘技／青春／ジム</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>実写映画（2008年）</t>
+          <t>同作者の『EDEN 〜It's an Endless World!〜』</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>罪を犯した少年が生き延びるために暴力を身につける、人間の暗部、孤独</t>
+          <t>普通の高校生が総合格闘技に打ち込む青春、幼なじみとの対立と和解、アマチュア競技のリアル</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>主人公の自己嫌悪・憎しみ・恐怖を容赦なく描く。救いの少ない心理描写。</t>
+          <t>勝ちたい気持ちと友情の揺れ、練習の地味さへの焦り、減量や試合前の不安を等身大に描く。</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>荒々しく冷たい言葉。内面語りは少なめで行動で示す。</t>
+          <t>日常会話は普通の高校生らしく軽い。技術解説は具体的で専門用語を噛み砕いて説明する。</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>劇画調の濃い陰影、暴力の生々しい描写、閉塞感のある画面。</t>
+          <t>寝技・関節技の体勢を正確に描き、アマ修斗のルールや試合運びを丁寧に見せる。派手な誇張は控えめ。</t>
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>ほぼなし。</t>
+          <t>ジム仲間や家族とのゆるい日常ギャグ、恋愛まわりの照れ。</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>技法：反面教師として、暴力だけの強さがいかに人を孤独にするかを示す作品。FLATUPの『強さ＝優しさ』の対比として、悪役側の心理の深さを学ぶ程度に留める。</t>
+          <t>技法：MMAのルールや技を初心者にも分かるよう噛み砕いて描く。地味な練習の積み重ねをドラマにする。オリジナル案：寝技の初体験で『怖い』が『おもしろい』に変わる瞬間を描く回。セリフ案『タップは負けじゃない。また練習できる合図だよ』。</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見、少年院から格闘家になる設定、過激な暴力・性暴力描写は絶対に真似しない（ブランドと完全に逆方向）。</t>
+          <t>主人公と幼なじみのキャラ造形、作中ジム名、実在団体（修斗）のロゴや公式表記の無断使用を避ける。</t>
         </is>
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>[事実] 原作者と作画者の間で著作権をめぐる裁判があったとされる。[感想] 迫力は高いが重く暗いという声。[推測] 一般向け・子ども向けには勧めにくい作品とみられる。X直接検索なし。</t>
+          <t>[事実] 修斗を題材にした作品として格闘技ファンに紹介される。[感想] 格闘技経験者から描写のリアルさを評価する声。[推測] MMA漫画の入門として勧められやすいとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000038793 | https://renote.net/reviews/5254 | https://www.cmoa.jp/title/87790</t>
+          <t>https://dic.nicovideo.jp/a/%E3%82%AA%E3%83%BC%E3%83%AB%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%80%E3%83%BC%E5%BB%BB | https://www.kodansha.co.jp/comic/products/0000038657 | https://bookwalker.jp/de77e612eb-ae5e-4edd-acd0-e2eb92f4eff0/</t>
         </is>
       </c>
       <c r="X113" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>キックの鬼</t>
+          <t>軍鶏</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>きっくのおに</t>
+          <t>しゃも</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -14843,62 +14843,62 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎</t>
+          <t>橋本以蔵（途中から作画者の単独名義とされる）</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>中城健（中城けんたろう）</t>
+          <t>たなか亜希夫</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>双葉社 → 講談社</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>週刊少年キング または 少年画報（資料により食い違い）</t>
+          <t>漫画アクション → イブニング</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>1969–1971（開始時期は資料により異なる）</t>
+          <t>1998–2015（完結年は二次情報）</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>全6巻（英語版Wikipedia）。他に3巻とする記述もあり未確定</t>
+          <t>全34巻（講談社イブニングKC）。再編集版の極厚版は全22巻</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／実録／梶原一騎</t>
+          <t>空手／総合格闘技／犯罪／暴力／ダーク</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（1970年）。同原作者の『あしたのジョー』『紅の挑戦者』</t>
+          <t>実写映画（2008年）</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>実在のキックボクサー沢村忠をモデルにした成り上がり、日本のキックボクシング黎明期</t>
+          <t>罪を犯した少年が生き延びるために暴力を身につける、人間の暗部、孤独</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>主人公の不屈の精神と根性を前面に出す。内面の弱さより覚悟を強調する昭和スポ根型。</t>
+          <t>主人公の自己嫌悪・憎しみ・恐怖を容赦なく描く。救いの少ない心理描写。</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>熱血で大仰な語り口、ナレーションで事実風に語るセミドキュメンタリー調。</t>
+          <t>荒々しく冷たい言葉。内面語りは少なめで行動で示す。</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>劇画調、飛び蹴りなど技の瞬間を大きく見せる。</t>
+          <t>劇画調の濃い陰影、暴力の生々しい描写、閉塞感のある画面。</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
@@ -14908,22 +14908,22 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>技法：実在の歴史を背景にした『物語として語る格闘技史』。オリジナル案：日本のキックボクシングの歴史を、会員向けにやさしく紹介する短編漫画（実在人物の扱いは要注意）。</t>
+          <t>技法：反面教師として、暴力だけの強さがいかに人を孤独にするかを示す作品。FLATUPの『強さ＝優しさ』の対比として、悪役側の心理の深さを学ぶ程度に留める。</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
-          <t>実在人物（沢村忠）の肖像やエピソードの流用、作中の技名、タイトルのもじりを避ける。</t>
+          <t>主人公の外見、少年院から格闘家になる設定、過激な暴力・性暴力描写は絶対に真似しない（ブランドと完全に逆方向）。</t>
         </is>
       </c>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>[事実] 沢村忠をモデルにした作品で、1970年にアニメ化された。[感想] 昭和のキックボクシングブームを伝える作品として語られる。[推測] 現在の読者は少ないとみられる。X直接検索なし。</t>
+          <t>[事実] 原作者と作画者の間で著作権をめぐる裁判があったとされる。[感想] 迫力は高いが重く暗いという声。[推測] 一般向け・子ども向けには勧めにくい作品とみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kick_no_Oni | https://mangapedia.com/%E3%82%AD%E3%83%83%E3%82%AF%E3%81%AE%E9%AC%BC-6rimm0fjt | https://comic.k-manga.jp/title/165/pv</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000038793 | https://renote.net/reviews/5254 | https://www.cmoa.jp/title/87790</t>
         </is>
       </c>
       <c r="X114" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -14945,12 +14945,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>モングレル</t>
+          <t>キックの鬼</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>もんぐれる</t>
+          <t>きっくのおに</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -14970,87 +14970,87 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>村瀬克俊</t>
+          <t>梶原一騎</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>村瀬克俊</t>
+          <t>中城健（中城けんたろう）</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>集英社</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングジャンプ</t>
+          <t>週刊少年キング または 少年画報（資料により食い違い）</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>2013–2014（単行本1巻2013年12月〜4巻2014年6月）</t>
+          <t>1969–1971（開始時期は資料により異なる）</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>全4巻（ヤングジャンプコミックス）</t>
+          <t>全6巻（英語版Wikipedia）。他に3巻とする記述もあり未確定</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／青年／ジム／リアル</t>
+          <t>キックボクシング／実録／梶原一騎</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>同作者の『K.O.SEN』『カラダ探し』（作画）</t>
+          <t>TVアニメ（1970年）。同原作者の『あしたのジョー』『紅の挑戦者』</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>格闘経験のない若者がジムに入りアマチュアから始める、身体能力を活かした成長</t>
+          <t>実在のキックボクサー沢村忠をモデルにした成り上がり、日本のキックボクシング黎明期</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>未経験者がジムに入る不安や、練習で少しずつ手応えを得る感覚をリアルに描く。</t>
+          <t>主人公の不屈の精神と根性を前面に出す。内面の弱さより覚悟を強調する昭和スポ根型。</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>等身大の若者口調、ジムの会話は現実的で落ち着いている。</t>
+          <t>熱血で大仰な語り口、ナレーションで事実風に語るセミドキュメンタリー調。</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>必殺技に頼らず、実際のキックの動きやジム練習をリアルに描く。</t>
+          <t>劇画調、飛び蹴りなど技の瞬間を大きく見せる。</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>控えめ。日常の軽いやりとり程度。</t>
+          <t>ほぼなし。</t>
         </is>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>技法：『ジムに入会する』ところから始めるリアルな導入。FLATUPの体験入会の流れとほぼ同じ構造なので、最も参考になる型。オリジナル案：体験レッスン当日の緊張→受付→初ミット→帰り道の高揚までを1話で描く。セリフ案『初日は誰でも初心者。それでいい』。</t>
+          <t>技法：実在の歴史を背景にした『物語として語る格闘技史』。オリジナル案：日本のキックボクシングの歴史を、会員向けにやさしく紹介する短編漫画（実在人物の扱いは要注意）。</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見や体操経験者という設定、作中ジム名を使わない。</t>
+          <t>実在人物（沢村忠）の肖像やエピソードの流用、作中の技名、タイトルのもじりを避ける。</t>
         </is>
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>[事実] 全4巻で終了。作者はキック王者との対談でリアルなキックを描きたかったと語った。[感想] もっと読みたかったという声がある。[推測] 短期終了のため知名度は低めとみられる。X直接検索なし。</t>
+          <t>[事実] 沢村忠をモデルにした作品で、1970年にアニメ化された。[感想] 昭和のキックボクシングブームを伝える作品として語られる。[推測] 現在の読者は少ないとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>https://comic.k-manga.jp/title/100297/pv | https://mangapedia.com/%E3%83%A2%E3%83%B3%E3%82%B0%E3%83%AC%E3%83%AB-e3btri2tc | https://sportiva.shueisha.co.jp/clm/othersports/fight/2013/12/19/___split_35/ | https://www.hatehate.jp/entry/mongrel</t>
+          <t>https://en.wikipedia.org/wiki/Kick_no_Oni | https://mangapedia.com/%E3%82%AD%E3%83%83%E3%82%AF%E3%81%AE%E9%AC%BC-6rimm0fjt | https://comic.k-manga.jp/title/165/pv</t>
         </is>
       </c>
       <c r="X115" s="2" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>レッドブルー</t>
+          <t>モングレル</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>れっどぶるー</t>
+          <t>もんぐれる</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -15097,87 +15097,87 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>波切敦</t>
+          <t>村瀬克俊</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>波切敦</t>
+          <t>村瀬克俊</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>集英社</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>週刊ヤングジャンプ</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2022–（2022年7号開始。現在の連載状況は未確認）</t>
+          <t>2013–2014（単行本1巻2013年12月〜4巻2014年6月）</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>未確認（2023年11月時点で7巻）</t>
+          <t>全4巻（ヤングジャンプコミックス）</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>MMA／総合格闘技／学園／成長</t>
+          <t>キックボクシング／青年／ジム／リアル</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>実写ドラマ（2024年12月）</t>
+          <t>同作者の『K.O.SEN』『カラダ探し』（作画）</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>根暗で病弱な少年が天才への反発からMMAを始める、劣等感と向き合う成長</t>
+          <t>格闘経験のない若者がジムに入りアマチュアから始める、身体能力を活かした成長</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>主人公の劣等感・ひねくれ・執念を正直に描き、『一発殴りたい』という負の動機が成長の原動力へ変わる過程を見せる。</t>
+          <t>未経験者がジムに入る不安や、練習で少しずつ手応えを得る感覚をリアルに描く。</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>主人公の皮肉っぽい独白と、ライバルの爽やかな口調の対比。</t>
+          <t>等身大の若者口調、ジムの会話は現実的で落ち着いている。</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>MMAの打・投・極の流れを分かりやすく描き、分析的なモノローグで戦術を見せる。</t>
+          <t>必殺技に頼らず、実際のキックの動きやジム練習をリアルに描く。</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>主人公のひねくれたリアクションや陰キャ的な自虐。</t>
+          <t>控えめ。日常の軽いやりとり程度。</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>技法：『かっこ悪い動機』から始めても成長できると示す。分析タイプの主人公で戦術を読者に解説。オリジナル案：運動が苦手な学生が、頭で考えるタイプとしてMMAで自分の勝ち方を見つける話。セリフ案『体力がないなら、考える力で一歩先に行こう』。</t>
+          <t>技法：『ジムに入会する』ところから始めるリアルな導入。FLATUPの体験入会の流れとほぼ同じ構造なので、最も参考になる型。オリジナル案：体験レッスン当日の緊張→受付→初ミット→帰り道の高揚までを1話で描く。セリフ案『初日は誰でも初心者。それでいい』。</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
-          <t>主人公とライバルの名前・外見、作中ジム名、赤と青の対比を軸にしたタイトル演出をそのまま使わない。</t>
+          <t>主人公の外見や体操経験者という設定、作中ジム名を使わない。</t>
         </is>
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>[事実] 2024年12月に実写ドラマ化された。[感想] 陰キャ主人公の成長がMMA初心者にも読みやすいという紹介がある。[推測] 近年の少年誌MMA漫画として注目度が高いとみられる。X直接検索なし。</t>
+          <t>[事実] 全4巻で終了。作者はキック王者との対談でリアルなキックを描きたかったと語った。[感想] もっと読みたかったという声がある。[推測] 短期終了のため知名度は低めとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986</t>
+          <t>https://comic.k-manga.jp/title/100297/pv | https://mangapedia.com/%E3%83%A2%E3%83%B3%E3%82%B0%E3%83%AC%E3%83%AB-e3btri2tc | https://sportiva.shueisha.co.jp/clm/othersports/fight/2013/12/19/___split_35/ | https://www.hatehate.jp/entry/mongrel</t>
         </is>
       </c>
       <c r="X116" s="2" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>紅の挑戦者</t>
+          <t>レッドブルー</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>くれないのちょうせんしゃ</t>
+          <t>れっどぶるー</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -15224,87 +15224,87 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>梶原一騎（高森朝雄名義とする資料もあるが未確認）</t>
+          <t>波切敦</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>中城健</t>
+          <t>波切敦</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>未確認（電子版の発行元はグループ・ゼロ）</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン（まとめサイトの記載。未確認）</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>1973–1975（まとめサイトの記載。未確認）</t>
+          <t>2022–（2022年7号開始。現在の連載状況は未確認）</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>全10巻（電子版）</t>
+          <t>未確認（2023年11月時点で7巻）</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>キックボクシング／ムエタイ／スポ根</t>
+          <t>MMA／総合格闘技／学園／成長</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>同原作者・作画者の『キックの鬼』</t>
+          <t>実写ドラマ（2024年12月）</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>高校サッカーのエースがキックボクシングに転向する挑戦、タイ・ムエタイとの対決</t>
+          <t>根暗で病弱な少年が天才への反発からMMAを始める、劣等感と向き合う成長</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>転向への迷いより、挑戦への覚悟を強調する昭和スポ根型。</t>
+          <t>主人公の劣等感・ひねくれ・執念を正直に描き、『一発殴りたい』という負の動機が成長の原動力へ変わる過程を見せる。</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>熱血で大げさな宣言調。</t>
+          <t>主人公の皮肉っぽい独白と、ライバルの爽やかな口調の対比。</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>劇画調、海外（タイ）を舞台にした異国感。</t>
+          <t>MMAの打・投・極の流れを分かりやすく描き、分析的なモノローグで戦術を見せる。</t>
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>ほぼなし。</t>
+          <t>主人公のひねくれたリアクションや陰キャ的な自虐。</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>技法：別競技からの転向者を主人公にすると、技術の違いを読者に説明しやすい。オリジナル案：サッカー経験者の会員が『蹴り』の感覚の違いに戸惑い、やがて武器にする話。</t>
+          <t>技法：『かっこ悪い動機』から始めても成長できると示す。分析タイプの主人公で戦術を読者に解説。オリジナル案：運動が苦手な学生が、頭で考えるタイプとしてMMAで自分の勝ち方を見つける話。セリフ案『体力がないなら、考える力で一歩先に行こう』。</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前・外見、サッカーからキックへの転向をバンコクで宣言する導入をそのまま使わない。</t>
+          <t>主人公とライバルの名前・外見、作中ジム名、赤と青の対比を軸にしたタイトル演出をそのまま使わない。</t>
         </is>
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>[事実] 電子版で全10巻が配信されている。[感想] 梶原一騎のキックボクシング作品として紹介される。[推測] 現在の知名度は低いとみられる。X直接検索なし。</t>
+          <t>[事実] 2024年12月に実写ドラマ化された。[感想] 陰キャ主人公の成長がMMA初心者にも読みやすいという紹介がある。[推測] 近年の少年誌MMA漫画として注目度が高いとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/</t>
+          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986</t>
         </is>
       </c>
       <c r="X117" s="2" t="inlineStr">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>YAWARA!</t>
+          <t>紅の挑戦者</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>やわら</t>
+          <t>くれないのちょうせんしゃ</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -15351,87 +15351,87 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>浦沢直樹</t>
+          <t>梶原一騎（高森朝雄名義とする資料もあるが未確認）</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>浦沢直樹</t>
+          <t>中城健</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>未確認（電子版の発行元はグループ・ゼロ）</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックスピリッツ</t>
+          <t>週刊少年マガジン（まとめサイトの記載。未確認）</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>1986–1993</t>
+          <t>1973–1975（まとめサイトの記載。未確認）</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックス全29巻／文庫版全19巻／完全版全20巻</t>
+          <t>全10巻（電子版）</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>柔道／女子／青春／ラブコメ／スポーツ</t>
+          <t>キックボクシング／ムエタイ／スポ根</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Happy!（同作者のスポーツもの）</t>
+          <t>同原作者・作画者の『キックの鬼』</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>才能と『普通の女の子でいたい』願いの葛藤、家族の期待、恋、自分で道を選ぶこと</t>
+          <t>高校サッカーのエースがキックボクシングに転向する挑戦、タイ・ムエタイとの対決</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>強さを隠したい本人の照れ・反発を丁寧に描き、周囲の期待とのズレを長期的な葛藤として育てる</t>
+          <t>転向への迷いより、挑戦への覚悟を強調する昭和スポ根型。</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>日常会話中心の自然な口語。祖父キャラの大げさな物言いと主人公の控えめな返しの対比（引用なし）</t>
+          <t>熱血で大げさな宣言調。</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>日常パートは軽い線と多めの間、試合は一瞬の技を見開きで見せる。観客・記者のリアクションで凄さを伝える</t>
+          <t>劇画調、海外（タイ）を舞台にした異国感。</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>強すぎる祖父の暴走、恋愛の勘違い、主人公が強さを隠そうとしてバレるお約束</t>
+          <t>ほぼなし。</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>技法：『強いのに普通でいたい』という主人公の心のズレで共感を作る。オリジナル案：家族に内緒で格闘技を始めた会社員女性が、通勤中に姿勢が良くなって同僚に気付かれるエピソード</t>
+          <t>技法：別競技からの転向者を主人公にすると、技術の違いを読者に説明しやすい。オリジナル案：サッカー経験者の会員が『蹴り』の感覚の違いに戸惑い、やがて武器にする話。</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
-          <t>主人公名・祖父キャラの造形、作品タイトルロゴ、特定の決め技の見せ方は使わない</t>
+          <t>主人公の名前・外見、サッカーからキックへの転向をバンコクで宣言する導入をそのまま使わない。</t>
         </is>
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>[事実]小学館漫画賞受賞作として紹介され、女子柔道ブームと結び付けて語られることが多い（X直接検索なし） [感想]ラブコメとしても楽しめるという声が多い</t>
+          <t>[事実] 電子版で全10巻が配信されている。[感想] 梶原一騎のキックボクシング作品として紹介される。[推測] 現在の知名度は低いとみられる。X直接検索なし。</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Yawara! | https://nlab.itmedia.co.jp/research/articles/128892/ | https://ranking.net/items/7c982a</t>
+          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/</t>
         </is>
       </c>
       <c r="X118" s="2" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>帯をギュッとね!</t>
+          <t>YAWARA!</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>おびをぎゅっとね</t>
+          <t>やわら</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>河合克敏</t>
+          <t>浦沢直樹</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>河合克敏</t>
+          <t>浦沢直樹</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -15493,72 +15493,72 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>週刊少年サンデー</t>
+          <t>ビッグコミックスピリッツ</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>1988または1989–1995（1995年52号終了。開始年は資料で食い違い）</t>
+          <t>1986–1993</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>少年サンデーコミックス全30巻／ワイド版全15巻／小学館文庫全16巻</t>
+          <t>ビッグコミックス全29巻／文庫版全19巻／完全版全20巻</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>柔道／学園／部活／青春／ギャグ</t>
+          <t>柔道／女子／青春／ラブコメ／スポーツ</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>モンキーターン（同作者）</t>
+          <t>Happy!（同作者のスポーツもの）</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ゼロから部を作る楽しさ、仲間、合理的な練習、楽しみながら強くなること</t>
+          <t>才能と『普通の女の子でいたい』願いの葛藤、家族の期待、恋、自分で道を選ぶこと</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>苦しさよりも工夫と仲間との時間を前面に出し、負けの悔しさは短く強く描いて次へ切り替える</t>
+          <t>強さを隠したい本人の照れ・反発を丁寧に描き、周囲の期待とのズレを長期的な葛藤として育てる</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>明るくテンポの良い掛け合い。技術解説を会話に溶け込ませる（引用なし）</t>
+          <t>日常会話中心の自然な口語。祖父キャラの大げさな物言いと主人公の控えめな返しの対比（引用なし）</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>作者の柔道経験を生かした技の分解描写、練習メニューの図解的コマ</t>
+          <t>日常パートは軽い線と多めの間、試合は一瞬の技を見開きで見せる。観客・記者のリアクションで凄さを伝える</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>部員同士のボケとツッコミ、恋愛がらみの勘違い、ゆるいキャラの脱力</t>
+          <t>強すぎる祖父の暴走、恋愛の勘違い、主人公が強さを隠そうとしてバレるお約束</t>
         </is>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>技法：技術の『なぜ』をキャラの会話で自然に説明する。オリジナル案：初心者が受け身を習う回で、コーチが『転び方が上手い人は人生でもケガしにくい』と語る短い場面</t>
+          <t>技法：『強いのに普通でいたい』という主人公の心のズレで共感を作る。オリジナル案：家族に内緒で格闘技を始めた会社員女性が、通勤中に姿勢が良くなって同僚に気付かれるエピソード</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
         <is>
-          <t>主要部員の外見・あだ名、部の名前、作中の学校名は使わない</t>
+          <t>主人公名・祖父キャラの造形、作品タイトルロゴ、特定の決め技の見せ方は使わない</t>
         </is>
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>[事実]第1回コミックグランプリ受賞作として紹介されている（X直接検索なし） [感想]『楽しい部活もの』として明るさを評価する声が多い</t>
+          <t>[事実]小学館漫画賞受賞作として紹介され、女子柔道ブームと結び付けて語られることが多い（X直接検索なし） [感想]ラブコメとしても楽しめるという声が多い</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>https://ranking.net/items/14d871 | https://comic.k-manga.jp/title/12315/pv | https://shopping.bookoff.co.jp/s/8800000124</t>
+          <t>https://en.wikipedia.org/wiki/Yawara! | https://nlab.itmedia.co.jp/research/articles/128892/ | https://ranking.net/items/7c982a</t>
         </is>
       </c>
       <c r="X119" s="2" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>火ノ丸相撲</t>
+          <t>帯をギュッとね!</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ひのまるずもう</t>
+          <t>おびをぎゅっとね</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -15605,87 +15605,87 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>川田</t>
+          <t>河合克敏</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>川田</t>
+          <t>河合克敏</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>集英社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>週刊少年ジャンプ</t>
+          <t>週刊少年サンデー</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2014–2019（2014年26号〜2019年34号）</t>
+          <t>1988または1989–1995（1995年52号終了。開始年は資料で食い違い）</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>ジャンプ・コミックス全28巻</t>
+          <t>少年サンデーコミックス全30巻／ワイド版全15巻／小学館文庫全16巻</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>相撲／学園／部活／スポーツ／王道少年</t>
+          <t>柔道／学園／部活／青春／ギャグ</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（GONZO制作）</t>
+          <t>モンキーターン（同作者）</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>体格のハンデを努力と技術で越える、仲間を集めて部を立て直す、誇り</t>
+          <t>ゼロから部を作る楽しさ、仲間、合理的な練習、楽しみながら強くなること</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>小柄な主人公の『足りなさ』を真正面から描き、負けの痛みと周囲の支えで立ち上がる</t>
+          <t>苦しさよりも工夫と仲間との時間を前面に出し、負けの悔しさは短く強く描いて次へ切り替える</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>熱量の高い独白と仲間の叫び、決意表明を短く重ねる（引用なし）</t>
+          <t>明るくテンポの良い掛け合い。技術解説を会話に溶け込ませる（引用なし）</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>立ち合いの一瞬を大ゴマと集中線で強調、土俵際の粘りを連続コマで引き延ばす</t>
+          <t>作者の柔道経験を生かした技の分解描写、練習メニューの図解的コマ</t>
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>部員の個性の掛け合い、日常パートの軽い誇張</t>
+          <t>部員同士のボケとツッコミ、恋愛がらみの勘違い、ゆるいキャラの脱力</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>技法：『小さい・弱いからこそ工夫する』を主題にする。オリジナル案：小柄な女性会員が、体格差を技術でかわすコツを覚えて笑顔になる回</t>
+          <t>技法：技術の『なぜ』をキャラの会話で自然に説明する。オリジナル案：初心者が受け身を習う回で、コーチが『転び方が上手い人は人生でもケガしにくい』と語る短い場面</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見・四股名・必殺技名・部の名称は使わない</t>
+          <t>主要部員の外見・あだ名、部の名前、作中の学校名は使わない</t>
         </is>
       </c>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>[事実]相撲漫画ランキングで上位に紹介されている（X直接検索なし） [感想]熱い王道スポーツ漫画として評価が高い</t>
+          <t>[事実]第1回コミックグランプリ受賞作として紹介されている（X直接検索なし） [感想]『楽しい部活もの』として明るさを評価する声が多い</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2 | https://mangapedia.com/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2-yq1wzu8h2 | https://www.b-ch.com/titles/6297/</t>
+          <t>https://ranking.net/items/14d871 | https://comic.k-manga.jp/title/12315/pv | https://shopping.bookoff.co.jp/s/8800000124</t>
         </is>
       </c>
       <c r="X120" s="2" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>ダンベル何キロ持てる？</t>
+          <t>火ノ丸相撲</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>だんべるなんきろもてる</t>
+          <t>ひのまるずもう</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -15732,87 +15732,87 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>サンドロビッチ・ヤバ子</t>
+          <t>川田</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>MAAM</t>
+          <t>川田</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>集英社</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>マンガワン／裏サンデー</t>
+          <t>週刊少年ジャンプ</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>2016–（連載中かどうかは未確認）</t>
+          <t>2014–2019（2014年26号〜2019年34号）</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>裏少年サンデーコミックス既刊20巻（2025年時点の資料。最新巻は未確認）</t>
+          <t>ジャンプ・コミックス全28巻</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>フィットネス／筋トレ／女子／ジム／ギャグ／教育</t>
+          <t>相撲／学園／部活／スポーツ／王道少年</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ化</t>
+          <t>TVアニメ（GONZO制作）</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>運動が苦手な人がジムに通い続ける楽しさ、正しい知識、仲間と続けること</t>
+          <t>体格のハンデを努力と技術で越える、仲間を集めて部を立て直す、誇り</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>ダイエット目的など軽い動機から始めて、できることが増える喜びに変わる過程</t>
+          <t>小柄な主人公の『足りなさ』を真正面から描き、負けの痛みと周囲の支えで立ち上がる</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>トレーナーの解説とキャラの素直なリアクションの掛け合い、ハイテンション（引用なし）</t>
+          <t>熱量の高い独白と仲間の叫び、決意表明を短く重ねる（引用なし）</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>筋肉の誇張表現と正しいフォームの図解を同じページで見せる</t>
+          <t>立ち合いの一瞬を大ゴマと集中線で強調、土俵際の粘りを連続コマで引き延ばす</t>
         </is>
       </c>
       <c r="S121" s="2" t="inlineStr">
         <is>
-          <t>筋肉キャラの過剰さ、主人公の食欲・怠けとのギャップ、真面目な解説へのズレたリアクション</t>
+          <t>部員の個性の掛け合い、日常パートの軽い誇張</t>
         </is>
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>技法：笑いの中に正しい運動知識を一つずつ入れる『学べるギャグ』。オリジナル案：体験に来た女性が『格闘技＝痛い』と思い込み、実際はストレッチから始まって拍子抜けする回</t>
+          <t>技法：『小さい・弱いからこそ工夫する』を主題にする。オリジナル案：小柄な女性会員が、体格差を技術でかわすコツを覚えて笑顔になる回</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
         <is>
-          <t>主人公・トレーナーのキャラデザ、ジム名、作中の掛け声や歌は使わない</t>
+          <t>主人公の外見・四股名・必殺技名・部の名称は使わない</t>
         </is>
       </c>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>[事実]アニメ化され、Kindle全巻セールが報じられている（X直接検索なし） [感想]筋トレ入門として役に立つという声が多い</t>
+          <t>[事実]相撲漫画ランキングで上位に紹介されている（X直接検索なし） [感想]熱い王道スポーツ漫画として評価が高い</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
         <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c</t>
+          <t>https://dic.nicovideo.jp/a/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2 | https://mangapedia.com/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2-yq1wzu8h2 | https://www.b-ch.com/titles/6297/</t>
         </is>
       </c>
       <c r="X121" s="2" t="inlineStr">
@@ -15834,12 +15834,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>ブラジュ～</t>
+          <t>ダンベル何キロ持てる？</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ぶらじゅ</t>
+          <t>だんべるなんきろもてる</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -15859,87 +15859,87 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>クリスティー田村</t>
+          <t>サンドロビッチ・ヤバ子</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>クリスティー田村</t>
+          <t>MAAM</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>ヤンマガWeb</t>
+          <t>マンガワン／裏サンデー</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2024–（連載中かどうかは未確認）</t>
+          <t>2016–（連載中かどうかは未確認）</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>1巻は2024年11月20日発売。既刊数は未確認</t>
+          <t>裏少年サンデーコミックス既刊20巻（2025年時点の資料。最新巻は未確認）</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>ブラジリアン柔術／初心者／学園／青春</t>
+          <t>フィットネス／筋トレ／女子／ジム／ギャグ／教育</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>TVアニメ化</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>格闘技を始めては辞めてきた高校生が柔術で続ける理由を見つける、知恵と経験が力に勝つ</t>
+          <t>運動が苦手な人がジムに通い続ける楽しさ、正しい知識、仲間と続けること</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>『どうせ続かない』という自己評価の低さから、小さな成功体験で変わる過程が軸（本編未読のため詳細は未確認）</t>
+          <t>ダイエット目的など軽い動機から始めて、できることが増える喜びに変わる過程</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>トレーナーの解説とキャラの素直なリアクションの掛け合い、ハイテンション（引用なし）</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>筋肉の誇張表現と正しいフォームの図解を同じページで見せる</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>筋肉キャラの過剰さ、主人公の食欲・怠けとのギャップ、真面目な解説へのズレたリアクション</t>
         </is>
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>技法：『飽きっぽい初心者が続く理由』を物語の芯にする。オリジナル案：三日坊主の中学生が、毎回1つだけ技を覚えて帰る『今日のひとつ』ノートで続けられるようになる話</t>
+          <t>技法：笑いの中に正しい運動知識を一つずつ入れる『学べるギャグ』。オリジナル案：体験に来た女性が『格闘技＝痛い』と思い込み、実際はストレッチから始まって拍子抜けする回</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
-          <t>主人公名・先輩キャラの造形、作品タイトルの言い回しは使わない</t>
+          <t>主人公・トレーナーのキャラデザ、ジム名、作中の掛け声や歌は使わない</t>
         </is>
       </c>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>[事実]柔術関係者のブログで連載開始が好意的に取り上げられている（X直接検索なし） [推測]柔術を正面から描く漫画が少ないため競技者の注目度は高い</t>
+          <t>[事実]アニメ化され、Kindle全巻セールが報じられている（X直接検索なし） [感想]筋トレ入門として役に立つという声が多い</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/labels/ymweb?page=15 | https://bookwalker.jp/de2c689ec9-3c95-40fb-9398-b5d5c42cf5d4/ | https://m-dojo.hatenadiary.com/entry/2024/08/26/215830</t>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c</t>
         </is>
       </c>
       <c r="X122" s="2" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -15961,12 +15961,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ROLLS</t>
+          <t>ブラジュ～</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ろーるず</t>
+          <t>ぶらじゅ</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -15986,37 +15986,37 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>カズ・ヤンセ</t>
+          <t>クリスティー田村</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>カズ・ヤンセ</t>
+          <t>クリスティー田村</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>少年画報社</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>ヤングキングBULL</t>
+          <t>ヤンマガWeb</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>未確認（2026年時点で連載中とする報道あり）</t>
+          <t>2024–（連載中かどうかは未確認）</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>1巻は2026年5月18日発売（YKコミックス）。既刊数は未確認</t>
+          <t>1巻は2024年11月20日発売。既刊数は未確認</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>ブラジリアン柔術／学園／青春／格闘技</t>
+          <t>ブラジリアン柔術／初心者／学園／青春</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -16026,47 +16026,47 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>高校1年生が柔術を嗜む先輩と出会って始まる青春格闘ストーリー（詳細は未確認）</t>
+          <t>格闘技を始めては辞めてきた高校生が柔術で続ける理由を見つける、知恵と経験が力に勝つ</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
+          <t>『どうせ続かない』という自己評価の低さから、小さな成功体験で変わる過程が軸（本編未読のため詳細は未確認）</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
           <t>未確認（本編未読）</t>
         </is>
       </c>
-      <c r="Q123" s="2" t="inlineStr">
+      <c r="R123" s="2" t="inlineStr">
         <is>
           <t>未確認（本編未読）</t>
         </is>
       </c>
-      <c r="R123" s="2" t="inlineStr">
+      <c r="S123" s="2" t="inlineStr">
         <is>
           <t>未確認（本編未読）</t>
         </is>
       </c>
-      <c r="S123" s="2" t="inlineStr">
-        <is>
-          <t>未確認（本編未読）</t>
-        </is>
-      </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>技法：『先輩との出会い』を入口にした入門もの。オリジナル案：帯の色が違う先輩が、初日の後輩に寝技の『逃げ方』だけを教えて安心させる場面</t>
+          <t>技法：『飽きっぽい初心者が続く理由』を物語の芯にする。オリジナル案：三日坊主の中学生が、毎回1つだけ技を覚えて帰る『今日のひとつ』ノートで続けられるようになる話</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
         <is>
-          <t>主人公・先輩の名前と外見、作品ロゴは使わない</t>
+          <t>主人公名・先輩キャラの造形、作品タイトルの言い回しは使わない</t>
         </is>
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>[事実]作者がXで柔術漫画として告知している（X直接検索なし、Web検索結果で確認） [推測]刊行直後のため評判の蓄積は少ない</t>
+          <t>[事実]柔術関係者のブログで連載開始が好意的に取り上げられている（X直接検索なし） [推測]柔術を正面から描く漫画が少ないため競技者の注目度は高い</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE</t>
+          <t>https://www.kodansha.co.jp/comic/labels/ymweb?page=15 | https://bookwalker.jp/de2c689ec9-3c95-40fb-9398-b5d5c42cf5d4/ | https://m-dojo.hatenadiary.com/entry/2024/08/26/215830</t>
         </is>
       </c>
       <c r="X123" s="2" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>鉄風</t>
+          <t>ROLLS</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>てっぷう</t>
+          <t>ろーるず</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -16113,37 +16113,37 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>太田モアレ</t>
+          <t>カズ・ヤンセ</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>太田モアレ</t>
+          <t>カズ・ヤンセ</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>少年画報社</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>good!アフタヌーン</t>
+          <t>ヤングキングBULL</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>未確認–2015（2015年8号で完結とする資料あり）</t>
+          <t>未確認（2026年時点で連載中とする報道あり）</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>全8巻</t>
+          <t>1巻は2026年5月18日発売（YKコミックス）。既刊数は未確認</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>総合格闘技／女子／グラップリング／青春</t>
+          <t>ブラジリアン柔術／学園／青春／格闘技</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -16153,47 +16153,47 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>才能ある少女が総合格闘技に出会い、勝ちたい・強くなりたい欲と向き合う</t>
+          <t>高校1年生が柔術を嗜む先輩と出会って始まる青春格闘ストーリー（詳細は未確認）</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>主人公の傲慢さや退屈さなど、きれいではない動機を隠さずに描く点が特徴（詳細は要再確認）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>淡々とした会話と短い心の声（引用なし。詳細は要再確認）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>組み技・関節技の体の絡みを細かく描く（詳細は要再確認）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>技法：女子が格闘技にのめり込む理由を『かっこいい』だけでなく本音で描く。オリジナル案：負けず嫌いな女子高生が、勝つことより『昨日の自分に勝つ』ことに価値を見つける話</t>
+          <t>技法：『先輩との出会い』を入口にした入門もの。オリジナル案：帯の色が違う先輩が、初日の後輩に寝技の『逃げ方』だけを教えて安心させる場面</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
         <is>
-          <t>主人公の外見・ジム名・対戦相手キャラの造形は使わない</t>
+          <t>主人公・先輩の名前と外見、作品ロゴは使わない</t>
         </is>
       </c>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>[感想]女子格闘技漫画のおすすめ記事で紹介されることがある（X直接検索なし） [推測]完結済みで知名度は中程度</t>
+          <t>[事実]作者がXで柔術漫画として告知している（X直接検索なし、Web検索結果で確認） [推測]刊行直後のため評判の蓄積は少ない</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/</t>
+          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE</t>
         </is>
       </c>
       <c r="X124" s="2" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -16215,12 +16215,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>もういっぽん！</t>
+          <t>鉄風</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>もういっぽん</t>
+          <t>てっぷう</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -16240,87 +16240,87 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>村岡ユウ</t>
+          <t>太田モアレ</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>村岡ユウ</t>
+          <t>太田モアレ</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>秋田書店</t>
+          <t>講談社</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン</t>
+          <t>good!アフタヌーン</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>2018–（終了時期は未確認）</t>
+          <t>未確認–2015（2015年8号で完結とする資料あり）</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>少年チャンピオン・コミックス。総巻数・完結有無は未確認</t>
+          <t>全8巻</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>柔道／女子／部活／青春／初心者</t>
+          <t>総合格闘技／女子／グラップリング／青春</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>TVアニメ（2023年冬、全13話）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>一度やめかけた柔道をもう一度好きになる、女子部員の友情、楽しむ気持ち</t>
+          <t>才能ある少女が総合格闘技に出会い、勝ちたい・強くなりたい欲と向き合う</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>勝ち負けより『好き』を取り戻す気持ちの揺れを、友達との会話の中で自然に描く</t>
+          <t>主人公の傲慢さや退屈さなど、きれいではない動機を隠さずに描く点が特徴（詳細は要再確認）</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>女子高生らしい明るい会話のテンポ、試合中は短い声かけ（引用なし）</t>
+          <t>淡々とした会話と短い心の声（引用なし。詳細は要再確認）</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>表情のアップを多用し、技の瞬間は爽やかな効果線で見せる</t>
+          <t>組み技・関節技の体の絡みを細かく描く（詳細は要再確認）</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
         <is>
-          <t>仲間同士のじゃれ合い、日常のゆるい会話のズレ</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>技法：『また来たくなる』気持ちを友達の存在で描く。オリジナル案：一度辞めたママ会員が子どもの練習を見学して『もう一回やりたい』と言い出す話</t>
+          <t>技法：女子が格闘技にのめり込む理由を『かっこいい』だけでなく本音で描く。オリジナル案：負けず嫌いな女子高生が、勝つことより『昨日の自分に勝つ』ことに価値を見つける話</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
         <is>
-          <t>主人公たちの外見・校名・部のユニフォームデザインは使わない</t>
+          <t>主人公の外見・ジム名・対戦相手キャラの造形は使わない</t>
         </is>
       </c>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>[事実]アニメ化されている（X直接検索なし） [感想]女子部活ものとして爽やかで読みやすいという声</t>
+          <t>[感想]女子格闘技漫画のおすすめ記事で紹介されることがある（X直接検索なし） [推測]完結済みで知名度は中程度</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253228039 | https://www.b-ch.com/titles/8013 | https://en.wikipedia.org/wiki/Ippon_Again!</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/</t>
         </is>
       </c>
       <c r="X125" s="2" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="Y125" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>あさひなぐ</t>
+          <t>もういっぽん！</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>あさひなぐ</t>
+          <t>もういっぽん</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -16367,87 +16367,87 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>こざき亜衣</t>
+          <t>村岡ユウ</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>こざき亜衣</t>
+          <t>村岡ユウ</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>小学館</t>
+          <t>秋田書店</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックスピリッツ</t>
+          <t>週刊少年チャンピオン</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2011–2020（2020年41号で完結）</t>
+          <t>2018–（終了時期は未確認）</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>ビッグコミックス全34巻</t>
+          <t>少年チャンピオン・コミックス。総巻数・完結有無は未確認</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>薙刀／女子／部活／初心者／青春</t>
+          <t>柔道／女子／部活／青春／初心者</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>実写映画・舞台（2017年）</t>
+          <t>TVアニメ（2023年冬、全13話）</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>運動経験ゼロの少女が武道を始め、弱さを認めながら強くなる</t>
+          <t>一度やめかけた柔道をもう一度好きになる、女子部員の友情、楽しむ気持ち</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>運動音痴の劣等感、仲間との差、怖さを丁寧に積み、少しずつ自信を得る過程を長く描く</t>
+          <t>勝ち負けより『好き』を取り戻す気持ちの揺れを、友達との会話の中で自然に描く</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>等身大の女子高生の会話、心の声で弱気と強がりを交互に見せる（引用なし）</t>
+          <t>女子高生らしい明るい会話のテンポ、試合中は短い声かけ（引用なし）</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>日常の柔らかい絵柄と、試合での鋭い目線・構えのアップの落差</t>
+          <t>表情のアップを多用し、技の瞬間は爽やかな効果線で見せる</t>
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>主人公のドジ、先輩の個性の誇張、真剣な稽古中のズレたリアクション</t>
+          <t>仲間同士のじゃれ合い、日常のゆるい会話のズレ</t>
         </is>
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>技法：『運動ができない子が主人公』で読者の入口を広げる。オリジナル案：体育が苦手だった女の子が、初めてミットを鳴らした音に自分でびっくりする場面</t>
+          <t>技法：『また来たくなる』気持ちを友達の存在で描く。オリジナル案：一度辞めたママ会員が子どもの練習を見学して『もう一回やりたい』と言い出す話</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
-          <t>主人公の眼鏡キャラ造形・名前、校名、薙刀部の固有設定は使わない</t>
+          <t>主人公たちの外見・校名・部のユニフォームデザインは使わない</t>
         </is>
       </c>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>[事実]小学館漫画賞（第60回）を受賞し、実写映画化された（X直接検索なし） [感想]運動が苦手な人ほど共感できるという声</t>
+          <t>[事実]アニメ化されている（X直接検索なし） [感想]女子部活ものとして爽やかで読みやすいという声</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
         <is>
-          <t>https://www.crank-in.net/news/80665 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=18369 | https://comic.k-manga.jp/title/57348/pv</t>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253228039 | https://www.b-ch.com/titles/8013 | https://en.wikipedia.org/wiki/Ippon_Again!</t>
         </is>
       </c>
       <c r="X126" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>クロオビ！隼太</t>
+          <t>あさひなぐ</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>くろおびはやた</t>
+          <t>あさひなぐ</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -16494,87 +16494,87 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>作田和哉</t>
+          <t>こざき亜衣</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>作田和哉</t>
+          <t>こざき亜衣</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>小学館</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>月刊少年ライバル</t>
+          <t>ビッグコミックスピリッツ</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>2011–2020（2020年41号で完結）</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>全9巻</t>
+          <t>ビッグコミックス全34巻</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>空手／キッズ／小学生／伝統派空手／道場</t>
+          <t>薙刀／女子／部活／初心者／青春</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>実写映画・舞台（2017年）</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>アニメヒーローに憧れる小学5年生が空手と出会い、道場で成長する</t>
+          <t>運動経験ゼロの少女が武道を始め、弱さを認めながら強くなる</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>子どもらしい憧れを入口に、稽古の地道さと向き合う過程（詳細は未確認）</t>
+          <t>運動音痴の劣等感、仲間との差、怖さを丁寧に積み、少しずつ自信を得る過程を長く描く</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>等身大の女子高生の会話、心の声で弱気と強がりを交互に見せる（引用なし）</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>日常の柔らかい絵柄と、試合での鋭い目線・構えのアップの落差</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
         <is>
-          <t>未確認（本編未読）</t>
+          <t>主人公のドジ、先輩の個性の誇張、真剣な稽古中のズレたリアクション</t>
         </is>
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>技法：『ヒーローへの憧れ』を入門の動機にする。オリジナル案：変身ヒーローごっこが好きな小1が、本物の構えを習って家で保護者に見せる回</t>
+          <t>技法：『運動ができない子が主人公』で読者の入口を広げる。オリジナル案：体育が苦手だった女の子が、初めてミットを鳴らした音に自分でびっくりする場面</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
         <is>
-          <t>主人公の名前・外見、作中の流派名や道場名は使わない</t>
+          <t>主人公の眼鏡キャラ造形・名前、校名、薙刀部の固有設定は使わない</t>
         </is>
       </c>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>[感想]キッズ空手サイトのおすすめ空手漫画として紹介されている（X直接検索なし）</t>
+          <t>[事実]小学館漫画賞（第60回）を受賞し、実写映画化された（X直接検索なし） [感想]運動が苦手な人ほど共感できるという声</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic</t>
+          <t>https://www.crank-in.net/news/80665 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=18369 | https://comic.k-manga.jp/title/57348/pv</t>
         </is>
       </c>
       <c r="X127" s="2" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>柔道部物語</t>
+          <t>クロオビ！隼太</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>じゅうどうぶものがたり</t>
+          <t>くろおびはやた</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>単独（小林まこと柔道作品群）</t>
+          <t>単独</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16621,12 +16621,12 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>小林まこと</t>
+          <t>作田和哉</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>小林まこと</t>
+          <t>作田和哉</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -16636,72 +16636,72 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングマガジン</t>
+          <t>月刊少年ライバル</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>1985–1991（1985年18号〜1991年32号とする資料あり）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>ヤンマガKCスペシャル全11巻／文庫版全7巻</t>
+          <t>全9巻</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>柔道／学園／部活／ギャグ／スポ根</t>
+          <t>空手／キッズ／小学生／伝統派空手／道場</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>JJM 女子柔道部物語（同作者の女子柔道もの）／1・2の三四郎（同作者）</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>素人が理不尽な部活文化の中で本物の強さを身につける成長、仲間意識、努力の積み重ね</t>
+          <t>アニメヒーローに憧れる小学5年生が空手と出会い、道場で成長する</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>入部直後の恐怖・場違い感を笑いで包みつつ、しごきを経て自信が芽生える過程を段階的に描く。勝負前の緊張は短い独白と表情で処理し、重くしすぎない</t>
+          <t>子どもらしい憧れを入口に、稽古の地道さと向き合う過程（詳細は未確認）</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>体育会系の掛け声と短い命令口調、方言まじりの軽口。真剣な場面ほどセリフを削る（引用なし）</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>投げ技の瞬間を大ゴマで止め、直前直後は小ゴマで畳みかける緩急。汗・畳の音などの描き文字で臨場感を出す</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>先輩後輩の上下関係の誇張、真顔で起きるズレ、極端なしごきを淡々と描く落差ギャグ</t>
+          <t>未確認（本編未読）</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>技法：初心者の『怖い→できた』を1話完結の小さな成功で積む構成。FLATUPでは逆に『しごきゼロ』を明示し、昔の部活の怖さと対比させる。オリジナル案：昔の部活トラウマを持つ大人会員が、優しいコーチに戸惑う『怒られないの？』ギャグ</t>
+          <t>技法：『ヒーローへの憧れ』を入門の動機にする。オリジナル案：変身ヒーローごっこが好きな小1が、本物の構えを習って家で保護者に見せる回</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>主人公・先輩キャラの外見や髪型、校名・部の固有名、特徴的な歌や儀式ネタは使わない</t>
+          <t>主人公の名前・外見、作中の流派名や道場名は使わない</t>
         </is>
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>[事実]柔道漫画ランキング記事で上位常連として紹介されている（X直接検索なし） [感想]経験者から『柔道部のリアル』と評されることが多い [推測]しごき描写は現代の価値観では賛否が分かれる</t>
+          <t>[感想]キッズ空手サイトのおすすめ空手漫画として紹介されている（X直接検索なし）</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>https://dic.nicovideo.jp/a/%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E | https://www.nihon-u.ac.jp/sports_sciences/files/news/689/pdf1.pdf | https://www.cmoa.jp/title/5030/</t>
+          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic</t>
         </is>
       </c>
       <c r="X128" s="2" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売</t>
+          <t>柔道部物語</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>けんかしょうばい</t>
+          <t>じゅうどうぶものがたり</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売シリーズ</t>
+          <t>単独（小林まこと柔道作品群）</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16748,12 +16748,12 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>小林まこと</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>木多康昭</t>
+          <t>小林まこと</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -16768,67 +16768,67 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>2005–2010（2005年6月〜2010年9月、第一部）</t>
+          <t>1985–1991（1985年18号〜1991年32号とする資料あり）</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>全24巻（ヤングマガジンコミックス）</t>
+          <t>ヤンマガKCスペシャル全11巻／文庫版全7巻</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>格闘技／喧嘩／ギャグ／心理戦</t>
+          <t>柔道／学園／部活／ギャグ／スポ根</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>喧嘩稼業（第二部）。同じ作者に幕張、泣くようぐいす</t>
+          <t>JJM 女子柔道部物語（同作者の女子柔道もの）／1・2の三四郎（同作者）</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>勝つための知恵と準備、恐怖の克服、強さへの執着</t>
+          <t>素人が理不尽な部活文化の中で本物の強さを身につける成長、仲間意識、努力の積み重ね</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>勝負の前の情報戦・読み合いを内面の思考で細かく描き、追い詰められた時の恐怖や覚悟を強調する</t>
+          <t>入部直後の恐怖・場違い感を笑いで包みつつ、しごきを経て自信が芽生える過程を段階的に描く。勝負前の緊張は短い独白と表情で処理し、重くしすぎない</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>格闘パートは理詰めの解説と短い言葉の読み合い、ギャグパートは下品さも含む過激なボケが続く</t>
+          <t>体育会系の掛け声と短い命令口調、方言まじりの軽口。真剣な場面ほどセリフを削る（引用なし）</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>技の仕組みを図解的に見せるコマ、決着の瞬間の大ゴマ。格闘とギャグで絵のタッチの密度を変える</t>
+          <t>投げ技の瞬間を大ゴマで止め、直前直後は小ゴマで畳みかける緩急。汗・畳の音などの描き文字で臨場感を出す</t>
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>実在人物いじりや下ネタなど過激な落差ギャグ（FLATUPでは使わない種類）</t>
+          <t>先輩後輩の上下関係の誇張、真顔で起きるズレ、極端なしごきを淡々と描く落差ギャグ</t>
         </is>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>技法：技の理屈を図解で見せて読者に『なるほど』と思わせる解説コマ、試合前の作戦会議で緊張を高める構成。アイデア：トレーナーが初心者に、ジャブがなぜ大事かを図解で説明する学習まんが風の回。オリジナルの一言案「勝ち方より、ケガしない負け方から覚えよう」</t>
+          <t>技法：初心者の『怖い→できた』を1話完結の小さな成功で積む構成。FLATUPでは逆に『しごきゼロ』を明示し、昔の部活の怖さと対比させる。オリジナル案：昔の部活トラウマを持つ大人会員が、優しいコーチに戸惑う『怒られないの？』ギャグ</t>
         </is>
       </c>
       <c r="U129" s="2" t="inlineStr">
         <is>
-          <t>主人公・師匠の外見、作中の流派名や秘技名、トーナメント名、実在人物いじりの手法を使わない。過激な下ネタや他者を傷つけるギャグはブランド方針に反する</t>
+          <t>主人公・先輩キャラの外見や髪型、校名・部の固有名、特徴的な歌や儀式ネタは使わない</t>
         </is>
       </c>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>[事実] 第一部24巻で完結し、第二部の喧嘩稼業へ続いた。[感想] 格闘の読み合いが面白いという声と、ギャグの過激さが好みを分けるという声がある。[推測] 格闘ファンの間でカルト的人気。X直接検索なし</t>
+          <t>[事実]柔道漫画ランキング記事で上位常連として紹介されている（X直接検索なし） [感想]経験者から『柔道部のリアル』と評されることが多い [推測]しごき描写は現代の価値観では賛否が分かれる</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000011088 | https://comic.k-manga.jp/title/103703/pv | https://dic.nicovideo.jp/a/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD</t>
+          <t>https://dic.nicovideo.jp/a/%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E | https://www.nihon-u.ac.jp/sports_sciences/files/news/689/pdf1.pdf | https://www.cmoa.jp/title/5030/</t>
         </is>
       </c>
       <c r="X129" s="2" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -16850,12 +16850,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>喧嘩稼業</t>
+          <t>喧嘩商売</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>けんかかぎょう</t>
+          <t>けんかしょうばい</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -16895,67 +16895,67 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2013年12月発売号（2014年2・3合併号）〜。長期休載があり現在の状況は未確認</t>
+          <t>2005–2010（2005年6月〜2010年9月、第一部）</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>未確認（講談社ページで5巻・7巻の刊行を確認。7巻は2016年6月発売）</t>
+          <t>全24巻（ヤングマガジンコミックス）</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>格闘技／トーナメント／心理戦／ギャグ</t>
+          <t>格闘技／喧嘩／ギャグ／心理戦</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>喧嘩商売（第一部）</t>
+          <t>喧嘩稼業（第二部）。同じ作者に幕張、泣くようぐいす</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>最強を決めるトーナメント、勝利への執念、師弟、因縁</t>
+          <t>勝つための知恵と準備、恐怖の克服、強さへの執着</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>各選手の過去と動機を試合ごとに掘り下げ、試合中の思考を細かく追う。読み合いの裏切りで緊張を保つ</t>
+          <t>勝負の前の情報戦・読み合いを内面の思考で細かく描き、追い詰められた時の恐怖や覚悟を強調する</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>解説役の分析と選手の内心が交互に入り、短いやり取りで駆け引きを見せる</t>
+          <t>格闘パートは理詰めの解説と短い言葉の読み合い、ギャグパートは下品さも含む過激なボケが続く</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>トーナメントの一試合を長く描き、決着の一撃に向けてコマを細かく刻んでから大ゴマで解放する</t>
+          <t>技の仕組みを図解的に見せるコマ、決着の瞬間の大ゴマ。格闘とギャグで絵のタッチの密度を変える</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>第一部よりギャグは減るが、試合の合間に過激な落差ギャグが入る</t>
+          <t>実在人物いじりや下ネタなど過激な落差ギャグ（FLATUPでは使わない種類）</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>技法：試合前に選手の背景回を入れて応援したくなる構造、細かいコマで時間を引き延ばしてから大ゴマで決める。アイデア：ジム内の初心者マス大会で、出場者それぞれの『始めた理由』を一話ずつ描く。オリジナルの一言案「ここに立った時点で、もう昨日の自分には勝ってる」</t>
+          <t>技法：技の理屈を図解で見せて読者に『なるほど』と思わせる解説コマ、試合前の作戦会議で緊張を高める構成。アイデア：トレーナーが初心者に、ジャブがなぜ大事かを図解で説明する学習まんが風の回。オリジナルの一言案「勝ち方より、ケガしない負け方から覚えよう」</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
-          <t>トーナメント名・出場者の外見や実在格闘家を思わせる造形、技名、試合カードの組み方を使わない</t>
+          <t>主人公・師匠の外見、作中の流派名や秘技名、トーナメント名、実在人物いじりの手法を使わない。過激な下ネタや他者を傷つけるギャグはブランド方針に反する</t>
         </is>
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>[事実] 長期休載が多い作品として記事で触れられている。[感想] 続きを待ち続けているという声が多い。[推測] 再開のたびに話題になる。X直接検索なし</t>
+          <t>[事実] 第一部24巻で完結し、第二部の喧嘩稼業へ続いた。[感想] 格闘の読み合いが面白いという声と、ギャグの過激さが好みを分けるという声がある。[推測] 格闘ファンの間でカルト的人気。X直接検索なし</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000011088 | https://comic.k-manga.jp/title/103703/pv | https://dic.nicovideo.jp/a/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD</t>
         </is>
       </c>
       <c r="X130" s="2" t="inlineStr">
@@ -16977,12 +16977,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>鉄拳チンミ</t>
+          <t>喧嘩稼業</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>てっけんちんみ</t>
+          <t>けんかかぎょう</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -16992,22 +16992,22 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>鉄拳チンミシリーズ</t>
+          <t>喧嘩商売シリーズ</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>本編</t>
+          <t>続編</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>木多康昭</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>前川たけし</t>
+          <t>木多康昭</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -17017,72 +17017,72 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>月刊少年マガジン</t>
+          <t>週刊ヤングマガジン</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>1983–1997（開始は1983年。終了年は二次情報による）</t>
+          <t>2013年12月発売号（2014年2・3合併号）〜。長期休載があり現在の状況は未確認</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>全35巻（講談社コミックス）</t>
+          <t>未確認（講談社ページで5巻・7巻の刊行を確認。7巻は2016年6月発売）</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>カンフー／修行／冒険／少年</t>
+          <t>格闘技／トーナメント／心理戦／ギャグ</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>続編：新・鉄拳チンミ、鉄拳チンミLegends。外伝：鉄拳チンミ外伝</t>
+          <t>喧嘩商売（第一部）</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>修行による成長、師弟関係、優しさと強さ、仲間との友情</t>
+          <t>最強を決めるトーナメント、勝利への執念、師弟、因縁</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>小さな少年が恐怖を感じながらも一歩踏み出す勇気を、素直な表情で描く。暴力的になりすぎず、相手を思いやる気持ちを大切にする。</t>
+          <t>各選手の過去と動機を試合ごとに掘り下げ、試合中の思考を細かく追う。読み合いの裏切りで緊張を保つ</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>やさしく分かりやすい言葉。師匠は短い言葉で教え、弟子は素直に返す。</t>
+          <t>解説役の分析と選手の内心が交互に入り、短いやり取りで駆け引きを見せる</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>丸みのある親しみやすい絵柄。技のコツを図解のように見せるコマ。動物キャラ（相棒）の表情で緊張をほぐす。</t>
+          <t>トーナメントの一試合を長く描き、決着の一撃に向けてコマを細かく刻んでから大ゴマで解放する</t>
         </is>
       </c>
       <c r="S131" s="2" t="inlineStr">
         <is>
-          <t>相棒の小動物のリアクション、子どもらしい食いしん坊さ、大人たちの大げさな驚き。</t>
+          <t>第一部よりギャグは減るが、試合の合間に過激な落差ギャグが入る</t>
         </is>
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>技法：『初心者が一歩ずつ上達する』を素直に描く少年漫画の型。FLATUPに最も近い思想の作品。FLATUP案：キッズ会員が受け身を覚えるまでの3話シリーズ。オリジナル台詞案『こわいって言えたら、もう一歩目だよ』。</t>
+          <t>技法：試合前に選手の背景回を入れて応援したくなる構造、細かいコマで時間を引き延ばしてから大ゴマで決める。アイデア：ジム内の初心者マス大会で、出場者それぞれの『始めた理由』を一話ずつ描く。オリジナルの一言案「ここに立った時点で、もう昨日の自分には勝ってる」</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
         <is>
-          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+          <t>トーナメント名・出場者の外見や実在格闘家を思わせる造形、技名、試合カードの組み方を使わない</t>
         </is>
       </c>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[事実]1987年に講談社漫画賞を受賞。[事実]1988年にTVアニメ化（二次情報）。[感想]子どもでも読める王道カンフー漫画として長く愛されている。</t>
+          <t>[事実] 長期休載が多い作品として記事で触れられている。[感想] 続きを待ち続けているという声が多い。[推測] 再開のたびに話題になる。X直接検索なし</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000043199 | https://www.cmoa.jp/title/5029</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q</t>
         </is>
       </c>
       <c r="X131" s="2" t="inlineStr">
@@ -17104,12 +17104,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>新・鉄拳チンミ</t>
+          <t>鉄拳チンミ</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>しん・てっけんちんみ</t>
+          <t>てっけんちんみ</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>続編</t>
+          <t>本編</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -17149,52 +17149,52 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>1990年代後半–2004年頃（第20巻の初出が2004年7月号–11月号。開始年は未確認）</t>
+          <t>1983–1997（開始は1983年。終了年は二次情報による）</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）</t>
+          <t>全35巻（講談社コミックス）</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>カンフー／冒険／少年</t>
+          <t>カンフー／修行／冒険／少年</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>前作：鉄拳チンミ。次作：鉄拳チンミLegends</t>
+          <t>続編：新・鉄拳チンミ、鉄拳チンミLegends。外伝：鉄拳チンミ外伝</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>成長した主人公の旅、守るための強さ</t>
+          <t>修行による成長、師弟関係、優しさと強さ、仲間との友情</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>少年から青年へ成長する主人公が、弟子や年下を守る側に回る責任感を描く。</t>
+          <t>小さな少年が恐怖を感じながらも一歩踏み出す勇気を、素直な表情で描く。暴力的になりすぎず、相手を思いやる気持ちを大切にする。</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>前作同様、分かりやすくやさしい語り口。</t>
+          <t>やさしく分かりやすい言葉。師匠は短い言葉で教え、弟子は素直に返す。</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>編（エピソード）ごとに舞台を変える冒険構成。</t>
+          <t>丸みのある親しみやすい絵柄。技のコツを図解のように見せるコマ。動物キャラ（相棒）の表情で緊張をほぐす。</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>相棒動物や旅の仲間の掛け合い。</t>
+          <t>相棒の小動物のリアクション、子どもらしい食いしん坊さ、大人たちの大げさな驚き。</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>技法：教わる側から教える側へ回る成長の描き方。FLATUP案：入会2年目の会員が、新しく来た初心者に準備運動を教える回。</t>
+          <t>技法：『初心者が一歩ずつ上達する』を素直に描く少年漫画の型。FLATUPに最も近い思想の作品。FLATUP案：キッズ会員が受け身を覚えるまでの3話シリーズ。オリジナル台詞案『こわいって言えたら、もう一歩目だよ』。</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -17204,12 +17204,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>X直接検索なし。[感想]前作の雰囲気を引き継いだ続編として読まれている。[推測]前作ほどの知名度はない。</t>
+          <t>X直接検索なし。[事実]1987年に講談社漫画賞を受賞。[事実]1988年にTVアニメ化（二次情報）。[感想]子どもでも読める王道カンフー漫画として長く愛されている。</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000043199 | https://www.cmoa.jp/title/5029</t>
         </is>
       </c>
       <c r="X132" s="2" t="inlineStr">
@@ -17231,127 +17231,254 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
+          <t>新・鉄拳チンミ</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>しん・てっけんちんみ</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>格闘技・武道</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>鉄拳チンミシリーズ</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>続編</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>前川たけし</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>講談社</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>月刊少年マガジン</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>1990年代後半–2004年頃（第20巻の初出が2004年7月号–11月号。開始年は未確認）</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>カンフー／冒険／少年</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>前作：鉄拳チンミ。次作：鉄拳チンミLegends</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>成長した主人公の旅、守るための強さ</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>少年から青年へ成長する主人公が、弟子や年下を守る側に回る責任感を描く。</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>前作同様、分かりやすくやさしい語り口。</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>編（エピソード）ごとに舞台を変える冒険構成。</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>相棒動物や旅の仲間の掛け合い。</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>技法：教わる側から教える側へ回る成長の描き方。FLATUP案：入会2年目の会員が、新しく来た初心者に準備運動を教える回。</t>
+        </is>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>X直接検索なし。[感想]前作の雰囲気を引き継いだ続編として読まれている。[推測]前作ほどの知名度はない。</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>W133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>鉄拳チンミLegends</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>てっけんちんみれじぇんず</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>格闘技・武道</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>鉄拳チンミシリーズ</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>続編</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>前川たけし</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>前川たけし</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>講談社</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>月刊少年マガジン</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr">
         <is>
           <t>2006–連載中（第1巻初出 2006年9月号〜。休載期間あり）</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr">
         <is>
           <t>既刊29巻（第29巻 2026年6月刊行）</t>
         </is>
       </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>カンフー／冒険／少年</t>
         </is>
       </c>
-      <c r="N133" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>前作：鉄拳チンミ、新・鉄拳チンミ</t>
         </is>
       </c>
-      <c r="O133" s="2" t="inlineStr">
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>伝説となった武術家の旅、正義と思いやり</t>
         </is>
       </c>
-      <c r="P133" s="2" t="inlineStr">
+      <c r="P134" s="2" t="inlineStr">
         <is>
           <t>長い連載の中で、主人公の落ち着きと周囲の若者の未熟さを対比させる。</t>
         </is>
       </c>
-      <c r="Q133" s="2" t="inlineStr">
+      <c r="Q134" s="2" t="inlineStr">
         <is>
           <t>シリーズ共通のやさしい語り口。</t>
         </is>
       </c>
-      <c r="R133" s="2" t="inlineStr">
+      <c r="R134" s="2" t="inlineStr">
         <is>
           <t>冒険活劇の構成と、技の見せ場の大ゴマ。</t>
         </is>
       </c>
-      <c r="S133" s="2" t="inlineStr">
+      <c r="S134" s="2" t="inlineStr">
         <is>
           <t>相棒動物・仲間の掛け合い。</t>
         </is>
       </c>
-      <c r="T133" s="2" t="inlineStr">
+      <c r="T134" s="2" t="inlineStr">
         <is>
           <t>技法：長期シリーズでも『やさしい強さ』の芯をぶらさない。FLATUP案：ブランドの思想（強さ＝やさしさ）を毎話の結末で確認する構成ルール。</t>
         </is>
       </c>
-      <c r="U133" s="2" t="inlineStr">
+      <c r="U134" s="2" t="inlineStr">
         <is>
           <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
         </is>
       </c>
-      <c r="V133" s="2" t="inlineStr">
+      <c r="V134" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]第28巻（2021年）から第29巻（2026年）まで刊行間隔が空き、連載再開が講談社から告知された。[感想]再開を喜ぶ長年の読者の声がある。</t>
         </is>
       </c>
-      <c r="W133" s="2" t="inlineStr">
+      <c r="W134" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000426730 | https://news.kodansha.co.jp/comics/8666 | https://www.kodansha.co.jp/comic/products/0000041420</t>
         </is>
       </c>
-      <c r="X133" s="2" t="inlineStr">
+      <c r="X134" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y133" s="2" t="inlineStr">
+      <c r="Y134" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y133"/>
+  <autoFilter ref="A1:Y134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17394,7 +17521,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -17439,7 +17566,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -17480,7 +17607,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/anime/manga_research/works_database.xlsx
+++ b/docs/anime/manga_research/works_database.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$Y$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'作品DB'!$A$1:$AA$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y134"/>
+  <dimension ref="A1:AA134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -451,12 +451,14 @@
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="50" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="50" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,30 +559,40 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>FLATUP優先度</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>演出モード</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>FLATUP活用案</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>著作権上の注意</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ネットの評判</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>情報源</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>確認日</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>確認状態</t>
         </is>
@@ -682,32 +694,34 @@
           <t>主人公の世間知らずによる勘違い、ヘタレぶり、仲間からのいじり</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>技法：①“場違いな弱い主人公”が居場所を得る成長譚 ②方言の迫力と温かさの両立 ③情けない顔と覚悟の顔の対比。FLATUP案：格闘技未経験のサラリーマンがジムで最初は縮こまり、少しずつ顔つきが変わる連作。オリジナルの一言案『怖いままでいい。それでも来たあんたが一番かっこええ』</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>極楽蝶など作中チーム名・ロゴ、主人公の名前・外見、広島の特定チーム設定を使わない。暴走族の美化を避ける</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>[事実]シリーズ累計5500万部超（2015年時点とする二次情報）。[事実]2025年にJO1の豆原一成主演で実写映画化。[事実]2026年にヤングキングで完全新作連載開始。[感想]90年代を代表する不良漫画として根強い人気。X直接検索なし</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>https://www.weblio.jp/content/BADBOYS | https://www.cmoa.jp/title/241/ | https://www.oricon.co.jp/news/2385533/full/ | https://www.toy-people.com/jp/?p=108156</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -809,32 +823,34 @@
           <t>仲間内のじゃれ合い、強面の意外な弱点</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>技法：リーダーの器を“守るもの”で描く。FLATUP案：ジムのキャプテンが大会より後輩の怪我を優先する選択回</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>廣島連合・陴威窠斗などのチーム名・当て字表記・ロゴ、主人公の名前・外見を使わない</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>[事実]英語圏DBでも全16巻・完結として登録。[感想]前作より抗争色が強いという評価。X直接検索なし</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Bad_Boys_(manga) | https://booklog.jp/item/1/4785921420 | https://mangapedia.com/BADBOYS%20%E3%82%B0%E3%83%AC%E3%82%A2%E3%83%BC-saan727zv</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -936,32 +952,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>技法：同じ世界観で作品をつなぐ“ユニバース”構成。FLATUP案：FLATUP作品群でも、ジム・商店街・学校を共通舞台にし、別作品のキャラが背景にさりげなく映る仕掛け</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>作中のチーム名・人物名・外見、広島ユニバースの固有設定を使わない</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>[事実]2026年9月発売のヤングキング目次に掲載があり連載継続中。評判は未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/11399/ | https://www.fujisan.co.jp/product/2678/b/2486919/ | https://mangapedia.com/%E7%94%B0%E4%B8%AD%E5%AE%8F-1zai5wxnx</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -1063,32 +1081,34 @@
           <t>元ヤン同士の昔話や、家族の前での不器用さ</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>技法：“元不良が親になる”視点で暴力と責任を描く。FLATUP案：昔やんちゃだった父親が、子どもと一緒にキッズクラスに通い始める親子回。オリジナルの一言案『昔は殴ってばかりだった手で、今日は息子の帯を結んだ』</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>作品タイトルの当て字読み、作中チーム名・人物名・外見を使わない</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>[事実]講談社の書誌で全11巻完結を確認。[感想]田中作品の中で大人向けの重いドラマという評価。X直接検索なし</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000008550 | https://www.kodansha.co.jp/comic/products/0000010760</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -1190,32 +1210,34 @@
           <t>見栄と勘違いからの大失敗、下心が裏目に出る落差、顔芸の誇張</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>技法：『強いのにウブ』というギャップで主人公を愛される存在にする。二人組のボケとツッコミで説明パートをテンポよく進める。オリジナル案：最強のトレーナー二人が、初心者の会員にかっこつけようとして毎回空回りし、結局『優しさ』だけが伝わる日常回</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>鬼塚英吉・弾間龍二の外見や髪型、チーム名『鬼爆』、作中の決め台詞、湘南の固有の族設定を真似しない</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>[事実]GTOの前作として位置づけられている（映像化の詳細は未確認）。[感想]GTOから入った読者が『前作の方がバカで好き』と語る声がある。[推測]90年代少年マガジンのヤンキー黄金期を代表する一作。X直接検索なし</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000006417 | https://www.cmoa.jp/title/135904/ | https://dime.jp/genre/955041/</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -1317,32 +1339,34 @@
           <t>常識外れのスケールの大きいバカ行動、下心と勘違い、エリート側との価値観の落差</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>技法：『怖そうな大人が実は一番優しい』という第一印象の反転。重い悩みの直後にギャグで救う緩急。オリジナル案：強面のトレーナーが、ミット打ちが怖くて泣きそうな子どもに、自分も最初は怖かったと失敗談を披露して笑わせる回。『見た目より中身で強くなろう』という独自の合言葉</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>鬼塚英吉の外見（金髪・特定の髪型）、『GTO』の略称や題名の構造、作中の名ゼリフ・名場面の再現、学校名・生徒キャラの設定を真似しない</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>[事実]第22回（1998年）講談社漫画賞少年部門を受賞。累計発行部数5000万部と紹介されている。ドラマ・アニメ化。[感想]『理想の先生像』として長く語られる。[推測]教育×不良というジャンルの定番を作った作品と見なされている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000006386 | https://dic.pixiv.net/history/GTO/8878455 | https://honcierge.jp/articles/shelf_story/1053</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -1444,32 +1468,34 @@
           <t>本編同様の下ネタと突飛な行動、湘南の旧友との掛け合い</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>技法：『期限付き』の物語構成（○日間で変わる）。オリジナル案：『体験から14日間』をテーマに、初心者が入会2週間で少しずつ表情が変わっていく連載形式のSNS漫画</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>題名の『○○ 14DAYS』の形式をそのまま使わない、施設名・キャラ設定・決め台詞を流用しない</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>[事実]GTO本編の時系列の途中に入るエピソードとして描かれた続編。[推測]本編ファン向けの再始動作として受け止められた。X直接検索なし</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>https://dic.pixiv.net/history/GTO/5324594/source | https://animenewsnetwork.com/news/2011-08-29/gto/shonan-14-days-sequel-manga-to-end-in-japan | https://cdn.animenewsnetwork.com/encyclopedia/releases.php?id=21895</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -1571,32 +1597,34 @@
           <t>本編同様の下ネタ・型破りな行動に加え、芸能界の風刺</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>技法：同じ主人公を新しい舞台に放り込み、時代の問題（SNS、炎上）と組み合わせる。オリジナル案：SNSで『強そうに見せる』ことに疲れた若者が、ジムで『ダサくても続ける強さ』を知るエピソード</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・設定、作中の学校名、芸能人キャラの設定を流用しない</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>[事実]掲載媒体の変更と改題を経て連載が続いている。[推測]長期シリーズの続編として古参ファンが追い続けている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/new-releases?page=70 | https://www.kinokuniya.co.jp/f/dsd-101001011040008--?p=17 | https://dic.pixiv.net/history/GTO/8627698</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -1698,32 +1726,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>技法：既存の世界観を『同じ場所の後輩世代』で描く関連作の作り方。オリジナル案：成田の各ジムや道場の『合同練習会』を舞台に、競い合いながら仲良くなる交流回</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>大会名『湘南セブン』、辻堂高校などの設定、GTOキャラクターの登場や言及を流用しない</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>[事実]完結済み。[推測]公式の『外伝』表記は確認できず、GTOとの関係は舞台・人物のつながりにとどまる可能性がある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/77999 | https://booklive.jp/focus/author/a_id/3538/sort/t1 | https://anime.jepang.org/en/manga/65683/Shonan_Seven | https://www.fujisan.co.jp/product/743/new/</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -1825,32 +1855,34 @@
           <t>はったりが偶然うまくいく勘違い連鎖、ビビりの顔芸、卑怯さと根性の落差</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>技法：『心の声』と『実際の行動』をずらして描く二重構造。偶然の勝利が誤解を呼ぶコメディ。オリジナル案：運動経験ゼロの会員が、ジム見学で緊張して強がった結果、なぜか『経験者』と思われて焦る回。最後は正直に『初心者です』と言えた勇気を描く</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>主人公・矢沢栄作の外見や名前、作中の舞台設定（松戸の学校名）、決め台詞やポーズを真似しない</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>[事実]第23回講談社漫画賞少年部門を受賞。OVAがブルーレイ化された。[感想]『弱い主人公の不良漫画』の元祖的存在として愛されている。[推測]累計3000万部という数字は宣伝記事のみで公式未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000052230 | https://news.denfaminicogamer.jp/news/240207l | https://www.cmoa.jp/title/18150/ | https://ndlsearch.ndl.go.jp/en/books/R100000002-I034660906</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -1952,32 +1984,34 @@
           <t>主役が女装という設定が紹介されている（詳細未確認）</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>技法：前作の舞台を『○年後』に設定し、新キャラで世界観を広げる続編の作り方。オリジナル案：FLATUP初期メンバーが卒業した後、新しい初心者世代が入ってくる『第2期』シリーズ</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>主人公の女装設定やキャラの外見、学校名、前作キャラの登場を真似しない</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>[事実]『カメレオン』14年ぶりの復活作と紹介されている。[推測]前作ファンの期待を背負った続編。X直接検索なし</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/titles/1000006688 | https://www.kodansha.co.jp/comic/products/0000047934 | https://mangapedia.com/%E5%8A%A0%E7%80%AC%E3%81%82%E3%81%A4%E3%81%97-8q6sb22ju</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2079,32 +2113,34 @@
           <t>強面の不良が女性や家族の前で急に弱くなる落差、仲間同士のボケとツッコミ、主人公の天然な行動による脱力</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>技法：①主人公を他人の視点で語らせて大きさを出す ②激しい場面の直後に静かな日常コマを置く緩急 ③行事（入会・昇級・卒業）を章の区切りにする。FLATUP案：初心者が先輩トレーナーを遠くから見て『あの人みたいに、怖がらずに立っていたい』と思う導入。ケンカではなく“初めてのミット打ち”を見開きの山場にする</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>鈴蘭男子高校・鳳仙学園・武装戦線などの校名・チーム名、坊屋春道など主要人物の外見（髪型・学ランの着こなし）、作中の街名、作品ロゴ、カラスのモチーフをそのまま使わない。名場面の構図再現や決めゼリフの言い換えも避ける</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>[事実]秋田書店の発表では『クローズ』『WORST』シリーズ（スピンオフ含む）累計発行部数は9000万部超。[事実]2026年に正統続編『ダストランド』の連載が始まり、PR展開が大きく行われた。[感想]不良漫画の金字塔・バイブルと呼ばれることが多い。[推測]映画『クローズZERO』から入った読者層も厚い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>https://koubo.jp/press-release/prtimes/c40601_r794 | https://www.oricon.co.jp/news/2430258/full/ | https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366 | https://dic.nicovideo.jp/t/a/%E3%82%AF%E3%83%AD%E3%83%BC%E3%82%BA%28%E6%BC%AB%E7%94%BB%29</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2206,32 +2242,34 @@
           <t>主人公の天然な勘違い・食いしん坊ぶり、強面キャラのギャップ、仲間同士のじゃれ合い</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>技法：①敵意を笑顔と素直さで溶かす主人公像 ②世代交代（先輩の卒業）で物語を区切る ③勢力図より“仲間の輪”が広がる様子を描く。FLATUP案：初心者が怖そうな常連に挨拶し続け、やがて一緒にスパーの順番を待つ仲になる話。オリジナルの一言案『また来週も、ここで会おうぜ』</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・名前、鈴蘭の一年戦争などの固有設定、武装戦線のロゴ・ジャケット、作中の地名（戸亜留市など）、キャラのニックネーム（ゼットン等）を使わない</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>[事実]秋田書店は2026年1月に全33巻分の無料公開キャンペーンを実施。[事実]映画『HiGH&amp;LOW THE WORST』とのコラボ作品が作られた。[感想]クローズより明るく読みやすいという声がある。[感想]後半は脇役の出入りが多くまとまりに欠けるという意見もファン百科に見られる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>https://koubo.jp/press-release/prtimes/c40601_r794 | https://animeanime.jp/release/prtimes/20251125/259000.html | https://www.cmoa.jp/title/175450/vol/9/ | https://dic.pixiv.net/a/worst</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2333,32 +2371,34 @@
           <t>元ヤンの教師が教育現場のルールに戸惑う、強面が慣れない敬語を使うギャップ、生徒からのいじりに本気で動揺する</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>技法：①強い大人が“力を使わない”ことで強さを見せる ②生徒一人ずつのエピソード回し ③日常と対決の交互配置。FLATUP案：元・荒れていたトレーナーが、いじめられっ子の会員に手加減の大切さを教える回。オリジナルの一言案『殴れることより、殴らないで済む強さを持とうな』</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・ニックネーム、鈴蘭の卒業生という設定、作中の高校名（天香国高校）、WORSTの人物の登場を想起させる設定を使わない</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>[事実]2026年10月20日に『ダストランド』2巻と同時に最新刊が発売され、記念キャンペーンが行われた。[感想]元ヤン教師ものとして人情が濃いという紹介が多い。[推測]FLATUPの『強さとは優しさ』に最も近い構造のシリーズ作品。X直接検索なし</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>https://akitashoten.co.jp/series/10595 | https://realsound.jp/book/2026/10/post-2556993.html | https://bookwalker.jp/series/275623/list/ | https://mangapedia.com/WORST%E5%A4%96%E4%BC%9D%E3%82%BC%E3%83%83%E3%83%88%E3%83%B3%E5%85%88%E7%94%9F-q9dvp5xny</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2460,32 +2500,34 @@
           <t>最強の主人公が恋や日常の小事に弱いギャップ、方言の掛け合い</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>技法：①方言でキャラの土地柄と温度を出す ②“最強の人の弱かった頃”を描く前日譚 ③相手のリアクションで強さを表す。FLATUP案：成田の空港の見える土手で、まだ泣き虫だった頃のジム代表を描く前日譚。千葉の言葉の語感を少し混ぜる</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見（体格・髪型）、本編での異名、博多の特定チーム名・人物名を使わない</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>[事実]週刊誌での長期連載で40巻規模に達している。[感想]本編を知らなくても読めるという声がある。[推測]スピンオフとしてシリーズで最も長く続いている作品の一つ。X直接検索なし</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>https://akitashoten.co.jp/series/9349 | https://www.cmoa.jp/title/175451/vol/26/ | https://www.maruzenjunkudo.co.jp/products/9784253254991 | https://mangapedia.com/WORST%E5%A4%96%E4%BC%9D%E3%82%B0%E3%83%AA%E3%82%B3-nrrtcjczv</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2587,32 +2629,34 @@
           <t>中学生らしい背伸びや見栄が空回りする笑い</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>技法：①憧れの集団に入るまでの“入門編” ②因縁の相手を影で見せる演出 ③先輩の一言で主人公が変わる転機。FLATUP案：入門をためらう少年がジムの窓越しに練習を覗き続け、ついにドアを開ける回。暴走族ではなく“ジムという居場所”への憧れに置き換える</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>武装戦線のチーム名・ロゴ・ドクロマーク・ジャケット、主人公の顔の傷などの外見的特徴、因縁の相手の異名を使わない。暴走族の美化も避ける</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>[事実]2025年に新章が始まり、単行本も継続刊行。[感想]シリーズ屈指の人気チームの前日譚として期待されたという紹介が多い。[推測]暴走族要素が強く、FLATUP作品では直接の参考にしにくい部分もある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>https://animeanime.jp/release/prtimes/20250711/238279.html | https://mechacomic.jp/books/133988 | https://www.ehonnavi.net/ehon00.asp?no=308897 | https://mangapedia.com/WORST%E5%A4%96%E4%BC%9D%E3%83%89%E3%82%AF%E3%83%AD-ate3z1jgj</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2714,32 +2758,34 @@
           <t>三人組のボケ・ツッコミ、勘違いと空回り、貧乏ネタ</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>技法：①主役ではない“名もなき人”の物語 ②三人組の役割分担（突っ込む・止める・ボケる）③生活感のある背景で親近感を出す。FLATUP案：ジムの体験に来た運動経験ゼロの三人組（会社員・主婦・高校生）の連作コメディ</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>三人の名前・外見、作中の団地名、シリーズの時代設定を示す固有の描写、カラスのモチーフをそのまま使わない</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>[事実]秋田書店が他の外伝と同時刊行フェアを行っている。[感想]有名キャラが出ない分、等身大で読みやすいという紹介がある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>https://www.ehonnavi.net/author.asp?n=122264 | https://www.ehonnavi.net/ehon00.asp?no=308882 | https://landing.akitashoten.co.jp/karasu/ | https://mangapedia.com/WORST%E5%A4%96%E4%BC%9D%E3%82%B5%E3%83%96%E3%83%AD%E3%82%AF%E3%82%B5%E3%83%B3%E3%82%BF%E5%90%8D%E3%82%82%E3%81%AA%E3%81%8D%E3%82%AB%E3%83%A9%E3%82%B9%E3%81%9F%E3%81%A1-2cllph9in</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2841,32 +2887,34 @@
           <t>コワモテ集団の内輪での抜けた会話（量は少なめ）</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>技法：①“チームが生まれるまで”を描く起源譚 ②俯瞰の群衆と正面のアップの切り替え。FLATUP案：FLATUP GYM創設期、会員3人から始まった“最初の合同練習”を描く起源回。対立ではなく、みんなでマットを敷く場面を山場にする</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>鳳仙学園の校名、坊主頭の集団という特徴的なビジュアル、“殺しの軍団”などの異名、主要人物の名前と外見を使わない</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>[事実]2026年1月の24巻で完結。[感想]本編で敵役だった学校の過去が分かる点が評価されている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/comics/4253252923 | https://www.ehonnavi.net/ehon00.asp?no=308859 | https://www.city.niigata.lg.jp/kanko/bunka/shinko/mangaanime_mati/creator-meikan.files/sagyou.pdf</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -2968,32 +3016,34 @@
           <t>未確認（暴力描写中心でギャグは少ないと思われる）</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>技法：①周囲の恐怖のリアクションで人物の怖さを表す。FLATUP案：逆に“見た目が怖いけど実は一番優しいトレーナー”の誤解を解く回に転用し、恐怖の目線が尊敬に変わる流れを描く</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・異名・外見、作中で“最強”とされる設定をそのまま使わない。暴力の美化を避ける</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店で全23巻・完結として配信されている。[推測]青年誌掲載のため本編より暴力描写が濃いと見られる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>https://booklive.jp/focus/author/a_id/19009 | https://ebookjapan.yahoo.co.jp/lists/authors/14329 | https://mangapedia.com/gd/q5ruq4yjk</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3095,32 +3145,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>技法：完成された強者の“未完成だった頃”を描く前日譚の型。FLATUP案：ジムの最強会員が、初めての試合で緊張して眠れなかった夜を描く短編</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・異名（リンダマン）・巨体の外見、鈴蘭の無敵設定を使わない</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店で全2巻として配信。評判は未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>https://booklive.jp/product/index/title_id/146518/vol_no/001 | https://wowma.jp/item/529439031</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3222,32 +3274,34 @@
           <t>脇役トリオの掛け合い</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>技法：脇役一人ずつに一話を与える短編集の型。FLATUP案：受付スタッフ、清掃担当、最年長会員など、ジムの脇役を一話ずつ主役にする番外編シリーズ</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>収録作の主人公（ボン・マコ・ヒロミ、坂東ヒデト、坊屋春道）の名前・外見・エピソードを使わない</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店でボン・マコ・ヒロミ、坂東ヒデト、坊屋春道の3編を収録した外伝として配信されている。評判は未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>https://mechacomic.jp/books/147009 | https://booklive.jp/focus/author/a_id/12526</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3349,32 +3403,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>技法：集団の“初代”を描く起源譚。FLATUP案：初代会員たちの記念写真から始まる回想短編</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>武装戦線の名前・ロゴ・ジャケット、初代メンバーの名前・外見を使わない</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>[事実]作者単独名義の外伝として新装版が電子書店で配信されているとの情報あり。評判は未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3476,32 +3532,34 @@
           <t>作家ごとに異なる</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>技法：同じ世界を複数の作り手が解釈するアンソロジー形式。FLATUP案：トレーナーや会員がそれぞれ“自分にとってのFLATUP”を4コマで描く企画</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>収録作に登場する本編キャラ・校名・名場面のオマージュ表現を流用しない</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店で3巻まで配信。評判は未確認。X直接検索なし</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>https://booklive.jp/product/index/title_id/379770/vol_no/001 | https://booklive.jp/product/index/title_id/379770/vol_no/003</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3603,32 +3661,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>技法：長寿シリーズを新世代で再起動する“正統続編”の作り方（旧作キャラの祝福演出・大型PR）。FLATUP案：ジムの周年企画で、歴代会員が新入会員を迎える“世代バトン”のショート動画</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>作品タイトル、鈴蘭男子高校、新キャラの名前・外見、宣伝ビジュアルを使わない</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>[事実]作者13年ぶりのシリーズ新作として大きく報道され、JR常磐線ジャック等のPRが行われた。[推測]連載開始から日が浅く評価は定まっていない。X直接検索なし</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>https://prtimes.jp/main/html/rd/p/000000782.000040601.html | https://www.oricon.co.jp/news/2430258/full/ | https://koubo.jp/press-release/prtimes/c40601_r858 | https://crowsworst.akitashoten.co.jp/</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -3730,32 +3790,34 @@
           <t>無口な主人公を周囲が勝手に誤解する勘違いギャグ、強面と行動の落差</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>技法：『喋らないキャラ』の心を周囲の反応と間で描く。オリジナル案：無口で強面の会員が、実は子どもクラスの片付けを毎回こっそり手伝っていたと判明する話。言葉ではなく行動で優しさを見せる</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>主人公・池戸定治の外見や『ゴリラーマン』という呼び名の構造、学校名（白武高）を真似しない</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>[事実]作者の連載デビュー作で、第14回講談社漫画賞一般部門を受賞。続編『ゴリラーマン40』が2022年に連載開始。[感想]『喋らない主人公』の発想が斬新と評価される。X直接検索なし</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Gorillaman | https://dic.nicovideo.jp/a/%E3%82%B4%E3%83%AA%E3%83%A9%E3%83%BC%E3%83%9E%E3%83%B3 | https://www.kodansha.co.jp/comic/products/0000016307</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3857,32 +3919,34 @@
           <t>未確認（家族編があると紹介されている）</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>技法：『あの頃の主人公が中年になったら』という後日談。オリジナル案：40代の元ヤン会員が、子どもと一緒に親子クラスに通う話</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・呼び名、前作の学校設定を真似しない</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>[事実]ヤングマガジン40周年企画から生まれた続編。X直接検索なし</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E3%82%B4%E3%83%AA%E3%83%A9%E3%83%BC%E3%83%9E%E3%83%B340-e3l54ku9q | https://www.kodansha.co.jp/comic/new-releases/p?page=244</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -3984,32 +4048,34 @@
           <t>カッコつけが空回りする『ちょっとカッコ悪いリアル系』の笑い</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>技法：『憧れから始まる』主人公。カッコ悪さを隠さないリアルさ。オリジナル案：格闘技漫画に憧れてジムに来た会員が、初日にジャブすらぎこちなくて落ち込むが、トレーナーに『憧れて来た時点で一番大事なものは持ってる』と励まされる話</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>高橋ヒロシ風のキャラデザイン、作中の学校名やキャラ設定、原作者の実話エピソードを真似しない</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>[事実]品川ヒロシの半自伝小説のコミカライズで、実写映画化もされた。[感想]紹介文でも『ちょっとカッコ悪いリアル系』と表現される。X直接検索なし</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E3%83%89%E3%83%AD%E3%83%83%E3%83%97-j9x6p0ah5 | https://www.cmoa.jp/title/110507/vol/14/ | https://comic.k-manga.jp/title/113964/pv | https://www.oricon.co.jp/news/2253611/full/</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4111,32 +4177,34 @@
           <t>大阪弁の掛け合い、主人公の下心による失敗、身内ノリの誇張</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>技法：方言の会話テンポでキャラを立てる。地域性（地元の道・街）を物語の舞台装置にする。オリジナル案：成田の地元（成田山参道、空港周辺）をロードワークで走る会員たちの会話劇。千葉ことばを少し取り入れた掛け合い</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>実在チームを想起させる名称や作中チーム名、キャラ外見、車のステッカー・デザインを真似しない。公道での危険走行を肯定する演出はFLATUPの思想に合わない</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>[事実]作者は後に『ザ・ファブル』でヒットしている。[感想]大阪弁の会話が面白いと評価する声がある。[推測]環状族という題材のニッチさから関西で特に人気。X直接検索なし</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E3%83%8A%E3%83%8B%E3%83%AF%E3%83%88%E3%83%A2%E3%82%A2%E3%83%AC-tcvgdo8z5 | https://www.kodansha.co.jp/comic/products/0000008589 | https://booklive.jp/focus/author/a_id/3869</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4238,32 +4306,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>技法：同じ読みのタイトルを表記違い（カタカナ→ひらがな・漢字）で続編化するネーミング手法。オリジナル案：FLATUPシリーズの第2部を表記だけ変えて区別する（例：『フラットアップ』と『ふらっとあっぷ』）</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>作中チーム名・キャラ・車のデザインを真似しない。危険走行を肯定しない</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>[事実]前作から連続して約14年続いたシリーズ。[推測]前作ファンがそのまま移行した長期続編。X直接検索なし</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E3%81%AA%E3%81%AB%E3%82%8F%E5%8F%8B%E3%81%82%E3%82%8C-3t35zu6ut | https://booklive.jp/focus/author/a_id/3869</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4365,32 +4435,34 @@
           <t>二重生活がバレそうになるドタバタ、家族の過剰なヤンキーぶり、勘違いの連鎖</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>技法：①二重生活によるサスペンスと笑い ②家族の愛を誇張したギャグで描く。FLATUP案：“格闘技が怖い子”が家族に内緒で体験に来る話。正体バレの代わりに“初めてのミット打ちを家族に見られる”山場</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>主人公一家の名字・外見、二重生活の具体的設定（ヤンキー一家と普通の学校の組み合わせ）、作中の学校名、決まった家族構成をそのまま使わない</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>[事実]2022年に地上波ドラマ化。[感想]不良漫画なのに家族愛に泣けるという声が多い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>https://ranking.net/items/c27482 | https://www.kinokuniya.co.jp/f/dsg-08-9981904201 | https://realsound.jp/movie/2022/01/post-950199.html</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4492,32 +4564,34 @@
           <t>前作同様のドタバタと家族ギャグ。終盤は控えめ</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>技法：シリーズ後半でギャグからシリアスへ比重を移す構成。FLATUP案：笑いの多い連作の最終章で、主人公が“初めての試合に出るかどうか”を自分で決める回</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>前作と同じく主人公一家・学校の固有設定、終盤の事件の展開をなぞらない</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店で全15巻完結。コミックシーモアで高評価（平均4.9）。[感想]シリーズの締めくくりとして満足度が高いという声。X直接検索なし</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/40994/ | https://booklive.jp/focus/author/a_id/10848 | https://renote.net/tags/17418</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4619,32 +4693,34 @@
           <t>主人公コンビのドジ、女子に振り回される落差、ケンカ後の間抜けなオチ</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>技法：二人組主人公の『漫才的な掛け合い』で長期連載を回す。日常とケンカの緩急。オリジナル案：ジムの同期入会コンビが毎回『どっちが先に縄跳び二重跳びできるか』で張り合う、ゆるい日常4コマ</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>トオル・ヒロシのキャラ外見（リーゼント等の組み合わせ）、愛徳高校などの学校名、タイトルロゴ、映画の名場面を真似しない</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>[事実]累計発行部数4000万部超とされ、実写映画6作などメディア展開が多い。第12回講談社漫画賞（一般部門とする資料あり、受賞年の記載に食い違いあり）。[感想]80年代ツッパリ文化の象徴として語られる。[推測]実写映画の影響で原作未読層にも知名度が高い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>https://renote.net/articles/15234 | https://www.netoff.co.jp/detail/0010117245/ | https://realsound.jp/book/2024/01/post-1559884.html/amp | https://movie.jorudan.co.jp/film/18144/</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4746,32 +4822,34 @@
           <t>シリアス主体だが、主人公の泣き顔やヘタレぶり、仲間内の軽いじゃれ合いで息抜き</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>技法：『弱いけど折れない』主人公に読者が感情移入する構造。毎話の終わりに次が気になる引きを作る。オリジナル案：何度ミット打ちで息切れしても『あと1ラウンドだけ』と立ち上がる会員の物語。強さ＝勝つことではなく『やめないこと』と定義する</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>『東京卍會』などのチーム名・卍マーク、キャラの外見（髪型・特攻服）、タイムリープの具体設定、作中の名ゼリフを真似しない。ロゴデザインにも注意</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>[事実]累計発行部数7000万部超と報じられ、アニメ・実写映画も大ヒットした。[感想]主人公の泣き虫ぶりに賛否はあるが『諦めない姿に泣ける』と語られる。[推測]2020年代にヤンキー漫画を若い世代へ再普及させた作品。X直接検索なし</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>https://av.watch.impress.co.jp/docs/news/1340171.html | https://animeanime.jp/article/2022/04/23/69070.html | https://kai-you.net/word/%E6%9D%B1%E4%BA%AC%E5%8D%8D%E3%83%AA%E3%83%99%E3%83%B3%E3%82%B8%E3%83%A3%E3%83%BC%E3%82%BA | https://bunshun.jp/articles/-/62450</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -4873,32 +4951,34 @@
           <t>見た目は真面目なのにケンカ最強という落差、勢いで振り回すドタバタ</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>技法：『見た目は真面目・中身は最強』のギャップヒロイン。ボケとツッコミのタンデム構造。オリジナル案：受付で丁寧に案内してくれるメガネのスタッフが、実はミット持ちが一番うまいトレーナーだったと判明する回</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>足立花・品川大地のキャラ外見、タイトルの『○○君と○○ちゃん』構造をそのまま使わない、学校名の設定を真似しない</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>[事実]作者のデビュー作で、テレビドラマ化された。[感想]明るく読みやすいヤンキーラブコメとして女性読者にも好まれる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000052061 | https://www.kodansha.co.jp/comic/products/0000012307 | https://www.cmoa.jp/title/41193</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -5000,32 +5080,34 @@
           <t>不良なのに手芸部という設定の落差、仲間の悪ノリ</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>技法：『怖い外見×意外な趣味』で親しみを出す設定。オリジナル案：いかついトレーナーの趣味が家庭菜園で、会員にジム産の野菜を配る回。強さと優しさの両立を象徴する</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>チーム名『湘南爆走族』、キャラの外見、特攻服、手芸部という具体設定をそのまま使わない</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>[事実]40周年記念グッズ（スイングトップ）が販売されるなど根強い人気がある。[感想]80年代の『明るい暴走族漫画』として懐かしまれる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>https://motor-fan.jp/article/51115/ | https://anime.eiga.com/program/105986/ | https://wowma.jp/item/529688650 | https://eiga.com/person/75701/wikipedia/</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -5127,32 +5209,34 @@
           <t>未確認（本文未読）</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>技法：『強い女性主人公』を正面から描く不良漫画の型。オリジナル案：女性会員クラスで、最初は人見知りだった会員が自分の強さに自信を持ち、後輩の初心者女性を励ます先輩になる話</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>チーム名・特攻服の刺繍・キャラ外見、作品名の『特攻』の読ませ方を真似しない</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>[事実]作者の連載デビュー作で6年以上連載された長期作品。[推測]女性主人公のヤンキー漫画として貴重な存在とされている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Kissh%C5%8D_Tennyo | https://pedia.3rd-in.co.jp/wiki/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3 | https://mangapedia.com/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3-uqec3f53z</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -5254,32 +5338,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>技法：実話ベースの『いじめられっ子からの成長』物語。オリジナル案：いじめで自信を失った中学生が、ジムで『誰かを殴るためではなく自分を守るため』の練習を通じて自信を取り戻す話。FLATUPの思想『不良漫画は好き、でも不良は嫌い』に合わせ、暴力での解決にしない</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>原作者の実話エピソード、実在チームを想起させる名称、キャラの外見を真似しない</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>[事実]2017年に実写映画化された。2026年に連載再開が告知された。[推測]原作者の知名度で芸人ファン層にも読まれている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/113839 | https://www.cmoa.jp/title/120153/vol/230/ | https://www.fujisan.co.jp/product/2682/b/623118/ | https://ciatr.jp/topics/313098</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -5381,32 +5467,34 @@
           <t>少なめ。主人公の不器用さによる小さな笑い</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>技法：①同じ出発点から違う道へ進んだ二人の対比 ②黒ベタと陰影で緊張を作る。FLATUP案：昔同じ道場にいた二人が、一人はトレーナー、一人は道を外れて再会する話。最後に“もう一度グローブを付ける”選択を描く</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>主人公・旧友の名前・異名（死神など）・外見、作中の組織名を使わない。裏社会の描写は避ける</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>[事実]スピンオフを元に2011年に実写ドラマ化（主演 斎藤工）。[感想]高橋作品の中でダークな異色作という評価が多い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>https://dic.pixiv.net/history/QP/2961307/source | https://comic.k-manga.jp/title/51360/pv | https://honcierge.jp/articles/shelf_story/7349</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -5508,32 +5596,34 @@
           <t>幼なじみ同士のボケ合い、恋愛での空回り、デフォルメ顔</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>技法：①固定メンバー（四人）で長期連載を回す ②卒業をゴールにした構成。FLATUP案：同じ日に入会した四人が、一年後の“初めての昇級審査”を一緒に迎えるまでを描く連作</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>四人の名前・外見、作中の高校名、四つ葉のクローバーをチームの象徴にする設定を使わない</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>[事実]電子書店で全43巻完結。[感想]明るく爽快な不良漫画という評価。[推測]チャンピオン系の“明るい不良もの”の代表格と見られる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>https://comic.k-manga.jp/title/112495/vol/43 | https://mangapedia.com/%E5%B9%B3%E5%B7%9D%E5%93%B2%E5%BC%98-0adjsc340 | https://justwatch.com/jp/%E3%83%86%E3%83%AC%E3%83%93%E7%95%AA%E7%B5%84/kuroba</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -5637,30 +5727,40 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
+          <t>C：大げさな劇画の雰囲気づくりの参考程度</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／群像・矜持</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>技法：集団の対峙を見開きで見せて緊張を作る、仲間の結束を象徴する小道具の使い方。アイデア：ジムの仲間でおそろいのタオルを作り、それが絆のしるしになる話。オリジナルの一言案「走る場所は道路じゃなくて、ロードワークのコースな」</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>チーム名・特攻服の刺繍デザイン・バイクの改造スタイル・キャラの外見を使わない。暴走行為を肯定的に描かない（ブランド方針）</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>[事実] OVA化・実写映画化されている。[事実] 累計650万部超とする資料あり。[推測] 80年代の月刊少年マガジンの代表的な暴走族漫画として世代人気が高い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/labels/gmaga?page=108 | https://www.allcinema.net/cinema/pdf/88636 | https://pedia.3rd-in.co.jp/wiki/%E3%83%A4%E3%83%B3%E3%82%AD%E3%83%BC%E7%83%88%E9%A2%A8%E9%9A%8A | https://eiga.com/movie/39865/</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -5719,7 +5819,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2002年12月号〜（終了時期は未確認）</t>
+          <t>2002年12月号〜（第17巻に2012年4月号掲載分までを確認。終了号は未確認）</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5764,30 +5864,40 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
+          <t>C：時代の空気を描く群像劇として参考程度で、暴走族への憧れは描かない</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t>技法：セリフのないコマで空気や心情を語らせる、時代の小物で世界観を作る。アイデア：閉館後のジムで、昔ヤンチャだったトレーナーが若い会員に昔話をする静かな回。オリジナルの一言案「あの頃は居場所がなかった。だから、ここを作った」</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>作中のチーム名・特攻服やバイクの具体的デザイン・主人公の外見を使わない。暴走行為を美化しない</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>[事実] 講談社アフタヌーン掲載作品として全巻が電子配信されている。[推測] 作者の画風と80年代描写を評価する大人の読者が中心。X直接検索なし</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000029856 | https://www.kodansha.co.jp/comic/products/0000029772 | https://www.cmoa.jp/title/71369 | https://booklive.jp/focus/author/a_id/3534</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -5891,30 +6001,40 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
+          <t>C：昔ながらのタイマンの友情ものとして参考程度</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t>技法：二人組の主人公でボケとツッコミ、熱さと冷静さを分担させる。アイデア：性格が真逆の二人のトレーナーが、それぞれのやり方で初心者を支える話。オリジナルの一言案「教え方は違っても、守りたいものは同じ」</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>主人公二人の名前・外見・学校名、地域対立の設定をそのまま使わない</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>[推測] 80年代少年チャンピオンの不良漫画として一部で根強い人気。評判の具体的な情報は確認できず。X直接検索なし</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>https://comic.k-manga.jp/title/113460/pv | https://comic.k-manga.jp/title/113460/vol/16</t>
         </is>
       </c>
-      <c r="X43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -6008,40 +6128,50 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>稚拙だが力強いと評される絵柄で、勢いのある作画をナンセンスな展開に合わせる（紹介記事による）</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>硬派な上下関係を誇張して笑いにする（詳細は未確認）</t>
+          <t>下ネタを含むドタバタ劇と、流行語になった奇声などの勢いで笑わせる。硬派な上下関係を誇張して笑いにする（紹介記事による。FLATUPでは下ネタは使わない）</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
+          <t>B：硬派ぶる人物を誇張して笑いにする手法は使えるが、下ネタは使わない</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
           <t>技法：怖そうな集団の内側の間抜けさを見せて親しみを作る落差。アイデア：見た目が怖い上級者たちが、実は初心者の名前を全員覚えている回。オリジナルの一言案「声がでかいのは、応援のためです」</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・応援団の団名・有名な決め台詞を使わない。先輩による理不尽な体罰的上下関係をそのまま肯定しない</t>
         </is>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>[事実] 1976年から実写映画化されている。[推測] 70年代の硬派ギャグ漫画の代表として世代人気が高い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>https://mangapedia.com/%E3%81%A9%E3%81%8A%E3%81%8F%E3%81%BE%E3%82%93-3dsaouojx | https://www.cmoa.jp/title/87416/ | https://renote.net/reviews/1463</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>https://mangapedia.com/%E3%81%A9%E3%81%8A%E3%81%8F%E3%81%BE%E3%82%93-3dsaouojx | https://www.cmoa.jp/title/87416/ | https://renote.net/reviews/1463 | https://mangapedia.com/%E5%97%9A%E5%91%BC%21%21%E8%8A%B1%E3%81%AE%E5%BF%9C%E6%8F%B4%E5%9B%A3-ht4vx2b0j</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -6145,30 +6275,40 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
+          <t>C：思春期の孤独の描き方の参考程度</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>技法：モノローグと余白で寂しさを表す、不良ものを女性視点で描く。アイデア：家に居場所がない女子中学生が、ジムの受付スタッフとの会話で少し笑えるようになる話。オリジナルの一言案「ここでは、がんばらなくてもいいよ」</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>主人公たちの名前・外見・暴走族チーム名・作中の象徴的なモノローグを使わない</t>
         </is>
       </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr">
         <is>
           <t>[事実] 2014年に実写映画化。[感想] 少女漫画に新しい世界を開いた名作という紹介がある。[推測] 80年代の女性読者に強く支持された。X直接検索なし</t>
         </is>
       </c>
-      <c r="W45" s="2" t="inlineStr">
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>https://www.ehonnavi.net/author.asp?n=32363 | https://renote.net/articles/143290 | https://mangapedia.com/%E7%B4%A1%E6%9C%A8%E3%81%9F%E3%81%8F-9c3plhzcp</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -6272,30 +6412,40 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
+          <t>A：強面に見える先生が生徒を守る落差が、FLATUPの指導者像に使える</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>技法：先生が生徒を守るためだけに本気を出すという、強さの使い方の描き方。アイデア：ふだんは穏やかな女性トレーナーが、会員がからまれた時だけ毅然と立ちはだかる回（暴力は使わずに場を収める）。オリジナルの一言案「この子は、うちの大事な会員です」</t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>主人公のジャージ・眼鏡・おさげの外見、ヤンクミなどの呼び名、学校名、家業の組名、ドラマ版の演出を使わない</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="X46" s="2" t="inlineStr">
         <is>
           <t>[事実] TVドラマ化されシリーズ化した。[感想] ドラマの印象が強いという声が多い。[推測] 不良と教師ものの組み合わせを広く一般層に広めた。X直接検索なし</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E6%A3%AE%E6%9C%AC%E6%A2%A2%E5%AD%90-68ix0qcya | https://bookmeter.com/books/302871 | https://www.cmoa.jp/title/65170</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -6369,60 +6519,70 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
+          <t>同じ作者に『ランブルフィッシュ』『GOLD』『半グレ―六本木 摩天楼のレクイエム―』（紹介記事・電子書店による）</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>過去の自分との決別、街を守る責任、仲間への義理</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>伝説的な不良だった主人公が過去の行いと向き合う葛藤を描く（詳細は未確認）</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>過去の自分との決別、街を守る責任、仲間への義理</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>伝説的な不良だった主人公が過去の行いと向き合う葛藤を描く（詳細は未確認）</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>舞台を学校ではなく渋谷の街に置き、一匹狼の主人公が勢力抗争に抗う、抗争色の強い群像劇の構成（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
+          <t>C：抗争色が強く、元不良が過去と向き合う葛藤の参考程度</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>技法：元・強者が自分の過去と向き合う『贖罪』の物語の型。アイデア：昔ケンカで人を傷つけたことを後悔している大人が、ジムで子どもたちに護身と礼儀を教える回。オリジナルの一言案「強さは、昔の自分を許すためにも使える」</t>
         </is>
       </c>
-      <c r="U47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・渋谷の具体的なチーム名や勢力図を使わない</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
         <is>
           <t>[推測] 2000年代後半のヤングジャンプの不良漫画として一定の人気。具体的な評判は確認できず。X直接検索なし</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>https://mangapedia.com/%E5%B1%B1%E6%9C%AC%E9%9A%86%E4%B8%80%E9%83%8E-pnt045wzo | https://dengekionline.com/article/202606/77670 | https://www.maruzenjunkudo.co.jp/products/9784088798219</t>
-        </is>
-      </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>https://mangapedia.com/%E5%B1%B1%E6%9C%AC%E9%9A%86%E4%B8%80%E9%83%8E-pnt045wzo | https://dengekionline.com/article/202606/77670 | https://www.maruzenjunkudo.co.jp/products/9784088798219 | https://weekly.ascii.jp/elem/000/004/408/4408909/ | https://booklive.jp/focus/author/a_id/148</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="AA47" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -6481,12 +6641,12 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>未確認（講談社の単行本情報で少なくとも1997年〜2002年以降の掲載分を確認）</t>
+          <t>未確認（講談社の単行本情報で少なくとも1997年〜2004年の掲載分を確認）</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>未確認（電子書店で第50巻まで完結作品として並ぶ。ほかに別巻『工業哀歌バレーボーイズ 虎子』あり）</t>
+          <t>全50巻（電子書店で完結表示。2026-10時点で確認）＋別巻『工業哀歌バレーボーイズ 虎子』（2018年12月配信開始）</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6496,7 +6656,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>別巻『工業哀歌バレーボーイズ 虎子』</t>
+          <t>後日譚『好色哀歌 元バレーボーイズ』全17巻（講談社。最終巻は2011年7月発売）、別巻『工業哀歌バレーボーイズ 虎子』</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -6526,30 +6686,40 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
+          <t>C：男子校ノリの笑いは下ネタが中心で、参考程度</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
           <t>技法：部活ものと不良ギャグの組み合わせで日常回を量産する型。アイデア：男子会員だけのクラス後の、プロテインの味をめぐるくだらない議論の4コマ。オリジナルの一言案「チョコ味かバニラ味か、それが問題だ」</t>
         </is>
       </c>
-      <c r="U48" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>学校名・キャラの外見・作中の下ネタ表現をそのまま使わない</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
         <is>
           <t>[事実] 50巻前後に及ぶ長期連載。[推測] ヤンマガ系のバカ系ヤンキーギャグとして男性読者に人気。X直接検索なし</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000008434 | https://www.kodansha.co.jp/comic/products/0000008662 | https://bookwalker.jp/series/4353/list/</t>
-        </is>
-      </c>
-      <c r="X48" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000008434 | https://www.kodansha.co.jp/comic/products/0000008662 | https://bookwalker.jp/series/4353/list/ | https://www.kodansha.co.jp/comic/products/0000016308 | https://www.kodansha.co.jp/comic/products/0000010603</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -6651,32 +6821,34 @@
           <t>仲間内の下品で勢いのある笑い、強面の意外な素直さ</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>技法：①“殴ってはいけない”制約が緊張を生む ②我慢の積み重ね→解放の構成。FLATUP案：試合前に怪我を抱えた選手が、スパーで無理をしない我慢を選ぶ回。解放は“ミット打ちの一発”で描く</t>
         </is>
       </c>
-      <c r="U49" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>実在の原作者をモデルにした主人公の名前・外見、作中の暴走族名、千葉の実在地名を使った同じ設定を使わない。実話ベースの人物を想起させる描写を避ける</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>[事実]2023年に実写映画化（監督・脚本 品川ヒロシ、主演 倉悠貴）。[感想]実話ベースの生々しさが人気という紹介が多い。[推測]同じ千葉が舞台の要素があり、FLATUP読者にも身近に感じられる可能性。X直接検索なし</t>
         </is>
       </c>
-      <c r="W49" s="2" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/2934?page=1 | https://www.weblio.jp/content/OUT+(%E4%BA%95%E5%8F%A3%E9%81%94%E4%B9%9F%E3%81%BF%E3%81%9A%E3%81%9F%E3%81%BE%E3%81%93%E3%81%A8%E3%81%AE%E6%BC%AB%E7%94%BB) | https://natalie.mu/comic/news/498042 | https://realsound.jp/movie/2023/05/post-1330445.html/amp</t>
         </is>
       </c>
-      <c r="X49" s="2" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -6778,32 +6950,34 @@
           <t>ノリの良いボケと仲間の総ツッコミ、デフォルメ顔</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr">
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>技法：①強さ＝生き方のかっこよさと定義し直す ②ファッション性のある立ち絵でキャラを立てる。FLATUP案：『強さとは優しさであり、かっこよさである』を正面から掲げ、ジムウェアの着こなしや礼の仕方まで“かっこいい”と描く回</t>
         </is>
       </c>
-      <c r="U50" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・髪型、作中チームの名前とロゴ、独特の手描き文字表現をそのまま使わない</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
         <is>
           <t>[事実]少年画報社から講談社へ移籍して完結した長期連載。[感想]名言が多い、生き方を学んだという読者の声が多いと紹介される。X直接検索なし</t>
         </is>
       </c>
-      <c r="W50" s="2" t="inlineStr">
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000352330 | https://comic.k-manga.jp/title/54964/pv | https://ja.wikid.org/%E3%82%AE%E3%83%A3%E3%83%B3%E3%82%B0%E3%82%AD%E3%83%B3%E3%82%B0 | https://shopping.bookoff.co.jp/new/0016453183</t>
         </is>
       </c>
-      <c r="X50" s="2" t="inlineStr">
+      <c r="Z50" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="AA50" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -6907,30 +7081,40 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
+          <t>C：番長ものの原点として、仲間が集まる構図の参考程度</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
           <t>技法：主人公の器の大きさに敵が惚れて仲間になる構図、ジャンプ王道の原点として学ぶ。アイデア：ライバルジムの選手と試合後に握手し、合同練習を始める回。オリジナルの一言案「勝ったら、次は一緒に練習しよう」</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・学ラン姿・作中の対決の舞台設定を使わない</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
         <is>
           <t>[事実] 初期のジャンプを支えた作品として紹介され、2026年に全集刊行が発表されている。[推測] 若い世代の認知は低く、漫画史の文脈で語られることが多い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/%E7%94%B7%E4%B8%80%E5%8C%B9%E3%82%AC%E3%82%AD%E5%A4%A7%E5%B0%86-cg488ve8f | https://koubo.jp/press-release/prtimes/c11454_r871 | https://www.animenewsnetwork.com/encyclopedia/anime.php?id=2377</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7032,32 +7216,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr">
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>技法：『筋を通す』主人公の一途さを軸にした人情劇。オリジナル案：約束を必ず守るトレーナーが、会員との『次の練習も来る』という小さな約束を大事にする話。FLATUPでは極道・暴力の美化はしない</t>
         </is>
       </c>
-      <c r="U52" s="2" t="inlineStr">
+      <c r="W52" s="2" t="inlineStr">
         <is>
           <t>主人公の名前『本気（マジ）』、キャラ外見、極道組織名、作中台詞を真似しない。極道の美化はFLATUPの思想と合わない</t>
         </is>
       </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="X52" s="2" t="inlineStr">
         <is>
           <t>[事実]全50巻の長期作品で、続編『終章 火薬』がヤングチャンピオンで展開された。作者は画業50周年。[推測]任侠漫画の代表作の一つとされる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W52" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/43916/ | https://bookwalker.jp/series/5784/list/ | https://www.fujisan.co.jp/product/2682/b/1922497/</t>
         </is>
       </c>
-      <c r="X52" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7161,30 +7347,40 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
+          <t>A：不良を見捨てず話を聞く先生の描き方が、FLATUPの優しい指導者像に使える</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生／群像・矜持</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>技法：一人ずつ過去を掘り下げて仲間に加わる『一話一人』構成、指導者の熱さで場の空気が変わる演出。アイデア：やる気のない中学生グループに、トレーナーが本気でミットを持ち続ける話。オリジナルの一言案「夢は、汗をかいた分だけ近くなる」</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr">
+      <c r="W53" s="2" t="inlineStr">
         <is>
           <t>ニコガク（二子玉川学園）などの校名、教師・部員の外見や名前、ユニフォームのデザイン、象徴的な決め台詞、ロゴを使わない</t>
         </is>
       </c>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="X53" s="2" t="inlineStr">
         <is>
           <t>[事実] TVドラマ・映画が作られ、原作も含めて広く知られている。[感想] 不良が夢に向かう王道の熱さが泣けるという声が多い。[推測] ドラマから入った層も原作に流れている。X直接検索なし</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/rookies | https://ranking.net/items/b61011 | https://www.netoff.co.jp/detail/0001269654/</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
+      <c r="Z53" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="AA53" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7243,7 +7439,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2005年開始（終了年は未確認）</t>
+          <t>2005年開始（2019年のドラマ化に合わせて連載再開とする資料あり。終了年は未確認）</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -7288,30 +7484,40 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
+          <t>B：漫才のボケとツッコミのテンポが、ギャグの間の取り方の参考になる</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
           <t>技法：笑いの『間』をコマの余白で作る、ボケとツッコミの役割を固定してテンポを出す。アイデア：初心者会員とトレーナーのコンビによる、ゆるい掛け合いの4コマ。オリジナルの一言案「息切れも、立派なリアクションです」</t>
         </is>
       </c>
-      <c r="U54" s="2" t="inlineStr">
+      <c r="W54" s="2" t="inlineStr">
         <is>
           <t>コンビ名・キャラの外見・ネタの内容そのものを使わない。作中の漫才台本を再現しない</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="X54" s="2" t="inlineStr">
         <is>
           <t>[事実] 2019年にドラマ化され、ニュース記事で取り上げられた。[感想] お笑い芸人の苦しさがリアルだという声がある。[推測] ろくでなしBLUESやROOKIESの読者が作者つながりで読んでいる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>https://realsound.jp/movie/2019/04/post-353756.html | https://honcierge.jp/articles/shelf_story/7835 | https://bookwalker.jp/series/480759/</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>https://realsound.jp/movie/2019/04/post-353756.html | https://honcierge.jp/articles/shelf_story/7835 | https://bookwalker.jp/series/480759/ | https://comic.k-manga.jp/title/100220</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7413,32 +7619,34 @@
           <t>主人公の小心さや勘違いを起点にした間の抜けたリアクション、シリアスな場面直後の脱力コマ</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr">
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>技法：文字（ルビ）の演出でキャラの格を上げる手法、気弱な主人公が怖がりながら前に出る『震える一歩』の描写。オリジナル案：ジムの初心者が初スパーで足が震えつつも『怖いままでいい、一回だけ前へ』と自分に言い聞かせる回。ルビ演出はFLATUP独自の造語（例：『優しさ』に独自の読みを振る）で行い、原作の当て字は使わない</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr">
+      <c r="W55" s="2" t="inlineStr">
         <is>
           <t>原作の当て字ルビの具体例・決め台詞、登場チーム名（族名）・特攻服の刺繍デザイン、主人公の髪型や外見、特定の改造バイクのデザインを真似しない</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="X55" s="2" t="inlineStr">
         <is>
           <t>[事実]連載終了25周年記念の復刻版が刊行され、根強い需要がある。[感想]独特のルビ文体がネットで頻繁にネタ化・パロディ化され、『読める人を選ぶ』と語られることが多い。[推測]ヤンキー漫画の『様式美』の代表として世代を超えて知名度がある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W55" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/titles/1000005685 | https://mangapedia.com/疾風伝説特攻の拓-645eremzo | https://game.watch.impress.co.jp/docs/news/1505517.html</t>
         </is>
       </c>
-      <c r="X55" s="2" t="inlineStr">
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7540,32 +7748,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr">
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>技法：本編の人気キャラの『過去編』で厚みを出すスピンオフの作り方。オリジナル案：FLATUPのトレーナーが格闘技を始める前の弱かった時代を描く短編を作り、本編の初心者に寄り添う理由を後から明かす</t>
         </is>
       </c>
-      <c r="U56" s="2" t="inlineStr">
+      <c r="W56" s="2" t="inlineStr">
         <is>
           <t>本編同様、ルビ表現・キャラ外見・族名・特攻服デザインを流用しない</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
         <is>
           <t>[事実]月刊ヤングマガジンで『復活』と宣伝された外伝である。[推測]本編ファン向けの位置づけ。X直接検索なし</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000016386 | https://www.kodansha.co.jp/comic/products/0000016037</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -7667,32 +7877,34 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T57" s="2" t="inlineStr">
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>技法：『あの頃の不良が大人になったら』という時間経過の設定で、強さの意味を問い直す続編構成。オリジナル案：昔ケンカに明け暮れた元ヤンが、30代でFLATUPに入会し『殴るためじゃなく守るための強さ』を学び直す話</t>
         </is>
       </c>
-      <c r="U57" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>本編キャラクターの成長後の姿・設定、族名、ルビ表現を流用しない</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>[事実]作画者が所十三から桑原真也に交代している。[推測]作画交代について本編ファンの間で賛否があると思われる（未検証）。X直接検索なし</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/new-releases?page=396 | https://booklive.jp/focus/author/a_id/96124 | https://wowma.jp/item/535774719 | https://en.wikipedia.org/wiki/Kaze_Densetsu:_Bukkomi_no_Taku</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -7796,32 +8008,42 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
+          <t>C：チームの誇りを描く群像として参考程度で、暴走族への憧れは描かない</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
           <t>技法：弱小グループが仲間を集めて強くなる成長ものの型。アイデア：会員が少ない平日の朝クラスに、少しずつ常連が増えていく話。オリジナルの一言案「最初は三人。でも、三人いれば始められる」</t>
         </is>
       </c>
-      <c r="U58" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>チーム名（虎武羅、輪蛇など）・特攻服のデザイン・キャラの外見を使わない。暴走行為を美化しない</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
         <is>
           <t>[推測] 湘南爆走族の作者による暴走族漫画として根強いファンがいる。具体的な評判は確認できず。X直接検索なし</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000013978 | https://www.cmoa.jp/title/55531</t>
-        </is>
-      </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000013978 | https://www.cmoa.jp/title/55531 | https://www.kodansha.co.jp/comic/products/0000013924 | https://movie.jorudan.co.jp/film/38436/</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -7923,30 +8145,40 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
+          <t>C：抗争中心の続編で、参考程度</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
           <t>技法：長い抗争の決着をつける完結編の構成（伏線の回収）。アイデア：シリーズの最終回で、初回に登場した初心者が今度は新人を迎える側になる。オリジナルの一言案「次は、お前が背中を見せる番だ」</t>
         </is>
       </c>
-      <c r="U59" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>チーム名（虎武羅、輪蛇）・主人公の名前と外見・湘南の具体的なたまり場設定を使わない</t>
         </is>
       </c>
-      <c r="V59" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>[推測] 本編の読者向けの完結編として読まれている。具体的な評判は確認できず。X直接検索なし</t>
         </is>
       </c>
-      <c r="W59" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/55531 | https://mangapedia.com/%E8%8D%92%E3%81%8F%E3%82%8CKNIGHT%E9%BB%92%E3%81%84%E6%AE%8B%E9%9F%BF%E5%AE%8C%E7%B5%90%E7%B7%A8-3wub7jslw</t>
         </is>
       </c>
-      <c r="X59" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y59" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8020,7 +8252,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>天使な小生意気、道士郎でござる、カナカナ（同じ作者）。2018年にTVドラマ化、2020年に劇場版。2018年に週刊少年サンデーSで続編が掲載されたとする記事あり（正式タイトル・詳細は未確認）</t>
+          <t>天使な小生意気、道士郎でござる、カナカナ（同じ作者）。2018年にTVドラマ化、2020年に劇場版。2018年に週刊少年サンデーSで続編の連載を開始したとする資料あり（正式タイトルは未確認）</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -8050,30 +8282,40 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
+          <t>A：シリアスに始めて脱力でオトす落差のギャグが、そのまま手本になる</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
           <t>技法：シリアスとギャグの顔を同じページで切り替える落差、ずるいけど憎めない主人公像。アイデア：口だけは強気な新入会員が、スパーで逃げ回りながらも最後に一歩前に出る話。オリジナルの一言案「逃げ足も、フットワークのうちだろ？」</t>
         </is>
       </c>
-      <c r="U60" s="2" t="inlineStr">
+      <c r="W60" s="2" t="inlineStr">
         <is>
           <t>金髪パーマ・ツンツン頭の二人組の外見、軟高・開久など校名、主人公の決めポーズや有名な口ぐせ、作品ロゴを使わない。ドラマ版の衣装や演出も参照しない</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>[事実] 2018年のドラマ化、2020年の映画化で再ブームになったと報じられている。[事実] 累計発行部数4000万部超とする記事あり。[感想] 笑えるヤンキー漫画の代表として推す声が多い。[推測] ドラマ世代の若年層にも認知が広がった。X直接検索なし</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>https://realsound.jp/book/2020/07/post-593760.html | https://natalie.mu/eiga/news/275565 | https://kai-you.net/article/51920 | https://ranking.net/items/337fd6</t>
-        </is>
-      </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>https://realsound.jp/book/2020/07/post-593760.html | https://natalie.mu/eiga/news/275565 | https://kai-you.net/article/51920 | https://ranking.net/items/337fd6 | https://rank-king.jp/article/24605</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8177,30 +8419,40 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
+          <t>A：弱い少年が個性的な師匠たちのもとで修行し、守るために強くなる流れがFLATUPの思想に近い</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
           <t>技法：『怖い修行』を笑いで包んで読者の心理的ハードルを下げる。多様な格闘技を師匠ごとに担当させる構成。オリジナル案：FLATUPの各クラス担当コーチが、それぞれのやり方で初心者を見守る群像。セリフ案『強くなるのは、守りたいものができたときだ』。※実際の練習は安全第一で、無茶な修行は描写上の誇張に留める。</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>梁山泊という道場名と達人6人の構成・外見、作中の流派名や必殺技名、ヒロインの外見を使わない。</t>
         </is>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>[事実] TVアニメ化され、2026年に続編連載が発表された。[感想] 武術の解説と熱いバトル、ギャグのバランスが好評。[推測] 終盤の駆け足展開に不満を持つ読者もいるとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E5%8F%B2%E4%B8%8A%E6%9C%80%E5%BC%B7%E3%81%AE%E5%BC%9F%E5%AD%90%E3%82%B1%E3%83%B3%E3%82%A4%E3%83%81 | https://news.denfaminicogamer.jp/news/260129c | https://dengekionline.com/article/202601/64507</t>
         </is>
       </c>
-      <c r="X61" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8304,30 +8556,40 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
+          <t>B：顔芸や独特の擬音など大真面目な誇張は劇画パロディに使えるが、暴力描写は避ける</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
           <t>技法：キャラの口癖や言い回しでキャラを強く立たせる。オリジナル案：FLATUP独自の『あいさつの口癖』を持つキャラを作り、会員がまねしたくなる言葉にする。</t>
         </is>
       </c>
-      <c r="U62" s="2" t="inlineStr">
+      <c r="W62" s="2" t="inlineStr">
         <is>
           <t>灘神影流という流派名と技名、主人公・父の外見、作中の独特な言い回し（ネットで『語録』化しているもの）を使わない。</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>[事実] シリーズ累計1600万部超とされる。[感想] ネットで作中の言い回しが『語録』としてネタ化され、新しい読者層を得ている。[推測] 本気の格闘漫画とネタ漫画の両面で楽しまれているとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>https://ranking.net/items/48e26a | https://dic.pixiv.net/a/タフ語録 | https://news.denfaminicogamer.jp/news/231225v</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="AA62" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8381,7 +8643,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>未確認（レーベルはチャンピオンREDコミックス）</t>
+          <t>チャンピオンRED（紹介記事・電子書店の掲載情報による。レーベルはチャンピオンREDコミックス）</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -8431,30 +8693,40 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
+          <t>B：根性で理屈を超える誇張と暴走族キャラの空気は劇画パロディに使えるが、暴走族への憧れは描かない</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
           <t>技法：才能ではなく『あきらめない心』を主役にする。ただしFLATUPでは不良性は採らず、『折れない＝やめない』として描く。FLATUP案：運動が苦手な会員が、半年休まず通ったことを表彰される回。</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>柴千春の外見（特攻服・リーゼント）、暴走族チーム名、当て字の決め文句を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]根性キャラの外伝として人気という声がある。[推測]不良漫画ファンにも届く作品。</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/series/12494 | https://www.akitashoten.co.jp/comics/4253322611 | https://www.akitashoten.co.jp/comics/4253322638</t>
-        </is>
-      </c>
-      <c r="X63" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/series/12494 | https://www.akitashoten.co.jp/comics/4253322611 | https://www.akitashoten.co.jp/comics/4253322638 | https://koubo.jp/article/80136 | https://ndlsearch.ndl.go.jp/books/R100000002-I033430881</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -8538,7 +8810,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>未確認（取材者の視点で主人公像を描く構成とされる）</t>
+          <t>（紹介記事による）フリーライターが主人公の伝説を本にするため取材する構成で、本人ではなく周囲の人物の証言から主人公像を浮かび上がらせる。</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8558,30 +8830,40 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
+          <t>B：取材者の証言で人物の伝説を浮かび上がらせる構成は使えるが、内容の詳細が未確認</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／群像・矜持</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
           <t>技法：インタビュー形式で主人公を語る構成。FLATUP案：入会1年の会員を、記者役のAIKAが取材して振り返るドキュメント風エピソード。</t>
         </is>
       </c>
-      <c r="U64" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>柴千春・花山薫ら固有キャラ、特攻服などの衣装を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V64" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[推測]2026年開始の新作で評判は未確認。</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cmoa.jp/title/111502/</t>
-        </is>
-      </c>
-      <c r="X64" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cmoa.jp/title/111502/ | https://koubo.jp/article/80136</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y64" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8685,30 +8967,40 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
+          <t>B：ギャグとアクロバットな格闘を混ぜるテンポが部分的に使える</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
           <t>技法：動きの頂点を見開きで止める『決め』、勢いで押し切るテンションの作り方。アイデア：体操経験のある会員が、前転やブリッジの動きを格闘技のウォームアップに活かす回。オリジナルの一言案「体がやわらかいと、ケガもしにくいんだよ」</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr">
+      <c r="W65" s="2" t="inlineStr">
         <is>
           <t>主人公の長身女子高生の外見・新体操技を使った格闘スタイルという設定・ランキングバトルの仕組み・キャラ名を使わない</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>[事実] 2003年にTVアニメ化。アニメは原作に追いつきオリジナルの結末になったとされる。[感想] 主人公がかっこいい、勢いがすごいという声がある一方、画力やストーリーより熱量で読む作品という評もある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>https://www.weblio.jp/content/Air+Master | https://renote.net/articles/6670 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=5090 | https://mangapedia.com/%E3%82%A8%E3%82%A2%E3%83%9E%E3%82%B9%E3%82%BF%E3%83%BC-4cujdz939</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8812,30 +9104,40 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
+          <t>B：トレーナーと選手の掛け合いや下町の人情は使えるが、悲劇的な結末の重さは避ける</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／劇画ヤンキー</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
           <t>技法：セリフなしのコマを続けて『言えない気持ち』を表現する。荒れた少年が人に必要とされて変わる流れ。オリジナル案：成田の商店街の子どもたちが、ぶっきらぼうな新人インストラクターを少しずつ慕っていく話。セリフ案『強いのは、誰かのために立てるやつだ』。</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr">
+      <c r="W66" s="2" t="inlineStr">
         <is>
           <t>主人公の帽子とマフラー姿などの外見、クロスカウンターなど作中を象徴する技の演出、丹下ジムの名称、眼帯のトレーナー像、最終回の象徴的なラストシーンを再現しない。</t>
         </is>
       </c>
-      <c r="V66" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>[事実] 単行本累計2000万部超とされ、アニメ・実写映画化された。[感想] ボクシング漫画の原点・金字塔として世代を超えて名前が挙がる。[推測] 若い読者には絵柄や時代背景の古さで手に取りにくい面があるとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W66" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
         <is>
           <t>https://ranking.net/items/e9817e | https://bunshun.jp/articles/-/52672 | https://www.kodansha.co.jp/comic/products/0000185790</t>
         </is>
       </c>
-      <c r="X66" s="2" t="inlineStr">
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y66" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -8939,30 +9241,40 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
+          <t>A：いじめられっ子が基本の練習を積み重ねて自信をつける心理描写が、初心者の物語にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／群像・矜持</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
           <t>技法：『基本の繰り返しが強さになる』ことを図解的に描く。不安な心をモノローグで正直に。オリジナル案：路上ではなく『ジム』が居場所になる物語として反転させる。暴力ではなく練習で自信を得る主人公。セリフ案『ここでは殴り合いじゃなく、教え合いをするんだ』。</t>
         </is>
       </c>
-      <c r="U67" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>主人公の外見（細身・パーカー姿など）、『ヤンキー狩り』という異名設定、作中の具体的な街の勢力構図を使わない。</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>[事実] ドラマ化・韓国ドラマ化された。[感想] 格闘技の基本や心理描写がリアルで、実際に格闘技を始めるきっかけになったという声がある。[推測] いじめ経験者の共感を集めやすい作品とみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Holyland_(manga) | https://ranking.net/items/5ef283 | https://www.cmoa.jp/title/9432/</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9066,30 +9378,40 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
+          <t>A：不良同士のバカなやりとりと勘違いギャグが、ヤンキー妄想ネタにすぐ使える</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／劇画ヤンキー</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
           <t>技法：不良ギャグとムエタイを組み合わせ、怖い格闘技をノリで親しみやすくする。オリジナル案：ケンカで有名な少年がジムで『首相撲』を教わり、ケンカより練習のほうが面白いと気づく話。セリフ案『肘と膝は、ルールの中で使うからかっこいいんだ』。</t>
         </is>
       </c>
-      <c r="U68" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・髪型、タイトルの『破壊王』フレーズ、作中の技名を使わない。</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>[事実] 1990年代の週刊少年マガジンで約3年連載された。[感想] ムエタイを扱った不良格闘漫画として懐かしむ声。[推測] 当時の読者中心の知名度とみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>https://id.ndl.go.jp/auth/ndlna/00408410 | https://mangapedia.com/%E5%88%83%E6%A3%AE%E5%B0%8A-aiqyh1iy5 | https://www.cmoa.jp/title/142327/ | https://www.kodansha.co.jp/comic/products/0000011066</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -9193,30 +9515,40 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
+          <t>B：不器用な主人公の空手部での成長とギャグの混ぜ方が部分的に使える</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
           <t>技法：『ケンカの強さ』と『武道の強さ』の対比。FLATUPの『不良は嫌い、強さは優しさ』に直結。オリジナル案：元ヤンの新入会員が、ルールと礼を学んで初めて『ありがとう』を言える回</t>
         </is>
       </c>
-      <c r="U69" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見、作中の学校名・部名は使わない</t>
         </is>
       </c>
-      <c r="V69" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>[事実]伝統派空手の組手を描く珍しい作品として紹介されている（X直接検索なし） [事実]作者は2013年に逝去</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>https://pedia.3rd-in.co.jp/wiki/ハンザスカイ | https://www.cmoa.jp/title/51347/vol/5/ | https://mangapedia.com/gd/dgl9yawxg</t>
         </is>
       </c>
-      <c r="X69" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y69" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9320,30 +9652,40 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
+          <t>C：不良校の空手部の喧嘩ものとして参考程度で、暴力描写は避ける</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
           <t>技法：『弱い主人公が怖い場所に飛び込む』導入。FLATUPでは逆に『怖くない場所』を描く対比素材として使う。オリジナル案：怖そうな見た目のコーチが実は一番やさしいギャップ回</t>
         </is>
       </c>
-      <c r="U70" s="2" t="inlineStr">
+      <c r="W70" s="2" t="inlineStr">
         <is>
           <t>校名・通称、主人公の名前と外見、部の固有の上下関係ルールは使わない</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="X70" s="2" t="inlineStr">
         <is>
           <t>[事実]長期連載作として電子版で再刊されている（X直接検索なし） [推測]不良漫画と空手漫画の両方の読者層がいる</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="Y70" s="2" t="inlineStr">
         <is>
           <t>https://mangapedia.com/gd/dgl9yawxg | https://mechacomic.jp/books/275438 | https://www.allcinema.net/cinema/pdf/88612</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="Z70" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="AA70" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9407,7 +9749,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>全42巻（ジャンプコミックス）。文庫版など他の版の巻数は未確認</t>
+          <t>全42巻（ジャンプコミックス）、文庫版全25巻（2002年12月〜2003年12月発売。古書店の書誌による）</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -9447,30 +9789,40 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
+          <t>A：見た目は怖い主人公が仲間思いで、ボクシングの描写と不良の群像を一緒に学べる</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
           <t>技法：激しい場面の直後に日常の小ネタを置く緩急、敵役にも背景を与えて和解させる構成。アイデア：ジムに来た元ケンカ自慢の高校生が、ミット打ちで初めて『誰も傷つけない強さ』を知る回。オリジナルの一言案「殴る相手はミットだけでいい」</t>
         </is>
       </c>
-      <c r="U71" s="2" t="inlineStr">
+      <c r="W71" s="2" t="inlineStr">
         <is>
           <t>主人公の髪型・学ラン姿・帝拳高校などの校名、四天王という構図、ボクシングジムの名前や固有キャラの関係性をそのまま使わない。作品ロゴの書体も真似しない</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>[事実] ジャンプ黄金期の代表的な不良漫画として、ランキング・まとめサイトで頻繁に取り上げられている。[感想] 喧嘩だけでなく友情や恋愛の青春ものとして好きだという声が多い。[推測] 1990年代に読んだ世代の懐かし需要が今も強い。X直接検索なし</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>https://renote.net/reviews/7277 | https://ranking.net/items/82e959 | https://www.toy-people.com/jp/?p=106622</t>
-        </is>
-      </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>https://renote.net/reviews/7277 | https://ranking.net/items/82e959 | https://www.toy-people.com/jp/?p=106622 | https://shopping.bookoff.co.jp/s/8800007740</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9574,30 +9926,40 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
+          <t>A：ヘタレな主人公と強面の先輩の意外な一面という落差ギャグが、優しい強面キャラ作りに使える</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／強面の先生</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
           <t>技法：ヘタレ主人公が笑いを取りながら少しずつ強くなる構成。空手からキックへの転向で技術の違いを描く。オリジナル案：別競技経験者がFLATUPのキックで『足の使い方が違う！』と驚く回。</t>
         </is>
       </c>
-      <c r="U72" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見、作中の空手部や道場名、お色気シーンの演出をそのまま使わない（FLATUPのブランド方針とも合わない）。</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>[事実] 12年続き全50巻の長期連載。[感想] 後半はキック漫画として楽しめるという紹介がある。[推測] お色気要素の評価は分かれるとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000381750 | https://www.kodansha.co.jp/comic/products/0000016049 | https://kick-times.com/archives/1363</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -9701,30 +10063,40 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
+          <t>B：強がる主人公の不器用な優しさと、コメディとシリアスの切り替えが学べる</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
           <t>技法：見た目と中身のギャップをキャラの核にする、表情の振り幅で笑いと迫力を両立。アイデア：小柄で控えめな女性会員が、ミット打ちで驚くほどいい音を鳴らし周りがざわつく回。オリジナルの一言案「小さいって、懐に入りやすいってことよ」</t>
         </is>
       </c>
-      <c r="U73" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>主人公の髪型・セーラー服姿・魔法で姿が変わったという設定、取り巻きの名前やリーゼントの見た目、作品ロゴを使わない</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>[事実] 小学館漫画賞受賞、TVアニメ化されている。[感想] ギャップのある女子主人公がかっこいいという声がある。[推測] 今日から俺は!!のファンが作者つながりで読む流れがある。X直接検索なし</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>https://www.kinokuniya.co.jp/f/dsg-08-9975735622 | https://mangapedia.com/西森博之-kuh704g21 | https://anime.eiga.com/program/101293/ | https://ja.wikid.org/%E5%A4%A9%E4%BD%BF%E3%81%AA%E5%B0%8F%E7%94%9F%E6%84%8F%E6%B0%97</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9798,7 +10170,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>続編『1・2の三四郎2』（講談社。掲載誌・巻数は未確認）／柔道部物語（同作者）</t>
+          <t>続編『1・2の三四郎2』全6巻（ヤンマガKCスペシャル、講談社、1995年3月〜1998年7月刊。掲載誌は未確認）／柔道部物語（同作者）</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -9828,30 +10200,40 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
+          <t>B：ギャグと格闘技の真剣勝負を行き来する構成が部分的に使える</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
           <t>技法：ギャグとシリアスの切り替えで『普段ゆるい人がやる時はやる』を見せる。オリジナル案：いつもふざけているキッズ会員が昇級審査の時だけ真顔になる話</t>
         </is>
       </c>
-      <c r="U74" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>主人公3人組の外見・役割配置、プロレス団体名やリングネームは使わない</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>[事実]小林まことの代表作として紹介される（X直接検索なし） [感想]昭和ギャグ格闘漫画の名作という声 [推測]若い世代の知名度は高くない</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>https://www.cmoa.jp/title/2497 | https://pedia.3rd-in.co.jp/wiki/1%E3%83%BB2%E3%81%AE%E4%B8%89%E5%9B%9B%E9%83%8E | https://eiga.com/movie/34785/</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -9910,7 +10292,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>未確認（高校生編は完結）</t>
+          <t>2016–2023（イブニング2016年17号〜。同誌休刊に伴い2023年にコミックDAYSへ移籍。高校生編は第15巻で完結）</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -9955,30 +10337,40 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
+          <t>B：実在の選手の経験に基づく稽古と成長の描写が部分的に使える</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
           <t>技法：『未経験女子が始める』を実話の手触りで描く。オリジナル案：運動未経験の女子大生が、受け身ができた日に家族へ写真を送る話</t>
         </is>
       </c>
-      <c r="U75" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・名前、作中の高校名、作画者特有のキャラデザを真似しない</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>[事実]柔道漫画ランキング記事で紹介されている（X直接検索なし） [感想]初心者目線で読みやすいという声</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/JJM:_Joshi_Judou-bu_Monogatari | https://mangapedia.com/JJM%E5%A5%B3%E5%AD%90%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E-chmf735o5 | https://www.cmoa.jp/title/124103</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10082,30 +10474,40 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
+          <t>C：社会人になってからの競技生活の描き方の参考程度</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
           <t>技法：『大人になってからも続ける』物語。オリジナル案：仕事帰りに週1で通う会員が、疲れていても道場に来ると元気になる理由を見つける話</t>
         </is>
       </c>
-      <c r="U76" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・名前、実在企業や実業団名は使わない</t>
         </is>
       </c>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>[推測]高校生編の読者が続けて読んでいる（X直接検索なし、評判は未確認）</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/titles/1000046074 | https://www.kodansha.co.jp/comic/products/0000393085 | https://mangapedia.com/JJM%E5%A5%B3%E5%AD%90%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E%E7%A4%BE%E4%BC%9A%E4%BA%BA%E7%B7%A8-72waebp36</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -10209,30 +10611,40 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
+          <t>C：非常識な天才の描き方は参考になるが、ブラックな作風はFLATUPと合わない</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
           <t>技法：生々しい会話で人物をリアルに立たせる。オリジナル案：自信満々で入会した若者が、基礎の大切さに気づき、礼儀を覚えて化けていく話。セリフ案『才能はスタート地点。続ける人がゴールに行く』。</t>
         </is>
       </c>
-      <c r="U77" s="2" t="inlineStr">
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見・板前志望からボクサーへの経歴、ライバル王者の造形を流用しない。</t>
         </is>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>[事実] 掲載誌の休刊で終了し続編へ移ったとされる。[感想] 作家性の強いボクシング漫画として評価する声。[推測] 一般知名度は高くないがマニア人気が高いとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/t/a/sugar%28%E6%96%B0%E4%BA%95%E8%8B%B1%E6%A8%B9%29 | https://mangapedia.com/%E3%82%B7%E3%83%A5%E3%82%AC%E3%83%BC-0du0d3nk0 | https://booklive.jp/focus/author/a_id/3681</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10281,12 +10693,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>講談社</t>
+          <t>講談社（ヤンマガKCスペシャル）／電子版はSMART COMICS（版により異なる）</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>未確認（ヤングマガジンアッパーズ休刊後に再開とされる）</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -10296,7 +10708,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>全4巻（電子書籍版の表記）</t>
+          <t>全4巻（完結）／『シュガー&amp;RIN』合本版 全5巻（電子）</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -10336,30 +10748,40 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
+          <t>C：前作の続きで作風が重く、参考程度</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
           <t>技法：大舞台の前の静けさを余白で表す。オリジナル案：初めての大会前夜、眠れない会員にコーチが電話で話す短編。</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>主人公・王者の名前と外見、世界ライト級戦という具体的な構図の流用を避ける。</t>
         </is>
       </c>
-      <c r="V78" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>[事実] 全4巻完結とされる。[感想] 前作ファンが続きを追う作品として語られる。[推測] 前作以上にマニア向けとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>https://bookwalker.jp/series/443916/list/ | https://www.cmoa.jp/title/280426/ | https://mangapedia.com/%E6%96%B0%E4%BA%95%E8%8B%B1%E6%A8%B9-o4gp3a9ch</t>
-        </is>
-      </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>https://bookwalker.jp/series/443916/list/ | https://www.cmoa.jp/title/280426/ | https://mangapedia.com/%E6%96%B0%E4%BA%95%E8%8B%B1%E6%A8%B9-o4gp3a9ch | https://www.cmoa.jp/title/109755</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10463,30 +10885,40 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
+          <t>B：小市民の主人公が強面たちに振り回されるリアクション芸は使えるが、試合描写は過激</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
           <t>技法：『普通の大人の目線』を狂言回しにして格闘技の世界を見せる。オリジナル案：会社帰りのサラリーマン会員が、自分の中の強さに気づく話。セリフ案『肩書きを脱いだら、ここではただの一年生』。</t>
         </is>
       </c>
-      <c r="U79" s="2" t="inlineStr">
+      <c r="W79" s="2" t="inlineStr">
         <is>
           <t>主人公の外見、拳願仕合という制度名、作中の企業名・技名・流派名を使わない。</t>
         </is>
       </c>
-      <c r="V79" s="2" t="inlineStr">
+      <c r="X79" s="2" t="inlineStr">
         <is>
           <t>[事実] Netflixでアニメ化された。[感想] 多彩なキャラと試合のテンポが好評。[推測] 海外ファンも多いとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr">
+      <c r="Y79" s="2" t="inlineStr">
         <is>
           <t>https://renote.net/reviews/7866 | https://eiga.com/news/20180408/8/ | https://en.wikipedia.org/wiki/Kengan_Ashura</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10550,7 +10982,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>既刊33巻以上（33巻は2026年6月配信。34巻は未確認）</t>
+          <t>既刊34巻（2026年9月時点。英語版Wikipediaと電子書店による。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -10590,30 +11022,40 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
+          <t>C：強面キャラのギャップ以外は参考程度</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
           <t>技法：前作ファンと新規読者の両方に向けた世代交代の作り方。オリジナル案：初代会員と新入会員がペアを組んで練習する回。</t>
         </is>
       </c>
-      <c r="U80" s="2" t="inlineStr">
+      <c r="W80" s="2" t="inlineStr">
         <is>
           <t>キャラの外見、作中組織名・技名を使わない。</t>
         </is>
       </c>
-      <c r="V80" s="2" t="inlineStr">
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>[事実] 2019年から連載が続いている。[感想] 前作キャラの再登場を喜ぶ声。[推測] 前作ほどの勢いではないとの評価もあるとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Kengan_Ashura | https://dengekionline.com/articles/109227 | https://bookwalker.jp/de33e41bcf-5f0f-4e5d-975d-38fe97798f21/</t>
-        </is>
-      </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kengan_Ashura | https://dengekionline.com/articles/109227 | https://bookwalker.jp/de33e41bcf-5f0f-4e5d-975d-38fe97798f21/ | https://bookwalker.jp/series/192695/list/</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10677,7 +11119,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>シリーズ通算130巻超（第9部『The JOJOLands』は通算第132巻〜。最新巻は未確認）</t>
+          <t>シリーズ通算140巻（第9部『The JOJOLands』9巻が2026年9月17日発売。同8巻を通算139巻とする資料による。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10717,30 +11159,40 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
+          <t>B：擬音の文字とキメポーズの誇張は使えるが、作品を強く連想させる要素は避ける</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>奇妙な冒険</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
           <t>①シリーズを「部」に分け、主人公が代替わりしても「やさしい強さ」が受け継がれる構成にする。②解説役が、マサキの半歩の意味（重心を読む、ケガをさせない）を大げさに解説する。③背景いっぱいの擬音の文字と、オリジナルのキメポーズ。オリジナル案：「震えるぜミット！ 鳴り響くほどビート!!」（※匂わせが強いので公開前に要確認）</t>
         </is>
       </c>
-      <c r="U81" s="2" t="inlineStr">
+      <c r="W81" s="2" t="inlineStr">
         <is>
           <t>原作の名ゼリフそのもの（有名な決めゼリフ、叫び声、口ぐせ）、『スタンド』などの固有の用語、キャラクターの外見・衣装・特定のポーズの再現、作品名・ロゴ・書体は使わない。擬音やポーズは、作品を特定できない一般的な形にする</t>
         </is>
       </c>
-      <c r="V81" s="2" t="inlineStr">
+      <c r="X81" s="2" t="inlineStr">
         <is>
           <t>[事実] 1987年から続く長期シリーズで、部ごとに主人公と舞台が替わる。 [感想] 独特のセリフ回しと擬音、立ちポーズがネットミームとして広く親しまれている。 X直接検索なし</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rere.jp/359256/ | https://dic.nicovideo.jp/a/%E3%82%B8%E3%83%A7%E3%82%B8%E3%83%A7%E3%81%AE%E5%A5%87%E5%A6%99%E3%81%AA%E5%86%92%E9%99%BA | https://news.mynavi.jp/article/20230323-2622596/</t>
-        </is>
-      </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rere.jp/359256/ | https://dic.nicovideo.jp/a/%E3%82%B8%E3%83%A7%E3%82%B8%E3%83%A7%E3%81%AE%E5%A5%87%E5%A6%99%E3%81%AA%E5%86%92%E9%99%BA | https://news.mynavi.jp/article/20230323-2622596/ | https://hmv.co.jp/news/article/2104051017/ | https://jojowiki.com/Volume_139</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10844,30 +11296,40 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
+          <t>C：前作と同じ誇張の参考程度で、内容は過激</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
           <t>技法：家族の因縁を軸にした長期ドラマ構成。オリジナル案：親子で入会した家族が、互いの頑張りを見て関係が変わる短編。</t>
         </is>
       </c>
-      <c r="U82" s="2" t="inlineStr">
+      <c r="W82" s="2" t="inlineStr">
         <is>
           <t>流派名・技名・キャラの外見・語録化した言い回しを使わない。</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="X82" s="2" t="inlineStr">
         <is>
           <t>[事実] 『高校鉄拳伝タフ』の続編。[感想] 衝撃的な展開がネットでネタにされることが多い。[推測] シリーズ全体で熱心なファンが多いとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="Y82" s="2" t="inlineStr">
         <is>
           <t>https://ranking.net/items/48e26a | https://bookwalker.jp/de0a604124-940e-46f8-9adc-bc6deee96a2a/ | https://www.goodreads.com/series/364786</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="Z82" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -10971,30 +11433,40 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
+          <t>C：誇張表現の参考程度</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
           <t>技法：前作主人公を『先輩・師』として新主人公を導かせる世代交代の構成。オリジナル案：古参会員が新しい会員を自然と面倒見る『バトン』の物語。</t>
         </is>
       </c>
-      <c r="U83" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>主人公たちの外見、流派名、出生の秘密などの設定、語録化した言い回しを使わない。</t>
         </is>
       </c>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>[事実] 2025年9月に完結し、『TOUGH 第二章』へ続いた。[感想] シリーズ恒例の展開をネタ込みで楽しむ読者が多い。[推測] 新規読者より既存ファン中心とみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>https://booklive.jp/bkmr/comic_m_completed_202509 | https://natalie.mu/comic/news/672517 | https://bookwalker.jp/series/513852/</t>
         </is>
       </c>
-      <c r="X83" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -11068,7 +11540,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>続編『リングにかけろ2』（スーパージャンプ、2000年または2001年開始・巻数は未確認）、TVアニメ（2004年〜）。同作者の『聖闘士星矢』『風魔の小次郎』『男坂』</t>
+          <t>続編『リングにかけろ2』（スーパージャンプ、2001年開始。巻数は未確認）、TVアニメ（2004年〜）。同作者の『聖闘士星矢』『風魔の小次郎』『男坂』</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -11098,30 +11570,40 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
+          <t>B：必殺技の大げさな見せ方は誇張ギャグに使えるが、現実の技術描写には使えない</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>奇妙な冒険／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
           <t>技法：一つの技を『名前＋ポーズ＋背景』でブランド化する見せ方。オリジナル案：FLATUPの基本コンビネーションを、子どもたちが自分で名前をつけて覚える回（安全な基本技のみ）。</t>
         </is>
       </c>
-      <c r="U84" s="2" t="inlineStr">
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>作中の必殺技名（ブーメランなど）とその背景演出、黄金のジュニアなどチーム名、主人公と姉のキャラ造形を使わない。</t>
         </is>
       </c>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>[事実] 大ヒットし集英社の社屋建て替えに貢献したと語られる。[感想] リアルなボクシングから必殺技バトルへ転じた作品として語り草。[推測] 後のジャンプ式トーナメントバトルの原型と見る声が多い。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E8%BB%8A%E7%94%B0%E6%AD%A3%E7%BE%8E | https://gendai.media/articles/-/99299 | https://bunshun.jp/articles/-/44683 | https://nlab.itmedia.co.jp/research/articles/190504/</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -11185,7 +11667,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>全31巻（講談社コミックス）／文庫版・超合本版あり（巻数未確認）</t>
+          <t>全31巻（講談社コミックス）／超合本版 全7巻（電子のみ、2020年配信）／文庫版あり（巻数未確認）</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -11225,30 +11707,40 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
+          <t>B：のんきな日常と戦いの鬼気迫る姿の落差、技の説明の演出は使える</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
           <t>技法：対戦相手にも人生の背景を与え、どちらにも感情移入させる。FLATUP案：大会で初心者会員が戦う相手にも『家族に見せたい』理由があると描き、勝ち負けより互いの礼で締める。</t>
         </is>
       </c>
-      <c r="U85" s="2" t="inlineStr">
+      <c r="W85" s="2" t="inlineStr">
         <is>
           <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。</t>
         </is>
       </c>
-      <c r="V85" s="2" t="inlineStr">
+      <c r="X85" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]講談社漫画賞を受賞したとの記載が二次情報にある（要確認）。[感想]格闘漫画の名作として挙げる声が多い。[推測]長期休載を経た続編で再評価された。</t>
         </is>
       </c>
-      <c r="W85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000033723 | https://www.kodansha.co.jp/comic/products/0000346993 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
-        </is>
-      </c>
-      <c r="X85" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000033723 | https://www.kodansha.co.jp/comic/products/0000346993 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80 | https://www.kodansha.co.jp/comic/products/0000346949</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11352,30 +11844,40 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
+          <t>C：前作の続きとして読む参考程度</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
           <t>技法：『帰ってくる』物語の作り方。FLATUP案：ケガで休会していた会員が復帰する日、仲間が名前を覚えていてくれた場面。オリジナル台詞案『おかえり。サンドバッグも待ってたよ』。</t>
         </is>
       </c>
-      <c r="U86" s="2" t="inlineStr">
+      <c r="W86" s="2" t="inlineStr">
         <is>
           <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。</t>
         </is>
       </c>
-      <c r="V86" s="2" t="inlineStr">
+      <c r="X86" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]長期休載後の再開を喜ぶ声が多かった。[推測]結末については賛否がある。</t>
         </is>
       </c>
-      <c r="W86" s="2" t="inlineStr">
+      <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000053262 | https://dic.nicovideo.jp/a/%E4%BF%AE%E7%BE%85%E3%81%AE%E9%96%80</t>
         </is>
       </c>
-      <c r="X86" s="2" t="inlineStr">
+      <c r="Z86" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y86" s="2" t="inlineStr">
+      <c r="AA86" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11439,7 +11941,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>既刊は資料により25〜27巻程度（正確な既刊数は未確認）／新装版（編ごと）あり</t>
+          <t>既刊26巻（月刊少年マガジンKC。第26巻 電子版 2025年10月配信。2026-10時点で確認）／新装版（講談社プラチナコミックス、編ごと）あり</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -11479,30 +11981,40 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
+          <t>C：時代ごとに主人公が替わる構成は参考になるが、内容は直接使いにくい</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
           <t>技法：1編完結の時代別オムニバス。FLATUP案：『昭和・平成・令和のFLATUP』のように、時代ごとの格闘技ジムの空気を描く短編シリーズ（実在人物は使わない）。</t>
         </is>
       </c>
-      <c r="U87" s="2" t="inlineStr">
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>陸奥圓明流などの固有流派名・技名、主人公の外見（細身・鋭い目）、一族が歴史の陰にいるという固有設定、決めゼリフを流用しない。実在の歴史人物と架空の流派を絡める構成をそのまま真似しない。</t>
         </is>
       </c>
-      <c r="V87" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2004年にTVアニメ化された（二次情報）。[感想]本編より好きという声もある。[推測]歴史好きにも読まれている。</t>
         </is>
       </c>
-      <c r="W87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000319630 | https://www.kodansha.co.jp/comic/products/0000325453 | https://www.hulu.jp/comic/series/103896</t>
-        </is>
-      </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000319630 | https://www.kodansha.co.jp/comic/products/0000325453 | https://www.hulu.jp/comic/series/103896 | https://bookwalker.jp/de0fbe921f-03e9-4e4b-a40e-e34d66d922ea/</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11606,30 +12118,40 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
+          <t>B：誇張した肉体表現と解説役のリアクションは使えるが、暴力描写が強く部分的な参考にとどまる</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
           <t>技法：解説役を置いて技の凄さを第三者に語らせる／強さを観客の表情で伝える。FLATUP案：初心者の会員が初めてミットを鳴らした瞬間を、先輩会員が驚く顔で見せる。オリジナル台詞案『今の音、自分で出したんだよ』。</t>
         </is>
       </c>
-      <c r="U88" s="2" t="inlineStr">
+      <c r="W88" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V88" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]シリーズ累計発行部数1億部突破と報じられた（2024年）。[事実]複数回アニメ化。[感想]誇張表現がネットミーム化しやすく、真面目さと笑いの両面で愛されている印象。[推測]初期作は格闘技ファン以外の入口になっている。</t>
         </is>
       </c>
-      <c r="W88" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/54 | https://realsound.jp/book/2024/05/post-1667170.html | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
         </is>
       </c>
-      <c r="X88" s="2" t="inlineStr">
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y88" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11693,7 +12215,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>全31巻（少年チャンピオン・コミックス）／完全版 全17巻（バキ完全版）／新装版あり（巻数未確認）</t>
+          <t>全31巻（少年チャンピオン・コミックス）／完全版 全17巻（バキ完全版）／新装版 全18巻（電子書店の表記。2018年頃刊行）</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11733,30 +12255,40 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
+          <t>B：強者同士の妙に礼儀正しいやり取りや日常とのずれは使えるが、流血描写は避ける必要がある</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
           <t>技法：勝敗の定義を問い直す構成。FLATUP案：『試合で勝つ』ではなく『昨日の自分に勝つ』を勝利と定義するエピソード。オリジナル台詞案『今日の勝ちは、来たことだよ』。</t>
         </is>
       </c>
-      <c r="U89" s="2" t="inlineStr">
+      <c r="W89" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。死刑囚5人という構成・設定も流用不可。</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2018年にNetflixでアニメ化（バキ）。[感想]死刑囚編は人気が高いという声が多い。[推測]後半は評価が分かれやすい。</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/series/8817 | https://www.akitashoten.co.jp/comics/4253218881 | https://en.wikipedia.org/wiki/Baki_the_Grappler</t>
-        </is>
-      </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/series/8817 | https://www.akitashoten.co.jp/comics/4253218881 | https://en.wikipedia.org/wiki/Baki_the_Grappler | https://www.maruzenjunkudo.co.jp/products/9784253253246 | https://comic.k-manga.jp/title/154612/pv</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11820,7 +12352,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>全37巻（少年チャンピオン・コミックス）／新装版あり（巻数未確認）</t>
+          <t>全37巻（少年チャンピオン・コミックス）／新装版 全21巻（電子書店の表記）</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11860,30 +12392,40 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
+          <t>C：親子の対立という骨格は参考になるが、描写が過激でFLATUPには直接使いにくい</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
           <t>技法：言葉に頼らず表情だけで心情を伝えるコマ。FLATUP案：口下手な父親会員が、子どもの帯昇級の日に何も言わず肩に手を置く場面。</t>
         </is>
       </c>
-      <c r="U90" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。原始人キャラの設定（化石からの蘇生など）も流用不可。</t>
         </is>
       </c>
-      <c r="V90" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2023年にアニメ化（範馬刃牙）。[感想]親子対決の結末は賛否が分かれるという声がある。[推測]シリーズの一区切りとして読まれることが多い。</t>
         </is>
       </c>
-      <c r="W90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/series/1976 | https://www.akitashoten.co.jp/comics/4253211178 | https://championcross.jp/series/83c15f6be5628</t>
-        </is>
-      </c>
-      <c r="X90" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/series/1976 | https://www.akitashoten.co.jp/comics/4253211178 | https://championcross.jp/series/83c15f6be5628 | https://comic.k-manga.jp/title/154612/pv</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y90" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -11987,30 +12529,40 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
+          <t>C：時代ギャップの笑いは参考になるが、本筋は命のやり取りで方向性が違う</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
           <t>技法：時代や文化の違う者同士の会話ギャップ。FLATUP案：70代の新入会員と10代の会員が、互いの『当たり前』の違いで笑い合う回。</t>
         </is>
       </c>
-      <c r="U91" s="2" t="inlineStr">
+      <c r="W91" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在の剣豪を現代に蘇らせる設定の組み立て方もそのままなぞらない。</t>
         </is>
       </c>
-      <c r="V91" s="2" t="inlineStr">
+      <c r="X91" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2026年にアニメ配信が始まったとの記載がWebにある（要確認）。[感想]主要キャラの退場が大きな話題になった。[推測]シリーズ内でも賛否が強い作品。</t>
         </is>
       </c>
-      <c r="W91" s="2" t="inlineStr">
+      <c r="Y91" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/4380 | https://www.akitashoten.co.jp/comics/4253223621</t>
         </is>
       </c>
-      <c r="X91" s="2" t="inlineStr">
+      <c r="Z91" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y91" s="2" t="inlineStr">
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -12114,30 +12666,40 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
+          <t>C：真顔の格闘論が飛躍する誇張は参考程度で、題材の相撲もFLATUPから遠い</t>
+        </is>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
           <t>技法：一つの競技を深掘りして『その競技ならではの強さ』を見せる。FLATUP案：キックボクシングとレスリング出身の会員が互いの基本動作を教え合う回。</t>
         </is>
       </c>
-      <c r="U92" s="2" t="inlineStr">
+      <c r="W92" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。古代相撲の継承者という設定は流用不可。</t>
         </is>
       </c>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2023年9月刊行の第17巻で完結。[感想]相撲題材は好みが分かれるという声がある。[推測]シリーズ固定ファン中心に読まれている。</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr">
+      <c r="Y92" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/9084 | https://www.akitashoten.co.jp/comics/4253281273</t>
         </is>
       </c>
-      <c r="X92" s="2" t="inlineStr">
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y92" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -12196,7 +12758,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>2023年頃開始（開始号は未確認）–連載中</t>
+          <t>2023（週刊少年チャンピオン2023年39号・8月24日発売号開始）–連載中</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -12241,30 +12803,40 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
+          <t>C：脱力タイトルと本編の重さの落差は参考になるが、内容は直接使いにくい</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
           <t>技法：主役ではなく脇役に焦点を当てる群像回。FLATUP案：受付スタッフや送迎の保護者が主役になる『ジムのらへん』的な短編。オリジナル台詞案『主役じゃなくても、ここは居場所』。</t>
         </is>
       </c>
-      <c r="U93" s="2" t="inlineStr">
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。タイトルの言い回しを模した作品名も避ける。</t>
         </is>
       </c>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2024年の累計1億部記念で巻頭カラー掲載があったと報じられた。[感想]タイトルのゆるさが話題になった。[推測]連載中のため評価は今後変わりうる。</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/series/12823 | https://www.akitashoten.co.jp/comics/4253284213 | https://www.akitashoten.co.jp/comics/4253011373</t>
-        </is>
-      </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/series/12823 | https://www.akitashoten.co.jp/comics/4253284213 | https://www.akitashoten.co.jp/comics/4253011373 | https://news.denfaminicogamer.jp/news/230824r</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -12368,30 +12940,40 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
+          <t>C：短編で人物を立てる構成は参考程度</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
           <t>技法：脇役の因縁だけで1冊を作るスピンオフ構成。FLATUP案：昔ライバルだった中年会員2人の『引退前の一戦』をスパーリング大会で描く。</t>
         </is>
       </c>
-      <c r="U94" s="2" t="inlineStr">
+      <c r="W94" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。実在人物を連想させるパロディ造形（名前のもじり）はFLATUPでは使わない。</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="X94" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]プロレス好きの読者に評価されているという声がある。[推測]知名度は本編より低い。</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>https://ciatr.jp/topics/326476 | https://mangapedia.com/gd/%E3%82%B0%E3%83%A9%E3%83%83%E3%83%97%E3%83%A9%E3%83%BC%E5%88%83%E7%89%99%E5%A4%96%E4%BC%9D-dc4q37bo9/1</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -12495,30 +13077,40 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
+          <t>C：格闘の文法を別ジャンルに転用する発想のみ参考で、内容は対象外</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
           <t>技法：本編と別媒体に分けて描くことで、作品のトーンを守る判断。FLATUP案：ブランドの本編（初心者向け・全年齢）と、大人向けの別企画を明確に分ける運用ルールの参考にする。性的表現はFLATUP作品では扱わない。</t>
         </is>
       </c>
-      <c r="U95" s="2" t="inlineStr">
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。性的描写を含むため、内容・構成ともFLATUPでは参考にしない。</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]本編とのギャップで話題に上ることが多い。[推測]青年誌掲載のため本編より読者は限られる。</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E3%83%90%E3%82%AD%E7%89%B9%E5%88%A5%E7%B7%A8%20saga%5B%E6%80%A7%5D | https://ciatr.jp/topics/326476</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -12622,30 +13214,40 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
+          <t>B：無口な強面の背中で語る演出は使えるが、喧嘩の美学はFLATUPの思想と逆なので技法だけ借りる</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／群像・矜持</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
           <t>技法：寡黙な主人公を周囲の反応で語らせる。FLATUP案：無口なベテラン会員が、初心者が転んだときだけ黙って手を差し出す。ただし『暴力の美学』は採らず、『耐える強さ＝やさしさ』に置き換える。</t>
         </is>
       </c>
-      <c r="U96" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>主人公の外見（大柄・顔や背中の傷・白スーツ）、任侠組織の設定、『喧嘩師』という肩書きの使い方をそのまま流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]花山薫ファンに支持される外伝という声がある。[推測]暴力団設定があるためFLATUPの思想とは距離がある。</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/1909 | https://www.akitashoten.co.jp/comics/4253231713 | https://www.cmoa.jp/title/41006/</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -12749,32 +13351,42 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
+          <t>A：怖そうな人物を学園コメディに置く落差は、強面だけど優しいコーチ像にそのまま使える</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／強面の先生</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
           <t>技法：強いキャラを日常に置いて笑いにする『場違いギャグ』。FLATUP案：プロ選手のトレーナーがキッズクラスで子どもに負けて本気で悔しがる回。</t>
         </is>
       </c>
-      <c r="U97" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>主人公の15歳時の外見・設定、学園の固有設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V97" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]前作と雰囲気が違う学園コメディとして紹介されている。[推測]シリアス目当ての読者には好みが分かれる。</t>
         </is>
       </c>
-      <c r="W97" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>https://www.akitashoten.co.jp/series/2957 | https://www.akitashoten.co.jp/comics/4253132618 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E5%89%B5%E9%9D%A2-652afhpws</t>
         </is>
       </c>
-      <c r="X97" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y97" s="2" t="inlineStr">
-        <is>
-          <t>確認済み</t>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>二次情報で確認</t>
         </is>
       </c>
     </row>
@@ -12876,30 +13488,40 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
+          <t>C：空手家の若き日の回想構成のみ参考程度</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
           <t>技法：ベテランキャラの『若い頃』を描く前日譚。FLATUP案：今は穏やかなジムの会長が、若い頃は負けず嫌いで失敗ばかりだった話を会員に語る回。</t>
         </is>
       </c>
-      <c r="U98" s="2" t="inlineStr">
+      <c r="W98" s="2" t="inlineStr">
         <is>
           <t>愚地独歩の外見（スキンヘッド・眼帯）、神心会という流派名を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[推測]全1巻の短期作のため知名度は高くない。[感想]独歩の若き日が見られる点を評価する声がある。</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>https://championcross.jp/series/f4d643b0590d6 | https://www.akitashoten.co.jp/comics/4253236219 | https://mangapedia.com/%E3%83%90%E3%82%AD%E5%A4%96%E4%BC%9D%E6%8B%B3%E5%88%83-r2t7o70mk</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -12953,7 +13575,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン（電子書店の分類による。未確認）</t>
+          <t>別冊少年チャンピオン（MyAnimeList系データによる）／週刊少年チャンピオン（電子書店の分類による）（資料により異なる）</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -13003,30 +13625,40 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
+          <t>A：格闘漫画の大げさな表現を日常の小さな出来事に当てる落差ギャグが、ジムの日常コメディに使える</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
           <t>技法：シリアス作品のキャラを使った公式ショートギャグで、SNS向けの軽い入口を作る。FLATUP案：AIKAやコーチ陣のデフォルメ4コマ『今日のジムあるある』。</t>
         </is>
       </c>
-      <c r="U99" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>刃牙キャラのデフォルメ絵や、原作名場面のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]原作ファン向けのパロディとして楽しまれているという声がある。[推測]原作を知らない読者には伝わりにくい。</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
-        <is>
-          <t>https://mangapedia.com/%E3%83%90%E3%82%AD%E3%81%A9%E3%82%82%E3%81%88-b9klm5pzx | https://mechacomic.jp/books/147011/reviews?score=1&amp;submitted=1</t>
-        </is>
-      </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>https://mangapedia.com/%E3%83%90%E3%82%AD%E3%81%A9%E3%82%82%E3%81%88-b9klm5pzx | https://mechacomic.jp/books/147011/reviews?score=1&amp;submitted=1 | https://myanimepulse.com/manga/100784/baki-domoe</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -13080,12 +13712,12 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>月刊少年チャンピオン（開始時の掲載媒体は未確認）</t>
+          <t>月刊少年チャンピオン</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2020年代前半開始（開始時期の詳細は未確認）–連載中</t>
+          <t>2020（月刊少年チャンピオン2020年12月号・11月6日発売号開始）–連載中（2026年8月にTVアニメ化発表）</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -13130,30 +13762,40 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
+          <t>B：武術の理屈を場違いな場面に真顔で持ち込むジャンル混合ギャグは使えるが、戦闘は過激</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／奇妙な冒険</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
           <t>技法：ジャンルを混ぜる『場違い』の面白さ。FLATUP案：AIKAがゲーム世界に入り込み、ジムで習った受け身で危機を切り抜ける短編（オリジナル世界観で）。</t>
         </is>
       </c>
-      <c r="U100" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
         <is>
           <t>烈海王の外見（辮髪・中国拳法着）、タイトルの言い回し、異世界転生の筋立てをそのまま使わない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]チャンピオンクロスの全話無料キャンペーンで外伝の一つとして公開された（2024年）。[感想]タイトルのインパクトで話題になった。[推測]異世界ものファンと刃牙ファンの両方に読まれている。</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/comics/4253012191 | https://landing.akitashoten.co.jp/isekairetsu/ | https://dengekionline.com/article/202405/5717</t>
-        </is>
-      </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/comics/4253012191 | https://landing.akitashoten.co.jp/isekairetsu/ | https://dengekionline.com/article/202405/5717 | https://nlab.itmedia.co.jp/nl/articles/2011/06/news012.html | https://dengekionline.com/article/202608/86053</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -13212,12 +13854,12 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>2022（2022年16号開始）–（現在の連載状況は未確認）</t>
+          <t>2022（週刊少年チャンピオン2022年16号開始）–連載中とみられる（2026年5月に第10巻刊行。完結の発表は見当たらない。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>既刊10巻（少年チャンピオン・コミックス）</t>
+          <t>既刊10巻（2026年5月時点。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -13257,30 +13899,40 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
+          <t>C：本格的な格闘描写の参考にはなるが、暗い作風でFLATUPには直接使いにくい</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
           <t>技法：ナレーションで技の理屈を一つずつ解説する。FLATUP案：初心者向け動画マニュアルで、ジャブの動きを3段階に分けて語りで解説する構成。</t>
         </is>
       </c>
-      <c r="U101" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>原作小説・漫画のキャラ・設定・ナレーション文を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V101" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]夢枕獏と刃牙の組み合わせを喜ぶ声がある。[推測]格闘小説ファン寄りの読者層。</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/series/11820 | https://www.akitashoten.co.jp/comics/4253015913 | https://championcross.jp/series/8a3b23bd8c6ce</t>
-        </is>
-      </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/series/11820 | https://www.akitashoten.co.jp/comics/4253015913 | https://championcross.jp/series/8a3b23bd8c6ce | https://dengekionline.com/article/202605/75980</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -13324,7 +13976,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>未確認（小説のため作画なし。挿絵の有無は未確認）</t>
+          <t>作画なし（小説）。挿絵：藤田勇利亜（紹介記事による）</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -13334,80 +13986,90 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>少年チャンピオン・ノベルズ（初出媒体は未確認）</t>
+          <t>週刊少年チャンピオン（電子書店の分類による）／単行本は少年チャンピオン・ノベルズ</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
+          <t>2020年11月開始とされる（電子書店の掲載情報による）–完結（終了時期は未確認）</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>全5巻（完結。紹介記事による。新書判）</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>格闘小説／異種格闘技</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>コミカライズ：漫画 ゆうえんち -バキ外伝-</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>格闘家同士の闘いと強さの探求</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>小説ならではの内面描写（恐怖、期待、身体感覚）を言葉で積み上げる。</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>短い文の連打で緊張を高める文体とされる（要確認）。</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>小説のため、改行と擬音で間を作る。</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>少なくとも2巻を確認（総巻数は未確認、新書判）</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>格闘小説／異種格闘技</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>コミカライズ：漫画 ゆうえんち -バキ外伝-</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>格闘家同士の闘いと強さの探求</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>小説ならではの内面描写（恐怖、期待、身体感覚）を言葉で積み上げる。</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>短い文の連打で緊張を高める文体とされる（要確認）。</t>
-        </is>
-      </c>
-      <c r="R102" s="2" t="inlineStr">
-        <is>
-          <t>小説のため、改行と擬音で間を作る。</t>
-        </is>
-      </c>
-      <c r="S102" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
+          <t>C：小説のため絵の演出は学べず、格闘の言葉での描写を知る参考程度</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
           <t>技法：身体感覚を言葉で描く。FLATUP案：SNSの短文投稿で『初めてミットを打った時の手のしびれ』など体験を言葉で伝える。</t>
         </is>
       </c>
-      <c r="U102" s="2" t="inlineStr">
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>小説本文・キャラ・設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V102" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[推測]漫画版の原作として知られる。評判の詳細は未確認。</t>
         </is>
       </c>
-      <c r="W102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253107617 | https://www.kinokuniya.co.jp/f/dsg-01-9784253107624</t>
-        </is>
-      </c>
-      <c r="X102" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253107617 | https://www.kinokuniya.co.jp/f/dsg-01-9784253107624 | https://bookwalker.jp/series/276238/ | https://dengekionline.com/article/202605/75980</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y102" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -13471,7 +14133,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>既刊巻数は未確認（第1巻 2023年3月刊行。二次情報では5巻以上）</t>
+          <t>既刊12巻（第12巻 2026年10月7日発売とする書店ページあり。第10巻は2026年3月刊行。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -13511,30 +14173,40 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
+          <t>A：強面の格闘家が家事や近所付き合いをするギャップ笑いが、FLATUPキャラの日常回にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／強面の先生</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
           <t>技法：ライバル同士の同居・日常コメディ。FLATUP案：スパーで勝ち負けを競う会員2人が、ジムの掃除当番でペアになる回。オリジナル台詞案『拭き掃除でも、負けたくないんだよな』。</t>
         </is>
       </c>
-      <c r="U103" s="2" t="inlineStr">
+      <c r="W103" s="2" t="inlineStr">
         <is>
           <t>ガイア・シコルスキーの外見、軍人・死刑囚という設定、人格切り替えの設定を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V103" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]週刊少年チャンピオンにも特別掲載された記録がある。[感想]意外な組み合わせの日常ギャグとして話題になった。[推測]本編を読んでいるほど笑える作り。</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.akitashoten.co.jp/comics/4253294162 | https://arc.akitashoten.co.jp/comics/gaishiko/1 | https://championcross.jp/series/e76cd5db52ef2</t>
-        </is>
-      </c>
-      <c r="X103" s="2" t="inlineStr">
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.akitashoten.co.jp/comics/4253294162 | https://arc.akitashoten.co.jp/comics/gaishiko/1 | https://championcross.jp/series/e76cd5db52ef2 | https://dengekionline.com/article/202603/66770 | https://www.maruzenjunkudo.co.jp/products/9784253020152</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y103" s="2" t="inlineStr">
+      <c r="AA103" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -13618,7 +14290,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>強者が一人で食事を味わう静かな時間を描くとされる（詳細未確認）。</t>
+          <t>（紹介記事による）達人が一人で酒と食事を味わう、戦いのない静かな時間を描くグルメ漫画。</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13633,35 +14305,45 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>武の達人が食事に武道の理屈を持ち込むずれと推測される（未確認）。</t>
+          <t>（紹介記事による）本編で知られる素手の技を居酒屋の食事場面で使うなど、本編へのオマージュを日常に持ち込む落差。</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
+          <t>A：強い人が静かにご飯を味わう落差は、優しく穏やかなコーチの日常回にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
           <t>技法：格闘キャラのグルメ・日常スピンオフ。FLATUP案：練習後にコーチが『減量中でも食べていいもの』を紹介する食レポ風SNS漫画。</t>
         </is>
       </c>
-      <c r="U104" s="2" t="inlineStr">
+      <c r="W104" s="2" t="inlineStr">
         <is>
           <t>愚地独歩の外見、神心会の名称、グルメ漫画のパロディ構図を流用しない。範馬勇次郎・刃牙ら固有キャラの外見（鬼の顔に見える背筋など）、キャラ名、地下闘技場という固有設定名、促音記号を重ねる特徴的な表記をそのまま流用しない。決めゼリフや名場面の構図の再現も不可。</t>
         </is>
       </c>
-      <c r="V104" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]2026年5月に連載開始が発表され、初回は表紙・巻頭カラー・3話掲載。[推測]評判はまだ未確認。</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr">
-        <is>
-          <t>https://prtimes.jp/main/html/rd/p/000000854.000040601.html | https://dengekionline.com/article/202604/72212 | https://x.com/teambaki/status/2056570540148588645</t>
-        </is>
-      </c>
-      <c r="X104" s="2" t="inlineStr">
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000854.000040601.html | https://dengekionline.com/article/202604/72212 | https://x.com/teambaki/status/2056570540148588645 | https://news.denfaminicogamer.jp/news/260617m | https://natalie.mu/comic/news/672601</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y104" s="2" t="inlineStr">
+      <c r="AA104" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -13765,30 +14447,40 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
+          <t>B：重いナレーションと逆光の演出は「世紀末」モードに使えるが、暴力描写は使わない</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>世紀末</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
           <t>「202X年」から始まる重いナレーション、荒野、雑魚の叫び声というジャンルの型を、世紀末パロディのオープニングに使う。強い者が弱い者を守るという芯は、FLATUPの「強さは優しさ」と相性がよい。オリジナル案：「殴る相手はミットだけでいい」</t>
         </is>
       </c>
-      <c r="U105" s="2" t="inlineStr">
+      <c r="W105" s="2" t="inlineStr">
         <is>
           <t>原作冒頭のナレーションの言い回し、有名な決めゼリフ、やられたときの叫び声、胸の七つの傷、トゲ付き肩パッド、拳法名・技名、経絡秘孔の設定、キャラクターの外見、主題歌、タイトルロゴの書体は使わない</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="X105" s="2" t="inlineStr">
         <is>
           <t>[事実] 累計発行部数は全世界1億部超（2019年11月時点の記事）とされる。 [事実] 雑魚キャラを主人公にしたギャグのスピンオフが公式に作られ、2026年1月にショートアニメ化された。 [感想] 雑魚キャラの叫び声がネットミームとして親しまれている。 X直接検索なし</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>https://bestcalendar.jp/dates/kinenbi/3791 | https://comic.k-manga.jp/title/67231/pv | https://renote.net/tags/246/articles</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
+      <c r="Z105" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -13827,54 +14519,54 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>未確認（原作者の監修のもとで制作されたとされる）</t>
+          <t>武論尊・原哲夫（原案）／河田雄志（シナリオ）</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
+          <t>行徒妹</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>未確認（レーベルはゼノンコミックス）</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>WEBコミックぜにょん（Yahoo!ブックストア内）</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>2013–（2013年3月1日連載開始。終了時期は未確認）</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>9巻（電子書店の配信巻数。2026-10時点で確認）</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>ギャグ／パロディ</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>北斗の拳（本編）。2015年にテレビアニメ化</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>本編の悪役を主人公にした、自分をパロディにするギャグ</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>ギャグ／パロディ</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>北斗の拳（本編）。2015年にテレビアニメ化</t>
-        </is>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>本編の悪役を主人公にした、自分をパロディにするギャグ</t>
-        </is>
-      </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
           <t>本編の重い言い回しを、日常のくだらない場面で使って落差を作る（紹介記事の説明による）</t>
@@ -13892,30 +14584,40 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
+          <t>A：シリアスな絵柄のままばかばかしいことをする落差のギャグがすぐ使える</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>世紀末</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
           <t>劇画の絵柄のまま、ジムの日常（ストレッチで太ももが伸びて感動する、など）を大真面目に描く落差の技法に使える</t>
         </is>
       </c>
-      <c r="U106" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
         </is>
       </c>
-      <c r="V106" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
         <is>
           <t>[事実] 2015年にテレビアニメ化された。 X直接検索なし</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr">
-        <is>
-          <t>https://mangapedia.com/gd/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3-chyqulnxj/</t>
-        </is>
-      </c>
-      <c r="X106" s="2" t="inlineStr">
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>https://mangapedia.com/gd/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3-chyqulnxj/ | https://www.cmoa.jp/title/105685 | https://dic.nicovideo.jp/a/%E5%8C%97%E6%96%97%E3%81%AE%E6%8B%B3%E3%82%A4%E3%83%81%E3%82%B4%E5%91%B3 | https://natalie.mu/comic/news/131255</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y106" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -13954,32 +14656,32 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
+          <t>武論尊・原哲夫（原案）</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>倉尾宏</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>倉尾宏</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>マンガほっと</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>2017–2020（2017年11月〜2020年3月）</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>全3巻（1巻は2018年9月発売。電子書店で完結表示）</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -14004,12 +14706,12 @@
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>下っ端の主人公のボケとツッコミが中心（紹介記事による）</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>ザコが次々に退場する「お約束」を、重くせず軽いテンポで見せる（紹介記事による）</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
@@ -14019,30 +14721,40 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
+          <t>A：怖い組織の下っ端が理不尽にふり回される笑いが、勘違いギャグに使える</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>世紀末</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
           <t>雑魚キャラの側から描く視点がとても参考になる。FLATUPの「ヒャッハー三人衆」を主人公にして、入会して少しずつ変わっていく話にできる</t>
         </is>
       </c>
-      <c r="U107" s="2" t="inlineStr">
+      <c r="W107" s="2" t="inlineStr">
         <is>
           <t>原作と同じく、キャラクター・セリフ・技名・ロゴは使わない</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="X107" s="2" t="inlineStr">
         <is>
           <t>[事実] 2026年1月5日からショートアニメが放送された。 X直接検索なし</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
-        <is>
-          <t>https://animeanime.jp/article/2025/12/25/94731.html | https://mangapedia.com/gd/ag0gpp5uc</t>
-        </is>
-      </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>https://animeanime.jp/article/2025/12/25/94731.html | https://mangapedia.com/gd/ag0gpp5uc | https://mechacomic.jp/books/128787 | https://honcierge.jp/articles/shelf_story/6260 | https://realsound.jp/movie/2026/03/post-2342417_2.html</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="AA107" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -14116,7 +14828,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>作画者の他作：『ジーザス』『闇のイージス』（いずれも原作 七月鏡一）。続編『拳児2』があるとする資料あり（詳細は未確認）</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
@@ -14146,30 +14858,40 @@
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
+          <t>B：祖父と孫の関係や、武術の体の使い方を丁寧に描く点は使える</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
           <t>技法：技の『理屈』を丁寧に描き、読者が学べる漫画にする。FLATUP案：AIKAがパンチの体重移動を図解で教えるミニ漫画（教育コンテンツ）。</t>
         </is>
       </c>
-      <c r="U108" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>主人公・師匠キャラの名前と外見、作中の流派・師弟系譜の描写を流用しない。</t>
         </is>
       </c>
-      <c r="V108" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]武術ファンの間で『中国武術に興味を持つきっかけ』として語られることが多い。[推測]実在武術の描写の丁寧さが評価されている。</t>
         </is>
       </c>
-      <c r="W108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv</t>
-        </is>
-      </c>
-      <c r="X108" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cmoa.jp/title/5905 | https://mangapedia.com/拳児-1453jqb69 | https://comic.k-manga.jp/title/13898/pv | https://mangapedia.com/%E8%97%A4%E5%8E%9F%E8%8A%B3%E7%A7%80-o98eim6id</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y108" s="2" t="inlineStr">
+      <c r="AA108" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -14273,30 +14995,40 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
+          <t>C：劇画調の誇張と昭和の空気は参考になるが、内容は過激で直接使えない</t>
+        </is>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
           <t>技法：ナレーションで物語の熱量を上げる劇画の手法。FLATUP案：ジム10周年の記念動画で、創設者の『最初の一日』を熱いナレーションで語る（実在人物の事実確認を前提に）。ただし『根性で痛みに耐える』表現は採らない。</t>
         </is>
       </c>
-      <c r="U109" s="2" t="inlineStr">
+      <c r="W109" s="2" t="inlineStr">
         <is>
           <t>実在の空手家をモデルにした人物像、劇画のナレーション文、修行エピソード（動物との対決など）を流用しない。</t>
         </is>
       </c>
-      <c r="V109" s="2" t="inlineStr">
+      <c r="X109" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]1973年にTVアニメ化（二次情報）。[感想]空手ブームに影響したと語られることが多い。[推測]実話と創作の境目について議論がある。</t>
         </is>
       </c>
-      <c r="W109" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Karate_Master | https://www.kodansha.co.jp/comic/new-releases/p?page=2201 | https://mangapedia.com/%E3%81%A4%E3%81%AE%E3%81%A0%E3%81%98%E3%82%8D%E3%81%86-3h7myqn64</t>
         </is>
       </c>
-      <c r="X109" s="2" t="inlineStr">
+      <c r="Z109" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y109" s="2" t="inlineStr">
+      <c r="AA109" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -14360,7 +15092,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>既刊145巻以上（145巻は2026年1月16日発売。以降の巻数は未確認）</t>
+          <t>既刊145巻以上（145巻は2026年1月16日発売。146巻以降は2026-10時点で確認できず）</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -14400,30 +15132,40 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
+          <t>A：気弱な初心者がジムの仲間に支えられて強くなる流れと、試合後の脱力ギャグがFLATUPにすぐ使える</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
           <t>技法：初心者の『怖さ』をモノローグで正直に描き、小さな一歩を大きく演出する。練習→試合の緩急、ジム仲間のいじり合いで温かさを出す。オリジナル案：初めてミットを打った会員が『音が鳴った』だけで目を輝かせる回。セリフ案『上手くなくていい。今日来たのがもう勝ち』。</t>
         </is>
       </c>
-      <c r="U110" s="2" t="inlineStr">
+      <c r="W110" s="2" t="inlineStr">
         <is>
           <t>主人公や鷹村・宮田など主要キャラの外見・髪型、鴨川ジムの名称やロゴ、デンプシーロールなど作中固有の必殺技名と象徴的な動き、釣り船屋という主人公の家業設定をそのまま使わない。</t>
         </is>
       </c>
-      <c r="V110" s="2" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>[事実] 1989年から30年以上続く長期連載で、ボクシング漫画の代表作として紹介されることが多い。[感想] 序盤〜中盤の試合描写や脇役の名勝負を高く評価する声が多い。[推測] 近年は展開の遅さや主人公の引退〜復帰の流れに賛否があるとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W110" s="2" t="inlineStr">
+      <c r="Y110" s="2" t="inlineStr">
         <is>
           <t>https://bunshun.jp/articles/-/88272 | https://game.watch.impress.co.jp/docs/news/1333266.html | https://www.kodansha.co.jp/comic/products/0000422841 | https://dengekionline.com/articles/208950/</t>
         </is>
       </c>
-      <c r="X110" s="2" t="inlineStr">
+      <c r="Z110" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y110" s="2" t="inlineStr">
+      <c r="AA110" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -14527,30 +15269,40 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
+          <t>A：子どもが父の背中を追って努力するほのぼのした成長物語が、キッズ向けにすぐ使える</t>
+        </is>
+      </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
           <t>技法：子ども時代から段階的に成長を見せる長期構成。柔らかい絵柄で格闘技の怖さを下げる。オリジナル案：キッズクラスの子が卒業までに少しずつ変わっていく年代記。セリフ案『昨日より一回多く、前に出られたね』。</t>
         </is>
       </c>
-      <c r="U111" s="2" t="inlineStr">
+      <c r="W111" s="2" t="inlineStr">
         <is>
           <t>主人公の名前や外見、父がボクサーで亡くなる設定の流用、作品タイトルのもじりを避ける。</t>
         </is>
       </c>
-      <c r="V111" s="2" t="inlineStr">
+      <c r="X111" s="2" t="inlineStr">
         <is>
           <t>[事実] 女子ボクシングの金メダリストが競技を始めるきっかけに挙げたと報じられた。[感想] 優しい絵柄と家族ドラマで泣ける作品として語られる。[推測] 知名度は世代差が大きいとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W111" s="2" t="inlineStr">
+      <c r="Y111" s="2" t="inlineStr">
         <is>
           <t>https://number.bunshun.jp/articles/-/849242 | https://www.cmoa.jp/title/528/ | https://mechacomic.jp/books/45940</t>
         </is>
       </c>
-      <c r="X111" s="2" t="inlineStr">
+      <c r="Z111" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y111" s="2" t="inlineStr">
+      <c r="AA111" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -14654,30 +15406,40 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
+          <t>B：軽口の青春ドタバタと格闘描写の切り替えは使えるが、後半の重さは参考程度</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
           <t>技法：音楽やリズムとボクシングのステップを重ねる演出。オリジナル案：会員がBGMに合わせてシャドーをするとステップが自然に良くなる回。セリフ案『リズムに乗れたら、体は勝手に動く』。</t>
         </is>
       </c>
-      <c r="U112" s="2" t="inlineStr">
+      <c r="W112" s="2" t="inlineStr">
         <is>
           <t>主人公の外見、ボクサーが傭兵になる大筋、作中のサックス奏者設定をそのまま使わない。</t>
         </is>
       </c>
-      <c r="V112" s="2" t="inlineStr">
+      <c r="X112" s="2" t="inlineStr">
         <is>
           <t>[事実] 作者インタビューで主人公が傭兵になる展開の誕生秘話が語られている。[感想] 前半のボクシングと後半の戦場編の落差が強く印象に残るという声。[推測] 現在の知名度は同時代のボクシング漫画より低めとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W112" s="2" t="inlineStr">
+      <c r="Y112" s="2" t="inlineStr">
         <is>
           <t>https://gendai.media/articles/-/100861 | https://mangapedia.com/gd/B%E3%83%BBB-9tbu6j1t4/ | https://ranking.net/rankings/best-shonensunday-comics/b6c541bd</t>
         </is>
       </c>
-      <c r="X112" s="2" t="inlineStr">
+      <c r="Z112" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y112" s="2" t="inlineStr">
+      <c r="AA112" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -14781,30 +15543,40 @@
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
+          <t>A：普通の高校生がMMAジムで基礎から学ぶ描写と、ジム仲間とのゆるい日常がFLATUPに直結する</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
           <t>技法：MMAのルールや技を初心者にも分かるよう噛み砕いて描く。地味な練習の積み重ねをドラマにする。オリジナル案：寝技の初体験で『怖い』が『おもしろい』に変わる瞬間を描く回。セリフ案『タップは負けじゃない。また練習できる合図だよ』。</t>
         </is>
       </c>
-      <c r="U113" s="2" t="inlineStr">
+      <c r="W113" s="2" t="inlineStr">
         <is>
           <t>主人公と幼なじみのキャラ造形、作中ジム名、実在団体（修斗）のロゴや公式表記の無断使用を避ける。</t>
         </is>
       </c>
-      <c r="V113" s="2" t="inlineStr">
+      <c r="X113" s="2" t="inlineStr">
         <is>
           <t>[事実] 修斗を題材にした作品として格闘技ファンに紹介される。[感想] 格闘技経験者から描写のリアルさを評価する声。[推測] MMA漫画の入門として勧められやすいとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W113" s="2" t="inlineStr">
+      <c r="Y113" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E3%82%AA%E3%83%BC%E3%83%AB%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%80%E3%83%BC%E5%BB%BB | https://www.kodansha.co.jp/comic/products/0000038657 | https://bookwalker.jp/de77e612eb-ae5e-4edd-acd0-e2eb92f4eff0/</t>
         </is>
       </c>
-      <c r="X113" s="2" t="inlineStr">
+      <c r="Z113" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y113" s="2" t="inlineStr">
+      <c r="AA113" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -14908,30 +15680,40 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
+          <t>C：暴力と転落の物語で、FLATUPの方向性とは逆。心理描写の参考程度</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
           <t>技法：反面教師として、暴力だけの強さがいかに人を孤独にするかを示す作品。FLATUPの『強さ＝優しさ』の対比として、悪役側の心理の深さを学ぶ程度に留める。</t>
         </is>
       </c>
-      <c r="U114" s="2" t="inlineStr">
+      <c r="W114" s="2" t="inlineStr">
         <is>
           <t>主人公の外見、少年院から格闘家になる設定、過激な暴力・性暴力描写は絶対に真似しない（ブランドと完全に逆方向）。</t>
         </is>
       </c>
-      <c r="V114" s="2" t="inlineStr">
+      <c r="X114" s="2" t="inlineStr">
         <is>
           <t>[事実] 原作者と作画者の間で著作権をめぐる裁判があったとされる。[感想] 迫力は高いが重く暗いという声。[推測] 一般向け・子ども向けには勧めにくい作品とみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W114" s="2" t="inlineStr">
+      <c r="Y114" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000038793 | https://renote.net/reviews/5254 | https://www.cmoa.jp/title/87790</t>
         </is>
       </c>
-      <c r="X114" s="2" t="inlineStr">
+      <c r="Z114" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y114" s="2" t="inlineStr">
+      <c r="AA114" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -14980,7 +15762,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>少年画報社（掲載誌の発行元。英語版Wikipediaによる）</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -15035,30 +15817,40 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
+          <t>B：キックボクシングを題材にした昭和劇画の空気は、劇画パロディの参考になる</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
           <t>技法：実在の歴史を背景にした『物語として語る格闘技史』。オリジナル案：日本のキックボクシングの歴史を、会員向けにやさしく紹介する短編漫画（実在人物の扱いは要注意）。</t>
         </is>
       </c>
-      <c r="U115" s="2" t="inlineStr">
+      <c r="W115" s="2" t="inlineStr">
         <is>
           <t>実在人物（沢村忠）の肖像やエピソードの流用、作中の技名、タイトルのもじりを避ける。</t>
         </is>
       </c>
-      <c r="V115" s="2" t="inlineStr">
+      <c r="X115" s="2" t="inlineStr">
         <is>
           <t>[事実] 沢村忠をモデルにした作品で、1970年にアニメ化された。[感想] 昭和のキックボクシングブームを伝える作品として語られる。[推測] 現在の読者は少ないとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W115" s="2" t="inlineStr">
+      <c r="Y115" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Kick_no_Oni | https://mangapedia.com/%E3%82%AD%E3%83%83%E3%82%AF%E3%81%AE%E9%AC%BC-6rimm0fjt | https://comic.k-manga.jp/title/165/pv</t>
         </is>
       </c>
-      <c r="X115" s="2" t="inlineStr">
+      <c r="Z115" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y115" s="2" t="inlineStr">
+      <c r="AA115" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15162,30 +15954,40 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
+          <t>B：格闘技の現場をリアルに描く点は使えるが、ギャグは控えめ</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
           <t>技法：『ジムに入会する』ところから始めるリアルな導入。FLATUPの体験入会の流れとほぼ同じ構造なので、最も参考になる型。オリジナル案：体験レッスン当日の緊張→受付→初ミット→帰り道の高揚までを1話で描く。セリフ案『初日は誰でも初心者。それでいい』。</t>
         </is>
       </c>
-      <c r="U116" s="2" t="inlineStr">
+      <c r="W116" s="2" t="inlineStr">
         <is>
           <t>主人公の外見や体操経験者という設定、作中ジム名を使わない。</t>
         </is>
       </c>
-      <c r="V116" s="2" t="inlineStr">
+      <c r="X116" s="2" t="inlineStr">
         <is>
           <t>[事実] 全4巻で終了。作者はキック王者との対談でリアルなキックを描きたかったと語った。[感想] もっと読みたかったという声がある。[推測] 短期終了のため知名度は低めとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W116" s="2" t="inlineStr">
+      <c r="Y116" s="2" t="inlineStr">
         <is>
           <t>https://comic.k-manga.jp/title/100297/pv | https://mangapedia.com/%E3%83%A2%E3%83%B3%E3%82%B0%E3%83%AC%E3%83%AB-e3btri2tc | https://sportiva.shueisha.co.jp/clm/othersports/fight/2013/12/19/___split_35/ | https://www.hatehate.jp/entry/mongrel</t>
         </is>
       </c>
-      <c r="X116" s="2" t="inlineStr">
+      <c r="Z116" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y116" s="2" t="inlineStr">
+      <c r="AA116" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15244,12 +16046,12 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>2022–（2022年7号開始。現在の連載状況は未確認）</t>
+          <t>2022（週刊少年サンデー2022年7号開始）–連載中（2026年6月時点で第197話掲載を確認）</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>未確認（2023年11月時点で7巻）</t>
+          <t>既刊18巻以上（電子書店の一覧による。2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -15289,30 +16091,40 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
+          <t>A：ひねくれた陰キャがMMAで自分を変えていく流れが、自信をなくした人の入門物語にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
           <t>技法：『かっこ悪い動機』から始めても成長できると示す。分析タイプの主人公で戦術を読者に解説。オリジナル案：運動が苦手な学生が、頭で考えるタイプとしてMMAで自分の勝ち方を見つける話。セリフ案『体力がないなら、考える力で一歩先に行こう』。</t>
         </is>
       </c>
-      <c r="U117" s="2" t="inlineStr">
+      <c r="W117" s="2" t="inlineStr">
         <is>
           <t>主人公とライバルの名前・外見、作中ジム名、赤と青の対比を軸にしたタイトル演出をそのまま使わない。</t>
         </is>
       </c>
-      <c r="V117" s="2" t="inlineStr">
+      <c r="X117" s="2" t="inlineStr">
         <is>
           <t>[事実] 2024年12月に実写ドラマ化された。[感想] 陰キャ主人公の成長がMMA初心者にも読みやすいという紹介がある。[推測] 近年の少年誌MMA漫画として注目度が高いとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W117" s="2" t="inlineStr">
-        <is>
-          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986</t>
-        </is>
-      </c>
-      <c r="X117" s="2" t="inlineStr">
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>https://mangapedia.com/波切敦-fjl2kkodq | https://oceans.tokyo.jp/article/detail/44582 | https://renote.net/tags/22986 | https://www.maruzenjunkudo.co.jp/products/4912206610760 | https://www.cmoa.jp/title/242392/vol/17/</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y117" s="2" t="inlineStr">
+      <c r="AA117" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15366,7 +16178,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>週刊少年マガジン（まとめサイトの記載。未確認）</t>
+          <t>週刊少年マガジン（まとめサイトの記載。未確認）／電子版の掲載誌表記は「マンガの金字塔」（資料により異なる）</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -15416,30 +16228,40 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
+          <t>C：キックボクシング題材の昭和劇画として参考程度</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
           <t>技法：別競技からの転向者を主人公にすると、技術の違いを読者に説明しやすい。オリジナル案：サッカー経験者の会員が『蹴り』の感覚の違いに戸惑い、やがて武器にする話。</t>
         </is>
       </c>
-      <c r="U118" s="2" t="inlineStr">
+      <c r="W118" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見、サッカーからキックへの転向をバンコクで宣言する導入をそのまま使わない。</t>
         </is>
       </c>
-      <c r="V118" s="2" t="inlineStr">
+      <c r="X118" s="2" t="inlineStr">
         <is>
           <t>[事実] 電子版で全10巻が配信されている。[感想] 梶原一騎のキックボクシング作品として紹介される。[推測] 現在の知名度は低いとみられる。X直接検索なし。</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr">
-        <is>
-          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/</t>
-        </is>
-      </c>
-      <c r="X118" s="2" t="inlineStr">
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>https://comic.k-manga.jp/title/16591/vol/1 | https://bookwalker.jp/de876054f1-f012-487c-b751-1e338df64937/ | https://kopenguin.com/post-78916/ | https://comic.k-manga.jp/title/16591/pv</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y118" s="2" t="inlineStr">
+      <c r="AA118" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15543,30 +16365,40 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
+          <t>B：主人公の普通の女の子らしさと、強さの落差が部分的に使える</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
           <t>技法：『強いのに普通でいたい』という主人公の心のズレで共感を作る。オリジナル案：家族に内緒で格闘技を始めた会社員女性が、通勤中に姿勢が良くなって同僚に気付かれるエピソード</t>
         </is>
       </c>
-      <c r="U119" s="2" t="inlineStr">
+      <c r="W119" s="2" t="inlineStr">
         <is>
           <t>主人公名・祖父キャラの造形、作品タイトルロゴ、特定の決め技の見せ方は使わない</t>
         </is>
       </c>
-      <c r="V119" s="2" t="inlineStr">
+      <c r="X119" s="2" t="inlineStr">
         <is>
           <t>[事実]小学館漫画賞受賞作として紹介され、女子柔道ブームと結び付けて語られることが多い（X直接検索なし） [感想]ラブコメとしても楽しめるという声が多い</t>
         </is>
       </c>
-      <c r="W119" s="2" t="inlineStr">
+      <c r="Y119" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Yawara! | https://nlab.itmedia.co.jp/research/articles/128892/ | https://ranking.net/items/7c982a</t>
         </is>
       </c>
-      <c r="X119" s="2" t="inlineStr">
+      <c r="Z119" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y119" s="2" t="inlineStr">
+      <c r="AA119" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15670,30 +16502,40 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
+          <t>A：弱小の部を仲間と作り、明るく続ける空気が初心者向けの話に使える</t>
+        </is>
+      </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
           <t>技法：技術の『なぜ』をキャラの会話で自然に説明する。オリジナル案：初心者が受け身を習う回で、コーチが『転び方が上手い人は人生でもケガしにくい』と語る短い場面</t>
         </is>
       </c>
-      <c r="U120" s="2" t="inlineStr">
+      <c r="W120" s="2" t="inlineStr">
         <is>
           <t>主要部員の外見・あだ名、部の名前、作中の学校名は使わない</t>
         </is>
       </c>
-      <c r="V120" s="2" t="inlineStr">
+      <c r="X120" s="2" t="inlineStr">
         <is>
           <t>[事実]第1回コミックグランプリ受賞作として紹介されている（X直接検索なし） [感想]『楽しい部活もの』として明るさを評価する声が多い</t>
         </is>
       </c>
-      <c r="W120" s="2" t="inlineStr">
+      <c r="Y120" s="2" t="inlineStr">
         <is>
           <t>https://ranking.net/items/14d871 | https://comic.k-manga.jp/title/12315/pv | https://shopping.bookoff.co.jp/s/8800000124</t>
         </is>
       </c>
-      <c r="X120" s="2" t="inlineStr">
+      <c r="Z120" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y120" s="2" t="inlineStr">
+      <c r="AA120" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15797,30 +16639,40 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
+          <t>B：小さい体で大きい相手に挑む工夫と熱さが部分的に使える</t>
+        </is>
+      </c>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
           <t>技法：『小さい・弱いからこそ工夫する』を主題にする。オリジナル案：小柄な女性会員が、体格差を技術でかわすコツを覚えて笑顔になる回</t>
         </is>
       </c>
-      <c r="U121" s="2" t="inlineStr">
+      <c r="W121" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・四股名・必殺技名・部の名称は使わない</t>
         </is>
       </c>
-      <c r="V121" s="2" t="inlineStr">
+      <c r="X121" s="2" t="inlineStr">
         <is>
           <t>[事実]相撲漫画ランキングで上位に紹介されている（X直接検索なし） [感想]熱い王道スポーツ漫画として評価が高い</t>
         </is>
       </c>
-      <c r="W121" s="2" t="inlineStr">
+      <c r="Y121" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2 | https://mangapedia.com/%E7%81%AB%E3%83%8E%E4%B8%B8%E7%9B%B8%E6%92%B2-yq1wzu8h2 | https://www.b-ch.com/titles/6297/</t>
         </is>
       </c>
-      <c r="X121" s="2" t="inlineStr">
+      <c r="Z121" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y121" s="2" t="inlineStr">
+      <c r="AA121" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -15879,12 +16731,12 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2016–（連載中かどうかは未確認）</t>
+          <t>2016–（連載中とする記事あり。2026-10時点で完結の情報なし）</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>裏少年サンデーコミックス既刊20巻（2025年時点の資料。最新巻は未確認）</t>
+          <t>既刊20巻（裏少年サンデーコミックス。電子書店の一覧で確認、2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -15924,30 +16776,40 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
+          <t>A：運動が苦手な人がジムで正しく続ける楽しさと、解説ギャグがそのまま参考になる</t>
+        </is>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／武術の修行</t>
+        </is>
+      </c>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
           <t>技法：笑いの中に正しい運動知識を一つずつ入れる『学べるギャグ』。オリジナル案：体験に来た女性が『格闘技＝痛い』と思い込み、実際はストレッチから始まって拍子抜けする回</t>
         </is>
       </c>
-      <c r="U122" s="2" t="inlineStr">
+      <c r="W122" s="2" t="inlineStr">
         <is>
           <t>主人公・トレーナーのキャラデザ、ジム名、作中の掛け声や歌は使わない</t>
         </is>
       </c>
-      <c r="V122" s="2" t="inlineStr">
+      <c r="X122" s="2" t="inlineStr">
         <is>
           <t>[事実]アニメ化され、Kindle全巻セールが報じられている（X直接検索なし） [感想]筋トレ入門として役に立つという声が多い</t>
         </is>
       </c>
-      <c r="W122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c</t>
-        </is>
-      </c>
-      <c r="X122" s="2" t="inlineStr">
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kinokuniya.co.jp/f/dsg-01-9784091274663 | https://mangapedia.com/%E3%83%80%E3%83%B3%E3%83%99%E3%83%AB%E4%BD%95%E3%82%AD%E3%83%AD%E6%8C%81%E3%81%A6%E3%82%8B%EF%BC%9F-d2owj6lc1 | https://news.denfaminicogamer.jp/news/250630c | https://bookwalker.jp/series/129327/list/</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y122" s="2" t="inlineStr">
+      <c r="AA122" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16051,30 +16913,40 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
+          <t>A：続かなかった初心者が柔術で居場所を見つける話で、FLATUPの入口の物語に近い</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／武術の修行</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
           <t>技法：『飽きっぽい初心者が続く理由』を物語の芯にする。オリジナル案：三日坊主の中学生が、毎回1つだけ技を覚えて帰る『今日のひとつ』ノートで続けられるようになる話</t>
         </is>
       </c>
-      <c r="U123" s="2" t="inlineStr">
+      <c r="W123" s="2" t="inlineStr">
         <is>
           <t>主人公名・先輩キャラの造形、作品タイトルの言い回しは使わない</t>
         </is>
       </c>
-      <c r="V123" s="2" t="inlineStr">
+      <c r="X123" s="2" t="inlineStr">
         <is>
           <t>[事実]柔術関係者のブログで連載開始が好意的に取り上げられている（X直接検索なし） [推測]柔術を正面から描く漫画が少ないため競技者の注目度は高い</t>
         </is>
       </c>
-      <c r="W123" s="2" t="inlineStr">
+      <c r="Y123" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/labels/ymweb?page=15 | https://bookwalker.jp/de2c689ec9-3c95-40fb-9398-b5d5c42cf5d4/ | https://m-dojo.hatenadiary.com/entry/2024/08/26/215830</t>
         </is>
       </c>
-      <c r="X123" s="2" t="inlineStr">
+      <c r="Z123" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y123" s="2" t="inlineStr">
+      <c r="AA123" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -16133,12 +17005,12 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>未確認（2026年時点で連載中とする報道あり）</t>
+          <t>未確認–（2026年のヤングキングBULL各号への掲載を確認。連載中）</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>1巻は2026年5月18日発売（YKコミックス）。既刊数は未確認</t>
+          <t>既刊1巻（2026年5月18日発売、YKコミックス。2026-10時点で確認。2巻の発売は未確認）</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -16178,30 +17050,40 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
+          <t>B：高校生が先輩と出会って柔術を始める入口の描き方が部分的に使える</t>
+        </is>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
           <t>技法：『先輩との出会い』を入口にした入門もの。オリジナル案：帯の色が違う先輩が、初日の後輩に寝技の『逃げ方』だけを教えて安心させる場面</t>
         </is>
       </c>
-      <c r="U124" s="2" t="inlineStr">
+      <c r="W124" s="2" t="inlineStr">
         <is>
           <t>主人公・先輩の名前と外見、作品ロゴは使わない</t>
         </is>
       </c>
-      <c r="V124" s="2" t="inlineStr">
+      <c r="X124" s="2" t="inlineStr">
         <is>
           <t>[事実]作者がXで柔術漫画として告知している（X直接検索なし、Web検索結果で確認） [推測]刊行直後のため評判の蓄積は少ない</t>
         </is>
       </c>
-      <c r="W124" s="2" t="inlineStr">
-        <is>
-          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE</t>
-        </is>
-      </c>
-      <c r="X124" s="2" t="inlineStr">
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>https://natalie.mu/comic/news/672419 | https://shopping.yahoo.co.jp/products/0184c19d53 | https://x.com/KAZU_YANSE | https://www.cmoa.jp/title/154134/vol/120/</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y124" s="2" t="inlineStr">
+      <c r="AA124" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16260,7 +17142,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>未確認–2015（2015年8号で完結とする資料あり）</t>
+          <t>2008–2015（good!アフタヌーン2008年初号〜2015年8号。2012年から休載し、2013年11月発売号で再開）</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -16305,30 +17187,40 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
+          <t>B：女子MMAの描写は学べるが、主人公の心の暗さはFLATUP向けに和らげる必要がある</t>
+        </is>
+      </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
           <t>技法：女子が格闘技にのめり込む理由を『かっこいい』だけでなく本音で描く。オリジナル案：負けず嫌いな女子高生が、勝つことより『昨日の自分に勝つ』ことに価値を見つける話</t>
         </is>
       </c>
-      <c r="U125" s="2" t="inlineStr">
+      <c r="W125" s="2" t="inlineStr">
         <is>
           <t>主人公の外見・ジム名・対戦相手キャラの造形は使わない</t>
         </is>
       </c>
-      <c r="V125" s="2" t="inlineStr">
+      <c r="X125" s="2" t="inlineStr">
         <is>
           <t>[感想]女子格闘技漫画のおすすめ記事で紹介されることがある（X直接検索なし） [推測]完結済みで知名度は中程度</t>
         </is>
       </c>
-      <c r="W125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/</t>
-        </is>
-      </c>
-      <c r="X125" s="2" t="inlineStr">
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000029696 | https://ja.wikid.org/%E9%89%84%E9%A2%A8 | https://www.cmoa.jp/title/47201/ | https://www.kodansha.co.jp/comic/products/0000029812 | https://mangapedia.com/%E9%89%84%E9%A2%A8-o5papvpyz</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y125" s="2" t="inlineStr">
+      <c r="AA125" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -16382,17 +17274,17 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>週刊少年チャンピオン</t>
+          <t>週刊少年チャンピオン → マンガクロス（2023年に移籍とする資料あり）</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2018–（終了時期は未確認）</t>
+          <t>2018–（週刊少年チャンピオンで2023年まで、その後マンガクロスへ移籍。終了は未確認）</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>少年チャンピオン・コミックス。総巻数・完結有無は未確認</t>
+          <t>既刊30巻（2024年8月時点の資料。2026-10時点の最新巻は未確認）</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -16432,30 +17324,40 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
+          <t>A：柔道が好きな仲間と続ける明るさと、試合の緊張の描き方が学べる</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
           <t>技法：『また来たくなる』気持ちを友達の存在で描く。オリジナル案：一度辞めたママ会員が子どもの練習を見学して『もう一回やりたい』と言い出す話</t>
         </is>
       </c>
-      <c r="U126" s="2" t="inlineStr">
+      <c r="W126" s="2" t="inlineStr">
         <is>
           <t>主人公たちの外見・校名・部のユニフォームデザインは使わない</t>
         </is>
       </c>
-      <c r="V126" s="2" t="inlineStr">
+      <c r="X126" s="2" t="inlineStr">
         <is>
           <t>[事実]アニメ化されている（X直接検索なし） [感想]女子部活ものとして爽やかで読みやすいという声</t>
         </is>
       </c>
-      <c r="W126" s="2" t="inlineStr">
+      <c r="Y126" s="2" t="inlineStr">
         <is>
           <t>https://www.kinokuniya.co.jp/f/dsg-01-9784253228039 | https://www.b-ch.com/titles/8013 | https://en.wikipedia.org/wiki/Ippon_Again!</t>
         </is>
       </c>
-      <c r="X126" s="2" t="inlineStr">
+      <c r="Z126" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y126" s="2" t="inlineStr">
+      <c r="AA126" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16559,30 +17461,40 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
+          <t>A：運動が苦手な初心者が小さな努力を積み重ねて強くなる過程が学べる</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行／武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
           <t>技法：『運動ができない子が主人公』で読者の入口を広げる。オリジナル案：体育が苦手だった女の子が、初めてミットを鳴らした音に自分でびっくりする場面</t>
         </is>
       </c>
-      <c r="U127" s="2" t="inlineStr">
+      <c r="W127" s="2" t="inlineStr">
         <is>
           <t>主人公の眼鏡キャラ造形・名前、校名、薙刀部の固有設定は使わない</t>
         </is>
       </c>
-      <c r="V127" s="2" t="inlineStr">
+      <c r="X127" s="2" t="inlineStr">
         <is>
           <t>[事実]小学館漫画賞（第60回）を受賞し、実写映画化された（X直接検索なし） [感想]運動が苦手な人ほど共感できるという声</t>
         </is>
       </c>
-      <c r="W127" s="2" t="inlineStr">
+      <c r="Y127" s="2" t="inlineStr">
         <is>
           <t>https://www.crank-in.net/news/80665 | https://www.animenewsnetwork.com/encyclopedia/manga.php?id=18369 | https://comic.k-manga.jp/title/57348/pv</t>
         </is>
       </c>
-      <c r="X127" s="2" t="inlineStr">
+      <c r="Z127" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y127" s="2" t="inlineStr">
+      <c r="AA127" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16641,24 +17553,24 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
+          <t>2008–2011（2008年5月号〜2011年3月号。英語版Wikipediaの掲載一覧による）</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>全9巻</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>空手／キッズ／小学生／伝統派空手／道場</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>全9巻</t>
-        </is>
-      </c>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t>空手／キッズ／小学生／伝統派空手／道場</t>
-        </is>
-      </c>
-      <c r="N128" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
           <t>アニメヒーローに憧れる小学5年生が空手と出会い、道場で成長する</t>
@@ -16686,30 +17598,40 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
+          <t>A：子どもが空手と出会い、稽古で成長していく流れがキッズクラス向けに使える</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
           <t>技法：『ヒーローへの憧れ』を入門の動機にする。オリジナル案：変身ヒーローごっこが好きな小1が、本物の構えを習って家で保護者に見せる回</t>
         </is>
       </c>
-      <c r="U128" s="2" t="inlineStr">
+      <c r="W128" s="2" t="inlineStr">
         <is>
           <t>主人公の名前・外見、作中の流派名や道場名は使わない</t>
         </is>
       </c>
-      <c r="V128" s="2" t="inlineStr">
+      <c r="X128" s="2" t="inlineStr">
         <is>
           <t>[感想]キッズ空手サイトのおすすめ空手漫画として紹介されている（X直接検索なし）</t>
         </is>
       </c>
-      <c r="W128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic</t>
-        </is>
-      </c>
-      <c r="X128" s="2" t="inlineStr">
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cmoa.jp/title/15594/ | https://bookpass.auone.jp/info/manga_feature/karate_manga/ | https://www.kids-karate.net/entry/comic | https://en.wikipedia.org/wiki/Monthly_Sh%C5%8Dnen_Rival</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y128" s="2" t="inlineStr">
+      <c r="AA128" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16813,30 +17735,40 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
+          <t>A：初心者が部活の理不尽と笑いの中で柔道に染まっていく過程が学べる</t>
+        </is>
+      </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技／青春不良コメディ</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
           <t>技法：初心者の『怖い→できた』を1話完結の小さな成功で積む構成。FLATUPでは逆に『しごきゼロ』を明示し、昔の部活の怖さと対比させる。オリジナル案：昔の部活トラウマを持つ大人会員が、優しいコーチに戸惑う『怒られないの？』ギャグ</t>
         </is>
       </c>
-      <c r="U129" s="2" t="inlineStr">
+      <c r="W129" s="2" t="inlineStr">
         <is>
           <t>主人公・先輩キャラの外見や髪型、校名・部の固有名、特徴的な歌や儀式ネタは使わない</t>
         </is>
       </c>
-      <c r="V129" s="2" t="inlineStr">
+      <c r="X129" s="2" t="inlineStr">
         <is>
           <t>[事実]柔道漫画ランキング記事で上位常連として紹介されている（X直接検索なし） [感想]経験者から『柔道部のリアル』と評されることが多い [推測]しごき描写は現代の価値観では賛否が分かれる</t>
         </is>
       </c>
-      <c r="W129" s="2" t="inlineStr">
+      <c r="Y129" s="2" t="inlineStr">
         <is>
           <t>https://dic.nicovideo.jp/a/%E6%9F%94%E9%81%93%E9%83%A8%E7%89%A9%E8%AA%9E | https://www.nihon-u.ac.jp/sports_sciences/files/news/689/pdf1.pdf | https://www.cmoa.jp/title/5030/</t>
         </is>
       </c>
-      <c r="X129" s="2" t="inlineStr">
+      <c r="Z129" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y129" s="2" t="inlineStr">
+      <c r="AA129" s="2" t="inlineStr">
         <is>
           <t>二次情報で確認</t>
         </is>
@@ -16940,30 +17872,40 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
+          <t>B：格闘技の理屈を説明する演出は使えるが、暴力と下品な笑いは避ける</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
           <t>技法：技の理屈を図解で見せて読者に『なるほど』と思わせる解説コマ、試合前の作戦会議で緊張を高める構成。アイデア：トレーナーが初心者に、ジャブがなぜ大事かを図解で説明する学習まんが風の回。オリジナルの一言案「勝ち方より、ケガしない負け方から覚えよう」</t>
         </is>
       </c>
-      <c r="U130" s="2" t="inlineStr">
+      <c r="W130" s="2" t="inlineStr">
         <is>
           <t>主人公・師匠の外見、作中の流派名や秘技名、トーナメント名、実在人物いじりの手法を使わない。過激な下ネタや他者を傷つけるギャグはブランド方針に反する</t>
         </is>
       </c>
-      <c r="V130" s="2" t="inlineStr">
+      <c r="X130" s="2" t="inlineStr">
         <is>
           <t>[事実] 第一部24巻で完結し、第二部の喧嘩稼業へ続いた。[感想] 格闘の読み合いが面白いという声と、ギャグの過激さが好みを分けるという声がある。[推測] 格闘ファンの間でカルト的人気。X直接検索なし</t>
         </is>
       </c>
-      <c r="W130" s="2" t="inlineStr">
+      <c r="Y130" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000011088 | https://comic.k-manga.jp/title/103703/pv | https://dic.nicovideo.jp/a/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD</t>
         </is>
       </c>
-      <c r="X130" s="2" t="inlineStr">
+      <c r="Z130" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y130" s="2" t="inlineStr">
+      <c r="AA130" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -17027,7 +17969,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>未確認（講談社ページで5巻・7巻の刊行を確認。7巻は2016年6月発売）</t>
+          <t>13巻まで（電子書店の配信巻数。2026-10時点で確認。紙の最新巻は講談社ページで要確認）</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -17067,30 +18009,40 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
+          <t>C：トーナメントの駆け引きの見せ方は参考になるが、暴力描写が強い</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>武道・格闘技</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
           <t>技法：試合前に選手の背景回を入れて応援したくなる構造、細かいコマで時間を引き延ばしてから大ゴマで決める。アイデア：ジム内の初心者マス大会で、出場者それぞれの『始めた理由』を一話ずつ描く。オリジナルの一言案「ここに立った時点で、もう昨日の自分には勝ってる」</t>
         </is>
       </c>
-      <c r="U131" s="2" t="inlineStr">
+      <c r="W131" s="2" t="inlineStr">
         <is>
           <t>トーナメント名・出場者の外見や実在格闘家を思わせる造形、技名、試合カードの組み方を使わない</t>
         </is>
       </c>
-      <c r="V131" s="2" t="inlineStr">
+      <c r="X131" s="2" t="inlineStr">
         <is>
           <t>[事実] 長期休載が多い作品として記事で触れられている。[感想] 続きを待ち続けているという声が多い。[推測] 再開のたびに話題になる。X直接検索なし</t>
         </is>
       </c>
-      <c r="W131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q</t>
-        </is>
-      </c>
-      <c r="X131" s="2" t="inlineStr">
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000016270 | https://www.kodansha.co.jp/comic/products/0000014954 | https://kai-you.net/article/29479 | https://mangapedia.com/%E6%9C%A8%E5%A4%9A%E5%BA%B7%E6%98%AD-ebbhlv10q | https://www.cmoa.jp/title/75163 | https://honto.jp/ebook/pd_28789081_094.html</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y131" s="2" t="inlineStr">
+      <c r="AA131" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -17194,30 +18146,40 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
+          <t>A：小さな子が師匠のもとで課題を一つずつクリアして成長する流れが、キッズクラスの物語にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行</t>
+        </is>
+      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
           <t>技法：『初心者が一歩ずつ上達する』を素直に描く少年漫画の型。FLATUPに最も近い思想の作品。FLATUP案：キッズ会員が受け身を覚えるまでの3話シリーズ。オリジナル台詞案『こわいって言えたら、もう一歩目だよ』。</t>
         </is>
       </c>
-      <c r="U132" s="2" t="inlineStr">
+      <c r="W132" s="2" t="inlineStr">
         <is>
           <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
         </is>
       </c>
-      <c r="V132" s="2" t="inlineStr">
+      <c r="X132" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]1987年に講談社漫画賞を受賞。[事実]1988年にTVアニメ化（二次情報）。[感想]子どもでも読める王道カンフー漫画として長く愛されている。</t>
         </is>
       </c>
-      <c r="W132" s="2" t="inlineStr">
+      <c r="Y132" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000043199 | https://www.cmoa.jp/title/5029</t>
         </is>
       </c>
-      <c r="X132" s="2" t="inlineStr">
+      <c r="Z132" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y132" s="2" t="inlineStr">
+      <c r="AA132" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -17276,12 +18238,12 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>1990年代後半–2004年頃（第20巻の初出が2004年7月号–11月号。開始年は未確認）</t>
+          <t>1997–2004（月刊少年マガジン1997年3月号–2004年11月号）</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）</t>
+          <t>全20巻（講談社コミックス。第20巻 2005年2月刊行）／全14巻とする資料もあり（資料により異なる）／超合本版あり（電子）</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -17321,30 +18283,40 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
+          <t>A：旅と仲間の掛け合いの中で礼や優しさを学ぶ描写が、初心者の成長物語に使える</t>
+        </is>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
           <t>技法：教わる側から教える側へ回る成長の描き方。FLATUP案：入会2年目の会員が、新しく来た初心者に準備運動を教える回。</t>
         </is>
       </c>
-      <c r="U133" s="2" t="inlineStr">
+      <c r="W133" s="2" t="inlineStr">
         <is>
           <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
         </is>
       </c>
-      <c r="V133" s="2" t="inlineStr">
+      <c r="X133" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[感想]前作の雰囲気を引き継いだ続編として読まれている。[推測]前作ほどの知名度はない。</t>
         </is>
       </c>
-      <c r="W133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809</t>
-        </is>
-      </c>
-      <c r="X133" s="2" t="inlineStr">
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kodansha.co.jp/comic/products/0000045830 | https://www.kodansha.co.jp/comic/products/0000319966 | https://www.cmoa.jp/title/45809 | https://mangapedia.com/%E6%96%B0%E9%89%84%E6%8B%B3%E3%83%81%E3%83%B3%E3%83%9F-uxn54ysyu | https://www.kodansha.co.jp/comic/products/0000319897</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y133" s="2" t="inlineStr">
+      <c r="AA133" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
@@ -17448,37 +18420,47 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
+          <t>A：やさしい絵柄と分かりやすい武術描写で、子ども向けの修行回の参考になる</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>武術の修行</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
           <t>技法：長期シリーズでも『やさしい強さ』の芯をぶらさない。FLATUP案：ブランドの思想（強さ＝やさしさ）を毎話の結末で確認する構成ルール。</t>
         </is>
       </c>
-      <c r="U134" s="2" t="inlineStr">
+      <c r="W134" s="2" t="inlineStr">
         <is>
           <t>チンミ・タンタン等のキャラ名と外見（坊主頭の小柄な少年・カンフー着）、大林寺などの寺院名、固有の技名を流用しない。</t>
         </is>
       </c>
-      <c r="V134" s="2" t="inlineStr">
+      <c r="X134" s="2" t="inlineStr">
         <is>
           <t>X直接検索なし。[事実]第28巻（2021年）から第29巻（2026年）まで刊行間隔が空き、連載再開が講談社から告知された。[感想]再開を喜ぶ長年の読者の声がある。</t>
         </is>
       </c>
-      <c r="W134" s="2" t="inlineStr">
+      <c r="Y134" s="2" t="inlineStr">
         <is>
           <t>https://www.kodansha.co.jp/comic/products/0000426730 | https://news.kodansha.co.jp/comics/8666 | https://www.kodansha.co.jp/comic/products/0000041420</t>
         </is>
       </c>
-      <c r="X134" s="2" t="inlineStr">
+      <c r="Z134" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Y134" s="2" t="inlineStr">
+      <c r="AA134" s="2" t="inlineStr">
         <is>
           <t>確認済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y134"/>
+  <autoFilter ref="A1:AA134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17489,7 +18471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17566,7 +18548,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -17587,26 +18569,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>確認状態</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
         <v>133</v>
       </c>
     </row>

--- a/docs/anime/manga_research/works_database.xlsx
+++ b/docs/anime/manga_research/works_database.xlsx
@@ -694,8 +694,16 @@
           <t>主人公の世間知らずによる勘違い、ヘタレぶり、仲間からのいじり</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>B：お坊ちゃんが不良の世界で一人前になる勘違いと成長は、初心者の話に応用できる</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>技法：①“場違いな弱い主人公”が居場所を得る成長譚 ②方言の迫力と温かさの両立 ③情けない顔と覚悟の顔の対比。FLATUP案：格闘技未経験のサラリーマンがジムで最初は縮こまり、少しずつ顔つきが変わる連作。オリジナルの一言案『怖いままでいい。それでも来たあんたが一番かっこええ』</t>
@@ -713,7 +721,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://www.weblio.jp/content/BADBOYS | https://www.cmoa.jp/title/241/ | https://www.oricon.co.jp/news/2385533/full/ | https://www.toy-people.com/jp/?p=108156</t>
+          <t>https://www.weblio.jp/content/BADBOYS | https://www.cmoa.jp/title/241/ | https://www.oricon.co.jp/news/2385533/full/ | https://www.toy-people.com/jp/?p=108156 | https://www.shonengahosha.co.jp/book_Info.php?id=6513 | https://www.shonengahosha.co.jp/badboys/hp/pc/index.html</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -723,7 +731,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -823,8 +831,16 @@
           <t>仲間内のじゃれ合い、強面の意外な弱点</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>C：世代を継ぐリーダーの描き方は参考程度</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>技法：リーダーの器を“守るもの”で描く。FLATUP案：ジムのキャプテンが大会より後輩の怪我を優先する選択回</t>
@@ -842,7 +858,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Bad_Boys_(manga) | https://booklog.jp/item/1/4785921420 | https://mangapedia.com/BADBOYS%20%E3%82%B0%E3%83%AC%E3%82%A2%E3%83%BC-saan727zv</t>
+          <t>https://en.wikipedia.org/wiki/Bad_Boys_(manga) | https://booklog.jp/item/1/4785921420 | https://mangapedia.com/BADBOYS%20%E3%82%B0%E3%83%AC%E3%82%A2%E3%83%BC-saan727zv | https://www.shonengahosha.co.jp/book_Info.php?id=7307 | https://www.shonengahosha.co.jp/book_Info.php?id=7293</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -909,12 +925,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2012頃–連載中（開始時期は未確定）</t>
+          <t>2012–2025（第1巻は2012年12月刊行、最終第30巻は2025年12月22日発売）</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>既刊27巻以上（27巻は2024年8月）</t>
+          <t>全30巻（第30巻は2025年12月22日発売の完結巻、少年画報社公式で確認）</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -934,26 +950,34 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>時代が変わる中で、出所した主要人物が仲間内で冷遇されるなど、不良たちの居場所の変化が描かれる（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>広島弁が基調と思われる（未確認）</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>広島弁が基調と思われる（未確認）</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>C：広島の不良群像は参考程度</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
           <t>技法：同じ世界観で作品をつなぐ“ユニバース”構成。FLATUP案：FLATUP作品群でも、ジム・商店街・学校を共通舞台にし、別作品のキャラが背景にさりげなく映る仕掛け</t>
@@ -971,7 +995,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/11399/ | https://www.fujisan.co.jp/product/2678/b/2486919/ | https://mangapedia.com/%E7%94%B0%E4%B8%AD%E5%AE%8F-1zai5wxnx</t>
+          <t>https://www.cmoa.jp/title/11399/ | https://www.fujisan.co.jp/product/2678/b/2486919/ | https://mangapedia.com/%E7%94%B0%E4%B8%AD%E5%AE%8F-1zai5wxnx | https://www.shonengahosha.co.jp/book_Info.php?id=11128 | https://www.shonengahosha.co.jp/book_Info.php?id=6970 | https://natalie.mu/profile/2285 | https://cdn.animenewsnetwork.com/news/2019-04-27/kippo-manga-final-arc-starts-in-14th-volume-this-summer/.146223</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1081,8 +1105,16 @@
           <t>元ヤン同士の昔話や、家族の前での不器用さ</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>C：大人になった元不良が家族を守る話は参考になるが、青年向けで重い</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
           <t>技法：“元不良が親になる”視点で暴力と責任を描く。FLATUP案：昔やんちゃだった父親が、子どもと一緒にキッズクラスに通い始める親子回。オリジナルの一言案『昔は殴ってばかりだった手で、今日は息子の帯を結んだ』</t>
@@ -1210,8 +1242,16 @@
           <t>見栄と勘違いからの大失敗、下心が裏目に出る落差、顔芸の誇張</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>A：キザな表情とシリアスからの脱力オチ、不器用な優しさの落差がそのまま学べる</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
           <t>技法：『強いのにウブ』というギャップで主人公を愛される存在にする。二人組のボケとツッコミで説明パートをテンポよく進める。オリジナル案：最強のトレーナー二人が、初心者の会員にかっこつけようとして毎回空回りし、結局『優しさ』だけが伝わる日常回</t>
@@ -1339,8 +1379,16 @@
           <t>常識外れのスケールの大きいバカ行動、下心と勘違い、エリート側との価値観の落差</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>A：見た目が怖い大人が一番まともに生徒と向き合う「強面の先生」の型が学べる</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生／青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t>技法：『怖そうな大人が実は一番優しい』という第一印象の反転。重い悩みの直後にギャグで救う緩急。オリジナル案：強面のトレーナーが、ミット打ちが怖くて泣きそうな子どもに、自分も最初は怖かったと失敗談を披露して笑わせる回。『見た目より中身で強くなろう』という独自の合言葉</t>
@@ -1430,7 +1478,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>全9巻（英語版9巻の刊行情報より。日本版の巻数は講談社公式で未確認）</t>
+          <t>全9巻（講談社コミックス。第9巻＜完＞は2011年11月17日発売、講談社公式で確認）。英語版も全9巻</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1468,8 +1516,16 @@
           <t>本編同様の下ネタと突飛な行動、湘南の旧友との掛け合い</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>B：居場所のない子どもと大人の関わり方は学べるが、テーマが重めなので扱いに注意</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生</t>
+        </is>
+      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
           <t>技法：『期限付き』の物語構成（○日間で変わる）。オリジナル案：『体験から14日間』をテーマに、初心者が入会2週間で少しずつ表情が変わっていく連載形式のSNS漫画</t>
@@ -1487,7 +1543,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://dic.pixiv.net/history/GTO/5324594/source | https://animenewsnetwork.com/news/2011-08-29/gto/shonan-14-days-sequel-manga-to-end-in-japan | https://cdn.animenewsnetwork.com/encyclopedia/releases.php?id=21895</t>
+          <t>https://dic.pixiv.net/history/GTO/5324594/source | https://animenewsnetwork.com/news/2011-08-29/gto/shonan-14-days-sequel-manga-to-end-in-japan | https://cdn.animenewsnetwork.com/encyclopedia/releases.php?id=21895 | https://www.kodansha.co.jp/comic/products/0000017369 | https://www.kodansha.co.jp/comic/products/0000016989</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1497,7 +1553,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1605,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>週刊ヤングマガジン（のちに掲載媒体を変え『GTO パラダイス・ロスト 改』に改題、ヤングマガジン掲載）</t>
+          <t>ヤングマガジン（2014年〜）。後半はマガジンポケット（『改』第22巻の初出に「マガジンポケット」2024年9月掲載の記載）</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1559,7 +1615,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>『改』第19巻（2026年4月20日発売）を確認。改題前の単独巻数は未確認</t>
+          <t>旧版『GTO パラダイス・ロスト』は第12巻（2019年11月発売）まで確認、旧版の最終巻数は未確認。『改』は作者が再構成・加筆した版で2025年7月から刊行、1〜11巻は旧版と同内容。『改』は第23巻（2026年6月、国立国会図書館の要約に「グランドフィナーレ」）まで確認（2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1597,8 +1653,16 @@
           <t>本編同様の下ネタ・型破りな行動に加え、芸能界の風刺</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>B：強面教師の型は使えるが、芸能界・炎上など大人向けの題材が多い</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生</t>
+        </is>
+      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
           <t>技法：同じ主人公を新しい舞台に放り込み、時代の問題（SNS、炎上）と組み合わせる。オリジナル案：SNSで『強そうに見せる』ことに疲れた若者が、ジムで『ダサくても続ける強さ』を知るエピソード</t>
@@ -1616,7 +1680,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/new-releases?page=70 | https://www.kinokuniya.co.jp/f/dsd-101001011040008--?p=17 | https://dic.pixiv.net/history/GTO/8627698</t>
+          <t>https://www.kodansha.co.jp/comic/new-releases?page=70 | https://www.kinokuniya.co.jp/f/dsd-101001011040008--?p=17 | https://dic.pixiv.net/history/GTO/8627698 | https://www.kodansha.co.jp/comic/products/0000409898 | https://www.kodansha.co.jp/comic/products/0000014870 | https://www.kodansha.co.jp/comic/products/0000426903 | https://ndlsearch.ndl.go.jp/books/R100000002-I034771819</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1626,7 +1690,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1772,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読）</t>
+          <t>湘南最強を争う7人制トーナメントの中で、ケンカ自慢の新入生が強豪校で居場所を勝ち取っていく成長が軸（紹介記事による）</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1723,11 +1787,19 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
+          <t>ケンカ描写の合間に、軽いお色気の笑いを挟むと紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>C：トーナメント形式で仲間を集める構成は参考になるが、ケンカ中心でFLATUP向けの要素は少ない</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>技法：既存の世界観を『同じ場所の後輩世代』で描く関連作の作り方。オリジナル案：成田の各ジムや道場の『合同練習会』を舞台に、競い合いながら仲良くなる交流回</t>
@@ -1745,7 +1817,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/77999 | https://booklive.jp/focus/author/a_id/3538/sort/t1 | https://anime.jepang.org/en/manga/65683/Shonan_Seven | https://www.fujisan.co.jp/product/743/new/</t>
+          <t>https://www.cmoa.jp/title/77999 | https://booklive.jp/focus/author/a_id/3538/sort/t1 | https://anime.jepang.org/en/manga/65683/Shonan_Seven | https://www.fujisan.co.jp/product/743/new/ | https://www.akitashoten.co.jp/comics/4253223311 | https://www.akitashoten.co.jp/comics/4253226833 | https://www.akitashoten.co.jp/m-champion/2019/8</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1755,7 +1827,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -1855,8 +1927,16 @@
           <t>はったりが偶然うまくいく勘違い連鎖、ビビりの顔芸、卑怯さと根性の落差</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>A：弱い主人公のはったりと勘違いが転がって大きくなるギャグの落差が学べる</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ／劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
           <t>技法：『心の声』と『実際の行動』をずらして描く二重構造。偶然の勝利が誤解を呼ぶコメディ。オリジナル案：運動経験ゼロの会員が、ジム見学で緊張して強がった結果、なぜか『経験者』と思われて焦る回。最後は正直に『初心者です』と言えた勇気を描く</t>
@@ -1941,7 +2021,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2013年12月頃または2014年開始〜（資料により差。終了年未確認）</t>
+          <t>2016年頃–2023年（第1巻初出は月刊少年マガジン2016年3月号〜8月号、最終第20巻の初出は2022年5月号〜2023年1月号。開始を2013年12月頃・2014年とする資料もあり、資料により異なる）</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1966,7 +2046,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読）</t>
+          <t>正体を隠して働く二重生活の緊張と、女装姿で出会った相手との恋愛のすれ違いが軸。巻が進むとタイムリープや三角関係も描かれる（紹介記事による）</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1981,11 +2061,19 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>主役が女装という設定が紹介されている（詳細未確認）</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr"/>
-      <c r="U12" s="2" t="inlineStr"/>
+          <t>女装した主人公が暴走族の抗争に巻き込まれる設定のギャップを笑いにする「女装ヤンキーラブコメ」と紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>B：正体を隠す主人公のギャップで笑わせる手法は使えるが、女装設定はFLATUPにそのままは合わない</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
           <t>技法：前作の舞台を『○年後』に設定し、新キャラで世界観を広げる続編の作り方。オリジナル案：FLATUP初期メンバーが卒業した後、新しい初心者世代が入ってくる『第2期』シリーズ</t>
@@ -2003,7 +2091,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/titles/1000006688 | https://www.kodansha.co.jp/comic/products/0000047934 | https://mangapedia.com/%E5%8A%A0%E7%80%AC%E3%81%82%E3%81%A4%E3%81%97-8q6sb22ju</t>
+          <t>https://www.kodansha.co.jp/titles/1000006688 | https://www.kodansha.co.jp/comic/products/0000047934 | https://mangapedia.com/%E5%8A%A0%E7%80%AC%E3%81%82%E3%81%A4%E3%81%97-8q6sb22ju | https://www.kodansha.co.jp/comic/products/0000373968</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2075,7 +2163,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>全26巻（少年チャンピオン・コミックス）＋作者による外伝。新装版は全22巻。完全版の巻数は情報源で食い違い（19巻説・21巻説）のため未確認</t>
+          <t>全26巻（少年チャンピオン・コミックス）＋外伝3巻。完全版は全19巻＋外伝2巻、新装版は全22巻＋外伝2巻（プレスリリースによる。以前の19巻説・21巻説の食い違いは、この区分で整理できる）</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2113,8 +2201,16 @@
           <t>強面の不良が女性や家族の前で急に弱くなる落差、仲間同士のボケとツッコミ、主人公の天然な行動による脱力</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr"/>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>B：仲間の並びの構図と短く言い切るセリフの間は学べるが、ケンカが中心</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>技法：①主人公を他人の視点で語らせて大きさを出す ②激しい場面の直後に静かな日常コマを置く緩急 ③行事（入会・昇級・卒業）を章の区切りにする。FLATUP案：初心者が先輩トレーナーを遠くから見て『あの人みたいに、怖がらずに立っていたい』と思う導入。ケンカではなく“初めてのミット打ち”を見開きの山場にする</t>
@@ -2132,7 +2228,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://koubo.jp/press-release/prtimes/c40601_r794 | https://www.oricon.co.jp/news/2430258/full/ | https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366 | https://dic.nicovideo.jp/t/a/%E3%82%AF%E3%83%AD%E3%83%BC%E3%82%BA%28%E6%BC%AB%E7%94%BB%29</t>
+          <t>https://koubo.jp/press-release/prtimes/c40601_r794 | https://www.oricon.co.jp/news/2430258/full/ | https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366 | https://dic.nicovideo.jp/t/a/%E3%82%AF%E3%83%AD%E3%83%BC%E3%82%BA%28%E6%BC%AB%E7%94%BB%29 | https://animeanime.jp/release/prtimes/20251125/259000.html</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2242,8 +2338,16 @@
           <t>主人公の天然な勘違い・食いしん坊ぶり、強面キャラのギャップ、仲間同士のじゃれ合い</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr"/>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>A：強さと優しさを両立させる主人公と、友達になることを大切にする空気がFLATUPの思想に近い</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>技法：①敵意を笑顔と素直さで溶かす主人公像 ②世代交代（先輩の卒業）で物語を区切る ③勢力図より“仲間の輪”が広がる様子を描く。FLATUP案：初心者が怖そうな常連に挨拶し続け、やがて一緒にスパーの順番を待つ仲になる話。オリジナルの一言案『また来週も、ここで会おうぜ』</t>
@@ -2371,8 +2475,16 @@
           <t>元ヤンの教師が教育現場のルールに戸惑う、強面が慣れない敬語を使うギャップ、生徒からのいじりに本気で動揺する</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr"/>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>A：元不良の先生が怒鳴らずに生徒と向き合う「強面の先生」の型がそのまま学べる</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>強面の先生</t>
+        </is>
+      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
           <t>技法：①強い大人が“力を使わない”ことで強さを見せる ②生徒一人ずつのエピソード回し ③日常と対決の交互配置。FLATUP案：元・荒れていたトレーナーが、いじめられっ子の会員に手加減の大切さを教える回。オリジナルの一言案『殴れることより、殴らないで済む強さを持とうな』</t>
@@ -2500,8 +2612,16 @@
           <t>最強の主人公が恋や日常の小事に弱いギャップ、方言の掛け合い</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr"/>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>C：最強の男の原点を描く前日譚の作り方は参考になるが、ケンカ中心</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>技法：①方言でキャラの土地柄と温度を出す ②“最強の人の弱かった頃”を描く前日譚 ③相手のリアクションで強さを表す。FLATUP案：成田の空港の見える土手で、まだ泣き虫だった頃のジム代表を描く前日譚。千葉の言葉の語感を少し混ぜる</t>
@@ -2629,8 +2749,16 @@
           <t>中学生らしい背伸びや見栄が空回りする笑い</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>C：チームへの憧れと加入の描き方は参考になるが、暴走族ものでFLATUPには合いにくい</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
           <t>技法：①憧れの集団に入るまでの“入門編” ②因縁の相手を影で見せる演出 ③先輩の一言で主人公が変わる転機。FLATUP案：入門をためらう少年がジムの窓越しに練習を覗き続け、ついにドアを開ける回。暴走族ではなく“ジムという居場所”への憧れに置き換える</t>
@@ -2758,8 +2886,16 @@
           <t>三人組のボケ・ツッコミ、勘違いと空回り、貧乏ネタ</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>B：名もない三人組の友情と団地の日常は、ジムに通う仲間の話に応用できる</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持／青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
           <t>技法：①主役ではない“名もなき人”の物語 ②三人組の役割分担（突っ込む・止める・ボケる）③生活感のある背景で親近感を出す。FLATUP案：ジムの体験に来た運動経験ゼロの三人組（会社員・主婦・高校生）の連作コメディ</t>
@@ -2887,8 +3023,16 @@
           <t>コワモテ集団の内輪での抜けた会話（量は少なめ）</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>C：集団の誕生と因縁の描き方は参考になるが、抗争が中心</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
           <t>技法：①“チームが生まれるまで”を描く起源譚 ②俯瞰の群衆と正面のアップの切り替え。FLATUP案：FLATUP GYM創設期、会員3人から始まった“最初の合同練習”を描く起源回。対立ではなく、みんなでマットを敷く場面を山場にする</t>
@@ -2953,7 +3097,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>鈴木大（原作クレジットの詳細は未確認）</t>
+          <t>鈴木大（秋田書店公式の書誌で著者として表記。高橋ヒロシの原作・監修としての関わり方は要確認）</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2973,12 +3117,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2012–終了年未確認</t>
+          <t>2012–2021（ヤングチャンピオン2012年No.5〜とする情報あり。第1巻は2012年7月6日、最終第23巻は2021年9月17日刊行）</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>全23巻（電子書店で完結表記）</t>
+          <t>全23巻（第23巻が最終巻、秋田書店公式で確認）</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3016,8 +3160,16 @@
           <t>未確認（暴力描写中心でギャグは少ないと思われる）</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr"/>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>C：怪物と恐れられた男の孤独は参考程度。暴力描写が中心</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
           <t>技法：①周囲の恐怖のリアクションで人物の怖さを表す。FLATUP案：逆に“見た目が怖いけど実は一番優しいトレーナー”の誤解を解く回に転用し、恐怖の目線が尊敬に変わる流れを描く</t>
@@ -3035,7 +3187,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://booklive.jp/focus/author/a_id/19009 | https://ebookjapan.yahoo.co.jp/lists/authors/14329 | https://mangapedia.com/gd/q5ruq4yjk</t>
+          <t>https://booklive.jp/focus/author/a_id/19009 | https://ebookjapan.yahoo.co.jp/lists/authors/14329 | https://mangapedia.com/gd/q5ruq4yjk | https://www.akitashoten.co.jp/comics/4253151019 | https://www.akitashoten.co.jp/comics/4253302149</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -3045,7 +3197,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3234,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>高橋ヒロシ（原作として表記）</t>
+          <t>監修：高橋ヒロシ（秋田書店公式の表記。販売サイトでは原作と表記するものもあり、資料により異なる）</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3097,56 +3249,64 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>未確認（単行本はヤングチャンピオン・コミックス）</t>
+          <t>ヤングチャンピオン（秋田書店公式の2009年No.15誌面ページが検索で該当。掲載期間の詳細は未確認）</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t>2009年頃（第1巻は2009年4月20日刊行、既刊2巻。正確な連載期間は未確認）</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>全2巻</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>不良／中学生／前日譚</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>『クローズ』</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>無敵と呼ばれた男の中学時代、強さの孤独</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>鈴蘭で無敵を誇った男の中学時代を描き、強さの原点に迫る前日譚と紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>全2巻</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>不良／中学生／前日譚</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>『クローズ』</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>無敵と呼ばれた男の中学時代、強さの孤独</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>未確認（無敵の人物の原点を描く前日譚であることのみ確認）</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>C：無敵の人物の原点を描く手法は参考程度</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
           <t>技法：完成された強者の“未完成だった頃”を描く前日譚の型。FLATUP案：ジムの最強会員が、初めての試合で緊張して眠れなかった夜を描く短編</t>
@@ -3164,7 +3324,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://booklive.jp/product/index/title_id/146518/vol_no/001 | https://wowma.jp/item/529439031</t>
+          <t>https://booklive.jp/product/index/title_id/146518/vol_no/001 | https://wowma.jp/item/529439031 | https://www.akitashoten.co.jp/comics/4253147216 | https://akitashoten.co.jp/series/2408 | https://akitashoten.co.jp/youngchampion/2009/15</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3231,12 +3391,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>単行本『クローズ外伝』は1995年10月6日、『続・クローズ外伝』は1998年9月4日刊行。雑誌掲載時期は未確認</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>巻数未確認（作者による外伝が3冊あるとする二次情報あり。新装版『クローズ外伝』も刊行）</t>
+          <t>単行本は『クローズ外伝』全1巻（番外編3編を収録）、『続・クローズ外伝』1巻など。シリーズ全体で単行本外伝3巻、完全版『CROWS外伝』2巻、新装版『クローズ外伝』2巻（プレスリリースによる。新装版は2016年5月6日から刊行）</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3246,7 +3406,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>『クローズ』本編</t>
+          <t>『クローズ』本編、『続・クローズ外伝』、完全版『CROWS外伝』、『新装版 クローズ外伝』。秋田書店公式に『クローズ外伝 片桐拳物語』のシリーズページもある（作者は未確認）</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3274,8 +3434,16 @@
           <t>脇役トリオの掛け合い</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>C：脇役を主役にする短編の作り方は参考程度</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
           <t>技法：脇役一人ずつに一話を与える短編集の型。FLATUP案：受付スタッフ、清掃担当、最年長会員など、ジムの脇役を一話ずつ主役にする番外編シリーズ</t>
@@ -3293,7 +3461,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://mechacomic.jp/books/147009 | https://booklive.jp/focus/author/a_id/12526</t>
+          <t>https://mechacomic.jp/books/147009 | https://booklive.jp/focus/author/a_id/12526 | https://www.akitashoten.co.jp/series/1191 | https://www.akitashoten.co.jp/series/1284 | https://www.akitashoten.co.jp/series/6470 | https://www.akitashoten.co.jp/comics/4253213022 | https://koubo.jp/press-release/prtimes/c40601_r794</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3365,7 +3533,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>未確認（新装版あり）</t>
+          <t>新装版『WORST外伝』は第2巻（2020年4月8日発売）まで秋田書店公式で確認。旧版の巻数は未確認</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3403,8 +3571,16 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr"/>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>C：チームの始まりを描く前日譚は参考程度</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
           <t>技法：集団の“初代”を描く起源譚。FLATUP案：初代会員たちの記念写真から始まる回想短編</t>
@@ -3422,7 +3598,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366</t>
+          <t>https://booklive.jp/search/keyword/a_ids/12526/tag_ids/100366 | https://www.akitashoten.co.jp/comics/4253254713</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3484,12 +3660,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>未確認（少年チャンピオン・コミックス エクストラ）</t>
+          <t>未確認（『クローズ』25周年記念のトリビュート作品集。少年チャンピオン・コミックス エクストラ）</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>未確認（3巻の電子版は2019年10月8日発売）</t>
+          <t>単行本は第1巻2016年6月、第2巻2019年2月、第3巻2019年10月刊行。各作品の初出時期は未確認</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3532,8 +3708,16 @@
           <t>作家ごとに異なる</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr"/>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>B：複数の作家が同じ世界を別の味で描く、オマージュの距離感の取り方が学べる</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
           <t>技法：同じ世界を複数の作り手が解釈するアンソロジー形式。FLATUP案：トレーナーや会員がそれぞれ“自分にとってのFLATUP”を4コマで描く企画</t>
@@ -3551,7 +3735,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://booklive.jp/product/index/title_id/379770/vol_no/001 | https://booklive.jp/product/index/title_id/379770/vol_no/003</t>
+          <t>https://booklive.jp/product/index/title_id/379770/vol_no/001 | https://booklive.jp/product/index/title_id/379770/vol_no/003 | https://www.akitashoten.co.jp/comics/4253131751 | https://www.akitashoten.co.jp/comics/4253131743 | https://www.akitashoten.co.jp/comics/4253131735</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3643,26 +3827,34 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>母を亡くした少年が、同じ棟に住む人物との出会いで変わっていく姿が軸と紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>B：喪失を抱えた少年が年上の人物との出会いで変わる導入は、入会前の不安を描く話に応用できる</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
           <t>技法：長寿シリーズを新世代で再起動する“正統続編”の作り方（旧作キャラの祝福演出・大型PR）。FLATUP案：ジムの周年企画で、歴代会員が新入会員を迎える“世代バトン”のショート動画</t>
@@ -3680,7 +3872,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://prtimes.jp/main/html/rd/p/000000782.000040601.html | https://www.oricon.co.jp/news/2430258/full/ | https://koubo.jp/press-release/prtimes/c40601_r858 | https://crowsworst.akitashoten.co.jp/</t>
+          <t>https://prtimes.jp/main/html/rd/p/000000782.000040601.html | https://www.oricon.co.jp/news/2430258/full/ | https://koubo.jp/press-release/prtimes/c40601_r858 | https://crowsworst.akitashoten.co.jp/ | https://www.inside-games.jp/release/prtimes/20261020/313495.html</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3790,8 +3982,16 @@
           <t>無口な主人公を周囲が勝手に誤解する勘違いギャグ、強面と行動の落差</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>A：無口で怖そうな見た目なのに実は頼れる、という見た目と中身の落差が学べる</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>技法：『喋らないキャラ』の心を周囲の反応と間で描く。オリジナル案：無口で強面の会員が、実は子どもクラスの片付けを毎回こっそり手伝っていたと判明する話。言葉ではなく行動で優しさを見せる</t>
@@ -3876,12 +4076,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2022年〜（2020年に40周年企画の読み切り、2022年17号から連載）。終了時期未確認</t>
+          <t>2022年（2020年に40周年企画の読み切り。週刊ヤングマガジン2022年17号から連載、2022年8月22日発売号で本編終了）。その後スピンオフ「ファミリー編」が2023–2024年に掲載（Wikipediaは2024年5月13日終了と記載）</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>第4巻（2024年4月5日発売）を確認、既刊5巻とする資料あり。完結は未確認</t>
+          <t>5巻まで（第5巻は2024年7月5日発売、講談社公式で確認。完結の明記は未確認）（2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3901,7 +4101,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読）</t>
+          <t>高校時代を過ごした商店街に40歳の主人公が戻り、現在と過去が重なる（紹介記事による）</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3916,11 +4116,19 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>未確認（家族編があると紹介されている）</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr"/>
-      <c r="U27" s="2" t="inlineStr"/>
+          <t>40歳になった無口な主人公と、異常な身体能力を持つ親族一家（ファミリー編）が草野球などで騒ぎを起こす落差で笑わせる（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>A：大人になった元不良と家族のギャグは、親世代向けのFLATUP作品にすぐ使える</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
           <t>技法：『あの頃の主人公が中年になったら』という後日談。オリジナル案：40代の元ヤン会員が、子どもと一緒に親子クラスに通う話</t>
@@ -3938,7 +4146,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/%E3%82%B4%E3%83%AA%E3%83%A9%E3%83%BC%E3%83%9E%E3%83%B340-e3l54ku9q | https://www.kodansha.co.jp/comic/new-releases/p?page=244</t>
+          <t>https://mangapedia.com/%E3%82%B4%E3%83%AA%E3%83%A9%E3%83%BC%E3%83%9E%E3%83%B340-e3l54ku9q | https://www.kodansha.co.jp/comic/new-releases/p?page=244 | https://www.kodansha.co.jp/comic/products/0000395175 | https://www.kodansha.co.jp/comic/products/0000352524 | https://kc.kodansha.co.jp/product?item=0000387615 | https://en.wikipedia.org/wiki/Gorillaman | https://admin.animenewsnetwork.com/news/2022-08-15/harold-sakuishi-gorillaman-40-manga-ends-on-august-22/.188668</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3948,7 +4156,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4048,8 +4256,16 @@
           <t>カッコつけが空回りする『ちょっとカッコ悪いリアル系』の笑い</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>B：不良に憧れる少年のカッコつけとカッコ悪さの落差は学べる</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
           <t>技法：『憧れから始まる』主人公。カッコ悪さを隠さないリアルさ。オリジナル案：格闘技漫画に憧れてジムに来た会員が、初日にジャブすらぎこちなくて落ち込むが、トレーナーに『憧れて来た時点で一番大事なものは持ってる』と励まされる話</t>
@@ -4067,7 +4283,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/%E3%83%89%E3%83%AD%E3%83%83%E3%83%97-j9x6p0ah5 | https://www.cmoa.jp/title/110507/vol/14/ | https://comic.k-manga.jp/title/113964/pv | https://www.oricon.co.jp/news/2253611/full/</t>
+          <t>https://mangapedia.com/%E3%83%89%E3%83%AD%E3%83%83%E3%83%97-j9x6p0ah5 | https://www.cmoa.jp/title/110507/vol/14/ | https://comic.k-manga.jp/title/113964/pv | https://www.oricon.co.jp/news/2253611/full/ | https://www.akitashoten.co.jp/comics/4253214274 | https://www.akitashoten.co.jp/comics/4253214282</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4077,7 +4293,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4177,8 +4393,16 @@
           <t>大阪弁の掛け合い、主人公の下心による失敗、身内ノリの誇張</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>C：方言のテンポと仲間内のバカ話は参考になるが、走り屋・車文化が中心</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
           <t>技法：方言の会話テンポでキャラを立てる。地域性（地元の道・街）を物語の舞台装置にする。オリジナル案：成田の地元（成田山参道、空港周辺）をロードワークで走る会員たちの会話劇。千葉ことばを少し取り入れた掛け合い</t>
@@ -4288,7 +4512,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読。前作と同様の作風と推測されるが未確認）</t>
+          <t>前作と比べて抗争や走りの描写が生々しくシリアスになったと評されている（紹介記事による）</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4303,11 +4527,19 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+          <t>シリアスな抗争の中に笑える場面を混ぜ、笑いと熱さを両立させていると評価されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>C：笑いと熱さの切り替えは参考になるが、走り屋・抗争が中心</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
           <t>技法：同じ読みのタイトルを表記違い（カタカナ→ひらがな・漢字）で続編化するネーミング手法。オリジナル案：FLATUPシリーズの第2部を表記だけ変えて区別する（例：『フラットアップ』と『ふらっとあっぷ』）</t>
@@ -4325,7 +4557,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://mangapedia.com/%E3%81%AA%E3%81%AB%E3%82%8F%E5%8F%8B%E3%81%82%E3%82%8C-3t35zu6ut | https://booklive.jp/focus/author/a_id/3869</t>
+          <t>https://mangapedia.com/%E3%81%AA%E3%81%AB%E3%82%8F%E5%8F%8B%E3%81%82%E3%82%8C-3t35zu6ut | https://booklive.jp/focus/author/a_id/3869 | https://www.kodansha.co.jp/comic/products/0000014874 | https://www.kodansha.co.jp/comic/products/0000010936</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4335,7 +4567,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4435,8 +4667,16 @@
           <t>二重生活がバレそうになるドタバタ、家族の過剰なヤンキーぶり、勘違いの連鎖</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>A：怖い家族に隠れて普通の高校生を演じる二重生活のギャグと優しさが、そのまま学べる</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
           <t>技法：①二重生活によるサスペンスと笑い ②家族の愛を誇張したギャグで描く。FLATUP案：“格闘技が怖い子”が家族に内緒で体験に来る話。正体バレの代わりに“初めてのミット打ちを家族に見られる”山場</t>
@@ -4454,7 +4694,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ranking.net/items/c27482 | https://www.kinokuniya.co.jp/f/dsg-08-9981904201 | https://realsound.jp/movie/2022/01/post-950199.html</t>
+          <t>https://ranking.net/items/c27482 | https://www.kinokuniya.co.jp/f/dsg-08-9981904201 | https://realsound.jp/movie/2022/01/post-950199.html | https://www.akitashoten.co.jp/series/1922 | https://www.akitashoten.co.jp/comics/4253211003</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4464,7 +4704,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4761,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2008頃–2011頃（シリーズ全体で2005–2011とする二次情報。正確な号は未確認）</t>
+          <t>2008–2011（週刊少年チャンピオン2008年49号で新連載。最終第15巻は2011年9月8日発売。最終回の掲載号は未確認）</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4564,8 +4804,16 @@
           <t>前作同様のドタバタと家族ギャグ。終盤は控えめ</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr"/>
-      <c r="U32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>A：「不良を辞める」主人公の葛藤と家族愛が、「不良は嫌い」の思想に近い</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
           <t>技法：シリーズ後半でギャグからシリアスへ比重を移す構成。FLATUP案：笑いの多い連作の最終章で、主人公が“初めての試合に出るかどうか”を自分で決める回</t>
@@ -4583,7 +4831,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/40994/ | https://booklive.jp/focus/author/a_id/10848 | https://renote.net/tags/17418</t>
+          <t>https://www.cmoa.jp/title/40994/ | https://booklive.jp/focus/author/a_id/10848 | https://renote.net/tags/17418 | https://www.akitashoten.co.jp/w-champion/2008/49 | https://www.akitashoten.co.jp/comics/4253215416 | https://www.akitashoten.co.jp/comics/4253216749</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4593,7 +4841,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4693,8 +4941,16 @@
           <t>主人公コンビのドジ、女子に振り回される落差、ケンカ後の間抜けなオチ</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr"/>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>B：ツッパリ二人組の掛け合いとケンカ後の脱力ギャグは学べるが、ケンカ描写が多い</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
           <t>技法：二人組主人公の『漫才的な掛け合い』で長期連載を回す。日常とケンカの緩急。オリジナル案：ジムの同期入会コンビが毎回『どっちが先に縄跳び二重跳びできるか』で張り合う、ゆるい日常4コマ</t>
@@ -4712,7 +4968,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://renote.net/articles/15234 | https://www.netoff.co.jp/detail/0010117245/ | https://realsound.jp/book/2024/01/post-1559884.html/amp | https://movie.jorudan.co.jp/film/18144/</t>
+          <t>https://renote.net/articles/15234 | https://www.netoff.co.jp/detail/0010117245/ | https://realsound.jp/book/2024/01/post-1559884.html/amp | https://movie.jorudan.co.jp/film/18144/ | https://kc.kodansha.co.jp/product?item=0000010537 | https://www.kodansha.co.jp/comic/products/0000006711</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4722,7 +4978,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4822,8 +5078,16 @@
           <t>シリアス主体だが、主人公の泣き顔やヘタレぶり、仲間内の軽いじゃれ合いで息抜き</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr"/>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>B：弱くても立ち向かう主人公の勇気と仲間の絆は学べるが、喪失や暴力が重い</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
           <t>技法：『弱いけど折れない』主人公に読者が感情移入する構造。毎話の終わりに次が気になる引きを作る。オリジナル案：何度ミット打ちで息切れしても『あと1ラウンドだけ』と立ち上がる会員の物語。強さ＝勝つことではなく『やめないこと』と定義する</t>
@@ -4841,7 +5105,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://av.watch.impress.co.jp/docs/news/1340171.html | https://animeanime.jp/article/2022/04/23/69070.html | https://kai-you.net/word/%E6%9D%B1%E4%BA%AC%E5%8D%8D%E3%83%AA%E3%83%99%E3%83%B3%E3%82%B8%E3%83%A3%E3%83%BC%E3%82%BA | https://bunshun.jp/articles/-/62450</t>
+          <t>https://av.watch.impress.co.jp/docs/news/1340171.html | https://animeanime.jp/article/2022/04/23/69070.html | https://kai-you.net/word/%E6%9D%B1%E4%BA%AC%E5%8D%8D%E3%83%AA%E3%83%99%E3%83%B3%E3%82%B8%E3%83%A3%E3%83%BC%E3%82%BA | https://bunshun.jp/articles/-/62450 | https://kc.kodansha.co.jp/product?item=0000372628 | https://cstation.kodansha.co.jp/mangaip/article/6973</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4851,7 +5115,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -4908,7 +5172,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2006–2011頃（2006年27号開始を確認。終了号は未確認）</t>
+          <t>2006–2011（週刊少年マガジン2006年27号〜2011年第25号。最終巻の初出に2011年第16号〜第25号の記載）</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4951,8 +5215,16 @@
           <t>見た目は真面目なのにケンカ最強という落差、勢いで振り回すドタバタ</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr"/>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>A：元ヤンの優しい委員長が不良を学校生活に引き込む構図が、初心者を迎える話に使える</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
           <t>技法：『見た目は真面目・中身は最強』のギャップヒロイン。ボケとツッコミのタンデム構造。オリジナル案：受付で丁寧に案内してくれるメガネのスタッフが、実はミット持ちが一番うまいトレーナーだったと判明する回</t>
@@ -4970,7 +5242,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000052061 | https://www.kodansha.co.jp/comic/products/0000012307 | https://www.cmoa.jp/title/41193</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000052061 | https://www.kodansha.co.jp/comic/products/0000012307 | https://www.cmoa.jp/title/41193 | https://www.kodansha.co.jp/comic/products/0000017290 | https://www.kodansha.co.jp/comic/products/0000053018</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -5080,8 +5352,16 @@
           <t>不良なのに手芸部という設定の落差、仲間の悪ノリ</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>A：暴走族なのに手芸部、という落差と仲間思いの明るさが学べる</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t>技法：『怖い外見×意外な趣味』で親しみを出す設定。オリジナル案：いかついトレーナーの趣味が家庭菜園で、会員にジム産の野菜を配る回。強さと優しさの両立を象徴する</t>
@@ -5206,11 +5486,19 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読）</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="2" t="inlineStr"/>
+          <t>ケンカは強いのに美形の男子に弱いという主人公の落差が紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>B：強い女性主人公の格好よさは学べるが、暴走族の抗争描写が中心</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー／群像・矜持</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
           <t>技法：『強い女性主人公』を正面から描く不良漫画の型。オリジナル案：女性会員クラスで、最初は人見知りだった会員が自分の強さに自信を持ち、後輩の初心者女性を励ます先輩になる話</t>
@@ -5228,7 +5516,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Kissh%C5%8D_Tennyo | https://pedia.3rd-in.co.jp/wiki/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3 | https://mangapedia.com/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3-uqec3f53z</t>
+          <t>https://en.wikipedia.org/wiki/Kissh%C5%8D_Tennyo | https://pedia.3rd-in.co.jp/wiki/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3 | https://mangapedia.com/%E7%89%B9%E6%94%BB%E5%A4%A9%E5%A5%B3-uqec3f53z | https://www.akitashoten.co.jp/series/5 | https://www.akitashoten.co.jp/comics/4253200508</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5238,7 +5526,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5583,12 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>開始年未確認（2011年4月の号に掲載を確認）〜2026年時点で連載再開・連載中</t>
+          <t>開始年未確認（2011年4月の号に掲載を確認）〜2026年時点で連載中（ヤングチャンピオン2026年No.22に掲載）</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39巻まで刊行（2026年時点、ヤングチャンピオン・コミックス）</t>
+          <t>39巻（2026年2月19日発売）まで秋田書店公式で確認。第40巻は2026年10月20日発売と告知（2026-10時点で確認）</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -5335,11 +5623,19 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr"/>
-      <c r="U38" s="2" t="inlineStr"/>
+          <t>いじめられっ子が不良に憧れて中学デビューする「泣き笑い青春グラフィティー」と公式に紹介されている（紹介記事による）</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>B：いじめられっ子が強さに目覚める成長は学べるが、暴走族の実話が中心</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>技法：実話ベースの『いじめられっ子からの成長』物語。オリジナル案：いじめで自信を失った中学生が、ジムで『誰かを殴るためではなく自分を守るため』の練習を通じて自信を取り戻す話。FLATUPの思想『不良漫画は好き、でも不良は嫌い』に合わせ、暴力での解決にしない</t>
@@ -5357,7 +5653,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/113839 | https://www.cmoa.jp/title/120153/vol/230/ | https://www.fujisan.co.jp/product/2682/b/623118/ | https://ciatr.jp/topics/313098</t>
+          <t>https://www.cmoa.jp/title/113839 | https://www.cmoa.jp/title/120153/vol/230/ | https://www.fujisan.co.jp/product/2682/b/623118/ | https://ciatr.jp/topics/313098 | https://www.akitashoten.co.jp/series/2558 | https://www.akitashoten.co.jp/comics/4253148263 | https://www.akitashoten.co.jp/youngchampion</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5367,7 +5663,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -5419,12 +5715,12 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ヤングキング（ヤングキングアワーズとする情報もあり、未確定）</t>
+          <t>ヤングキングアワーズ（多くの二次情報による。ヤングキングとする資料もあり、資料により異なる）</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1998–2000頃（情報源で食い違いあり）</t>
+          <t>1998–2001頃（単行本第1巻1999年〜第8巻2001年刊行。少年画報社公式の外伝紹介に2001年終了の記載。開始は1998年・2000年など資料により異なる）</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5467,8 +5763,16 @@
           <t>少なめ。主人公の不器用さによる小さな笑い</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr"/>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>C：親友が別の道へ進む悲しさは参考になるが、裏社会が中心</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>技法：①同じ出発点から違う道へ進んだ二人の対比 ②黒ベタと陰影で緊張を作る。FLATUP案：昔同じ道場にいた二人が、一人はトレーナー、一人は道を外れて再会する話。最後に“もう一度グローブを付ける”選択を描く</t>
@@ -5486,7 +5790,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://dic.pixiv.net/history/QP/2961307/source | https://comic.k-manga.jp/title/51360/pv | https://honcierge.jp/articles/shelf_story/7349</t>
+          <t>https://dic.pixiv.net/history/QP/2961307/source | https://comic.k-manga.jp/title/51360/pv | https://honcierge.jp/articles/shelf_story/7349 | https://www.shonengahosha.co.jp/book_Info.php?id=7610 | https://www.shonengahosha.co.jp/book_Info.php?id=5908 | https://www.shonengahosha.co.jp/book_Info.php?id=5909</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5568,7 +5872,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2012年テレビ東京系でドラマ化（監督 入江悠）。同作者の後続作は未確認</t>
+          <t>2012年テレビ東京系でドラマ化（監督 入江悠）。同作者の後続作に『ヒマワリ』（週刊少年チャンピオン2017年42号〜）、『ナインピークス NINE PEAKS』（2022年〜）</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5596,8 +5900,16 @@
           <t>幼なじみ同士のボケ合い、恋愛での空回り、デフォルメ顔</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>B：幼なじみの友情とケンカ後のギャグは学べる</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>青春不良コメディ</t>
+        </is>
+      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>技法：①固定メンバー（四人）で長期連載を回す ②卒業をゴールにした構成。FLATUP案：同じ日に入会した四人が、一年後の“初めての昇級審査”を一緒に迎えるまでを描く連作</t>
@@ -5615,7 +5927,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://comic.k-manga.jp/title/112495/vol/43 | https://mangapedia.com/%E5%B9%B3%E5%B7%9D%E5%93%B2%E5%BC%98-0adjsc340 | https://justwatch.com/jp/%E3%83%86%E3%83%AC%E3%83%93%E7%95%AA%E7%B5%84/kuroba</t>
+          <t>https://comic.k-manga.jp/title/112495/vol/43 | https://mangapedia.com/%E5%B9%B3%E5%B7%9D%E5%93%B2%E5%BC%98-0adjsc340 | https://justwatch.com/jp/%E3%83%86%E3%83%AC%E3%83%93%E7%95%AA%E7%B5%84/kuroba | https://www.akitashoten.co.jp/comics/4253215742 | https://mangapedia.com/平川哲弘-0adjsc340</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5625,7 +5937,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -6821,8 +7133,16 @@
           <t>仲間内の下品で勢いのある笑い、強面の意外な素直さ</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr"/>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>B：更生の緊張と恩人への義理の描き方は、「不良は更生する側」の描写に使える</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
           <t>技法：①“殴ってはいけない”制約が緊張を生む ②我慢の積み重ね→解放の構成。FLATUP案：試合前に怪我を抱えた選手が、スパーで無理をしない我慢を選ぶ回。解放は“ミット打ちの一発”で描く</t>
@@ -6950,8 +7270,16 @@
           <t>ノリの良いボケと仲間の総ツッコミ、デフォルメ顔</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>B：かっこいい生き方とは何かを問う姿勢は使えるが、ギャング文化はそのまま使えない</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
           <t>技法：①強さ＝生き方のかっこよさと定義し直す ②ファッション性のある立ち絵でキャラを立てる。FLATUP案：『強さとは優しさであり、かっこよさである』を正面から掲げ、ジムウェアの着こなしや礼の仕方まで“かっこいい”と描く回</t>
@@ -7173,51 +7501,59 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
+          <t>1986年頃–1996年頃（週刊少年チャンピオン。単行本は第1巻1987年1月16日〜第50巻1996年10月11日刊行。正確な掲載号は未確認）</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>全50巻（少年チャンピオン・コミックス、完結）</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>極道／任侠／不良／人情</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>『本気! 終章 火薬』（ヤングチャンピオン掲載）、『本気! II』（1998–2000年刊行）、『本気! 番外編（2）命』（1997年）、『本気! Samdhana（サンダーナ）』（ヤングチャンピオン、2003–2005年刊行）</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>極道の世界での男の純情、義理人情、筋を通す生き方</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>主人公の一途さと純情を中心に、極道の世界で生きる者の葛藤を描く</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>任侠・極道らしい重い言葉と、人情味のある語り</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>未確認（本文未読）</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>全50巻（少年チャンピオン・コミックス、完結）</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>極道／任侠／不良／人情</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>『本気! 終章 火薬』（ヤングチャンピオン掲載）</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>極道の世界での男の純情、義理人情、筋を通す生き方</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>主人公の一途さと純情を中心に、極道の世界で生きる者の葛藤を描く</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>任侠・極道らしい重い言葉と、人情味のある語り</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>未確認（本文未読）</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr"/>
-      <c r="U52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>C：義理人情の言い切りは参考になるが、極道ものでFLATUPには合わない</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>群像・矜持</t>
+        </is>
+      </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
           <t>技法：『筋を通す』主人公の一途さを軸にした人情劇。オリジナル案：約束を必ず守るトレーナーが、会員との『次の練習も来る』という小さな約束を大事にする話。FLATUPでは極道・暴力の美化はしない</t>
@@ -7235,7 +7571,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://www.cmoa.jp/title/43916/ | https://bookwalker.jp/series/5784/list/ | https://www.fujisan.co.jp/product/2682/b/1922497/</t>
+          <t>https://www.cmoa.jp/title/43916/ | https://bookwalker.jp/series/5784/list/ | https://www.fujisan.co.jp/product/2682/b/1922497/ | https://www.akitashoten.co.jp/series/1314 | https://akitashoten.co.jp/comics/4253048668 | https://akitashoten.co.jp/series/87 | https://akitashoten.co.jp/series/259</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -7245,7 +7581,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -7619,8 +7955,16 @@
           <t>主人公の小心さや勘違いを起点にした間の抜けたリアクション、シリアスな場面直後の脱力コマ</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr"/>
-      <c r="U55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>B：弱い主人公が憧れから一歩踏み出す心理と、当て字ルビの大げさな独白の型が学べる（暴力の重さは参考にとどめる）</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
           <t>技法：文字（ルビ）の演出でキャラの格を上げる手法、気弱な主人公が怖がりながら前に出る『震える一歩』の描写。オリジナル案：ジムの初心者が初スパーで足が震えつつも『怖いままでいい、一回だけ前へ』と自分に言い聞かせる回。ルビ演出はFLATUP独自の造語（例：『優しさ』に独自の読みを振る）で行い、原作の当て字は使わない</t>
@@ -7638,7 +7982,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/titles/1000005685 | https://mangapedia.com/疾風伝説特攻の拓-645eremzo | https://game.watch.impress.co.jp/docs/news/1505517.html</t>
+          <t>https://www.kodansha.co.jp/titles/1000005685 | https://mangapedia.com/疾風伝説特攻の拓-645eremzo | https://game.watch.impress.co.jp/docs/news/1505517.html | https://www.kodansha.co.jp/comic/products/0000373906 | https://kc.kodansha.co.jp/product?item=0000005482</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7648,7 +7992,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -7705,7 +8049,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2011年〜（初出に月刊ヤングマガジン2011年第4号〜第8号の記載あり。終了時期は未確認）</t>
+          <t>2011–2013（月刊ヤングマガジン2011年第4号〜2013年第7号とする資料あり。講談社公式の第5巻初出は2013年第2・3・5〜7号。第5巻は2013年8月6日発売で完結）</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -7748,8 +8092,16 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr"/>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>C：本編キャラの過去を掘る前日譚の作り方は参考になるが、FLATUP向けの要素は少ない</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
           <t>技法：本編の人気キャラの『過去編』で厚みを出すスピンオフの作り方。オリジナル案：FLATUPのトレーナーが格闘技を始める前の弱かった時代を描く短編を作り、本編の初心者に寄り添う理由を後から明かす</t>
@@ -7767,7 +8119,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/products/0000016386 | https://www.kodansha.co.jp/comic/products/0000016037</t>
+          <t>https://www.kodansha.co.jp/comic/products/0000016386 | https://www.kodansha.co.jp/comic/products/0000016037 | https://www.maruzenjunkudo.co.jp/products/9784063823394 | https://mangapedia.com/%E7%96%BE%E9%A2%A8%E4%BC%9D%E8%AA%AC%E7%89%B9%E6%94%BB%E3%81%AE%E6%8B%93%E5%A4%96%E4%BC%9D%EF%BD%9EEarlyDays%EF%BD%9E-t56aw6k1b</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7834,12 +8186,12 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2017年〜（終了時期未確認。資料により記載が食い違う）</t>
+          <t>2017–2022（月刊ヤングマガジン2017年3号〜2022年3号）</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>全9巻とする販売情報あり（第8巻は2023年6月20日発売）。完結の公式告知は未確認</t>
+          <t>全9巻（第9巻は2022年4月20日発売、講談社公式で「完結」と紹介。電子版は2023年6月20日配信）</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7859,7 +8211,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>未確認（本文未読）</t>
+          <t>かつての不良が約10年後に刑事として事件に向き合う、大人になった主人公の立場の変化が軸（紹介記事による）</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7877,8 +8229,16 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="T57" s="2" t="inlineStr"/>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>C：大人になった元不良の描き方は参考になるが、事件ものの比重が高い</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>劇画ヤンキー</t>
+        </is>
+      </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
           <t>技法：『あの頃の不良が大人になったら』という時間経過の設定で、強さの意味を問い直す続編構成。オリジナル案：昔ケンカに明け暮れた元ヤンが、30代でFLATUPに入会し『殴るためじゃなく守るための強さ』を学び直す話</t>
@@ -7896,7 +8256,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://www.kodansha.co.jp/comic/new-releases?page=396 | https://booklive.jp/focus/author/a_id/96124 | https://wowma.jp/item/535774719 | https://en.wikipedia.org/wiki/Kaze_Densetsu:_Bukkomi_no_Taku</t>
+          <t>https://www.kodansha.co.jp/comic/new-releases?page=396 | https://booklive.jp/focus/author/a_id/96124 | https://wowma.jp/item/535774719 | https://en.wikipedia.org/wiki/Kaze_Densetsu:_Bukkomi_no_Taku | https://kc.kodansha.co.jp/product?item=0000363918 | https://www.kodansha.co.jp/titles/1000029655 | https://mangapedia.com/%E7%96%BE%E9%A2%A8%E4%BC%9D%E8%AA%AC%E7%89%B9%E6%94%BB%E3%81%AE%E6%8B%93%EF%BD%9EAfterDecade%EF%BD%9E-8o5xflo50</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7906,7 +8266,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
     </row>
@@ -18544,11 +18904,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>二次情報で確認</t>
+          <t>確認済み</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -18559,11 +18919,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>確認済み</t>
+          <t>二次情報で確認</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
